--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="1354">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716745138168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367179751396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380497127771378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789375543594</t>
+    <t xml:space="preserve">0.382716685533524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367179721593857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3804971575737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789345741272</t>
   </si>
   <si>
     <t xml:space="preserve">0.352276921272278</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">0.36813098192215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38715586066246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936921834946</t>
+    <t xml:space="preserve">0.387155830860138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936951637268</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009582042694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521327972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886884689331</t>
+    <t xml:space="preserve">0.373521357774734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886825084686</t>
   </si>
   <si>
     <t xml:space="preserve">0.335471630096436</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.34561824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361472278833389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341496139764786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355130642652512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352594017982483</t>
+    <t xml:space="preserve">0.361472338438034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341496199369431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355130672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352594047784805</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447459697723</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.360838115215302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35735023021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357984393835068</t>
+    <t xml:space="preserve">0.357350200414658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35798442363739</t>
   </si>
   <si>
     <t xml:space="preserve">0.35069152712822</t>
@@ -113,82 +113,82 @@
     <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291714489459991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297739028930664</t>
+    <t xml:space="preserve">0.291714459657669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297739058732986</t>
   </si>
   <si>
     <t xml:space="preserve">0.27586042881012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276240944862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304461151361465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326593369245529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789066076279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329130053520203</t>
+    <t xml:space="preserve">0.276240974664688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304461121559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326593339443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789036273956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329129993915558</t>
   </si>
   <si>
     <t xml:space="preserve">0.348471969366074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3275445997715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671158790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330081284046173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33420330286026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838734149933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356398969888687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36876517534256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325325071811676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318032175302505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306236773729324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308329522609711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331032544374466</t>
+    <t xml:space="preserve">0.327544659376144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671128988266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330081254243851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334203332662582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386838793754578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356398940086365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368765145540237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325325101613998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318032205104828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306236803531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308329492807388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331032514572144</t>
   </si>
   <si>
     <t xml:space="preserve">0.322788417339325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319934666156769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153944253922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331666678190231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320251762866974</t>
+    <t xml:space="preserve">0.319934695959091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153914451599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331666707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320251733064651</t>
   </si>
   <si>
     <t xml:space="preserve">0.310802757740021</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">0.308836847543716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306300193071365</t>
+    <t xml:space="preserve">0.306300222873688</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880487680435</t>
@@ -209,181 +209,181 @@
     <t xml:space="preserve">0.28588017821312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267743140459061</t>
+    <t xml:space="preserve">0.267743170261383</t>
   </si>
   <si>
     <t xml:space="preserve">0.260767340660095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267489463090897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258738040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288543701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371618896722794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364643067121506</t>
+    <t xml:space="preserve">0.267489492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738070726395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288543671369553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371618866920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364643096923828</t>
   </si>
   <si>
     <t xml:space="preserve">0.367496848106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369716376066208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399309158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388741195201874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387790083885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370033502578735</t>
+    <t xml:space="preserve">0.36971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399279356003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388741225004196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387790024280548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370033532381058</t>
   </si>
   <si>
     <t xml:space="preserve">0.357033163309097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3741554915905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377643436193466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370984703302383</t>
+    <t xml:space="preserve">0.374155551195145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377643406391144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370984643697739</t>
   </si>
   <si>
     <t xml:space="preserve">0.372253060340881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387472897768021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377326369285583</t>
+    <t xml:space="preserve">0.387472927570343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377326339483261</t>
   </si>
   <si>
     <t xml:space="preserve">0.439791232347488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453425735235214</t>
+    <t xml:space="preserve">0.453425794839859</t>
   </si>
   <si>
     <t xml:space="preserve">0.454059928655624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461669832468033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133237600327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455645382404327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456279456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840620756149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792250156403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485767960548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477841019630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483231395483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484816819429398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497817128896713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489255964756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475621372461319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476889759302139</t>
+    <t xml:space="preserve">0.461669862270355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133207798004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455645352602005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456279516220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840710163116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792279958725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485768049955368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47784098982811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483231425285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484816789627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497817069292068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489255875349045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475621402263641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476889729499817</t>
   </si>
   <si>
     <t xml:space="preserve">0.488304674625397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493695110082626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489890098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548682451248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645662069321</t>
+    <t xml:space="preserve">0.493695050477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489890038967133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548801660538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468645632266998</t>
   </si>
   <si>
     <t xml:space="preserve">0.473084807395935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495280474424362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486719280481339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484182596206665</t>
+    <t xml:space="preserve">0.495280504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486719250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48418253660202</t>
   </si>
   <si>
     <t xml:space="preserve">0.497500002384186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50732946395874</t>
+    <t xml:space="preserve">0.507329523563385</t>
   </si>
   <si>
     <t xml:space="preserve">0.507963716983795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514939427375793</t>
+    <t xml:space="preserve">0.514939486980438</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183274745941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515890657901764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354372501373</t>
+    <t xml:space="preserve">0.515890717506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354432106018</t>
   </si>
   <si>
     <t xml:space="preserve">0.525720238685608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529525220394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535866856575012</t>
+    <t xml:space="preserve">0.52952516078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535866796970367</t>
   </si>
   <si>
     <t xml:space="preserve">0.540305912494659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620844483375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625917851924896</t>
+    <t xml:space="preserve">0.620844542980194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625917792320251</t>
   </si>
   <si>
     <t xml:space="preserve">0.627503156661987</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">0.597697556018829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596112251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57708740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561867415904999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583428978919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569160282611847</t>
+    <t xml:space="preserve">0.596112132072449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577087342739105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561867475509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428919315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569160342216492</t>
   </si>
   <si>
     <t xml:space="preserve">0.566940724849701</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">0.529208064079285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516842007637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516207754611969</t>
+    <t xml:space="preserve">0.516841948032379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476141452789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516207814216614</t>
   </si>
   <si>
     <t xml:space="preserve">0.465791910886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4835484623909</t>
+    <t xml:space="preserve">0.483548432588577</t>
   </si>
   <si>
     <t xml:space="preserve">0.549184203147888</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">0.586599707603455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613868653774261</t>
+    <t xml:space="preserve">0.613868713378906</t>
   </si>
   <si>
     <t xml:space="preserve">0.654455065727234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665869951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655089199542999</t>
+    <t xml:space="preserve">0.665870010852814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655089318752289</t>
   </si>
   <si>
     <t xml:space="preserve">0.62306410074234</t>
@@ -467,28 +467,28 @@
     <t xml:space="preserve">0.633844792842865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62211287021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618941962718964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615137040615082</t>
+    <t xml:space="preserve">0.622112810611725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618942022323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615137100219727</t>
   </si>
   <si>
     <t xml:space="preserve">0.631625294685364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628771543502808</t>
+    <t xml:space="preserve">0.628771603107452</t>
   </si>
   <si>
     <t xml:space="preserve">0.63416188955307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629088521003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643674433231354</t>
+    <t xml:space="preserve">0.629088580608368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643674373626709</t>
   </si>
   <si>
     <t xml:space="preserve">0.644308507442474</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">0.64557683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636064350605011</t>
+    <t xml:space="preserve">0.636064410209656</t>
   </si>
   <si>
     <t xml:space="preserve">0.63479608297348</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">0.628454446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632259488105774</t>
+    <t xml:space="preserve">0.632259368896484</t>
   </si>
   <si>
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234829425812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602453768253326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588185250759125</t>
+    <t xml:space="preserve">0.626234889030457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602453827857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58818519115448</t>
   </si>
   <si>
     <t xml:space="preserve">0.590087592601776</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">0.619893252849579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592941343784332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600551307201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595795154571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594526827335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591673135757446</t>
+    <t xml:space="preserve">0.592941403388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600551247596741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595795094966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594526767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
     <t xml:space="preserve">0.601185500621796</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">0.603087902069092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609746694564819</t>
+    <t xml:space="preserve">0.60974657535553</t>
   </si>
   <si>
     <t xml:space="preserve">0.611332058906555</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">0.614185810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611966252326965</t>
+    <t xml:space="preserve">0.611966192722321</t>
   </si>
   <si>
     <t xml:space="preserve">0.605941712856293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598648846149445</t>
+    <t xml:space="preserve">0.5986487865448</t>
   </si>
   <si>
     <t xml:space="preserve">0.593258440494537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588502168655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380459308624</t>
+    <t xml:space="preserve">0.588502287864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380518913269</t>
   </si>
   <si>
     <t xml:space="preserve">0.617673695087433</t>
@@ -584,52 +584,52 @@
     <t xml:space="preserve">0.61101508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604039132595062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605307519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61006373167038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649465084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039561271667</t>
+    <t xml:space="preserve">0.604039192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605307579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610063791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039442062378</t>
   </si>
   <si>
     <t xml:space="preserve">0.61038076877594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596429288387299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591355919837952</t>
+    <t xml:space="preserve">0.596429228782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591356039047241</t>
   </si>
   <si>
     <t xml:space="preserve">0.589770615100861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565355241298676</t>
+    <t xml:space="preserve">0.56535530090332</t>
   </si>
   <si>
     <t xml:space="preserve">0.523183584213257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481963008642197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493377983570099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492109596729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508280813694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513988256454468</t>
+    <t xml:space="preserve">0.481963038444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493377864360809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492109686136246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508280754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513988196849823</t>
   </si>
   <si>
     <t xml:space="preserve">0.509231984615326</t>
@@ -638,31 +638,31 @@
     <t xml:space="preserve">0.509549081325531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51779317855835</t>
+    <t xml:space="preserve">0.517793238162994</t>
   </si>
   <si>
     <t xml:space="preserve">0.548550069332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544110894203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521598160266876</t>
+    <t xml:space="preserve">0.544110953807831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521598219871521</t>
   </si>
   <si>
     <t xml:space="preserve">0.53047639131546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546013295650482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540940165519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532695949077606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538720488548279</t>
+    <t xml:space="preserve">0.546013355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54094010591507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532696008682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538720607757568</t>
   </si>
   <si>
     <t xml:space="preserve">0.539037585258484</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">0.532061874866486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568843245506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570428609848022</t>
+    <t xml:space="preserve">0.568843185901642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570428669452667</t>
   </si>
   <si>
     <t xml:space="preserve">0.566306591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549501240253448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560599088668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564404129981995</t>
+    <t xml:space="preserve">0.549501299858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560599207878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56440407037735</t>
   </si>
   <si>
     <t xml:space="preserve">0.550452530384064</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">0.542842626571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545062124729156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521281123161316</t>
+    <t xml:space="preserve">0.545062184333801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521281063556671</t>
   </si>
   <si>
     <t xml:space="preserve">0.516524910926819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50669538974762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528256833553314</t>
+    <t xml:space="preserve">0.506695330142975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528256893157959</t>
   </si>
   <si>
     <t xml:space="preserve">0.519695699214935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526037335395813</t>
+    <t xml:space="preserve">0.526037275791168</t>
   </si>
   <si>
     <t xml:space="preserve">0.518744468688965</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">0.511451601982117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514305293560028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523817777633667</t>
+    <t xml:space="preserve">0.514305353164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523817658424377</t>
   </si>
   <si>
     <t xml:space="preserve">0.508597791194916</t>
@@ -737,46 +737,46 @@
     <t xml:space="preserve">0.522549390792847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513671100139618</t>
+    <t xml:space="preserve">0.513671159744263</t>
   </si>
   <si>
     <t xml:space="preserve">0.511134505271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504158735275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506061196327209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505109965801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510500431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499719619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512085676193237</t>
+    <t xml:space="preserve">0.504158675670624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506061136722565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505110025405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510500311851501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499719500541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
     <t xml:space="preserve">0.541574239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550769567489624</t>
+    <t xml:space="preserve">0.550769686698914</t>
   </si>
   <si>
     <t xml:space="preserve">0.553623378276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560282051563263</t>
+    <t xml:space="preserve">0.560281991958618</t>
   </si>
   <si>
     <t xml:space="preserve">0.569794476032257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575501978397369</t>
+    <t xml:space="preserve">0.575501918792725</t>
   </si>
   <si>
     <t xml:space="preserve">0.627820312976837</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.682358145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762262582778931</t>
+    <t xml:space="preserve">0.762262642383575</t>
   </si>
   <si>
     <t xml:space="preserve">0.736896097660065</t>
@@ -806,205 +806,205 @@
     <t xml:space="preserve">0.733091235160828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748945355415344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747676968574524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754652738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755286872386932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76036012172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81806892156601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799678146839142</t>
+    <t xml:space="preserve">0.74894517660141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747676849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754652678966522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755286812782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760360181331635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81806880235672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799678206443787</t>
   </si>
   <si>
     <t xml:space="preserve">0.771140873432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768604278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720407962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727383732795715</t>
+    <t xml:space="preserve">0.768604218959808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720408022403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727383613586426</t>
   </si>
   <si>
     <t xml:space="preserve">0.740701079368591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73816442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774945795536041</t>
+    <t xml:space="preserve">0.73816454410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774945855140686</t>
   </si>
   <si>
     <t xml:space="preserve">0.78382408618927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801580607891083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849777042865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884021639823914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851045310497284</t>
+    <t xml:space="preserve">0.801580727100372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849776983261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884021699428558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851045370101929</t>
   </si>
   <si>
     <t xml:space="preserve">0.878314197063446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894168198108673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876438617706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924607932567596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887826800346375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901778340339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881484985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412354946136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875143468379974</t>
+    <t xml:space="preserve">0.894168317317963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876319408417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924607992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887826681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901778280735016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881485044956207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87514340877533</t>
   </si>
   <si>
     <t xml:space="preserve">0.896070778369904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.91065639257431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910022258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729082584381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892900109291077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863094329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860557734966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533504962921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875777721405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868167638778687</t>
+    <t xml:space="preserve">0.910656571388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827359676361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91002231836319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889729142189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892899811267853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436644554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863094389438629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860557675361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533564567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87577760219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868167579174042</t>
   </si>
   <si>
     <t xml:space="preserve">0.756555140018463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788897275924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812995493412018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807288110256195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838362097740173</t>
+    <t xml:space="preserve">0.788897395133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812995553016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80728805065155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838362157344818</t>
   </si>
   <si>
     <t xml:space="preserve">0.790165722370148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786360740661621</t>
+    <t xml:space="preserve">0.786360800266266</t>
   </si>
   <si>
     <t xml:space="preserve">0.811727225780487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83011794090271</t>
+    <t xml:space="preserve">0.830118000507355</t>
   </si>
   <si>
     <t xml:space="preserve">0.814898014068604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792702376842499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803483188152313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804117262363434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776848375797272</t>
+    <t xml:space="preserve">0.792702436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803483128547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804117441177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776848316192627</t>
   </si>
   <si>
     <t xml:space="preserve">0.780019164085388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781921684741974</t>
+    <t xml:space="preserve">0.781921625137329</t>
   </si>
   <si>
     <t xml:space="preserve">0.791434049606323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78509247303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970704078674</t>
+    <t xml:space="preserve">0.785092353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786994993686676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79397064447403</t>
   </si>
   <si>
     <t xml:space="preserve">0.789531588554382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.773677468299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775580167770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769872665405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767335951328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77177494764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628448963165</t>
+    <t xml:space="preserve">0.773677587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775580048561096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769872546195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767335891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771775007247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761628389358521</t>
   </si>
   <si>
     <t xml:space="preserve">0.795873165130615</t>
@@ -1013,85 +1013,85 @@
     <t xml:space="preserve">0.811093091964722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843435406684875</t>
+    <t xml:space="preserve">0.84343546628952</t>
   </si>
   <si>
     <t xml:space="preserve">0.832654595375061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872606754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460196018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866899311542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840264499187469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830752015113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855484426021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801153659821</t>
+    <t xml:space="preserve">0.872606813907623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460076808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866899251937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840264558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830752074718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855484306812286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801094055176</t>
   </si>
   <si>
     <t xml:space="preserve">0.849142789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820605635643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824410498142242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826947033405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806019842624664</t>
+    <t xml:space="preserve">0.820605516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824410378932953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826947152614594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80601978302002</t>
   </si>
   <si>
     <t xml:space="preserve">0.799043953418732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804751515388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785726606845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778750717639923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777482390403748</t>
+    <t xml:space="preserve">0.804751455783844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7857266664505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778750896453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777482450008392</t>
   </si>
   <si>
     <t xml:space="preserve">0.802214860916138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806653797626495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807922422885895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854850292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857386767864227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852313637733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863728523254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86499685049057</t>
+    <t xml:space="preserve">0.80665397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80792236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854850232601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857386827468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852313578128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863728582859039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864996790885925</t>
   </si>
   <si>
     <t xml:space="preserve">0.850411117076874</t>
@@ -1100,61 +1100,61 @@
     <t xml:space="preserve">0.840898752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996112346649</t>
+    <t xml:space="preserve">0.834557116031647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996052742004</t>
   </si>
   <si>
     <t xml:space="preserve">0.827581226825714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826312839984894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805385589599609</t>
+    <t xml:space="preserve">0.826312959194183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805385708808899</t>
   </si>
   <si>
     <t xml:space="preserve">0.814263820648193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81870299577713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819337129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79650741815567</t>
+    <t xml:space="preserve">0.81870311498642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81933718919754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796507358551025</t>
   </si>
   <si>
     <t xml:space="preserve">0.809190571308136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809824764728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797775745391846</t>
+    <t xml:space="preserve">0.809824705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797775626182556</t>
   </si>
   <si>
     <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817434728145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823142230510712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812361419200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819971263408661</t>
+    <t xml:space="preserve">0.817434787750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823142170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812361478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819971323013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.797141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.716602921485901</t>
+    <t xml:space="preserve">0.716602981090546</t>
   </si>
   <si>
     <t xml:space="preserve">0.704553842544556</t>
@@ -1163,76 +1163,76 @@
     <t xml:space="preserve">0.736261963844299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772409200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776214063167572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784458220005035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783189952373505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752115905284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760994255542755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790799975395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810458958148956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311721324921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781287491321564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795239090919495</t>
+    <t xml:space="preserve">0.759725868701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77240926027298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776214241981506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784458339214325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78318989276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752116084098816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7609943151474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823526859283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701638698578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790799915790558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810459017753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311661720276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781287431716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79523903131485</t>
   </si>
   <si>
     <t xml:space="preserve">0.800312280654907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815532267093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764799177646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731822907924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711529672145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.693773031234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739432752132416</t>
+    <t xml:space="preserve">0.815532207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764799296855927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731822967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711529612541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.693773150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739432811737061</t>
   </si>
   <si>
     <t xml:space="preserve">0.70391970872879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695041477680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683626532554626</t>
+    <t xml:space="preserve">0.695041358470917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683626472949982</t>
   </si>
   <si>
     <t xml:space="preserve">0.660796761512756</t>
@@ -1250,46 +1250,46 @@
     <t xml:space="preserve">0.678553283214569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.687431514263153</t>
+    <t xml:space="preserve">0.687431454658508</t>
   </si>
   <si>
     <t xml:space="preserve">0.717871248722076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730554521083832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710261285305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697578132152557</t>
+    <t xml:space="preserve">0.730554461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710261344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697578072547913</t>
   </si>
   <si>
     <t xml:space="preserve">0.714066326618195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729286134243011</t>
+    <t xml:space="preserve">0.729286193847656</t>
   </si>
   <si>
     <t xml:space="preserve">0.753384292125702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748310983181</t>
+    <t xml:space="preserve">0.748311102390289</t>
   </si>
   <si>
     <t xml:space="preserve">0.757189333438873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758457660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763530969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74957937002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042655944824</t>
+    <t xml:space="preserve">0.758457601070404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763530850410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749579429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042715549469</t>
   </si>
   <si>
     <t xml:space="preserve">0.735627770423889</t>
@@ -1298,88 +1298,88 @@
     <t xml:space="preserve">0.745774388313293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743237793445587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.741969406604767</t>
+    <t xml:space="preserve">0.743237733840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.741969287395477</t>
   </si>
   <si>
     <t xml:space="preserve">0.744506120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722944557666779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.700114727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456363201141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846459388733</t>
+    <t xml:space="preserve">0.722944676876068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700114667415619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456303596497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846518993378</t>
   </si>
   <si>
     <t xml:space="preserve">0.72548121213913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71533465385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712797939777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69250476360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705188035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68108993768692</t>
+    <t xml:space="preserve">0.715334713459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712797880172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692504823207855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705188095569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.681089878082275</t>
   </si>
   <si>
     <t xml:space="preserve">0.701383054256439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696309804916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688699841499329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686163306236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679821670055389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672211527824402</t>
+    <t xml:space="preserve">0.696309745311737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688699781894684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686163187026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679821610450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672211587429047</t>
   </si>
   <si>
     <t xml:space="preserve">0.646845102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677284896373749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658260107040405</t>
+    <t xml:space="preserve">0.677284836769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658259987831116</t>
   </si>
   <si>
     <t xml:space="preserve">0.659528374671936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651918470859528</t>
+    <t xml:space="preserve">0.651918411254883</t>
   </si>
   <si>
     <t xml:space="preserve">0.648113429546356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641771733760834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635430157184601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643040180206299</t>
+    <t xml:space="preserve">0.641771852970123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635430216789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643040239810944</t>
   </si>
   <si>
     <t xml:space="preserve">0.639235198497772</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">0.637966930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594209671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596746325492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609429597854614</t>
+    <t xml:space="preserve">0.594209611415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596746385097504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609429657459259</t>
   </si>
   <si>
     <t xml:space="preserve">0.598014712333679</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">0.599917113780975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603722155094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573916435241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621478676795959</t>
+    <t xml:space="preserve">0.603722214698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573916554450989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621478736400604</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">0.6233811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612600386142731</t>
+    <t xml:space="preserve">0.612600445747375</t>
   </si>
   <si>
     <t xml:space="preserve">0.591038942337036</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">0.584063172340393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580892324447632</t>
+    <t xml:space="preserve">0.580892205238342</t>
   </si>
   <si>
     <t xml:space="preserve">0.565672397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570745766162872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561233222484589</t>
+    <t xml:space="preserve">0.570745646953583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
     <t xml:space="preserve">0.572648167610168</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">0.559964954853058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135243415833</t>
+    <t xml:space="preserve">0.537135183811188</t>
   </si>
   <si>
     <t xml:space="preserve">0.528891026973724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573282361030579</t>
+    <t xml:space="preserve">0.573282420635223</t>
   </si>
   <si>
     <t xml:space="preserve">0.569477379322052</t>
@@ -1466,25 +1466,25 @@
     <t xml:space="preserve">0.608795404434204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618307888507843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630356967449188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604990482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580258131027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572014093399048</t>
+    <t xml:space="preserve">0.618307828903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356907844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604990422725677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580258190631866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572013974189758</t>
   </si>
   <si>
     <t xml:space="preserve">0.568209111690521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554891586303711</t>
+    <t xml:space="preserve">0.554891645908356</t>
   </si>
   <si>
     <t xml:space="preserve">0.629722714424133</t>
@@ -1493,46 +1493,46 @@
     <t xml:space="preserve">0.721676230430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766067504882812</t>
+    <t xml:space="preserve">0.766067564487457</t>
   </si>
   <si>
     <t xml:space="preserve">0.782555818557739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828215539455414</t>
+    <t xml:space="preserve">0.828215420246124</t>
   </si>
   <si>
     <t xml:space="preserve">0.825678825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873875021934509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871338427066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753312587738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880216777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903046607971191</t>
+    <t xml:space="preserve">0.873875141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871338486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880216658115387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903046548366547</t>
   </si>
   <si>
     <t xml:space="preserve">0.922071397304535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937291324138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918266475200653</t>
+    <t xml:space="preserve">0.937291264533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918266415596008</t>
   </si>
   <si>
     <t xml:space="preserve">0.86626523733139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839630365371704</t>
+    <t xml:space="preserve">0.839630424976349</t>
   </si>
   <si>
     <t xml:space="preserve">0.896704912185669</t>
@@ -1541,106 +1541,106 @@
     <t xml:space="preserve">0.876411736011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868801772594452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070040225983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559591770172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934754610061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314815998077</t>
+    <t xml:space="preserve">0.868801832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070159435272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559651374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93475466966629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314875602722</t>
   </si>
   <si>
     <t xml:space="preserve">0.905583202838898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929681241512299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144706249237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906851470470428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930949807167053</t>
+    <t xml:space="preserve">0.929681420326233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144765853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906851589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930949687957764</t>
   </si>
   <si>
     <t xml:space="preserve">0.891631603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833288729190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873843669891</t>
+    <t xml:space="preserve">0.833288788795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873903274536</t>
   </si>
   <si>
     <t xml:space="preserve">0.802848935127258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755921065807343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640503525733948</t>
+    <t xml:space="preserve">0.755920946598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640503466129303</t>
   </si>
   <si>
     <t xml:space="preserve">0.636698544025421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627019226551056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641851961612701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625670731067657</t>
+    <t xml:space="preserve">0.627019286155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641852021217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625670850276947</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534986972809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616905987262726</t>
+    <t xml:space="preserve">0.616906046867371</t>
   </si>
   <si>
     <t xml:space="preserve">0.618928611278534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595331192016602</t>
+    <t xml:space="preserve">0.595331132411957</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597353756427765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596005380153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60207337141037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598028004169464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594656944274902</t>
+    <t xml:space="preserve">0.59735381603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596005439758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602073311805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598028063774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594657063484192</t>
   </si>
   <si>
     <t xml:space="preserve">0.610838115215302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593982756137848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631064534187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623648166656494</t>
+    <t xml:space="preserve">0.593982696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631064474582672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623648107051849</t>
   </si>
   <si>
     <t xml:space="preserve">0.65398782491684</t>
@@ -1649,85 +1649,85 @@
     <t xml:space="preserve">0.656684637069702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637132406234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626345038414001</t>
+    <t xml:space="preserve">0.637132465839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626344978809357</t>
   </si>
   <si>
     <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624322354793549</t>
+    <t xml:space="preserve">0.624322414398193</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716098308563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627693474292755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614883422851562</t>
+    <t xml:space="preserve">0.6276935338974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614883363246918</t>
   </si>
   <si>
     <t xml:space="preserve">0.608815431594849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61758029460907</t>
+    <t xml:space="preserve">0.61758017539978</t>
   </si>
   <si>
     <t xml:space="preserve">0.635784029960632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624996542930603</t>
+    <t xml:space="preserve">0.624996483325958</t>
   </si>
   <si>
     <t xml:space="preserve">0.614209175109863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605444312095642</t>
+    <t xml:space="preserve">0.605444371700287</t>
   </si>
   <si>
     <t xml:space="preserve">0.606118559837341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630390286445618</t>
+    <t xml:space="preserve">0.630390346050262</t>
   </si>
   <si>
     <t xml:space="preserve">0.643200397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656010448932648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633761405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61218649148941</t>
+    <t xml:space="preserve">0.656010389328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633761346340179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612186551094055</t>
   </si>
   <si>
     <t xml:space="preserve">0.621625483036041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608141243457794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610163807868958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549484610557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56162041425705</t>
+    <t xml:space="preserve">0.608141183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610163867473602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549484550952911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561620533466339</t>
   </si>
   <si>
     <t xml:space="preserve">0.552855670452118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565665781497955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578475773334503</t>
+    <t xml:space="preserve">0.565665721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578475832939148</t>
   </si>
   <si>
     <t xml:space="preserve">0.558923602104187</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">0.563643097877502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569711029529572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249413967133</t>
+    <t xml:space="preserve">0.569710969924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249354362488</t>
   </si>
   <si>
     <t xml:space="preserve">0.562294661998749</t>
@@ -1748,49 +1748,49 @@
     <t xml:space="preserve">0.573082089424133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583869516849518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584543645381927</t>
+    <t xml:space="preserve">0.583869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584543704986572</t>
   </si>
   <si>
     <t xml:space="preserve">0.567014157772064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566339910030365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593308508396149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599376499652863</t>
+    <t xml:space="preserve">0.56633996963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593308448791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599376440048218</t>
   </si>
   <si>
     <t xml:space="preserve">0.586566388607025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591285824775696</t>
+    <t xml:space="preserve">0.591285884380341</t>
   </si>
   <si>
     <t xml:space="preserve">0.600050628185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60274749994278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60746705532074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590611696243286</t>
+    <t xml:space="preserve">0.602747440338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607466995716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590611577033997</t>
   </si>
   <si>
     <t xml:space="preserve">0.592634320259094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914884090424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618254423141479</t>
+    <t xml:space="preserve">0.587914705276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618254482746124</t>
   </si>
   <si>
     <t xml:space="preserve">0.639829277992249</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">0.588589012622833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598702192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620277106761932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62297397851944</t>
+    <t xml:space="preserve">0.598702251911163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620277047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622973918914795</t>
   </si>
   <si>
     <t xml:space="preserve">0.609489679336548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615557610988617</t>
+    <t xml:space="preserve">0.615557551383972</t>
   </si>
   <si>
     <t xml:space="preserve">0.620951354503632</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">0.648594081401825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604770183563232</t>
+    <t xml:space="preserve">0.604770123958588</t>
   </si>
   <si>
     <t xml:space="preserve">0.604095995426178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603421688079834</t>
+    <t xml:space="preserve">0.603421747684479</t>
   </si>
   <si>
     <t xml:space="preserve">0.639155089855194</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">0.638480842113495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655336141586304</t>
+    <t xml:space="preserve">0.655336260795593</t>
   </si>
   <si>
     <t xml:space="preserve">0.695789039134979</t>
@@ -1850,10 +1850,10 @@
     <t xml:space="preserve">0.702531278133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.699834406375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716015517711639</t>
+    <t xml:space="preserve">0.69983434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716015458106995</t>
   </si>
   <si>
     <t xml:space="preserve">0.728151440620422</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">0.717363953590393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726802945137024</t>
+    <t xml:space="preserve">0.726802885532379</t>
   </si>
   <si>
     <t xml:space="preserve">0.722757697105408</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">0.721409261226654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711970210075378</t>
+    <t xml:space="preserve">0.711970269680023</t>
   </si>
   <si>
     <t xml:space="preserve">0.701182782649994</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">0.694440603256226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683653235435486</t>
+    <t xml:space="preserve">0.689046919345856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683653295040131</t>
   </si>
   <si>
     <t xml:space="preserve">0.679607927799225</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">0.680956363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672191619873047</t>
+    <t xml:space="preserve">0.672191500663757</t>
   </si>
   <si>
     <t xml:space="preserve">0.68500167131424</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">0.668146312236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631738722324371</t>
+    <t xml:space="preserve">0.631738662719727</t>
   </si>
   <si>
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919893264771</t>
+    <t xml:space="preserve">0.647919952869415</t>
   </si>
   <si>
     <t xml:space="preserve">0.645897269248962</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">0.636458218097687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633087158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611512243747711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574430525302887</t>
+    <t xml:space="preserve">0.63308721780777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611512303352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">0.589263260364532</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">0.560271978378296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553529798984528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538697242736816</t>
+    <t xml:space="preserve">0.553529858589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538697123527527</t>
   </si>
   <si>
     <t xml:space="preserve">0.527235507965088</t>
@@ -1946,43 +1946,43 @@
     <t xml:space="preserve">0.478692084550858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463859379291534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458465695381165</t>
+    <t xml:space="preserve">0.463859438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45846563577652</t>
   </si>
   <si>
     <t xml:space="preserve">0.391044229269028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419361174106598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394415318965912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387673139572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388347417116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380256831645966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403180122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412619024515152</t>
+    <t xml:space="preserve">0.41936120390892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394415259361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387673169374466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388347387313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380256861448288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403180062770844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412619143724442</t>
   </si>
   <si>
     <t xml:space="preserve">0.431497097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46520784497261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927310943604</t>
+    <t xml:space="preserve">0.465207815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927340745926</t>
   </si>
   <si>
     <t xml:space="preserve">0.479366362094879</t>
@@ -1991,34 +1991,34 @@
     <t xml:space="preserve">0.489479511976242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474646866321564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473298460245132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411610126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498918533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496895849704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495547443628311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511054456233978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482063144445419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490827918052673</t>
+    <t xml:space="preserve">0.474646747112274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473298400640488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533627033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411580324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918563127518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496895909309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495547503232956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511054396629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482063174247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490827947854996</t>
   </si>
   <si>
     <t xml:space="preserve">0.484760016202927</t>
@@ -2027,58 +2027,58 @@
     <t xml:space="preserve">0.480714738368988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482737362384796</t>
+    <t xml:space="preserve">0.482737421989441</t>
   </si>
   <si>
     <t xml:space="preserve">0.485434234142303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488131105899811</t>
+    <t xml:space="preserve">0.488131076097488</t>
   </si>
   <si>
     <t xml:space="preserve">0.481388956308365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472624182701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42745178937912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434868186712265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438239246606827</t>
+    <t xml:space="preserve">0.472624152898788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427451878786087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434868156909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43823915719986</t>
   </si>
   <si>
     <t xml:space="preserve">0.443632960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430148661136627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40924808382988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434212148189545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410049825906754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892401218414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449135988950729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4512679874897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456953287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486800849437714</t>
+    <t xml:space="preserve">0.43014869093895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409248024225235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434212177991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410049855709076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892431020737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449136048555374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451268017292023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456953257322311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486800909042358</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
@@ -2090,43 +2090,43 @@
     <t xml:space="preserve">0.453399956226349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466191828250885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46690246462822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480404913425446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498882114887238</t>
+    <t xml:space="preserve">0.466191798448563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466902494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480404943227768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498882085084915</t>
   </si>
   <si>
     <t xml:space="preserve">0.48822221159935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477562338113785</t>
+    <t xml:space="preserve">0.477562308311462</t>
   </si>
   <si>
     <t xml:space="preserve">0.445582717657089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442740052938461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452689379453659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447004050016403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450557321310043</t>
+    <t xml:space="preserve">0.442740082740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452689349651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447003990411758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450557380914688</t>
   </si>
   <si>
     <t xml:space="preserve">0.448425322771072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442029356956482</t>
+    <t xml:space="preserve">0.442029386758804</t>
   </si>
   <si>
     <t xml:space="preserve">0.42994824051857</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">0.438476145267487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429237514734268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447714686393738</t>
+    <t xml:space="preserve">0.429237574338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447714656591415</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463349133729935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458374559879303</t>
+    <t xml:space="preserve">0.463349193334579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458374530076981</t>
   </si>
   <si>
     <t xml:space="preserve">0.444161415100098</t>
@@ -2159,55 +2159,55 @@
     <t xml:space="preserve">0.449846655130386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455531895160675</t>
+    <t xml:space="preserve">0.455531924962997</t>
   </si>
   <si>
     <t xml:space="preserve">0.443450748920441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430658906698227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420709639787674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427816271781921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413603067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417156428098679</t>
+    <t xml:space="preserve">0.430658876895905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420709669589996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427816212177277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413603127002716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417156398296356</t>
   </si>
   <si>
     <t xml:space="preserve">0.416445732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427105575799942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437054842710495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432080179452896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434922784566879</t>
+    <t xml:space="preserve">0.427105605602264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437054812908173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432080209255219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434922873973846</t>
   </si>
   <si>
     <t xml:space="preserve">0.422841668128967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417867064476013</t>
+    <t xml:space="preserve">0.417867034673691</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40791779756546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397968590259552</t>
+    <t xml:space="preserve">0.407917827367783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397968620061874</t>
   </si>
   <si>
     <t xml:space="preserve">0.403653919696808</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">0.401521891355515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405075162649155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400811225175858</t>
+    <t xml:space="preserve">0.405075222253799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400811284780502</t>
   </si>
   <si>
     <t xml:space="preserve">0.387308746576309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385176748037338</t>
+    <t xml:space="preserve">0.385176718235016</t>
   </si>
   <si>
     <t xml:space="preserve">0.400100588798523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41573503613472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398679256439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409339159727097</t>
+    <t xml:space="preserve">0.415735006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398679226636887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409339129924774</t>
   </si>
   <si>
     <t xml:space="preserve">0.395836621522903</t>
@@ -2246,58 +2246,58 @@
     <t xml:space="preserve">0.382334113121033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370963633060455</t>
+    <t xml:space="preserve">0.370963603258133</t>
   </si>
   <si>
     <t xml:space="preserve">0.383755475282669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366699606180191</t>
+    <t xml:space="preserve">0.366699635982513</t>
   </si>
   <si>
     <t xml:space="preserve">0.363146334886551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3539077937603</t>
+    <t xml:space="preserve">0.353907823562622</t>
   </si>
   <si>
     <t xml:space="preserve">0.356750428676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359593033790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358882427215576</t>
+    <t xml:space="preserve">0.359593063592911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358882397413254</t>
   </si>
   <si>
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730019330978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151411294937</t>
+    <t xml:space="preserve">0.388730078935623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151351690292</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372384935617447</t>
+    <t xml:space="preserve">0.372384905815125</t>
   </si>
   <si>
     <t xml:space="preserve">0.36385703086853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361725062131882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355329126119614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353552490472794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354618489742279</t>
+    <t xml:space="preserve">0.361725032329559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355329096317291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353552460670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354618459939957</t>
   </si>
   <si>
     <t xml:space="preserve">0.351775825023651</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">0.351065158843994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334009379148483</t>
+    <t xml:space="preserve">0.334009349346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.323349505662918</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">0.361014395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360303729772568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389440715312958</t>
+    <t xml:space="preserve">0.36030375957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389440685510635</t>
   </si>
   <si>
     <t xml:space="preserve">0.396547317504883</t>
@@ -2339,28 +2339,28 @@
     <t xml:space="preserve">0.41218176484108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421420305967331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415024399757385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419999003410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313733577728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405785858631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402232527732849</t>
+    <t xml:space="preserve">0.421420365571976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415024369955063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419999063014984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313763380051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405785828828812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402232557535172</t>
   </si>
   <si>
     <t xml:space="preserve">0.418577671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419288337230682</t>
+    <t xml:space="preserve">0.419288396835327</t>
   </si>
   <si>
     <t xml:space="preserve">0.399389892816544</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">0.40436452627182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395125985145569</t>
+    <t xml:space="preserve">0.395126014947891</t>
   </si>
   <si>
     <t xml:space="preserve">0.386598110198975</t>
@@ -2390,61 +2390,61 @@
     <t xml:space="preserve">0.380202174186707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806238174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369542241096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368831634521484</t>
+    <t xml:space="preserve">0.373806208372116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369542270898819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368831604719162</t>
   </si>
   <si>
     <t xml:space="preserve">0.364567697048187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428526878356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423552364110947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436344116926193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.426394939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440608084201813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897477626801</t>
+    <t xml:space="preserve">0.428526937961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423552274703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43634420633316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42639496922493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440608114004135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897418022156</t>
   </si>
   <si>
     <t xml:space="preserve">0.464770466089249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471877038478851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478983670473099</t>
+    <t xml:space="preserve">0.471877068281174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478983640670776</t>
   </si>
   <si>
     <t xml:space="preserve">0.492486149072647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515227198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512384653091431</t>
+    <t xml:space="preserve">0.515227258205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512384533882141</t>
   </si>
   <si>
     <t xml:space="preserve">0.506699323654175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517359137535095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120596408844</t>
+    <t xml:space="preserve">0.51735919713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120656013489</t>
   </si>
   <si>
     <t xml:space="preserve">0.513805866241455</t>
@@ -2459,31 +2459,31 @@
     <t xml:space="preserve">0.513095259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522333800792694</t>
+    <t xml:space="preserve">0.522333860397339</t>
   </si>
   <si>
     <t xml:space="preserve">0.537257611751556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523755073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525887072086334</t>
+    <t xml:space="preserve">0.523755133152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525887131690979</t>
   </si>
   <si>
     <t xml:space="preserve">0.526597738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525176465511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530151009559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524465799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538679003715515</t>
+    <t xml:space="preserve">0.525176405906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530151069164276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52446573972702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
     <t xml:space="preserve">0.544364213943481</t>
@@ -2492,25 +2492,25 @@
     <t xml:space="preserve">0.541521608829498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536546945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528729796409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518780529499054</t>
+    <t xml:space="preserve">0.536547005176544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528729736804962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518780469894409</t>
   </si>
   <si>
     <t xml:space="preserve">0.515937864780426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523044466972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54223221540451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531572461128235</t>
+    <t xml:space="preserve">0.523044526576996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542232275009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531572341918945</t>
   </si>
   <si>
     <t xml:space="preserve">0.542942881584167</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">0.549338817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5649733543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550941228866577</t>
+    <t xml:space="preserve">0.564973294734955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550941288471222</t>
   </si>
   <si>
     <t xml:space="preserve">0.549464225769043</t>
@@ -2531,22 +2531,22 @@
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647724151611</t>
+    <t xml:space="preserve">0.537647783756256</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569902896881</t>
+    <t xml:space="preserve">0.526569843292236</t>
   </si>
   <si>
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753460884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518446147441864</t>
+    <t xml:space="preserve">0.514753401279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518446087837219</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">0.546510100364685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553156852722168</t>
+    <t xml:space="preserve">0.553156912326813</t>
   </si>
   <si>
     <t xml:space="preserve">0.56128066778183</t>
@@ -2573,25 +2573,25 @@
     <t xml:space="preserve">0.563496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566450417041779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572358548641205</t>
+    <t xml:space="preserve">0.566450297832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57235848903656</t>
   </si>
   <si>
     <t xml:space="preserve">0.581220924854279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584174990653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58343642950058</t>
+    <t xml:space="preserve">0.584175050258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583436489105225</t>
   </si>
   <si>
     <t xml:space="preserve">0.575312674045563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56866592168808</t>
+    <t xml:space="preserve">0.568665862083435</t>
   </si>
   <si>
     <t xml:space="preserve">0.54281747341156</t>
@@ -2603,10 +2603,10 @@
     <t xml:space="preserve">0.536170721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527308404445648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522877216339111</t>
+    <t xml:space="preserve">0.527308344841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522877275943756</t>
   </si>
   <si>
     <t xml:space="preserve">0.53543221950531</t>
@@ -2618,34 +2618,34 @@
     <t xml:space="preserve">0.51696902513504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511060833930969</t>
+    <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
     <t xml:space="preserve">0.511799335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50958377122879</t>
+    <t xml:space="preserve">0.509583711624146</t>
   </si>
   <si>
     <t xml:space="preserve">0.506629586219788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487427949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48816642165184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735263347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488905012607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48078116774559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48151969909668</t>
+    <t xml:space="preserve">0.487427920103073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488166481256485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735293149948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488904982805252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480781227350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481519728899002</t>
   </si>
   <si>
     <t xml:space="preserve">0.492597579956055</t>
@@ -2654,31 +2654,31 @@
     <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525831341743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534693658351898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532478153705597</t>
+    <t xml:space="preserve">0.525831401348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534693598747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532478034496307</t>
   </si>
   <si>
     <t xml:space="preserve">0.519923150539398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517707526683807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512537896633148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514014840126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525092899799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545033037662506</t>
+    <t xml:space="preserve">0.517707586288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512537777423859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514014899730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525092840194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545032978057861</t>
   </si>
   <si>
     <t xml:space="preserve">0.528785467147827</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">0.533216595649719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520661592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515491902828217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508106648921967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505152583122253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50219851732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495551735162735</t>
+    <t xml:space="preserve">0.520661652088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515491962432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508106708526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505152523517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502198457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495551764965057</t>
   </si>
   <si>
     <t xml:space="preserve">0.498505830764771</t>
@@ -2711,28 +2711,28 @@
     <t xml:space="preserve">0.502937018871307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504414081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500721454620361</t>
+    <t xml:space="preserve">0.504414021968842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500721395015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.545771598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540601909160614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553895354270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55020272731781</t>
+    <t xml:space="preserve">0.540601849555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55389541387558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550202786922455</t>
   </si>
   <si>
     <t xml:space="preserve">0.547987163066864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538386285305023</t>
+    <t xml:space="preserve">0.538386225700378</t>
   </si>
   <si>
     <t xml:space="preserve">0.530262470245361</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">0.539863348007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613716006278992</t>
+    <t xml:space="preserve">0.613716065883636</t>
   </si>
   <si>
     <t xml:space="preserve">0.641780138015747</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">0.622578382492065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627009570598602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612977504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616670191287994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629963636398315</t>
+    <t xml:space="preserve">0.627009510993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612977564334869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61667013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62996369600296</t>
   </si>
   <si>
     <t xml:space="preserve">0.620362818241119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615193128585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601161062717438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594514429569244</t>
+    <t xml:space="preserve">0.61519318819046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601161122322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594514310359955</t>
   </si>
   <si>
     <t xml:space="preserve">0.599684000015259</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">0.607069313526154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593037247657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597468495368958</t>
+    <t xml:space="preserve">0.593037307262421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597468435764313</t>
   </si>
   <si>
     <t xml:space="preserve">0.592298746109009</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">0.641041576862335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664674460887909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6668900847435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658766269683838</t>
+    <t xml:space="preserve">0.664674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66688996553421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658766210079193</t>
   </si>
   <si>
     <t xml:space="preserve">0.653596520423889</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.667628526687622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648426830768585</t>
+    <t xml:space="preserve">0.64842689037323</t>
   </si>
   <si>
     <t xml:space="preserve">0.647688329219818</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">0.629225134849548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642518579959869</t>
+    <t xml:space="preserve">0.642518699169159</t>
   </si>
   <si>
     <t xml:space="preserve">0.640303015708923</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">0.649165391921997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655812084674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655073583126068</t>
+    <t xml:space="preserve">0.65581214427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655073642730713</t>
   </si>
   <si>
     <t xml:space="preserve">0.635871887207031</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">0.618147253990173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625532567501068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638087511062622</t>
+    <t xml:space="preserve">0.625532507896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638087451457977</t>
   </si>
   <si>
     <t xml:space="preserve">0.643995702266693</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">0.62627100944519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630702197551727</t>
+    <t xml:space="preserve">0.630702137947083</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2882,22 +2882,22 @@
     <t xml:space="preserve">0.662458837032318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678706407546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676490843296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673536777496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661720395088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635133326053619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576789736747742</t>
+    <t xml:space="preserve">0.678706467151642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676490902900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673536837100983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661720335483551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635133385658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576789677143097</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">0.587867677211761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507368147373199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529523909091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711736679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564234733581543</t>
+    <t xml:space="preserve">0.507368087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529523968696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711796283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564234793186188</t>
   </si>
   <si>
     <t xml:space="preserve">0.582697927951813</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">0.567188858985901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579743802547455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562019109725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557588040828705</t>
+    <t xml:space="preserve">0.5797438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562019169330597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55758798122406</t>
   </si>
   <si>
     <t xml:space="preserve">0.543555974960327</t>
@@ -2957,292 +2957,295 @@
     <t xml:space="preserve">0.569404423236847</t>
   </si>
   <si>
+    <t xml:space="preserve">0.574574053287506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58257657289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973668575287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576174676418304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570572912693024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568172216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169756412506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562570512294769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569772720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578575372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566571712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571373164653778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564971208572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552967607975006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546565651893616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537762999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755738735199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516156435012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525759339332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521758139133453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536962747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548166155815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526559591293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522558391094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532961547374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524959087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508153975009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484146744012833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48094579577446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5057532787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493749648332596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487347722053528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488147974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561770260334015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56097000837326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58897852897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568972408771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572173416614532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575374364852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577775120735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565771520137787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580976128578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581776320934296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58337676525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576974868774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579375565052032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584977269172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586577773094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585777521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591379284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564170956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555368304252625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567371964454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563370764255524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544164955615997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54096394777298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543364703655243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542564392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535362303256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536162495613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520957887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528960347175598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528160095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523358643054962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516956686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515356242656708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508954226970673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506553530693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502552330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517756938934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510554730892181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524158835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529760539531708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531361043453217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550566911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532161295413971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530560791492462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527359783649445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512155175209045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534561991691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520157635211945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540163695812225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54736590385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552167356014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556168556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557769060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548966348171234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556968808174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558569312095642</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.574574112892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582576513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973668575287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576174676418304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570572972297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568172216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169816017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562570512294769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569772720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566571712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571373164653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564971208572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552967607975006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54656571149826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537762999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755679130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516156435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525759339332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521758139133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536962747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548166155815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526559591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522558391094208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532961547374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524959087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508153975009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484146744012833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480945765972137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5057532787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493749648332596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48734775185585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48814794421196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56177031993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56097000837326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588978469371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568972527980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572173416614532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575374364852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577775120735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565771460533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580976068973541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581776320934296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58337676525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576974928379059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579375565052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584977269172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586577773094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585777580738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591379284858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564170956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555368363857269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567371904850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563370764255524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544164955615997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54096394777298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543364703655243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542564451694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535362303256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536162495613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520957887172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528960287570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528160095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523358643054962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516956686973572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515356183052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508954226970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506553530693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502552330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517756938934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510554790496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524158835411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529760599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531361043453217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550566852092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532161295413971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530560791492462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527359843254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51215523481369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534561991691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520157635211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540163695812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54736590385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552167356014252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556168556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557769060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548966348171234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559369564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556968748569489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558569252490997</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.584177076816559</t>
   </si>
   <si>
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773860931396</t>
+    <t xml:space="preserve">0.573773920536041</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612185537815094</t>
+    <t xml:space="preserve">0.612185478210449</t>
   </si>
   <si>
     <t xml:space="preserve">0.616986989974976</t>
@@ -3251,19 +3254,19 @@
     <t xml:space="preserve">0.621788501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624189138412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622588694095612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620187938213348</t>
+    <t xml:space="preserve">0.62418919801712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622588634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620187878608704</t>
   </si>
   <si>
     <t xml:space="preserve">0.599381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60418313741684</t>
+    <t xml:space="preserve">0.604183077812195</t>
   </si>
   <si>
     <t xml:space="preserve">0.602582693099976</t>
@@ -3281,25 +3284,25 @@
     <t xml:space="preserve">0.616186738014221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624989449977875</t>
+    <t xml:space="preserve">0.62498939037323</t>
   </si>
   <si>
     <t xml:space="preserve">0.628190398216248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636192858219147</t>
+    <t xml:space="preserve">0.636192798614502</t>
   </si>
   <si>
     <t xml:space="preserve">0.640194058418274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643394947052002</t>
+    <t xml:space="preserve">0.643395006656647</t>
   </si>
   <si>
     <t xml:space="preserve">0.637793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641794502735138</t>
+    <t xml:space="preserve">0.641794443130493</t>
   </si>
   <si>
     <t xml:space="preserve">0.647396206855774</t>
@@ -3311,19 +3314,19 @@
     <t xml:space="preserve">0.633792042732239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620988190174103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628990709781647</t>
+    <t xml:space="preserve">0.620988249778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.635921716690063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651516497135162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641986310482025</t>
+    <t xml:space="preserve">0.651516437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64198637008667</t>
   </si>
   <si>
     <t xml:space="preserve">0.631589770317078</t>
@@ -3332,34 +3335,31 @@
     <t xml:space="preserve">0.627257883548737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615128636360168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262163639069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663043498993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197629451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615995049476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62119323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628990650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640253603458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723357200623</t>
+    <t xml:space="preserve">0.615128576755524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197569847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464803218842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615994989871979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621193289756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64025354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723416805267</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732036590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619460463523865</t>
+    <t xml:space="preserve">0.604732096195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61946052312851</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395810127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331216335297</t>
+    <t xml:space="preserve">0.612529516220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395869731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331156730652</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62032687664032</t>
+    <t xml:space="preserve">0.620326936244965</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801029682159</t>
+    <t xml:space="preserve">0.597801089286804</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658823013306</t>
+    <t xml:space="preserve">0.624658763408661</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861402988434</t>
+    <t xml:space="preserve">0.617727696895599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861343383789</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387190341949</t>
+    <t xml:space="preserve">0.639387130737305</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382910251617</t>
+    <t xml:space="preserve">0.652382850646973</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848383903503</t>
+    <t xml:space="preserve">0.655848443508148</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042344093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687037944793701</t>
+    <t xml:space="preserve">0.674042284488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687038004398346</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682706117630005</t>
+    <t xml:space="preserve">0.68270605802536</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637184143066</t>
+    <t xml:space="preserve">0.689637124538422</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739887058734894</t>
+    <t xml:space="preserve">0.739886999130249</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412905693054</t>
+    <t xml:space="preserve">0.762412965297699</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3587,118 +3587,121 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
+    <t xml:space="preserve">0.779740452766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76846718788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757193803787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745920479297638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751557111740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753435969352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742162644863129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7346470952034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.732768177986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727131485939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723373711109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73088926076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725252628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729010403156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712100386619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713979244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719615936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717737019062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704584777355194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708342611789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691432535648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702705919742584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69894814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697069227695465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70082700252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706463634967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710221469402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715858161449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721494853496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69519031047821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676401436328888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740283727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73652595281601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749678194522858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760951578617096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787256062030792</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.779740512371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76846718788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76658821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757193803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745920479297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751557111740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753435969352722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742162644863129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7346470952034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.732768177986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727131485939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723373711109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73088926076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725252628326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729010403156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712100386619568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713979244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719615936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717737019062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704584777355194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708342611789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691432535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702705919742584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697069227695465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70082700252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706463634967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710221469402313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715858161449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721494853496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69519031047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676401436328888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740283727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73652595281601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738404870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749678194522858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760951578617096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787256062030792</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -51357,7 +51360,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="s">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51591,7 +51594,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1815" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51617,7 +51620,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51695,7 +51698,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1819" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51799,7 +51802,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="s">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51825,7 +51828,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="s">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51903,7 +51906,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52241,7 +52244,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G1840" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52267,7 +52270,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1841" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52293,7 +52296,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1842" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52319,7 +52322,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1843" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52345,7 +52348,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1844" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52371,7 +52374,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1845" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52397,7 +52400,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52423,7 +52426,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1847" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52449,7 +52452,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52475,7 +52478,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52501,7 +52504,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52527,7 +52530,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1851" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52553,7 +52556,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1852" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52579,7 +52582,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1853" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52605,7 +52608,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1854" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52631,7 +52634,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52657,7 +52660,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1856" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52683,7 +52686,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1857" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52709,7 +52712,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1858" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52735,7 +52738,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1859" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52761,7 +52764,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52787,7 +52790,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1861" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52813,7 +52816,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1862" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52839,7 +52842,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1863" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52865,7 +52868,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1864" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52891,7 +52894,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1865" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52917,7 +52920,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1866" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52943,7 +52946,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1867" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52969,7 +52972,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52995,7 +52998,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53021,7 +53024,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1870" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53047,7 +53050,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1871" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53073,7 +53076,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1872" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53099,7 +53102,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53125,7 +53128,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1874" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53151,7 +53154,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1875" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53177,7 +53180,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53203,7 +53206,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1877" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53229,7 +53232,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53255,7 +53258,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1879" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53281,7 +53284,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1880" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53307,7 +53310,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1881" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53333,7 +53336,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53359,7 +53362,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53385,7 +53388,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53411,7 +53414,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1885" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53437,7 +53440,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1886" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53463,7 +53466,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53489,7 +53492,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1888" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53515,7 +53518,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1889" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53541,7 +53544,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1890" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53567,7 +53570,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1891" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53593,7 +53596,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1892" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53619,7 +53622,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1893" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53645,7 +53648,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53671,7 +53674,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1895" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53697,7 +53700,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53723,7 +53726,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53853,7 +53856,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53983,7 +53986,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54035,7 +54038,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54165,7 +54168,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1914" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54191,7 +54194,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54243,7 +54246,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1917" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54321,7 +54324,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1920" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54373,7 +54376,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1922" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54451,7 +54454,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1925" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54477,7 +54480,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54607,7 +54610,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1931" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54633,7 +54636,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1932" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54659,7 +54662,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1933" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54711,7 +54714,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54815,7 +54818,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54841,7 +54844,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1940" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54945,7 +54948,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54971,7 +54974,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1945" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55023,7 +55026,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1947" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55257,7 +55260,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1956" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55387,7 +55390,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1961" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55413,7 +55416,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1962" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55439,7 +55442,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1963" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55465,7 +55468,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1964" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55491,7 +55494,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1965" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55647,7 +55650,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1971" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56037,7 +56040,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1986" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56271,7 +56274,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1995" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56349,7 +56352,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1998" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56401,7 +56404,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2000" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56479,7 +56482,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2003" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56505,7 +56508,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2004" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56531,7 +56534,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2005" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56557,7 +56560,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2006" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56583,7 +56586,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2007" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56687,7 +56690,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2011" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56869,7 +56872,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2018" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56895,7 +56898,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57207,7 +57210,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57233,7 +57236,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57311,7 +57314,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57337,7 +57340,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58143,7 +58146,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G2067" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58299,7 +58302,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58377,7 +58380,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58481,7 +58484,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58559,7 +58562,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -63239,7 +63242,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1191</v>
+        <v>1229</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63265,7 +63268,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63291,7 +63294,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63317,7 +63320,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63343,7 +63346,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63369,7 +63372,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63395,7 +63398,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63421,7 +63424,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63447,7 +63450,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63473,7 +63476,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63499,7 +63502,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63525,7 +63528,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63551,7 +63554,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63577,7 +63580,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63603,7 +63606,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63629,7 +63632,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63655,7 +63658,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63681,7 +63684,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63707,7 +63710,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63733,7 +63736,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63759,7 +63762,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63785,7 +63788,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63811,7 +63814,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63837,7 +63840,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63863,7 +63866,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63889,7 +63892,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63915,7 +63918,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63941,7 +63944,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63967,7 +63970,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63993,7 +63996,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64019,7 +64022,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64045,7 +64048,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64071,7 +64074,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64097,7 +64100,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64123,7 +64126,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64149,7 +64152,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64175,7 +64178,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64201,7 +64204,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64227,7 +64230,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64253,7 +64256,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64279,7 +64282,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64305,7 +64308,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64331,7 +64334,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64357,7 +64360,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64383,7 +64386,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64409,7 +64412,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64435,7 +64438,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64461,7 +64464,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64487,7 +64490,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64513,7 +64516,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64539,7 +64542,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64565,7 +64568,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64591,7 +64594,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64617,7 +64620,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64643,7 +64646,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64669,7 +64672,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64695,7 +64698,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64721,7 +64724,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64747,7 +64750,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64773,7 +64776,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64799,7 +64802,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64825,7 +64828,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64851,7 +64854,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64877,7 +64880,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64903,7 +64906,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64929,7 +64932,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64955,7 +64958,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64981,7 +64984,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65007,7 +65010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65033,7 +65036,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65059,7 +65062,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65085,7 +65088,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65111,7 +65114,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65137,7 +65140,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65163,7 +65166,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65189,7 +65192,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65215,7 +65218,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65241,7 +65244,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65267,7 +65270,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65293,7 +65296,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65319,7 +65322,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65345,7 +65348,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65371,7 +65374,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65397,7 +65400,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65423,7 +65426,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65449,7 +65452,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65475,7 +65478,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65501,7 +65504,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65527,7 +65530,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65553,7 +65556,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65579,7 +65582,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65605,7 +65608,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65631,7 +65634,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65657,7 +65660,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65683,7 +65686,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65709,7 +65712,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65735,7 +65738,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65761,7 +65764,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65787,7 +65790,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65813,7 +65816,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65839,7 +65842,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65865,7 +65868,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65891,7 +65894,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65917,7 +65920,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65943,7 +65946,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65969,7 +65972,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65995,7 +65998,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66021,7 +66024,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66047,7 +66050,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66073,7 +66076,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66099,7 +66102,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66125,7 +66128,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66151,7 +66154,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66177,7 +66180,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66203,7 +66206,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66229,7 +66232,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66255,7 +66258,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66281,7 +66284,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66307,7 +66310,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66333,7 +66336,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66359,7 +66362,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66385,7 +66388,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66411,7 +66414,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66437,7 +66440,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66463,7 +66466,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66489,7 +66492,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66515,7 +66518,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66541,7 +66544,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66567,7 +66570,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66593,7 +66596,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66619,7 +66622,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66645,7 +66648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66671,7 +66674,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66697,7 +66700,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66723,7 +66726,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66749,7 +66752,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66775,7 +66778,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66801,7 +66804,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66827,7 +66830,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66853,7 +66856,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66879,7 +66882,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66905,7 +66908,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66931,7 +66934,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66957,7 +66960,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66983,7 +66986,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67009,7 +67012,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67035,7 +67038,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67061,7 +67064,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67087,7 +67090,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67113,7 +67116,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67139,7 +67142,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67165,7 +67168,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67191,7 +67194,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67217,7 +67220,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67243,7 +67246,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67269,7 +67272,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67295,7 +67298,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67321,7 +67324,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67347,7 +67350,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67373,7 +67376,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67399,7 +67402,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67425,7 +67428,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67451,7 +67454,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67477,7 +67480,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67503,7 +67506,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67529,7 +67532,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67555,7 +67558,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67581,7 +67584,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67607,7 +67610,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67633,7 +67636,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67659,7 +67662,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67685,7 +67688,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67711,7 +67714,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67737,7 +67740,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67763,7 +67766,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67789,7 +67792,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67815,7 +67818,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67841,7 +67844,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67867,7 +67870,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67893,7 +67896,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67919,7 +67922,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67945,7 +67948,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67971,7 +67974,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67997,7 +68000,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68023,7 +68026,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68049,7 +68052,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68075,7 +68078,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68101,7 +68104,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68127,7 +68130,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68153,7 +68156,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68179,7 +68182,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68205,7 +68208,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68231,7 +68234,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68257,7 +68260,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68283,7 +68286,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68309,7 +68312,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68335,7 +68338,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68361,7 +68364,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68387,7 +68390,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68413,7 +68416,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68439,7 +68442,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68465,7 +68468,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68491,7 +68494,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68517,7 +68520,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68543,7 +68546,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68569,7 +68572,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68595,7 +68598,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68621,7 +68624,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68647,7 +68650,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68673,7 +68676,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68699,7 +68702,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68725,7 +68728,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68751,7 +68754,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68777,7 +68780,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68803,7 +68806,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68829,7 +68832,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68855,7 +68858,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68881,7 +68884,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68907,7 +68910,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68933,7 +68936,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68959,7 +68962,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68985,7 +68988,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69011,7 +69014,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69037,7 +69040,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69045,7 +69048,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6497685185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>216472</v>
@@ -69063,9 +69066,35 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6513425926</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>150944</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>1.04799997806549</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>1.03199994564056</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1353">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594666719437</t>
+    <t xml:space="preserve">0.378594696521759</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716685533524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367179721593857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3804971575737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789345741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352276921272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36813098192215</t>
+    <t xml:space="preserve">0.382716715335846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367179751396179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380497127771378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789375543594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3522769510746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368131011724472</t>
   </si>
   <si>
     <t xml:space="preserve">0.387155830860138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410936951637268</t>
+    <t xml:space="preserve">0.410936862230301</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009582042694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521357774734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886825084686</t>
+    <t xml:space="preserve">0.373521387577057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886884689331</t>
   </si>
   <si>
     <t xml:space="preserve">0.335471630096436</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.34561824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361472338438034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341496199369431</t>
+    <t xml:space="preserve">0.361472278833389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341496229171753</t>
   </si>
   <si>
     <t xml:space="preserve">0.355130672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352594047784805</t>
+    <t xml:space="preserve">0.352593988180161</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447459697723</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">0.360838115215302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357350200414658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35798442363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35069152712822</t>
+    <t xml:space="preserve">0.35735023021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357984393835068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350691497325897</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
@@ -116,43 +116,43 @@
     <t xml:space="preserve">0.291714459657669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297739058732986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27586042881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276240974664688</t>
+    <t xml:space="preserve">0.297739028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.275860399007797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276240944862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.304461121559143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326593339443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789036273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329129993915558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348471969366074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327544659376144</t>
+    <t xml:space="preserve">0.326593399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789066076279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32913002371788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348471999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327544629573822</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671128988266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330081254243851</t>
+    <t xml:space="preserve">0.330081284046173</t>
   </si>
   <si>
     <t xml:space="preserve">0.334203332662582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838793754578</t>
+    <t xml:space="preserve">0.386838763952255</t>
   </si>
   <si>
     <t xml:space="preserve">0.356398940086365</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">0.368765145540237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325325101613998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318032205104828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306236803531647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308329492807388</t>
+    <t xml:space="preserve">0.325325071811676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31803223490715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306236773729324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308329522609711</t>
   </si>
   <si>
     <t xml:space="preserve">0.331032514572144</t>
@@ -179,28 +179,28 @@
     <t xml:space="preserve">0.322788417339325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319934695959091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153914451599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331666707992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320251733064651</t>
+    <t xml:space="preserve">0.319934666156769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153974056244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331666678190231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320251762866974</t>
   </si>
   <si>
     <t xml:space="preserve">0.310802757740021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32342255115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308836847543716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306300222873688</t>
+    <t xml:space="preserve">0.323422580957413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308836817741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306300193071365</t>
   </si>
   <si>
     <t xml:space="preserve">0.298880487680435</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">0.260767340660095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267489492893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258738070726395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288543671369553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371618866920471</t>
+    <t xml:space="preserve">0.267489463090897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288543701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
     <t xml:space="preserve">0.364643096923828</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.367496848106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36971640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399279356003</t>
+    <t xml:space="preserve">0.369716376066208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399338960648</t>
   </si>
   <si>
     <t xml:space="preserve">0.388741225004196</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">0.387790024280548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033532381058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357033163309097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374155551195145</t>
+    <t xml:space="preserve">0.370033472776413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357033133506775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3741554915905</t>
   </si>
   <si>
     <t xml:space="preserve">0.377643406391144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370984643697739</t>
+    <t xml:space="preserve">0.370984673500061</t>
   </si>
   <si>
     <t xml:space="preserve">0.372253060340881</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">0.387472927570343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377326339483261</t>
+    <t xml:space="preserve">0.377326369285583</t>
   </si>
   <si>
     <t xml:space="preserve">0.439791232347488</t>
@@ -275,97 +275,97 @@
     <t xml:space="preserve">0.453425794839859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454059928655624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461669862270355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133207798004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455645352602005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456279516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840710163116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792279958725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485768049955368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47784098982811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483231425285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484816789627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497817069292068</t>
+    <t xml:space="preserve">0.454059958457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461669772863388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133177995682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45564529299736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456279456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840680360794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792250156403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485767930746078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477841019630432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483231365680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484816819429398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497817158699036</t>
   </si>
   <si>
     <t xml:space="preserve">0.489255875349045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475621402263641</t>
+    <t xml:space="preserve">0.475621432065964</t>
   </si>
   <si>
     <t xml:space="preserve">0.476889729499817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488304674625397</t>
+    <t xml:space="preserve">0.48830458521843</t>
   </si>
   <si>
     <t xml:space="preserve">0.493695050477982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489890038967133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548801660538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645632266998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084807395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495280504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486719250679016</t>
+    <t xml:space="preserve">0.489890098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548742055893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468645662069321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084777593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49528044462204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486719220876694</t>
   </si>
   <si>
     <t xml:space="preserve">0.48418253660202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497500002384186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507329523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507963716983795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514939486980438</t>
+    <t xml:space="preserve">0.497500091791153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50732958316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50796365737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514939427375793</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183274745941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515890717506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354432106018</t>
+    <t xml:space="preserve">0.515890657901764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354372501373</t>
   </si>
   <si>
     <t xml:space="preserve">0.525720238685608</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">0.52952516078949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535866796970367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540305912494659</t>
+    <t xml:space="preserve">0.535866856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540305852890015</t>
   </si>
   <si>
     <t xml:space="preserve">0.620844542980194</t>
@@ -389,97 +389,97 @@
     <t xml:space="preserve">0.627503156661987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597697556018829</t>
+    <t xml:space="preserve">0.597697615623474</t>
   </si>
   <si>
     <t xml:space="preserve">0.596112132072449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577087342739105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561867475509644</t>
+    <t xml:space="preserve">0.57708740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561867356300354</t>
   </si>
   <si>
     <t xml:space="preserve">0.583428919315338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569160342216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566940724849701</t>
+    <t xml:space="preserve">0.569160282611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566940784454346</t>
   </si>
   <si>
     <t xml:space="preserve">0.559013724327087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551720857620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529208064079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516841948032379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476141452789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516207814216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465791910886765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483548432588577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549184203147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547281682491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558379590511322</t>
+    <t xml:space="preserve">0.551720798015594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529208123683929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516842007637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516207754611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465791970491409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4835484623909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549184143543243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558379530906677</t>
   </si>
   <si>
     <t xml:space="preserve">0.585965573787689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586599707603455</t>
+    <t xml:space="preserve">0.586599826812744</t>
   </si>
   <si>
     <t xml:space="preserve">0.613868713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654455065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.665870010852814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655089318752289</t>
+    <t xml:space="preserve">0.654455006122589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.665869951248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655089259147644</t>
   </si>
   <si>
     <t xml:space="preserve">0.62306410074234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633844792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622112810611725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618942022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615137100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631625294685364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628771603107452</t>
+    <t xml:space="preserve">0.63384485244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62211287021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618942081928253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615137040615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631625235080719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628771543502808</t>
   </si>
   <si>
     <t xml:space="preserve">0.63416188955307</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">0.643674373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644308507442474</t>
+    <t xml:space="preserve">0.64430844783783</t>
   </si>
   <si>
     <t xml:space="preserve">0.64557683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636064410209656</t>
+    <t xml:space="preserve">0.636064469814301</t>
   </si>
   <si>
     <t xml:space="preserve">0.63479608297348</t>
@@ -512,46 +512,46 @@
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234889030457</t>
+    <t xml:space="preserve">0.626234948635101</t>
   </si>
   <si>
     <t xml:space="preserve">0.602453827857971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58818519115448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590087592601776</t>
+    <t xml:space="preserve">0.588185131549835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590087652206421</t>
   </si>
   <si>
     <t xml:space="preserve">0.58913642168045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.619893252849579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592941403388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600551247596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595795094966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594526767730713</t>
+    <t xml:space="preserve">0.619893312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592941462993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600551307201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595795035362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594526827335358</t>
   </si>
   <si>
     <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601185500621796</t>
+    <t xml:space="preserve">0.601185441017151</t>
   </si>
   <si>
     <t xml:space="preserve">0.603087902069092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60974657535553</t>
+    <t xml:space="preserve">0.609746634960175</t>
   </si>
   <si>
     <t xml:space="preserve">0.611332058906555</t>
@@ -560,79 +560,79 @@
     <t xml:space="preserve">0.614185810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611966192722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605941712856293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5986487865448</t>
+    <t xml:space="preserve">0.61196631193161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605941653251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598648846149445</t>
   </si>
   <si>
     <t xml:space="preserve">0.593258440494537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588502287864685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380518913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617673695087433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61101508140564</t>
+    <t xml:space="preserve">0.58850222826004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380578517914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617673635482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61101496219635</t>
   </si>
   <si>
     <t xml:space="preserve">0.604039192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605307579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610063791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039442062378</t>
+    <t xml:space="preserve">0.605307519435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61006373167038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649465084076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039561271667</t>
   </si>
   <si>
     <t xml:space="preserve">0.61038076877594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596429228782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591356039047241</t>
+    <t xml:space="preserve">0.596429288387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591355979442596</t>
   </si>
   <si>
     <t xml:space="preserve">0.589770615100861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56535530090332</t>
+    <t xml:space="preserve">0.565355360507965</t>
   </si>
   <si>
     <t xml:space="preserve">0.523183584213257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481963038444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493377864360809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492109686136246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508280754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513988196849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509231984615326</t>
+    <t xml:space="preserve">0.481963068246841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493377923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492109626531601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508280813694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513988316059113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509232044219971</t>
   </si>
   <si>
     <t xml:space="preserve">0.509549081325531</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">0.517793238162994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548550069332123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544110953807831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521598219871521</t>
+    <t xml:space="preserve">0.548550128936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544110894203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521598160266876</t>
   </si>
   <si>
     <t xml:space="preserve">0.53047639131546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546013355255127</t>
+    <t xml:space="preserve">0.546013414859772</t>
   </si>
   <si>
     <t xml:space="preserve">0.54094010591507</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">0.532696008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538720607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539037585258484</t>
+    <t xml:space="preserve">0.538720548152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539037644863129</t>
   </si>
   <si>
     <t xml:space="preserve">0.533330142498016</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">0.532061874866486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568843185901642</t>
+    <t xml:space="preserve">0.568843245506287</t>
   </si>
   <si>
     <t xml:space="preserve">0.570428669452667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566306591033936</t>
+    <t xml:space="preserve">0.566306531429291</t>
   </si>
   <si>
     <t xml:space="preserve">0.549501299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560599207878113</t>
+    <t xml:space="preserve">0.560599148273468</t>
   </si>
   <si>
     <t xml:space="preserve">0.56440407037735</t>
@@ -695,40 +695,40 @@
     <t xml:space="preserve">0.550452530384064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542842626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545062184333801</t>
+    <t xml:space="preserve">0.54284256696701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545062124729156</t>
   </si>
   <si>
     <t xml:space="preserve">0.521281063556671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516524910926819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506695330142975</t>
+    <t xml:space="preserve">0.516524851322174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50669538974762</t>
   </si>
   <si>
     <t xml:space="preserve">0.528256893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519695699214935</t>
+    <t xml:space="preserve">0.519695639610291</t>
   </si>
   <si>
     <t xml:space="preserve">0.526037275791168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518744468688965</t>
+    <t xml:space="preserve">0.51874440908432</t>
   </si>
   <si>
     <t xml:space="preserve">0.511451601982117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514305353164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523817658424377</t>
+    <t xml:space="preserve">0.514305293560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523817718029022</t>
   </si>
   <si>
     <t xml:space="preserve">0.508597791194916</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">0.513671159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511134505271912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504158675670624</t>
+    <t xml:space="preserve">0.511134445667267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504158794879913</t>
   </si>
   <si>
     <t xml:space="preserve">0.506061136722565</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">0.510500311851501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499719500541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512085735797882</t>
+    <t xml:space="preserve">0.499719560146332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512085855007172</t>
   </si>
   <si>
     <t xml:space="preserve">0.541574239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550769686698914</t>
+    <t xml:space="preserve">0.550769627094269</t>
   </si>
   <si>
     <t xml:space="preserve">0.553623378276825</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">0.655723452568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358145713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262642383575</t>
+    <t xml:space="preserve">0.682358205318451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76226270198822</t>
   </si>
   <si>
     <t xml:space="preserve">0.736896097660065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.707724750041962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696943938732147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733091235160828</t>
+    <t xml:space="preserve">0.707724690437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733091115951538</t>
   </si>
   <si>
     <t xml:space="preserve">0.74894517660141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747676849365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754652678966522</t>
+    <t xml:space="preserve">0.747676908969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754652738571167</t>
   </si>
   <si>
     <t xml:space="preserve">0.755286812782288</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">0.760360181331635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81806880235672</t>
+    <t xml:space="preserve">0.818068861961365</t>
   </si>
   <si>
     <t xml:space="preserve">0.799678206443787</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">0.768604218959808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720408022403717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727383613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740701079368591</t>
+    <t xml:space="preserve">0.720407903194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727383673191071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">0.73816454410553</t>
@@ -848,37 +848,37 @@
     <t xml:space="preserve">0.774945855140686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78382408618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801580727100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849776983261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884021699428558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851045370101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878314197063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894168317317963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876319408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924607992172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887826681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901778280735016</t>
+    <t xml:space="preserve">0.783824145793915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801580607891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849777042865753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884021639823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851045250892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878314316272736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894168198108673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876498222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924608051776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88782674074173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901778221130371</t>
   </si>
   <si>
     <t xml:space="preserve">0.881485044956207</t>
@@ -887,43 +887,43 @@
     <t xml:space="preserve">0.902412414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87514340877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896070778369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910656571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827359676361</t>
+    <t xml:space="preserve">0.875143468379974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896070718765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9106565117836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827300071716</t>
   </si>
   <si>
     <t xml:space="preserve">0.91002231836319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.889729142189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892899811267853</t>
+    <t xml:space="preserve">0.889729082584381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892900049686432</t>
   </si>
   <si>
     <t xml:space="preserve">0.895436644554138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863094389438629</t>
+    <t xml:space="preserve">0.86309427022934</t>
   </si>
   <si>
     <t xml:space="preserve">0.860557675361633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.867533564567566</t>
+    <t xml:space="preserve">0.867533624172211</t>
   </si>
   <si>
     <t xml:space="preserve">0.87577760219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868167579174042</t>
+    <t xml:space="preserve">0.868167638778687</t>
   </si>
   <si>
     <t xml:space="preserve">0.756555140018463</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">0.788897395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812995553016663</t>
+    <t xml:space="preserve">0.812995433807373</t>
   </si>
   <si>
     <t xml:space="preserve">0.80728805065155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838362157344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790165722370148</t>
+    <t xml:space="preserve">0.838362038135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790165841579437</t>
   </si>
   <si>
     <t xml:space="preserve">0.786360800266266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811727225780487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830118000507355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814898014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792702436447144</t>
+    <t xml:space="preserve">0.811727166175842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830117881298065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814898073673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792702376842499</t>
   </si>
   <si>
     <t xml:space="preserve">0.803483128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804117441177368</t>
+    <t xml:space="preserve">0.804117381572723</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848316192627</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">0.791434049606323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785092353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994993686676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79397064447403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531588554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773677587509155</t>
+    <t xml:space="preserve">0.785092532634735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786994874477386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793970763683319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531528949738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77367752790451</t>
   </si>
   <si>
     <t xml:space="preserve">0.775580048561096</t>
@@ -1004,34 +1004,34 @@
     <t xml:space="preserve">0.771775007247925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.761628389358521</t>
+    <t xml:space="preserve">0.761628448963165</t>
   </si>
   <si>
     <t xml:space="preserve">0.795873165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811093091964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84343546628952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606813907623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460076808929</t>
+    <t xml:space="preserve">0.811093032360077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435406684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460255622864</t>
   </si>
   <si>
     <t xml:space="preserve">0.866899251937866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840264558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830752074718475</t>
+    <t xml:space="preserve">0.840264499187469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830751955509186</t>
   </si>
   <si>
     <t xml:space="preserve">0.855484306812286</t>
@@ -1046,196 +1046,196 @@
     <t xml:space="preserve">0.820605516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824410378932953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826947152614594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80601978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799043953418732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804751455783844</t>
+    <t xml:space="preserve">0.824410617351532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826947093009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806019723415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799044013023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804751634597778</t>
   </si>
   <si>
     <t xml:space="preserve">0.7857266664505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778750896453857</t>
+    <t xml:space="preserve">0.778750836849213</t>
   </si>
   <si>
     <t xml:space="preserve">0.777482450008392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802214860916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80665397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80792236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854850232601166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857386827468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852313578128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863728582859039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864996790885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850411117076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840898752212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834557116031647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996052742004</t>
+    <t xml:space="preserve">0.802214741706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665385723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807922303676605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854850292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857386887073517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85231351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863728523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864996731281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850410997867584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84089857339859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996231555939</t>
   </si>
   <si>
     <t xml:space="preserve">0.827581226825714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826312959194183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805385708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814263820648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81870311498642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81933718919754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796507358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809190571308136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809824705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797775626182556</t>
+    <t xml:space="preserve">0.826312899589539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805385649204254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814263999462128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81870299577713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819337248802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796507298946381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809190630912781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809824764728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797775685787201</t>
   </si>
   <si>
     <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817434787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823142170906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812361478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819971323013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797141551971436</t>
+    <t xml:space="preserve">0.817434668540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823142111301422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812361359596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81997138261795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797141492366791</t>
   </si>
   <si>
     <t xml:space="preserve">0.716602981090546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.704553842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736261963844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759725868701935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240926027298</t>
+    <t xml:space="preserve">0.7045539021492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736262023448944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75972592830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">0.776214241981506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784458339214325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78318989276886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752116084098816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7609943151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823526859283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701638698578</t>
+    <t xml:space="preserve">0.78445827960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783189952373505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752116024494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760994255542755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701817512512</t>
   </si>
   <si>
     <t xml:space="preserve">0.790799915790558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810459017753601</t>
+    <t xml:space="preserve">0.810458898544312</t>
   </si>
   <si>
     <t xml:space="preserve">0.774311661720276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781287431716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79523903131485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800312280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815532207489014</t>
+    <t xml:space="preserve">0.781287491321564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795239090919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800312340259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815532267093658</t>
   </si>
   <si>
     <t xml:space="preserve">0.764799296855927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731822967529297</t>
+    <t xml:space="preserve">0.731822848320007</t>
   </si>
   <si>
     <t xml:space="preserve">0.711529612541199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.693773150444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739432811737061</t>
+    <t xml:space="preserve">0.693773090839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739432752132416</t>
   </si>
   <si>
     <t xml:space="preserve">0.70391970872879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695041358470917</t>
+    <t xml:space="preserve">0.695041418075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.683626472949982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660796761512756</t>
+    <t xml:space="preserve">0.660796701908112</t>
   </si>
   <si>
     <t xml:space="preserve">0.684894919395447</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">0.678553283214569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.687431454658508</t>
+    <t xml:space="preserve">0.687431514263153</t>
   </si>
   <si>
     <t xml:space="preserve">0.717871248722076</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">0.710261344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697578072547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714066326618195</t>
+    <t xml:space="preserve">0.697578132152557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71406626701355</t>
   </si>
   <si>
     <t xml:space="preserve">0.729286193847656</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">0.753384292125702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748311102390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757189333438873</t>
+    <t xml:space="preserve">0.748310983181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757189393043518</t>
   </si>
   <si>
     <t xml:space="preserve">0.758457601070404</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">0.749579429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747042715549469</t>
+    <t xml:space="preserve">0.747042775154114</t>
   </si>
   <si>
     <t xml:space="preserve">0.735627770423889</t>
@@ -1298,28 +1298,28 @@
     <t xml:space="preserve">0.745774388313293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743237733840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.741969287395477</t>
+    <t xml:space="preserve">0.743237793445587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.741969347000122</t>
   </si>
   <si>
     <t xml:space="preserve">0.744506120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722944676876068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.700114667415619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456303596497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846518993378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72548121213913</t>
+    <t xml:space="preserve">0.722944557666779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700114727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456422805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846399784088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725481331348419</t>
   </si>
   <si>
     <t xml:space="preserve">0.715334713459015</t>
@@ -1328,40 +1328,40 @@
     <t xml:space="preserve">0.712797880172729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.692504823207855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705188095569611</t>
+    <t xml:space="preserve">0.69250476360321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705187976360321</t>
   </si>
   <si>
     <t xml:space="preserve">0.681089878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701383054256439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696309745311737</t>
+    <t xml:space="preserve">0.701382994651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
     <t xml:space="preserve">0.688699781894684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.686163187026978</t>
+    <t xml:space="preserve">0.686163127422333</t>
   </si>
   <si>
     <t xml:space="preserve">0.679821610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672211587429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646845102310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.677284836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658259987831116</t>
+    <t xml:space="preserve">0.672211647033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646845161914825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.677284896373749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65826004743576</t>
   </si>
   <si>
     <t xml:space="preserve">0.659528374671936</t>
@@ -1373,22 +1373,22 @@
     <t xml:space="preserve">0.648113429546356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641771852970123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635430216789246</t>
+    <t xml:space="preserve">0.641771793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635430157184601</t>
   </si>
   <si>
     <t xml:space="preserve">0.643040239810944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639235198497772</t>
+    <t xml:space="preserve">0.639235138893127</t>
   </si>
   <si>
     <t xml:space="preserve">0.637966930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594209611415863</t>
+    <t xml:space="preserve">0.594209671020508</t>
   </si>
   <si>
     <t xml:space="preserve">0.596746385097504</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">0.609429657459259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598014712333679</t>
+    <t xml:space="preserve">0.598014652729034</t>
   </si>
   <si>
     <t xml:space="preserve">0.599917113780975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603722214698792</t>
+    <t xml:space="preserve">0.603722155094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.573916554450989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478736400604</t>
+    <t xml:space="preserve">0.621478676795959</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
@@ -1418,19 +1418,19 @@
     <t xml:space="preserve">0.62274694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615771234035492</t>
+    <t xml:space="preserve">0.615771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">0.6233811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612600445747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591038942337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584063172340393</t>
+    <t xml:space="preserve">0.612600386142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591038823127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584063112735748</t>
   </si>
   <si>
     <t xml:space="preserve">0.580892205238342</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572648167610168</t>
+    <t xml:space="preserve">0.572648227214813</t>
   </si>
   <si>
     <t xml:space="preserve">0.559964954853058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135183811188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528891026973724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573282420635223</t>
+    <t xml:space="preserve">0.537135124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528891086578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573282361030579</t>
   </si>
   <si>
     <t xml:space="preserve">0.569477379322052</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">0.608795404434204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618307828903198</t>
+    <t xml:space="preserve">0.618307948112488</t>
   </si>
   <si>
     <t xml:space="preserve">0.630356907844543</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">0.604990422725677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580258190631866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572013974189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568209111690521</t>
+    <t xml:space="preserve">0.580258250236511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572014033794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568209052085876</t>
   </si>
   <si>
     <t xml:space="preserve">0.554891645908356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629722714424133</t>
+    <t xml:space="preserve">0.629722774028778</t>
   </si>
   <si>
     <t xml:space="preserve">0.721676230430603</t>
@@ -1496,73 +1496,73 @@
     <t xml:space="preserve">0.766067564487457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.782555818557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215420246124</t>
+    <t xml:space="preserve">0.78255569934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215479850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.825678825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873875141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753372192383</t>
+    <t xml:space="preserve">0.873875081539154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871338367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753491401672</t>
   </si>
   <si>
     <t xml:space="preserve">0.880216658115387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903046548366547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922071397304535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937291264533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918266415596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86626523733139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630424976349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896704912185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876411736011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070159435272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559651374817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93475466966629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314875602722</t>
+    <t xml:space="preserve">0.903046488761902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92207145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937291324138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918266355991364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866265177726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630305767059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896705031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87641179561615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801891803741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070099830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559591770172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934754610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314935207367</t>
   </si>
   <si>
     <t xml:space="preserve">0.905583202838898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929681420326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144765853882</t>
+    <t xml:space="preserve">0.929681360721588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144646644592</t>
   </si>
   <si>
     <t xml:space="preserve">0.906851589679718</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">0.930949687957764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891631603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833288788795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873903274536</t>
+    <t xml:space="preserve">0.891631662845612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833288729190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873724460602</t>
   </si>
   <si>
     <t xml:space="preserve">0.802848935127258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755920946598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640503466129303</t>
+    <t xml:space="preserve">0.755921065807343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640503525733948</t>
   </si>
   <si>
     <t xml:space="preserve">0.636698544025421</t>
@@ -1595,19 +1595,19 @@
     <t xml:space="preserve">0.627019286155701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641852021217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625670850276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534986972809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616906046867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618928611278534</t>
+    <t xml:space="preserve">0.641851961612701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625670790672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613535046577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616906106472015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618928670883179</t>
   </si>
   <si>
     <t xml:space="preserve">0.595331132411957</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">0.59667956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59735381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596005439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602073311805725</t>
+    <t xml:space="preserve">0.597353756427765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596005380153656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60207325220108</t>
   </si>
   <si>
     <t xml:space="preserve">0.598028063774109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594657063484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838115215302</t>
+    <t xml:space="preserve">0.594656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838055610657</t>
   </si>
   <si>
     <t xml:space="preserve">0.593982696533203</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">0.631064474582672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623648107051849</t>
+    <t xml:space="preserve">0.623648166656494</t>
   </si>
   <si>
     <t xml:space="preserve">0.65398782491684</t>
@@ -1652,100 +1652,100 @@
     <t xml:space="preserve">0.637132465839386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626344978809357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62836766242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624322414398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629716098308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6276935338974</t>
+    <t xml:space="preserve">0.626345038414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628367602825165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624322354793549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629716157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62769341468811</t>
   </si>
   <si>
     <t xml:space="preserve">0.614883363246918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608815431594849</t>
+    <t xml:space="preserve">0.608815491199493</t>
   </si>
   <si>
     <t xml:space="preserve">0.61758017539978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635784029960632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624996483325958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614209175109863</t>
+    <t xml:space="preserve">0.635783970355988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624996602535248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614209234714508</t>
   </si>
   <si>
     <t xml:space="preserve">0.605444371700287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606118559837341</t>
+    <t xml:space="preserve">0.606118619441986</t>
   </si>
   <si>
     <t xml:space="preserve">0.630390346050262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643200397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656010389328003</t>
+    <t xml:space="preserve">0.64320033788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656010448932648</t>
   </si>
   <si>
     <t xml:space="preserve">0.633761346340179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612186551094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621625483036041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608141183853149</t>
+    <t xml:space="preserve">0.61218649148941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621625542640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608141243457794</t>
   </si>
   <si>
     <t xml:space="preserve">0.610163867473602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549484550952911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561620533466339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552855670452118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578475832939148</t>
+    <t xml:space="preserve">0.549484670162201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561620473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552855610847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565665781497955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578475773334503</t>
   </si>
   <si>
     <t xml:space="preserve">0.558923602104187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563643097877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569710969924927</t>
+    <t xml:space="preserve">0.563643038272858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569711089134216</t>
   </si>
   <si>
     <t xml:space="preserve">0.558249354362488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.562294661998749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573082089424133</t>
+    <t xml:space="preserve">0.562294721603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573082149028778</t>
   </si>
   <si>
     <t xml:space="preserve">0.583869457244873</t>
@@ -1760,40 +1760,40 @@
     <t xml:space="preserve">0.56633996963501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593308448791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599376440048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586566388607025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591285884380341</t>
+    <t xml:space="preserve">0.593308568000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599376380443573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58656632900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591285824775696</t>
   </si>
   <si>
     <t xml:space="preserve">0.600050628185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602747440338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607466995716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590611577033997</t>
+    <t xml:space="preserve">0.602747559547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60746693611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590611636638641</t>
   </si>
   <si>
     <t xml:space="preserve">0.592634320259094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618254482746124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639829277992249</t>
+    <t xml:space="preserve">0.587914764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618254363536835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639829337596893</t>
   </si>
   <si>
     <t xml:space="preserve">0.641177654266357</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">0.588589012622833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598702251911163</t>
+    <t xml:space="preserve">0.598702311515808</t>
   </si>
   <si>
     <t xml:space="preserve">0.620277047157288</t>
@@ -1817,43 +1817,43 @@
     <t xml:space="preserve">0.615557551383972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620951354503632</t>
+    <t xml:space="preserve">0.620951294898987</t>
   </si>
   <si>
     <t xml:space="preserve">0.648594081401825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604770123958588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604095995426178</t>
+    <t xml:space="preserve">0.604770183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604095935821533</t>
   </si>
   <si>
     <t xml:space="preserve">0.603421747684479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639155089855194</t>
+    <t xml:space="preserve">0.639155030250549</t>
   </si>
   <si>
     <t xml:space="preserve">0.638480842113495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655336260795593</t>
+    <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
     <t xml:space="preserve">0.695789039134979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714667022228241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702531278133392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69983434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716015458106995</t>
+    <t xml:space="preserve">0.714667081832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702531218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699834406375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716015517711639</t>
   </si>
   <si>
     <t xml:space="preserve">0.728151440620422</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">0.721409261226654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711970269680023</t>
+    <t xml:space="preserve">0.711970210075378</t>
   </si>
   <si>
     <t xml:space="preserve">0.701182782649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694440603256226</t>
+    <t xml:space="preserve">0.69444066286087</t>
   </si>
   <si>
     <t xml:space="preserve">0.689046919345856</t>
@@ -1886,19 +1886,19 @@
     <t xml:space="preserve">0.683653295040131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.679607927799225</t>
+    <t xml:space="preserve">0.67960786819458</t>
   </si>
   <si>
     <t xml:space="preserve">0.680956363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672191500663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68500167131424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675562620162964</t>
+    <t xml:space="preserve">0.672191560268402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.685001611709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675562560558319</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146312236786</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919952869415</t>
+    <t xml:space="preserve">0.647919893264771</t>
   </si>
   <si>
     <t xml:space="preserve">0.645897269248962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636458218097687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63308721780777</t>
+    <t xml:space="preserve">0.636458277702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633087158203125</t>
   </si>
   <si>
     <t xml:space="preserve">0.611512303352356</t>
@@ -1934,37 +1934,37 @@
     <t xml:space="preserve">0.560271978378296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553529858589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538697123527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527235507965088</t>
+    <t xml:space="preserve">0.553529798984528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538697183132172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527235448360443</t>
   </si>
   <si>
     <t xml:space="preserve">0.478692084550858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463859438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45846563577652</t>
+    <t xml:space="preserve">0.463859379291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458465695381165</t>
   </si>
   <si>
     <t xml:space="preserve">0.391044229269028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41936120390892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394415259361267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387673169374466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388347387313843</t>
+    <t xml:space="preserve">0.419361263513565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394415289163589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387673199176788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38834735751152</t>
   </si>
   <si>
     <t xml:space="preserve">0.380256861448288</t>
@@ -1976,64 +1976,64 @@
     <t xml:space="preserve">0.412619143724442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431497097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465207815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927340745926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479366362094879</t>
+    <t xml:space="preserve">0.431497067213058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46520784497261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927281141281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479366302490234</t>
   </si>
   <si>
     <t xml:space="preserve">0.489479511976242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474646747112274</t>
+    <t xml:space="preserve">0.474646836519241</t>
   </si>
   <si>
     <t xml:space="preserve">0.473298400640488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464533627033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411580324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498918563127518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496895909309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495547503232956</t>
+    <t xml:space="preserve">0.464533567428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411550521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496895879507065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495547473430634</t>
   </si>
   <si>
     <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482063174247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490827947854996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484760016202927</t>
+    <t xml:space="preserve">0.482063204050064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490827858448029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484760046005249</t>
   </si>
   <si>
     <t xml:space="preserve">0.480714738368988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482737421989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485434234142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488131076097488</t>
+    <t xml:space="preserve">0.482737392187119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485434263944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488131046295166</t>
   </si>
   <si>
     <t xml:space="preserve">0.481388956308365</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">0.434868156909943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43823915719986</t>
+    <t xml:space="preserve">0.438239306211472</t>
   </si>
   <si>
     <t xml:space="preserve">0.443632960319519</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">0.434212177991867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410049855709076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892431020737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449136048555374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451268017292023</t>
+    <t xml:space="preserve">0.410049796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892401218414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449136018753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4512679874897</t>
   </si>
   <si>
     <t xml:space="preserve">0.456953257322311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486800909042358</t>
+    <t xml:space="preserve">0.486800879240036</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
@@ -2087,58 +2087,58 @@
     <t xml:space="preserve">0.446293383836746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453399956226349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466191798448563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466902494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480404943227768</t>
+    <t xml:space="preserve">0.453399986028671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466191828250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46690246462822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48040497303009</t>
   </si>
   <si>
     <t xml:space="preserve">0.498882085084915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48822221159935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477562308311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445582717657089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442740082740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452689349651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447003990411758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450557380914688</t>
+    <t xml:space="preserve">0.488222181797028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47756227850914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445582747459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442740112543106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452689290046692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447004020214081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450557351112366</t>
   </si>
   <si>
     <t xml:space="preserve">0.448425322771072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442029386758804</t>
+    <t xml:space="preserve">0.442029416561127</t>
   </si>
   <si>
     <t xml:space="preserve">0.42994824051857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438476145267487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429237574338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447714656591415</t>
+    <t xml:space="preserve">0.438476055860519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429237604141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447714686393738</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
@@ -2147,25 +2147,25 @@
     <t xml:space="preserve">0.463349193334579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458374530076981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444161415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456242561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449846655130386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455531924962997</t>
+    <t xml:space="preserve">0.458374559879303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444161355495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456242620944977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449846684932709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455531865358353</t>
   </si>
   <si>
     <t xml:space="preserve">0.443450748920441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430658876895905</t>
+    <t xml:space="preserve">0.430658906698227</t>
   </si>
   <si>
     <t xml:space="preserve">0.420709669589996</t>
@@ -2174,76 +2174,76 @@
     <t xml:space="preserve">0.427816212177277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413603127002716</t>
+    <t xml:space="preserve">0.413603097200394</t>
   </si>
   <si>
     <t xml:space="preserve">0.417156398296356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416445732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427105605602264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437054812908173</t>
+    <t xml:space="preserve">0.416445761919022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427105635404587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437054842710495</t>
   </si>
   <si>
     <t xml:space="preserve">0.432080209255219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434922873973846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422841668128967</t>
+    <t xml:space="preserve">0.434922844171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42284169793129</t>
   </si>
   <si>
     <t xml:space="preserve">0.417867034673691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406496524810791</t>
+    <t xml:space="preserve">0.406496554613113</t>
   </si>
   <si>
     <t xml:space="preserve">0.407917827367783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397968620061874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403653919696808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401521891355515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405075222253799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400811284780502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387308746576309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385176718235016</t>
+    <t xml:space="preserve">0.397968590259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403653889894485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401521921157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405075162649155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400811225175858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387308716773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385176748037338</t>
   </si>
   <si>
     <t xml:space="preserve">0.400100588798523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415735006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398679226636887</t>
+    <t xml:space="preserve">0.41573503613472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398679286241531</t>
   </si>
   <si>
     <t xml:space="preserve">0.409339129924774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395836621522903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382334113121033</t>
+    <t xml:space="preserve">0.395836651325226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382334142923355</t>
   </si>
   <si>
     <t xml:space="preserve">0.370963603258133</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">0.366699635982513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363146334886551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353907823562622</t>
+    <t xml:space="preserve">0.363146364688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3539077937603</t>
   </si>
   <si>
     <t xml:space="preserve">0.356750428676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359593063592911</t>
+    <t xml:space="preserve">0.359593033790588</t>
   </si>
   <si>
     <t xml:space="preserve">0.358882397413254</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730078935623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151351690292</t>
+    <t xml:space="preserve">0.388730019330978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151381492615</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372384905815125</t>
+    <t xml:space="preserve">0.372384876012802</t>
   </si>
   <si>
     <t xml:space="preserve">0.36385703086853</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">0.361725032329559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355329096317291</t>
+    <t xml:space="preserve">0.355329126119614</t>
   </si>
   <si>
     <t xml:space="preserve">0.353552460670471</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">0.351775825023651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065158843994</t>
+    <t xml:space="preserve">0.351065188646317</t>
   </si>
   <si>
     <t xml:space="preserve">0.334009349346161</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">0.323349505662918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342181950807571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337207317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337562650442123</t>
+    <t xml:space="preserve">0.342181921005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337207347154617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337562680244446</t>
   </si>
   <si>
     <t xml:space="preserve">0.343958586454391</t>
@@ -2330,58 +2330,58 @@
     <t xml:space="preserve">0.36030375957489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389440685510635</t>
+    <t xml:space="preserve">0.389440715312958</t>
   </si>
   <si>
     <t xml:space="preserve">0.396547317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41218176484108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421420365571976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415024369955063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419999063014984</t>
+    <t xml:space="preserve">0.412181794643402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421420335769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415024399757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419999033212662</t>
   </si>
   <si>
     <t xml:space="preserve">0.414313763380051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405785828828812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402232557535172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418577671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419288396835327</t>
+    <t xml:space="preserve">0.405785858631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402232527732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418577700853348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41928830742836</t>
   </si>
   <si>
     <t xml:space="preserve">0.399389892816544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393704682588577</t>
+    <t xml:space="preserve">0.393704652786255</t>
   </si>
   <si>
     <t xml:space="preserve">0.392993986606598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391572713851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397257953882217</t>
+    <t xml:space="preserve">0.391572684049606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39725798368454</t>
   </si>
   <si>
     <t xml:space="preserve">0.40436452627182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395126014947891</t>
+    <t xml:space="preserve">0.395125985145569</t>
   </si>
   <si>
     <t xml:space="preserve">0.386598110198975</t>
@@ -2390,67 +2390,67 @@
     <t xml:space="preserve">0.380202174186707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806208372116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369542270898819</t>
+    <t xml:space="preserve">0.373806267976761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369542241096497</t>
   </si>
   <si>
     <t xml:space="preserve">0.368831604719162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364567697048187</t>
+    <t xml:space="preserve">0.364567667245865</t>
   </si>
   <si>
     <t xml:space="preserve">0.428526937961578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423552274703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43634420633316</t>
+    <t xml:space="preserve">0.423552334308624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436344176530838</t>
   </si>
   <si>
     <t xml:space="preserve">0.42639496922493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440608114004135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897418022156</t>
+    <t xml:space="preserve">0.44060817360878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897477626801</t>
   </si>
   <si>
     <t xml:space="preserve">0.464770466089249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471877068281174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478983640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492486149072647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515227258205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512384533882141</t>
+    <t xml:space="preserve">0.471877038478851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478983670473099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492486208677292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515227198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
     <t xml:space="preserve">0.506699323654175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51735919713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120656013489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513805866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510963261127472</t>
+    <t xml:space="preserve">0.517359137535095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120596408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5138059258461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510963201522827</t>
   </si>
   <si>
     <t xml:space="preserve">0.507409989833832</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">0.513095259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522333860397339</t>
+    <t xml:space="preserve">0.522333800792694</t>
   </si>
   <si>
     <t xml:space="preserve">0.537257611751556</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">0.526597738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525176405906677</t>
+    <t xml:space="preserve">0.525176465511322</t>
   </si>
   <si>
     <t xml:space="preserve">0.530151069164276</t>
@@ -2486,31 +2486,31 @@
     <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544364213943481</t>
+    <t xml:space="preserve">0.544364154338837</t>
   </si>
   <si>
     <t xml:space="preserve">0.541521608829498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536547005176544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528729736804962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518780469894409</t>
+    <t xml:space="preserve">0.536546945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528729677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518780529499054</t>
   </si>
   <si>
     <t xml:space="preserve">0.515937864780426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523044526576996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542232275009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531572341918945</t>
+    <t xml:space="preserve">0.523044407367706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54223221540451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53157240152359</t>
   </si>
   <si>
     <t xml:space="preserve">0.542942881584167</t>
@@ -2519,31 +2519,31 @@
     <t xml:space="preserve">0.549338817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564973294734955</t>
+    <t xml:space="preserve">0.5649733543396</t>
   </si>
   <si>
     <t xml:space="preserve">0.550941288471222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549464225769043</t>
+    <t xml:space="preserve">0.549464166164398</t>
   </si>
   <si>
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647783756256</t>
+    <t xml:space="preserve">0.537647724151611</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569843292236</t>
+    <t xml:space="preserve">0.526569902896881</t>
   </si>
   <si>
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753401279449</t>
+    <t xml:space="preserve">0.514753460884094</t>
   </si>
   <si>
     <t xml:space="preserve">0.518446087837219</t>
@@ -2555,16 +2555,16 @@
     <t xml:space="preserve">0.533955156803131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544294476509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556849479675293</t>
+    <t xml:space="preserve">0.544294536113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556849539279938</t>
   </si>
   <si>
     <t xml:space="preserve">0.546510100364685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553156912326813</t>
+    <t xml:space="preserve">0.553156852722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.56128066778183</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">0.57235848903656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581220924854279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584175050258636</t>
+    <t xml:space="preserve">0.581220865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584174990653992</t>
   </si>
   <si>
     <t xml:space="preserve">0.583436489105225</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">0.575312674045563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568665862083435</t>
+    <t xml:space="preserve">0.56866592168808</t>
   </si>
   <si>
     <t xml:space="preserve">0.54281747341156</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">0.536170721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527308344841003</t>
+    <t xml:space="preserve">0.527308404445648</t>
   </si>
   <si>
     <t xml:space="preserve">0.522877275943756</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511799335479736</t>
+    <t xml:space="preserve">0.511799395084381</t>
   </si>
   <si>
     <t xml:space="preserve">0.509583711624146</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">0.506629586219788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487427920103073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488166481256485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735293149948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488904982805252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480781227350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481519728899002</t>
+    <t xml:space="preserve">0.487427949905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488166451454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735203742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488905012607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480781197547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48151969909668</t>
   </si>
   <si>
     <t xml:space="preserve">0.492597579956055</t>
@@ -2654,22 +2654,22 @@
     <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525831401348114</t>
+    <t xml:space="preserve">0.525831341743469</t>
   </si>
   <si>
     <t xml:space="preserve">0.534693598747253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532478034496307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519923150539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517707586288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512537777423859</t>
+    <t xml:space="preserve">0.532478094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519923090934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517707467079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512537837028503</t>
   </si>
   <si>
     <t xml:space="preserve">0.514014899730682</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">0.525092840194702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545032978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528785467147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533216595649719</t>
+    <t xml:space="preserve">0.545033037662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528785526752472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533216655254364</t>
   </si>
   <si>
     <t xml:space="preserve">0.520661652088165</t>
@@ -2696,34 +2696,34 @@
     <t xml:space="preserve">0.508106708526611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505152523517609</t>
+    <t xml:space="preserve">0.505152583122253</t>
   </si>
   <si>
     <t xml:space="preserve">0.502198457717896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495551764965057</t>
+    <t xml:space="preserve">0.495551705360413</t>
   </si>
   <si>
     <t xml:space="preserve">0.498505830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502937018871307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504414021968842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.500721395015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771598815918</t>
+    <t xml:space="preserve">0.502936959266663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504414081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.500721335411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771658420563</t>
   </si>
   <si>
     <t xml:space="preserve">0.540601849555969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55389541387558</t>
+    <t xml:space="preserve">0.553895354270935</t>
   </si>
   <si>
     <t xml:space="preserve">0.550202786922455</t>
@@ -2732,31 +2732,31 @@
     <t xml:space="preserve">0.547987163066864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538386225700378</t>
+    <t xml:space="preserve">0.538386285305023</t>
   </si>
   <si>
     <t xml:space="preserve">0.530262470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539863348007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613716065883636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641780138015747</t>
+    <t xml:space="preserve">0.539863407611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613716125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641780078411102</t>
   </si>
   <si>
     <t xml:space="preserve">0.622578382492065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627009510993958</t>
+    <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
     <t xml:space="preserve">0.612977564334869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61667013168335</t>
+    <t xml:space="preserve">0.616670191287994</t>
   </si>
   <si>
     <t xml:space="preserve">0.62996369600296</t>
@@ -2771,28 +2771,28 @@
     <t xml:space="preserve">0.601161122322083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594514310359955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599684000015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589344680309296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600422561168671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607069313526154</t>
+    <t xml:space="preserve">0.5945143699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599684059619904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589344620704651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600422620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607069373130798</t>
   </si>
   <si>
     <t xml:space="preserve">0.593037307262421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597468435764313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592298746109009</t>
+    <t xml:space="preserve">0.597468495368958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592298805713654</t>
   </si>
   <si>
     <t xml:space="preserve">0.603376686573029</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">0.664674401283264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66688996553421</t>
+    <t xml:space="preserve">0.666890025138855</t>
   </si>
   <si>
     <t xml:space="preserve">0.658766210079193</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.667628526687622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64842689037323</t>
+    <t xml:space="preserve">0.648426830768585</t>
   </si>
   <si>
     <t xml:space="preserve">0.647688329219818</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">0.629225134849548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642518699169159</t>
+    <t xml:space="preserve">0.642518639564514</t>
   </si>
   <si>
     <t xml:space="preserve">0.640303015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63365626335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675752401351929</t>
+    <t xml:space="preserve">0.633656322956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675752341747284</t>
   </si>
   <si>
     <t xml:space="preserve">0.649165391921997</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">0.65581214427948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655073642730713</t>
+    <t xml:space="preserve">0.655073583126068</t>
   </si>
   <si>
     <t xml:space="preserve">0.635871887207031</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638825953006744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62627100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702137947083</t>
+    <t xml:space="preserve">0.638826012611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626271069049835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702197551727</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2882,22 +2882,22 @@
     <t xml:space="preserve">0.662458837032318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678706467151642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676490902900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673536837100983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661720335483551</t>
+    <t xml:space="preserve">0.678706526756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676490843296051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673536777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661720395088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.635133385658264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576789677143097</t>
+    <t xml:space="preserve">0.576789736747742</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
@@ -2915,19 +2915,19 @@
     <t xml:space="preserve">0.565711796283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564234793186188</t>
+    <t xml:space="preserve">0.564234733581543</t>
   </si>
   <si>
     <t xml:space="preserve">0.582697927951813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570881485939026</t>
+    <t xml:space="preserve">0.570881545543671</t>
   </si>
   <si>
     <t xml:space="preserve">0.559803605079651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547248661518097</t>
+    <t xml:space="preserve">0.547248601913452</t>
   </si>
   <si>
     <t xml:space="preserve">0.536909222602844</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">0.542078971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567188858985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5797438621521</t>
+    <t xml:space="preserve">0.567188918590546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579743921756744</t>
   </si>
   <si>
     <t xml:space="preserve">0.562019169330597</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">0.555372416973114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569404423236847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574053287506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58257657289505</t>
+    <t xml:space="preserve">0.569404482841492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574112892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582576513290405</t>
   </si>
   <si>
     <t xml:space="preserve">0.572973668575287</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572912693024</t>
+    <t xml:space="preserve">0.570572972297668</t>
   </si>
   <si>
     <t xml:space="preserve">0.568172216415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560169756412506</t>
+    <t xml:space="preserve">0.560169816017151</t>
   </si>
   <si>
     <t xml:space="preserve">0.562570512294769</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">0.552967607975006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546565651893616</t>
+    <t xml:space="preserve">0.54656571149826</t>
   </si>
   <si>
     <t xml:space="preserve">0.537762999534607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513755738735199</t>
+    <t xml:space="preserve">0.513755679130554</t>
   </si>
   <si>
     <t xml:space="preserve">0.516156435012817</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">0.484146744012833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48094579577446</t>
+    <t xml:space="preserve">0.480945765972137</t>
   </si>
   <si>
     <t xml:space="preserve">0.5057532787323</t>
@@ -3053,22 +3053,22 @@
     <t xml:space="preserve">0.493749648332596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487347722053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488147974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561770260334015</t>
+    <t xml:space="preserve">0.48734775185585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48814794421196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56177031993866</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58897852897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568972408771515</t>
+    <t xml:space="preserve">0.588978469371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568972527980804</t>
   </si>
   <si>
     <t xml:space="preserve">0.572173416614532</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">0.577775120735168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565771520137787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580976128578186</t>
+    <t xml:space="preserve">0.565771460533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580976068973541</t>
   </si>
   <si>
     <t xml:space="preserve">0.581776320934296</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">0.58337676525116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576974868774414</t>
+    <t xml:space="preserve">0.576974928379059</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">0.586577773094177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585777521133423</t>
+    <t xml:space="preserve">0.585777580738068</t>
   </si>
   <si>
     <t xml:space="preserve">0.591379284858704</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">0.564170956611633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555368304252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567371964454651</t>
+    <t xml:space="preserve">0.555368363857269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567371904850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">0.543364703655243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542564392089844</t>
+    <t xml:space="preserve">0.542564451694489</t>
   </si>
   <si>
     <t xml:space="preserve">0.535362303256989</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">0.520957887172699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528960347175598</t>
+    <t xml:space="preserve">0.528960287570953</t>
   </si>
   <si>
     <t xml:space="preserve">0.528160095214844</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">0.516956686973572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515356242656708</t>
+    <t xml:space="preserve">0.515356183052063</t>
   </si>
   <si>
     <t xml:space="preserve">0.508954226970673</t>
@@ -3170,19 +3170,19 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554730892181</t>
+    <t xml:space="preserve">0.510554790496826</t>
   </si>
   <si>
     <t xml:space="preserve">0.524158835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529760539531708</t>
+    <t xml:space="preserve">0.529760599136353</t>
   </si>
   <si>
     <t xml:space="preserve">0.531361043453217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550566911697388</t>
+    <t xml:space="preserve">0.550566852092743</t>
   </si>
   <si>
     <t xml:space="preserve">0.532161295413971</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">0.530560791492462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527359783649445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512155175209045</t>
+    <t xml:space="preserve">0.527359843254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51215523481369</t>
   </si>
   <si>
     <t xml:space="preserve">0.534561991691589</t>
@@ -3224,13 +3224,10 @@
     <t xml:space="preserve">0.559369564056396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556968808174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558569312095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574112892151</t>
+    <t xml:space="preserve">0.556968748569489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558569252490997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584177076816559</t>
@@ -3239,13 +3236,13 @@
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773920536041</t>
+    <t xml:space="preserve">0.573773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612185478210449</t>
+    <t xml:space="preserve">0.612185537815094</t>
   </si>
   <si>
     <t xml:space="preserve">0.616986989974976</t>
@@ -3254,19 +3251,19 @@
     <t xml:space="preserve">0.621788501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62418919801712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622588634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620187878608704</t>
+    <t xml:space="preserve">0.624189138412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622588694095612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620187938213348</t>
   </si>
   <si>
     <t xml:space="preserve">0.599381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604183077812195</t>
+    <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
     <t xml:space="preserve">0.602582693099976</t>
@@ -3284,25 +3281,25 @@
     <t xml:space="preserve">0.616186738014221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62498939037323</t>
+    <t xml:space="preserve">0.624989449977875</t>
   </si>
   <si>
     <t xml:space="preserve">0.628190398216248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636192798614502</t>
+    <t xml:space="preserve">0.636192858219147</t>
   </si>
   <si>
     <t xml:space="preserve">0.640194058418274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643395006656647</t>
+    <t xml:space="preserve">0.643394947052002</t>
   </si>
   <si>
     <t xml:space="preserve">0.637793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641794443130493</t>
+    <t xml:space="preserve">0.641794502735138</t>
   </si>
   <si>
     <t xml:space="preserve">0.647396206855774</t>
@@ -3314,52 +3311,55 @@
     <t xml:space="preserve">0.633792042732239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620988249778748</t>
+    <t xml:space="preserve">0.620988190174103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628990709781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635921716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651516497135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641986310482025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631589770317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627257883548737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615128636360168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262163639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663043498993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197629451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615995049476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62119323015213</t>
   </si>
   <si>
     <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635921716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651516437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64198637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631589770317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627257883548737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615128576755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663103103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197569847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464803218842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615994989871979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621193289756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64025354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723416805267</t>
+    <t xml:space="preserve">0.640253603458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723357200623</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732096195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61946052312851</t>
+    <t xml:space="preserve">0.604732036590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619460463523865</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395869731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331156730652</t>
+    <t xml:space="preserve">0.612529456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395810127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331216335297</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620326936244965</t>
+    <t xml:space="preserve">0.62032687664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801089286804</t>
+    <t xml:space="preserve">0.597801029682159</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658763408661</t>
+    <t xml:space="preserve">0.624658823013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727696895599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861343383789</t>
+    <t xml:space="preserve">0.617727756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861402988434</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387130737305</t>
+    <t xml:space="preserve">0.639387190341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382850646973</t>
+    <t xml:space="preserve">0.652382910251617</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848443508148</t>
+    <t xml:space="preserve">0.655848383903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042284488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687038004398346</t>
+    <t xml:space="preserve">0.674042344093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68270605802536</t>
+    <t xml:space="preserve">0.682706117630005</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637124538422</t>
+    <t xml:space="preserve">0.689637184143066</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739886999130249</t>
+    <t xml:space="preserve">0.739887058734894</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412965297699</t>
+    <t xml:space="preserve">0.762412905693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779740452766418</t>
+    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.76846718788147</t>
@@ -3699,9 +3699,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.787256062030792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -51360,7 +51357,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51594,7 +51591,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1815" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51620,7 +51617,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51698,7 +51695,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1819" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51802,7 +51799,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51828,7 +51825,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51906,7 +51903,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52244,7 +52241,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G1840" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52270,7 +52267,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1841" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52296,7 +52293,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1842" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52322,7 +52319,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1843" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52348,7 +52345,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1844" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52374,7 +52371,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1845" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52400,7 +52397,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52426,7 +52423,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1847" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52452,7 +52449,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52478,7 +52475,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52504,7 +52501,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52530,7 +52527,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1851" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52556,7 +52553,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1852" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52582,7 +52579,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1853" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52608,7 +52605,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1854" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52634,7 +52631,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52660,7 +52657,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1856" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52686,7 +52683,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1857" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52712,7 +52709,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1858" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52738,7 +52735,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1859" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52764,7 +52761,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52790,7 +52787,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1861" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52816,7 +52813,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1862" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52842,7 +52839,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1863" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52868,7 +52865,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1864" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52894,7 +52891,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1865" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52920,7 +52917,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1866" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52946,7 +52943,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1867" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52972,7 +52969,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52998,7 +52995,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53024,7 +53021,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1870" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53050,7 +53047,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1871" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53076,7 +53073,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1872" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53102,7 +53099,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53128,7 +53125,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1874" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53154,7 +53151,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1875" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53180,7 +53177,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53206,7 +53203,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1877" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53232,7 +53229,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53258,7 +53255,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1879" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53284,7 +53281,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1880" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53310,7 +53307,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1881" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53336,7 +53333,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53362,7 +53359,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53388,7 +53385,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53414,7 +53411,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1885" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53440,7 +53437,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1886" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53466,7 +53463,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53492,7 +53489,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1888" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53518,7 +53515,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1889" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53544,7 +53541,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1890" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53570,7 +53567,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1891" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53596,7 +53593,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1892" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53622,7 +53619,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1893" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53648,7 +53645,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53674,7 +53671,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1895" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53700,7 +53697,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53726,7 +53723,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53856,7 +53853,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53986,7 +53983,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54038,7 +54035,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54168,7 +54165,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1914" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54194,7 +54191,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54246,7 +54243,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1917" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54324,7 +54321,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1920" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54376,7 +54373,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1922" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54454,7 +54451,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1925" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54480,7 +54477,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54610,7 +54607,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1931" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54636,7 +54633,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1932" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54662,7 +54659,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1933" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54714,7 +54711,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54818,7 +54815,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54844,7 +54841,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1940" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54948,7 +54945,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54974,7 +54971,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1945" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55026,7 +55023,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1947" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55260,7 +55257,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1956" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55390,7 +55387,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1961" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55416,7 +55413,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1962" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55442,7 +55439,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1963" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55468,7 +55465,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1964" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55494,7 +55491,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1965" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55650,7 +55647,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1971" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56040,7 +56037,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1986" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56274,7 +56271,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1995" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56352,7 +56349,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1998" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56404,7 +56401,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2000" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56482,7 +56479,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2003" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56508,7 +56505,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2004" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56534,7 +56531,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2005" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56560,7 +56557,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2006" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56586,7 +56583,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2007" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56690,7 +56687,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2011" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56872,7 +56869,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2018" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56898,7 +56895,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57210,7 +57207,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57236,7 +57233,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57314,7 +57311,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57340,7 +57337,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58146,7 +58143,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G2067" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58302,7 +58299,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58380,7 +58377,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58484,7 +58481,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58562,7 +58559,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -63242,7 +63239,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1229</v>
+        <v>1191</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63268,7 +63265,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63294,7 +63291,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63320,7 +63317,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63346,7 +63343,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63372,7 +63369,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63398,7 +63395,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63424,7 +63421,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63450,7 +63447,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63476,7 +63473,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63502,7 +63499,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63528,7 +63525,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63554,7 +63551,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63580,7 +63577,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63606,7 +63603,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63632,7 +63629,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63658,7 +63655,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63684,7 +63681,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63710,7 +63707,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63736,7 +63733,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63762,7 +63759,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63788,7 +63785,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63814,7 +63811,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63840,7 +63837,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63866,7 +63863,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63892,7 +63889,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63918,7 +63915,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63944,7 +63941,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63970,7 +63967,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63996,7 +63993,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64022,7 +64019,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64048,7 +64045,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64074,7 +64071,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64100,7 +64097,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64126,7 +64123,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64152,7 +64149,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64178,7 +64175,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64204,7 +64201,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64230,7 +64227,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64256,7 +64253,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64282,7 +64279,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64308,7 +64305,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64334,7 +64331,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64360,7 +64357,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64386,7 +64383,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64412,7 +64409,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64438,7 +64435,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64464,7 +64461,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64490,7 +64487,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64516,7 +64513,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64542,7 +64539,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64568,7 +64565,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64594,7 +64591,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64620,7 +64617,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64646,7 +64643,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64672,7 +64669,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64698,7 +64695,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64724,7 +64721,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64750,7 +64747,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64776,7 +64773,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64802,7 +64799,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64828,7 +64825,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64854,7 +64851,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64880,7 +64877,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64906,7 +64903,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64932,7 +64929,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64958,7 +64955,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64984,7 +64981,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65010,7 +65007,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65036,7 +65033,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65062,7 +65059,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65088,7 +65085,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65114,7 +65111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65140,7 +65137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65166,7 +65163,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65192,7 +65189,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65218,7 +65215,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65244,7 +65241,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65270,7 +65267,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65296,7 +65293,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65322,7 +65319,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65348,7 +65345,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65374,7 +65371,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65400,7 +65397,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65426,7 +65423,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65452,7 +65449,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65478,7 +65475,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65504,7 +65501,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65530,7 +65527,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65556,7 +65553,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65582,7 +65579,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65608,7 +65605,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65634,7 +65631,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65660,7 +65657,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65686,7 +65683,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65712,7 +65709,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65738,7 +65735,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65764,7 +65761,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65790,7 +65787,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65816,7 +65813,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65842,7 +65839,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65868,7 +65865,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65894,7 +65891,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65920,7 +65917,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65946,7 +65943,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65972,7 +65969,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65998,7 +65995,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66024,7 +66021,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66050,7 +66047,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66076,7 +66073,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66102,7 +66099,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66128,7 +66125,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66154,7 +66151,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66180,7 +66177,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66206,7 +66203,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66232,7 +66229,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66258,7 +66255,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66284,7 +66281,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66310,7 +66307,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66336,7 +66333,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66362,7 +66359,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66388,7 +66385,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66414,7 +66411,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66440,7 +66437,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66466,7 +66463,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66492,7 +66489,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66518,7 +66515,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66544,7 +66541,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66570,7 +66567,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66596,7 +66593,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66622,7 +66619,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66648,7 +66645,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66674,7 +66671,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66700,7 +66697,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66726,7 +66723,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66752,7 +66749,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66778,7 +66775,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66804,7 +66801,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66830,7 +66827,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66856,7 +66853,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66882,7 +66879,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66908,7 +66905,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66934,7 +66931,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66960,7 +66957,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66986,7 +66983,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67012,7 +67009,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67038,7 +67035,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67064,7 +67061,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67090,7 +67087,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67116,7 +67113,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67142,7 +67139,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67168,7 +67165,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67194,7 +67191,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67220,7 +67217,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67246,7 +67243,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67272,7 +67269,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67298,7 +67295,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67324,7 +67321,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67350,7 +67347,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67376,7 +67373,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67402,7 +67399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67428,7 +67425,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67454,7 +67451,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67480,7 +67477,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67506,7 +67503,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67532,7 +67529,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67558,7 +67555,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67584,7 +67581,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67610,7 +67607,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67636,7 +67633,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67662,7 +67659,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67688,7 +67685,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67714,7 +67711,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67740,7 +67737,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67766,7 +67763,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67792,7 +67789,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67818,7 +67815,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67844,7 +67841,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67870,7 +67867,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67896,7 +67893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67922,7 +67919,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67948,7 +67945,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67974,7 +67971,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68000,7 +67997,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68026,7 +68023,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68052,7 +68049,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68078,7 +68075,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68104,7 +68101,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68130,7 +68127,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68156,7 +68153,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68182,7 +68179,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68208,7 +68205,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68234,7 +68231,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68260,7 +68257,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68286,7 +68283,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68312,7 +68309,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68338,7 +68335,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68364,7 +68361,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68390,7 +68387,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68416,7 +68413,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68442,7 +68439,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68468,7 +68465,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68494,7 +68491,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68520,7 +68517,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68546,7 +68543,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68572,7 +68569,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68598,7 +68595,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68624,7 +68621,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68650,7 +68647,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68676,7 +68673,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68702,7 +68699,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68728,7 +68725,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68754,7 +68751,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68780,7 +68777,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68806,7 +68803,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68832,7 +68829,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68858,7 +68855,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68884,7 +68881,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68910,7 +68907,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68936,7 +68933,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68962,7 +68959,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68988,7 +68985,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69014,7 +69011,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69040,7 +69037,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69066,7 +69063,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69074,7 +69071,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6513425926</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>150944</v>
@@ -69092,9 +69089,35 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493287037</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>168065</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>1.02799999713898</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="1352">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594696521759</t>
+    <t xml:space="preserve">0.378594666719437</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">0.382716715335846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367179751396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380497127771378</t>
+    <t xml:space="preserve">0.367179781198502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380497187376022</t>
   </si>
   <si>
     <t xml:space="preserve">0.361789375543594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3522769510746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368131011724472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387155830860138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936862230301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390009582042694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373521387577057</t>
+    <t xml:space="preserve">0.352276891469955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36813098192215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387155801057816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936892032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390009552240372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373521327972412</t>
   </si>
   <si>
     <t xml:space="preserve">0.359886884689331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335471630096436</t>
+    <t xml:space="preserve">0.335471600294113</t>
   </si>
   <si>
     <t xml:space="preserve">0.34561824798584</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">0.361472278833389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341496229171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355130672454834</t>
+    <t xml:space="preserve">0.341496199369431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355130702257156</t>
   </si>
   <si>
     <t xml:space="preserve">0.352593988180161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342447459697723</t>
+    <t xml:space="preserve">0.342447429895401</t>
   </si>
   <si>
     <t xml:space="preserve">0.360838115215302</t>
@@ -113,31 +113,31 @@
     <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291714459657669</t>
+    <t xml:space="preserve">0.291714489459991</t>
   </si>
   <si>
     <t xml:space="preserve">0.297739028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275860399007797</t>
+    <t xml:space="preserve">0.27586042881012</t>
   </si>
   <si>
     <t xml:space="preserve">0.276240944862366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304461121559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326593399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789066076279</t>
+    <t xml:space="preserve">0.304461181163788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326593369245529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789036273956</t>
   </si>
   <si>
     <t xml:space="preserve">0.32913002371788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348471999168396</t>
+    <t xml:space="preserve">0.348471969366074</t>
   </si>
   <si>
     <t xml:space="preserve">0.327544629573822</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">0.334203332662582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838763952255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356398940086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368765145540237</t>
+    <t xml:space="preserve">0.386838734149933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356398969888687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36876517534256</t>
   </si>
   <si>
     <t xml:space="preserve">0.325325071811676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31803223490715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306236773729324</t>
+    <t xml:space="preserve">0.318032205104828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306236803531647</t>
   </si>
   <si>
     <t xml:space="preserve">0.308329522609711</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">0.322788417339325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319934666156769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153974056244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331666678190231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320251762866974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310802757740021</t>
+    <t xml:space="preserve">0.319934636354446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153914451599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331666707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320251733064651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310802727937698</t>
   </si>
   <si>
     <t xml:space="preserve">0.323422580957413</t>
@@ -200,43 +200,43 @@
     <t xml:space="preserve">0.308836817741394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306300193071365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880487680435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28588017821312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267743170261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260767340660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489463090897</t>
+    <t xml:space="preserve">0.306300222873688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880517482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285880208015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267743140459061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260767370462418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489492893219</t>
   </si>
   <si>
     <t xml:space="preserve">0.258738040924072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288543701171875</t>
+    <t xml:space="preserve">0.288543671369553</t>
   </si>
   <si>
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643096923828</t>
+    <t xml:space="preserve">0.364643067121506</t>
   </si>
   <si>
     <t xml:space="preserve">0.367496848106384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369716376066208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399338960648</t>
+    <t xml:space="preserve">0.36971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399279356003</t>
   </si>
   <si>
     <t xml:space="preserve">0.388741225004196</t>
@@ -245,88 +245,88 @@
     <t xml:space="preserve">0.387790024280548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033472776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357033133506775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3741554915905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377643406391144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370984673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372253060340881</t>
+    <t xml:space="preserve">0.370033532381058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35703319311142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374155521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377643436193466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370984703302383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372253030538559</t>
   </si>
   <si>
     <t xml:space="preserve">0.387472927570343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377326369285583</t>
+    <t xml:space="preserve">0.377326339483261</t>
   </si>
   <si>
     <t xml:space="preserve">0.439791232347488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453425794839859</t>
+    <t xml:space="preserve">0.453425735235214</t>
   </si>
   <si>
     <t xml:space="preserve">0.454059958457947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461669772863388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133177995682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45564529299736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456279456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840680360794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792250156403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485767930746078</t>
+    <t xml:space="preserve">0.461669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133207798004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455645352602005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45627948641777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840650558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485767990350723</t>
   </si>
   <si>
     <t xml:space="preserve">0.477841019630432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483231365680695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484816819429398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497817158699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489255875349045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475621432065964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476889729499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48830458521843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493695050477982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489890098571777</t>
+    <t xml:space="preserve">0.483231335878372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484816759824753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497817128896713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48925593495369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475621402263641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476889759302139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304644823074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493695080280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489890038967133</t>
   </si>
   <si>
     <t xml:space="preserve">0.496548742055893</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">0.468645662069321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473084777593613</t>
+    <t xml:space="preserve">0.473084807395935</t>
   </si>
   <si>
     <t xml:space="preserve">0.49528044462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486719220876694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48418253660202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497500091791153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50732958316803</t>
+    <t xml:space="preserve">0.486719250679016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484182596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497500032186508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507329523563385</t>
   </si>
   <si>
     <t xml:space="preserve">0.50796365737915</t>
@@ -362,49 +362,49 @@
     <t xml:space="preserve">0.510183274745941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515890657901764</t>
+    <t xml:space="preserve">0.515890717506409</t>
   </si>
   <si>
     <t xml:space="preserve">0.526354372501373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525720238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52952516078949</t>
+    <t xml:space="preserve">0.525720179080963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529525101184845</t>
   </si>
   <si>
     <t xml:space="preserve">0.535866856575012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540305852890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620844542980194</t>
+    <t xml:space="preserve">0.540305972099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620844423770905</t>
   </si>
   <si>
     <t xml:space="preserve">0.625917792320251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627503156661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597697615623474</t>
+    <t xml:space="preserve">0.627503216266632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597697556018829</t>
   </si>
   <si>
     <t xml:space="preserve">0.596112132072449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57708740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561867356300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583428919315338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569160282611847</t>
+    <t xml:space="preserve">0.577087342739105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561867415904999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428978919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569160223007202</t>
   </si>
   <si>
     <t xml:space="preserve">0.566940784454346</t>
@@ -413,43 +413,43 @@
     <t xml:space="preserve">0.559013724327087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551720798015594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529208123683929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516842007637024</t>
+    <t xml:space="preserve">0.551720857620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529208064079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516841948032379</t>
   </si>
   <si>
     <t xml:space="preserve">0.517476081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516207754611969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465791970491409</t>
+    <t xml:space="preserve">0.516207814216614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465791910886765</t>
   </si>
   <si>
     <t xml:space="preserve">0.4835484623909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549184143543243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547281742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585965573787689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586599826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613868713378906</t>
+    <t xml:space="preserve">0.549184203147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547281682491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558379590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585965633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586599767208099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613868653774261</t>
   </si>
   <si>
     <t xml:space="preserve">0.654455006122589</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">0.62306410074234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63384485244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62211287021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618942081928253</t>
+    <t xml:space="preserve">0.633844792842865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622112810611725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618942022323608</t>
   </si>
   <si>
     <t xml:space="preserve">0.615137040615082</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.63416188955307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629088580608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643674373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64430844783783</t>
+    <t xml:space="preserve">0.629088640213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643674314022064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.644308507442474</t>
   </si>
   <si>
     <t xml:space="preserve">0.64557683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636064469814301</t>
+    <t xml:space="preserve">0.636064410209656</t>
   </si>
   <si>
     <t xml:space="preserve">0.63479608297348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628454446792603</t>
+    <t xml:space="preserve">0.628454387187958</t>
   </si>
   <si>
     <t xml:space="preserve">0.632259368896484</t>
@@ -512,43 +512,43 @@
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234948635101</t>
+    <t xml:space="preserve">0.626234889030457</t>
   </si>
   <si>
     <t xml:space="preserve">0.602453827857971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588185131549835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590087652206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58913642168045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619893312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592941462993622</t>
+    <t xml:space="preserve">0.58818519115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590087592601776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589136481285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619893252849579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592941343784332</t>
   </si>
   <si>
     <t xml:space="preserve">0.600551307201385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595795035362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594526827335358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591673076152802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601185441017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603087902069092</t>
+    <t xml:space="preserve">0.595795094966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594526767730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591673016548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60118556022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603087961673737</t>
   </si>
   <si>
     <t xml:space="preserve">0.609746634960175</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">0.614185810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61196631193161</t>
+    <t xml:space="preserve">0.611966252326965</t>
   </si>
   <si>
     <t xml:space="preserve">0.605941653251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598648846149445</t>
+    <t xml:space="preserve">0.598648905754089</t>
   </si>
   <si>
     <t xml:space="preserve">0.593258440494537</t>
@@ -575,40 +575,40 @@
     <t xml:space="preserve">0.58850222826004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597380578517914</t>
+    <t xml:space="preserve">0.597380459308624</t>
   </si>
   <si>
     <t xml:space="preserve">0.617673635482788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61101496219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604039192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605307519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61006373167038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649465084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039561271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61038076877594</t>
+    <t xml:space="preserve">0.611015021800995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604039311408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605307638645172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610063791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649584293365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039501667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610380828380585</t>
   </si>
   <si>
     <t xml:space="preserve">0.596429288387299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591355979442596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589770615100861</t>
+    <t xml:space="preserve">0.591355919837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589770555496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.565355360507965</t>
@@ -617,49 +617,49 @@
     <t xml:space="preserve">0.523183584213257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481963068246841</t>
+    <t xml:space="preserve">0.481963008642197</t>
   </si>
   <si>
     <t xml:space="preserve">0.493377923965454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492109626531601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508280813694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513988316059113</t>
+    <t xml:space="preserve">0.492109686136246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508280754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513988256454468</t>
   </si>
   <si>
     <t xml:space="preserve">0.509232044219971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509549081325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517793238162994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548550128936768</t>
+    <t xml:space="preserve">0.509549140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51779317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548550069332123</t>
   </si>
   <si>
     <t xml:space="preserve">0.544110894203186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521598160266876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53047639131546</t>
+    <t xml:space="preserve">0.521598219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530476450920105</t>
   </si>
   <si>
     <t xml:space="preserve">0.546013414859772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54094010591507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532696008682251</t>
+    <t xml:space="preserve">0.540940046310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532695949077606</t>
   </si>
   <si>
     <t xml:space="preserve">0.538720548152924</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">0.539037644863129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533330142498016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532061874866486</t>
+    <t xml:space="preserve">0.533330202102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532061815261841</t>
   </si>
   <si>
     <t xml:space="preserve">0.568843245506287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570428669452667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566306531429291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549501299858093</t>
+    <t xml:space="preserve">0.570428609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56630665063858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549501180648804</t>
   </si>
   <si>
     <t xml:space="preserve">0.560599148273468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56440407037735</t>
+    <t xml:space="preserve">0.564404129981995</t>
   </si>
   <si>
     <t xml:space="preserve">0.550452530384064</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">0.545062124729156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521281063556671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516524851322174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50669538974762</t>
+    <t xml:space="preserve">0.521281123161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516524910926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506695330142975</t>
   </si>
   <si>
     <t xml:space="preserve">0.528256893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519695639610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526037275791168</t>
+    <t xml:space="preserve">0.51969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526037335395813</t>
   </si>
   <si>
     <t xml:space="preserve">0.51874440908432</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">0.511451601982117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514305293560028</t>
+    <t xml:space="preserve">0.514305353164673</t>
   </si>
   <si>
     <t xml:space="preserve">0.523817718029022</t>
@@ -740,46 +740,46 @@
     <t xml:space="preserve">0.513671159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511134445667267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504158794879913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506061136722565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505110025405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510500311851501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499719560146332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512085855007172</t>
+    <t xml:space="preserve">0.511134505271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504158735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506061196327209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505109965801239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510500371456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499719589948654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
     <t xml:space="preserve">0.541574239730835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550769627094269</t>
+    <t xml:space="preserve">0.550769686698914</t>
   </si>
   <si>
     <t xml:space="preserve">0.553623378276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560281991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569794476032257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575501918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627820312976837</t>
+    <t xml:space="preserve">0.560282111167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569794535636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57550185918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627820372581482</t>
   </si>
   <si>
     <t xml:space="preserve">0.658894240856171</t>
@@ -788,52 +788,52 @@
     <t xml:space="preserve">0.655723452568054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358205318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76226270198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736896097660065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707724690437317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696943998336792</t>
+    <t xml:space="preserve">0.682358145713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736896157264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707724750041962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696943938732147</t>
   </si>
   <si>
     <t xml:space="preserve">0.733091115951538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.74894517660141</t>
+    <t xml:space="preserve">0.748945236206055</t>
   </si>
   <si>
     <t xml:space="preserve">0.747676908969879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754652738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755286812782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760360181331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818068861961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799678206443787</t>
+    <t xml:space="preserve">0.754652678966522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755286872386932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76036012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818068742752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799678146839142</t>
   </si>
   <si>
     <t xml:space="preserve">0.771140873432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768604218959808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720407903194427</t>
+    <t xml:space="preserve">0.768604278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720408022403717</t>
   </si>
   <si>
     <t xml:space="preserve">0.727383673191071</t>
@@ -848,91 +848,91 @@
     <t xml:space="preserve">0.774945855140686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783824145793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801580607891083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849777042865753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884021639823914</t>
+    <t xml:space="preserve">0.783824026584625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801580667495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849776983261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884021699428558</t>
   </si>
   <si>
     <t xml:space="preserve">0.851045250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878314316272736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894168198108673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876498222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924608051776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88782674074173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901778221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881485044956207</t>
+    <t xml:space="preserve">0.878314256668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894168257713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876438617706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924607992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887826681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901778280735016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881485104560852</t>
   </si>
   <si>
     <t xml:space="preserve">0.902412414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.875143468379974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896070718765259</t>
+    <t xml:space="preserve">0.875143527984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896070837974548</t>
   </si>
   <si>
     <t xml:space="preserve">0.9106565117836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.913827300071716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91002231836319</t>
+    <t xml:space="preserve">0.913827240467072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910022377967834</t>
   </si>
   <si>
     <t xml:space="preserve">0.889729082584381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892900049686432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436644554138</t>
+    <t xml:space="preserve">0.892899930477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436584949493</t>
   </si>
   <si>
     <t xml:space="preserve">0.86309427022934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860557675361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533624172211</t>
+    <t xml:space="preserve">0.860557734966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533445358276</t>
   </si>
   <si>
     <t xml:space="preserve">0.87577760219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868167638778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756555140018463</t>
+    <t xml:space="preserve">0.868167519569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756555080413818</t>
   </si>
   <si>
     <t xml:space="preserve">0.788897395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812995433807373</t>
+    <t xml:space="preserve">0.812995493412018</t>
   </si>
   <si>
     <t xml:space="preserve">0.80728805065155</t>
@@ -944,37 +944,37 @@
     <t xml:space="preserve">0.790165841579437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786360800266266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811727166175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830117881298065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814898073673248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792702376842499</t>
+    <t xml:space="preserve">0.786360740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811727225780487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830118000507355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814897954463959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792702436447144</t>
   </si>
   <si>
     <t xml:space="preserve">0.803483128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804117381572723</t>
+    <t xml:space="preserve">0.804117262363434</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848316192627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780019164085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781921625137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791434049606323</t>
+    <t xml:space="preserve">0.780019104480743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781921744346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791433990001678</t>
   </si>
   <si>
     <t xml:space="preserve">0.785092532634735</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">0.786994874477386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793970763683319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531528949738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77367752790451</t>
+    <t xml:space="preserve">0.793970704078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531588554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773677468299866</t>
   </si>
   <si>
     <t xml:space="preserve">0.775580048561096</t>
@@ -1001,121 +1001,121 @@
     <t xml:space="preserve">0.767335891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771775007247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628448963165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795873165130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811093032360077</t>
+    <t xml:space="preserve">0.77177506685257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76162850856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79587322473526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811093091964722</t>
   </si>
   <si>
     <t xml:space="preserve">0.843435406684875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832654476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460255622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866899251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840264499187469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830751955509186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855484306812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801094055176</t>
+    <t xml:space="preserve">0.832654535770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606873512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460196018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866899430751801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840264618396759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830752074718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855484247207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801213264465</t>
   </si>
   <si>
     <t xml:space="preserve">0.849142789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820605516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824410617351532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826947093009949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806019723415375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799044013023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804751634597778</t>
+    <t xml:space="preserve">0.820605576038361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824410438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826947152614594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806019842624664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799043953418732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804751515388489</t>
   </si>
   <si>
     <t xml:space="preserve">0.7857266664505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778750836849213</t>
+    <t xml:space="preserve">0.778750777244568</t>
   </si>
   <si>
     <t xml:space="preserve">0.777482450008392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802214741706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80665385723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807922303676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854850292205811</t>
+    <t xml:space="preserve">0.802214801311493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806653916835785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80792224407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854850351810455</t>
   </si>
   <si>
     <t xml:space="preserve">0.857386887073517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85231351852417</t>
+    <t xml:space="preserve">0.852313578128815</t>
   </si>
   <si>
     <t xml:space="preserve">0.863728523254395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.864996731281281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850410997867584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84089857339859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996231555939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581226825714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826312899589539</t>
+    <t xml:space="preserve">0.86499685049057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850411117076874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84089869260788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834557116031647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996112346649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581286430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826312959194183</t>
   </si>
   <si>
     <t xml:space="preserve">0.805385649204254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814263999462128</t>
+    <t xml:space="preserve">0.814263939857483</t>
   </si>
   <si>
     <t xml:space="preserve">0.81870299577713</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">0.819337248802185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.796507298946381</t>
+    <t xml:space="preserve">0.79650741815567</t>
   </si>
   <si>
     <t xml:space="preserve">0.809190630912781</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817434668540955</t>
+    <t xml:space="preserve">0.817434787750244</t>
   </si>
   <si>
     <t xml:space="preserve">0.823142111301422</t>
@@ -1148,31 +1148,31 @@
     <t xml:space="preserve">0.812361359596252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81997138261795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797141492366791</t>
+    <t xml:space="preserve">0.819971323013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797141432762146</t>
   </si>
   <si>
     <t xml:space="preserve">0.716602981090546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7045539021492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736262023448944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772409200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776214241981506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78445827960968</t>
+    <t xml:space="preserve">0.704553782939911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736261963844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759725868701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772409319877625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776214122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784458339214325</t>
   </si>
   <si>
     <t xml:space="preserve">0.783189952373505</t>
@@ -1181,37 +1181,37 @@
     <t xml:space="preserve">0.752116024494171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760994255542755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701817512512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790799915790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810458898544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311661720276</t>
+    <t xml:space="preserve">0.760994374752045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823526859283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790799856185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810458958148956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311602115631</t>
   </si>
   <si>
     <t xml:space="preserve">0.781287491321564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795239090919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800312340259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815532267093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764799296855927</t>
+    <t xml:space="preserve">0.795238971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800312399864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815532147884369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764799237251282</t>
   </si>
   <si>
     <t xml:space="preserve">0.731822848320007</t>
@@ -1220,76 +1220,76 @@
     <t xml:space="preserve">0.711529612541199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.693773090839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739432752132416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70391970872879</t>
+    <t xml:space="preserve">0.693773150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739432811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703919768333435</t>
   </si>
   <si>
     <t xml:space="preserve">0.695041418075562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683626472949982</t>
+    <t xml:space="preserve">0.683626532554626</t>
   </si>
   <si>
     <t xml:space="preserve">0.660796701908112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684894919395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.670943260192871</t>
+    <t xml:space="preserve">0.684894859790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.670943200588226</t>
   </si>
   <si>
     <t xml:space="preserve">0.69123649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678553283214569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687431514263153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717871248722076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730554461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710261344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697578132152557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71406626701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729286193847656</t>
+    <t xml:space="preserve">0.678553223609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687431454658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717871308326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730554521083832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710261404514313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697578072547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714066386222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729286134243011</t>
   </si>
   <si>
     <t xml:space="preserve">0.753384292125702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748310983181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757189393043518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758457601070404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763530850410461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749579429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042775154114</t>
+    <t xml:space="preserve">0.748311042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757189333438873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758457660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763530969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749579310417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042655944824</t>
   </si>
   <si>
     <t xml:space="preserve">0.735627770423889</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">0.743237793445587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.741969347000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.744506120681763</t>
+    <t xml:space="preserve">0.741969406604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744506061077118</t>
   </si>
   <si>
     <t xml:space="preserve">0.722944557666779</t>
@@ -1313,22 +1313,22 @@
     <t xml:space="preserve">0.700114727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706456422805786</t>
+    <t xml:space="preserve">0.706456303596497</t>
   </si>
   <si>
     <t xml:space="preserve">0.698846399784088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725481331348419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715334713459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712797880172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69250476360321</t>
+    <t xml:space="preserve">0.72548121213913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71533465385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712797939777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6925048828125</t>
   </si>
   <si>
     <t xml:space="preserve">0.705187976360321</t>
@@ -1343,31 +1343,31 @@
     <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699781894684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686163127422333</t>
+    <t xml:space="preserve">0.688699722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686163246631622</t>
   </si>
   <si>
     <t xml:space="preserve">0.679821610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672211647033691</t>
+    <t xml:space="preserve">0.672211587429047</t>
   </si>
   <si>
     <t xml:space="preserve">0.646845161914825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677284896373749</t>
+    <t xml:space="preserve">0.677284836769104</t>
   </si>
   <si>
     <t xml:space="preserve">0.65826004743576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659528374671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651918411254883</t>
+    <t xml:space="preserve">0.659528315067291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651918470859528</t>
   </si>
   <si>
     <t xml:space="preserve">0.648113429546356</t>
@@ -1379,34 +1379,34 @@
     <t xml:space="preserve">0.635430157184601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643040239810944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639235138893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637966930866241</t>
+    <t xml:space="preserve">0.643040180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639235258102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637966871261597</t>
   </si>
   <si>
     <t xml:space="preserve">0.594209671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596746385097504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609429657459259</t>
+    <t xml:space="preserve">0.596746325492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609429538249969</t>
   </si>
   <si>
     <t xml:space="preserve">0.598014652729034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599917113780975</t>
+    <t xml:space="preserve">0.59991717338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.603722155094147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573916554450989</t>
+    <t xml:space="preserve">0.573916435241699</t>
   </si>
   <si>
     <t xml:space="preserve">0.621478676795959</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615771174430847</t>
+    <t xml:space="preserve">0.622747004032135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615771234035492</t>
   </si>
   <si>
     <t xml:space="preserve">0.6233811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612600386142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591038823127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584063112735748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580892205238342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565672397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570745646953583</t>
+    <t xml:space="preserve">0.612600445747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591038882732391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584063172340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580892384052277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56567245721817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570745706558228</t>
   </si>
   <si>
     <t xml:space="preserve">0.561233282089233</t>
@@ -1448,37 +1448,37 @@
     <t xml:space="preserve">0.572648227214813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559964954853058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537135124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528891086578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573282361030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569477379322052</t>
+    <t xml:space="preserve">0.559965014457703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537135183811188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52889096736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573282301425934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569477438926697</t>
   </si>
   <si>
     <t xml:space="preserve">0.608795404434204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618307948112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630356907844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604990422725677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580258250236511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572014033794403</t>
+    <t xml:space="preserve">0.618307828903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356967449188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604990482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580258190631866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572013974189758</t>
   </si>
   <si>
     <t xml:space="preserve">0.568209052085876</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">0.721676230430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766067564487457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78255569934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215479850769</t>
+    <t xml:space="preserve">0.766067624092102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782555818557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215420246124</t>
   </si>
   <si>
     <t xml:space="preserve">0.825678825378418</t>
@@ -1511,22 +1511,22 @@
     <t xml:space="preserve">0.871338367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882753491401672</t>
+    <t xml:space="preserve">0.882753252983093</t>
   </si>
   <si>
     <t xml:space="preserve">0.880216658115387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903046488761902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92207145690918</t>
+    <t xml:space="preserve">0.903046607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922071397304535</t>
   </si>
   <si>
     <t xml:space="preserve">0.937291324138641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918266355991364</t>
+    <t xml:space="preserve">0.918266415596008</t>
   </si>
   <si>
     <t xml:space="preserve">0.866265177726746</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">0.839630305767059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896705031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87641179561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801891803741</t>
+    <t xml:space="preserve">0.896704912185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876411557197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801832199097</t>
   </si>
   <si>
     <t xml:space="preserve">0.870070099830627</t>
@@ -1553,19 +1553,19 @@
     <t xml:space="preserve">0.934754610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904314935207367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583202838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929681360721588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144646644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906851589679718</t>
+    <t xml:space="preserve">0.904314875602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583083629608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929681301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144825458527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906851470470428</t>
   </si>
   <si>
     <t xml:space="preserve">0.930949687957764</t>
@@ -1574,25 +1574,25 @@
     <t xml:space="preserve">0.891631662845612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833288729190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873724460602</t>
+    <t xml:space="preserve">0.833288788795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873784065247</t>
   </si>
   <si>
     <t xml:space="preserve">0.802848935127258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755921065807343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640503525733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636698544025421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627019286155701</t>
+    <t xml:space="preserve">0.755920946598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640503466129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636698484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627019226551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.641851961612701</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">0.625670790672302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613535046577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616906106472015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618928670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595331132411957</t>
+    <t xml:space="preserve">0.613534986972809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616905987262726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618928611278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">0.596005380153656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60207325220108</t>
+    <t xml:space="preserve">0.60207337141037</t>
   </si>
   <si>
     <t xml:space="preserve">0.598028063774109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594656944274902</t>
+    <t xml:space="preserve">0.594657003879547</t>
   </si>
   <si>
     <t xml:space="preserve">0.610838055610657</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">0.631064474582672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623648166656494</t>
+    <t xml:space="preserve">0.623648107051849</t>
   </si>
   <si>
     <t xml:space="preserve">0.65398782491684</t>
@@ -1649,52 +1649,52 @@
     <t xml:space="preserve">0.656684637069702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637132465839386</t>
+    <t xml:space="preserve">0.637132406234741</t>
   </si>
   <si>
     <t xml:space="preserve">0.626345038414001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628367602825165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624322354793549</t>
+    <t xml:space="preserve">0.62836766242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624322295188904</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716157913208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62769341468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614883363246918</t>
+    <t xml:space="preserve">0.627693474292755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614883422851562</t>
   </si>
   <si>
     <t xml:space="preserve">0.608815491199493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61758017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635783970355988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624996602535248</t>
+    <t xml:space="preserve">0.617580235004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635784029960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624996483325958</t>
   </si>
   <si>
     <t xml:space="preserve">0.614209234714508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605444371700287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606118619441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630390346050262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64320033788681</t>
+    <t xml:space="preserve">0.605444431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606118559837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630390286445618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643200397491455</t>
   </si>
   <si>
     <t xml:space="preserve">0.656010448932648</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">0.621625542640686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608141243457794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610163867473602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549484670162201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561620473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552855610847473</t>
+    <t xml:space="preserve">0.608141183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610163807868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549484550952911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56162041425705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552855670452118</t>
   </si>
   <si>
     <t xml:space="preserve">0.565665781497955</t>
@@ -1733,91 +1733,91 @@
     <t xml:space="preserve">0.558923602104187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563643038272858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569711089134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249354362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562294721603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573082149028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583869457244873</t>
+    <t xml:space="preserve">0.563643157482147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569710969924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249413967133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562294602394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583869516849518</t>
   </si>
   <si>
     <t xml:space="preserve">0.584543704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567014157772064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56633996963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593308568000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599376380443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58656632900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591285824775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600050628185272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602747559547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60746693611145</t>
+    <t xml:space="preserve">0.567014217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566339910030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593308508396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599376440048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586566388607025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591285884380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600050687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60274749994278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60746705532074</t>
   </si>
   <si>
     <t xml:space="preserve">0.590611636638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592634320259094</t>
+    <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
     <t xml:space="preserve">0.587914764881134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618254363536835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639829337596893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641177654266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588589012622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598702311515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620277047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622973918914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609489679336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615557551383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620951294898987</t>
+    <t xml:space="preserve">0.618254423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639829277992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641177713871002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588589072227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598702251911163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620277106761932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62297397851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609489619731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615557610988617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620951354503632</t>
   </si>
   <si>
     <t xml:space="preserve">0.648594081401825</t>
@@ -1829,34 +1829,34 @@
     <t xml:space="preserve">0.604095935821533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603421747684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639155030250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638480842113495</t>
+    <t xml:space="preserve">0.603421688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639155089855194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63848090171814</t>
   </si>
   <si>
     <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695789039134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714667081832886</t>
+    <t xml:space="preserve">0.695788979530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714667022228241</t>
   </si>
   <si>
     <t xml:space="preserve">0.702531218528748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.699834406375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716015517711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728151440620422</t>
+    <t xml:space="preserve">0.69983434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716015636920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728151381015778</t>
   </si>
   <si>
     <t xml:space="preserve">0.717363953590393</t>
@@ -1865,43 +1865,43 @@
     <t xml:space="preserve">0.726802885532379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722757697105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409261226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711970210075378</t>
+    <t xml:space="preserve">0.722757756710052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711970269680023</t>
   </si>
   <si>
     <t xml:space="preserve">0.701182782649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69444066286087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689046919345856</t>
+    <t xml:space="preserve">0.694440603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689046859741211</t>
   </si>
   <si>
     <t xml:space="preserve">0.683653295040131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67960786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.680956363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672191560268402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.685001611709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675562560558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668146312236786</t>
+    <t xml:space="preserve">0.679607927799225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.680956304073334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672191500663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68500167131424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675562620162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668146252632141</t>
   </si>
   <si>
     <t xml:space="preserve">0.631738662719727</t>
@@ -1910,10 +1910,10 @@
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645897269248962</t>
+    <t xml:space="preserve">0.647919833660126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645897209644318</t>
   </si>
   <si>
     <t xml:space="preserve">0.636458277702332</t>
@@ -1922,31 +1922,31 @@
     <t xml:space="preserve">0.633087158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611512303352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574430465698242</t>
+    <t xml:space="preserve">0.611512243747711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574430584907532</t>
   </si>
   <si>
     <t xml:space="preserve">0.589263260364532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560271978378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553529798984528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538697183132172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527235448360443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478692084550858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463859379291534</t>
+    <t xml:space="preserve">0.560272037982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553529858589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538697123527527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527235567569733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478692024946213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463859409093857</t>
   </si>
   <si>
     <t xml:space="preserve">0.458465695381165</t>
@@ -1955,100 +1955,100 @@
     <t xml:space="preserve">0.391044229269028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419361263513565</t>
+    <t xml:space="preserve">0.419361233711243</t>
   </si>
   <si>
     <t xml:space="preserve">0.394415289163589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387673199176788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38834735751152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380256861448288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403180062770844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412619143724442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431497067213058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46520784497261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927281141281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479366302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489479511976242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474646836519241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473298400640488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411550521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498918533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496895879507065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495547473430634</t>
+    <t xml:space="preserve">0.387673139572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388347387313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380256831645966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403180092573166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412619084119797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431497097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465207874774933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927310943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479366391897202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489479541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474646806716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47329843044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533597230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411610126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918503522873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496895909309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495547413825989</t>
   </si>
   <si>
     <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482063204050064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.490827858448029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484760046005249</t>
+    <t xml:space="preserve">0.482063174247742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.490827947854996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484760016202927</t>
   </si>
   <si>
     <t xml:space="preserve">0.480714738368988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482737392187119</t>
+    <t xml:space="preserve">0.482737362384796</t>
   </si>
   <si>
     <t xml:space="preserve">0.485434263944626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488131046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481388956308365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472624152898788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427451878786087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434868156909943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438239306211472</t>
+    <t xml:space="preserve">0.488131105899811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481388926506042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472624212503433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42745178937912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43486812710762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438239246606827</t>
   </si>
   <si>
     <t xml:space="preserve">0.443632960319519</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">0.449136018753052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4512679874897</t>
+    <t xml:space="preserve">0.451267957687378</t>
   </si>
   <si>
     <t xml:space="preserve">0.456953257322311</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">0.446293383836746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453399986028671</t>
+    <t xml:space="preserve">0.453399926424026</t>
   </si>
   <si>
     <t xml:space="preserve">0.466191828250885</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">0.48040497303009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498882085084915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488222181797028</t>
+    <t xml:space="preserve">0.498882114887238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488222151994705</t>
   </si>
   <si>
     <t xml:space="preserve">0.47756227850914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445582747459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442740112543106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.452689290046692</t>
+    <t xml:space="preserve">0.445582717657089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442740082740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.452689349651337</t>
   </si>
   <si>
     <t xml:space="preserve">0.447004020214081</t>
@@ -2126,22 +2126,22 @@
     <t xml:space="preserve">0.448425322771072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442029416561127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42994824051857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438476055860519</t>
+    <t xml:space="preserve">0.442029386758804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429948270320892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438476085662842</t>
   </si>
   <si>
     <t xml:space="preserve">0.429237604141235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447714686393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439186781644821</t>
+    <t xml:space="preserve">0.447714656591415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439186751842499</t>
   </si>
   <si>
     <t xml:space="preserve">0.463349193334579</t>
@@ -2150,22 +2150,22 @@
     <t xml:space="preserve">0.458374559879303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444161355495453</t>
+    <t xml:space="preserve">0.444161385297775</t>
   </si>
   <si>
     <t xml:space="preserve">0.456242620944977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449846684932709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455531865358353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450748920441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430658906698227</t>
+    <t xml:space="preserve">0.449846655130386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455531924962997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430658876895905</t>
   </si>
   <si>
     <t xml:space="preserve">0.420709669589996</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">0.413603097200394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417156398296356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416445761919022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427105635404587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437054842710495</t>
+    <t xml:space="preserve">0.417156428098679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416445732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427105605602264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437054812908173</t>
   </si>
   <si>
     <t xml:space="preserve">0.432080209255219</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">0.434922844171524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42284169793129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417867034673691</t>
+    <t xml:space="preserve">0.422841668128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417867064476013</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496554613113</t>
@@ -2216,34 +2216,34 @@
     <t xml:space="preserve">0.401521921157837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405075162649155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400811225175858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387308716773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385176748037338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400100588798523</t>
+    <t xml:space="preserve">0.405075132846832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400811284780502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387308746576309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385176777839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400100558996201</t>
   </si>
   <si>
     <t xml:space="preserve">0.41573503613472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398679286241531</t>
+    <t xml:space="preserve">0.398679256439209</t>
   </si>
   <si>
     <t xml:space="preserve">0.409339129924774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395836651325226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382334142923355</t>
+    <t xml:space="preserve">0.395836621522903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382334113121033</t>
   </si>
   <si>
     <t xml:space="preserve">0.370963603258133</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">0.366699635982513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363146364688873</t>
+    <t xml:space="preserve">0.363146305084229</t>
   </si>
   <si>
     <t xml:space="preserve">0.3539077937603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356750428676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359593033790588</t>
+    <t xml:space="preserve">0.356750398874283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359593063592911</t>
   </si>
   <si>
     <t xml:space="preserve">0.358882397413254</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">0.388730019330978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390151381492615</t>
+    <t xml:space="preserve">0.390151411294937</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372384876012802</t>
+    <t xml:space="preserve">0.372384905815125</t>
   </si>
   <si>
     <t xml:space="preserve">0.36385703086853</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">0.361725032329559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355329126119614</t>
+    <t xml:space="preserve">0.355329096317291</t>
   </si>
   <si>
     <t xml:space="preserve">0.353552460670471</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">0.351775825023651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065188646317</t>
+    <t xml:space="preserve">0.351065158843994</t>
   </si>
   <si>
     <t xml:space="preserve">0.334009349346161</t>
@@ -2312,46 +2312,46 @@
     <t xml:space="preserve">0.323349505662918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342181921005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337207347154617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337562680244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343958586454391</t>
+    <t xml:space="preserve">0.342181950807571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337207317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337562650442123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343958616256714</t>
   </si>
   <si>
     <t xml:space="preserve">0.361014395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36030375957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389440715312958</t>
+    <t xml:space="preserve">0.360303729772568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38944074511528</t>
   </si>
   <si>
     <t xml:space="preserve">0.396547317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412181794643402</t>
+    <t xml:space="preserve">0.412181824445724</t>
   </si>
   <si>
     <t xml:space="preserve">0.421420335769653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415024399757385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419999033212662</t>
+    <t xml:space="preserve">0.415024369955063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419999003410339</t>
   </si>
   <si>
     <t xml:space="preserve">0.414313763380051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405785858631134</t>
+    <t xml:space="preserve">0.405785828828812</t>
   </si>
   <si>
     <t xml:space="preserve">0.402232527732849</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">0.418577700853348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41928830742836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399389892816544</t>
+    <t xml:space="preserve">0.419288337230682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399389863014221</t>
   </si>
   <si>
     <t xml:space="preserve">0.393704652786255</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">0.391572684049606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39725798368454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40436452627182</t>
+    <t xml:space="preserve">0.397257953882217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404364556074142</t>
   </si>
   <si>
     <t xml:space="preserve">0.395125985145569</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">0.373806267976761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369542241096497</t>
+    <t xml:space="preserve">0.369542270898819</t>
   </si>
   <si>
     <t xml:space="preserve">0.368831604719162</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">0.364567667245865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428526937961578</t>
+    <t xml:space="preserve">0.428526908159256</t>
   </si>
   <si>
     <t xml:space="preserve">0.423552334308624</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">0.42639496922493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44060817360878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897477626801</t>
+    <t xml:space="preserve">0.440608114004135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897447824478</t>
   </si>
   <si>
     <t xml:space="preserve">0.464770466089249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471877038478851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478983670473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492486208677292</t>
+    <t xml:space="preserve">0.471877008676529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478983700275421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492486149072647</t>
   </si>
   <si>
     <t xml:space="preserve">0.515227198600769</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">0.506699323654175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517359137535095</t>
+    <t xml:space="preserve">0.51735919713974</t>
   </si>
   <si>
     <t xml:space="preserve">0.508120596408844</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">0.525176465511322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530151069164276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52446573972702</t>
+    <t xml:space="preserve">0.530151128768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524465799331665</t>
   </si>
   <si>
     <t xml:space="preserve">0.53867894411087</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.528729677200317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518780529499054</t>
+    <t xml:space="preserve">0.518780589103699</t>
   </si>
   <si>
     <t xml:space="preserve">0.515937864780426</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">0.523044407367706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54223221540451</t>
+    <t xml:space="preserve">0.542232275009155</t>
   </si>
   <si>
     <t xml:space="preserve">0.53157240152359</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569902896881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516230523586273</t>
+    <t xml:space="preserve">0.526569843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516230463981628</t>
   </si>
   <si>
     <t xml:space="preserve">0.514753460884094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518446087837219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52435427904129</t>
+    <t xml:space="preserve">0.518446028232574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524354219436646</t>
   </si>
   <si>
     <t xml:space="preserve">0.533955156803131</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">0.575312674045563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56866592168808</t>
+    <t xml:space="preserve">0.568665862083435</t>
   </si>
   <si>
     <t xml:space="preserve">0.54281747341156</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">0.53543221950531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531001031398773</t>
+    <t xml:space="preserve">0.531000971794128</t>
   </si>
   <si>
     <t xml:space="preserve">0.51696902513504</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511799395084381</t>
+    <t xml:space="preserve">0.511799335479736</t>
   </si>
   <si>
     <t xml:space="preserve">0.509583711624146</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">0.506629586219788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487427949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488166451454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735203742981</t>
+    <t xml:space="preserve">0.487427979707718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488166511058807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735263347626</t>
   </si>
   <si>
     <t xml:space="preserve">0.488905012607574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480781197547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48151969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492597579956055</t>
+    <t xml:space="preserve">0.480781227350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481519728899002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492597639560699</t>
   </si>
   <si>
     <t xml:space="preserve">0.522138714790344</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">0.512537837028503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514014899730682</t>
+    <t xml:space="preserve">0.514014840126038</t>
   </si>
   <si>
     <t xml:space="preserve">0.525092840194702</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">0.545033037662506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528785526752472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533216655254364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520661652088165</t>
+    <t xml:space="preserve">0.528785467147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533216595649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520661592483521</t>
   </si>
   <si>
     <t xml:space="preserve">0.515491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508106708526611</t>
+    <t xml:space="preserve">0.508106648921967</t>
   </si>
   <si>
     <t xml:space="preserve">0.505152583122253</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">0.502198457717896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495551705360413</t>
+    <t xml:space="preserve">0.495551735162735</t>
   </si>
   <si>
     <t xml:space="preserve">0.498505830764771</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721335411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771658420563</t>
+    <t xml:space="preserve">0.500721395015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771598815918</t>
   </si>
   <si>
     <t xml:space="preserve">0.540601849555969</t>
@@ -2741,31 +2741,31 @@
     <t xml:space="preserve">0.539863407611847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613716125488281</t>
+    <t xml:space="preserve">0.613716065883636</t>
   </si>
   <si>
     <t xml:space="preserve">0.641780078411102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622578382492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627009570598602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612977564334869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616670191287994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62996369600296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620362818241119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61519318819046</t>
+    <t xml:space="preserve">0.622578322887421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627009510993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612977504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61667013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629963636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620362758636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615193128585815</t>
   </si>
   <si>
     <t xml:space="preserve">0.601161122322083</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">0.600422620773315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607069373130798</t>
+    <t xml:space="preserve">0.607069313526154</t>
   </si>
   <si>
     <t xml:space="preserve">0.593037307262421</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">0.603376686573029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641041576862335</t>
+    <t xml:space="preserve">0.64104151725769</t>
   </si>
   <si>
     <t xml:space="preserve">0.664674401283264</t>
@@ -2807,28 +2807,28 @@
     <t xml:space="preserve">0.666890025138855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658766210079193</t>
+    <t xml:space="preserve">0.658766269683838</t>
   </si>
   <si>
     <t xml:space="preserve">0.653596520423889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667628526687622</t>
+    <t xml:space="preserve">0.667628586292267</t>
   </si>
   <si>
     <t xml:space="preserve">0.648426830768585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647688329219818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639564514160156</t>
+    <t xml:space="preserve">0.647688269615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639564454555511</t>
   </si>
   <si>
     <t xml:space="preserve">0.629225134849548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642518639564514</t>
+    <t xml:space="preserve">0.642518579959869</t>
   </si>
   <si>
     <t xml:space="preserve">0.640303015708923</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">0.633656322956085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675752341747284</t>
+    <t xml:space="preserve">0.675752401351929</t>
   </si>
   <si>
     <t xml:space="preserve">0.649165391921997</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">0.65581214427948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655073583126068</t>
+    <t xml:space="preserve">0.655073642730713</t>
   </si>
   <si>
     <t xml:space="preserve">0.635871887207031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618147253990173</t>
+    <t xml:space="preserve">0.618147194385529</t>
   </si>
   <si>
     <t xml:space="preserve">0.625532507896423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638087451457977</t>
+    <t xml:space="preserve">0.638087511062622</t>
   </si>
   <si>
     <t xml:space="preserve">0.643995702266693</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">0.638826012611389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626271069049835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702197551727</t>
+    <t xml:space="preserve">0.62627100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702137947083</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">0.676490843296051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673536777496338</t>
+    <t xml:space="preserve">0.673536837100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.661720395088196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635133385658264</t>
+    <t xml:space="preserve">0.635133326053619</t>
   </si>
   <si>
     <t xml:space="preserve">0.576789736747742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60411524772644</t>
+    <t xml:space="preserve">0.604115188121796</t>
   </si>
   <si>
     <t xml:space="preserve">0.587867677211761</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">0.582697927951813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570881545543671</t>
+    <t xml:space="preserve">0.570881485939026</t>
   </si>
   <si>
     <t xml:space="preserve">0.559803605079651</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">0.55758798122406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543555974960327</t>
+    <t xml:space="preserve">0.543555915355682</t>
   </si>
   <si>
     <t xml:space="preserve">0.555372416973114</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572972297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568172216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169816017151</t>
+    <t xml:space="preserve">0.570572912693024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56817215681076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169756412506</t>
   </si>
   <si>
     <t xml:space="preserve">0.562570512294769</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">0.569772720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578575372695923</t>
+    <t xml:space="preserve">0.578575313091278</t>
   </si>
   <si>
     <t xml:space="preserve">0.566571712493896</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">0.537762999534607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513755679130554</t>
+    <t xml:space="preserve">0.513755738735199</t>
   </si>
   <si>
     <t xml:space="preserve">0.516156435012817</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">0.521758139133453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536962747573853</t>
+    <t xml:space="preserve">0.536962687969208</t>
   </si>
   <si>
     <t xml:space="preserve">0.548166155815125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526559591293335</t>
+    <t xml:space="preserve">0.52655953168869</t>
   </si>
   <si>
     <t xml:space="preserve">0.522558391094208</t>
@@ -3032,34 +3032,34 @@
     <t xml:space="preserve">0.532961547374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524959087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508153975009918</t>
+    <t xml:space="preserve">0.524959146976471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508154034614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.504152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484146744012833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480945765972137</t>
+    <t xml:space="preserve">0.484146773815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48094579577446</t>
   </si>
   <si>
     <t xml:space="preserve">0.5057532787323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493749648332596</t>
+    <t xml:space="preserve">0.493749618530273</t>
   </si>
   <si>
     <t xml:space="preserve">0.48734775185585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48814794421196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56177031993866</t>
+    <t xml:space="preserve">0.488147974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561770260334015</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">0.588978469371796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568972527980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572173416614532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575374364852905</t>
+    <t xml:space="preserve">0.56897246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572173357009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57537442445755</t>
   </si>
   <si>
     <t xml:space="preserve">0.577775120735168</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">0.581776320934296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58337676525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576974928379059</t>
+    <t xml:space="preserve">0.583376824855804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576974868774414</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584977269172668</t>
+    <t xml:space="preserve">0.584977328777313</t>
   </si>
   <si>
     <t xml:space="preserve">0.586577773094177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585777580738068</t>
+    <t xml:space="preserve">0.585777521133423</t>
   </si>
   <si>
     <t xml:space="preserve">0.591379284858704</t>
@@ -3116,25 +3116,25 @@
     <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567371904850006</t>
+    <t xml:space="preserve">0.567371964454651</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544164955615997</t>
+    <t xml:space="preserve">0.544164896011353</t>
   </si>
   <si>
     <t xml:space="preserve">0.54096394777298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543364703655243</t>
+    <t xml:space="preserve">0.543364644050598</t>
   </si>
   <si>
     <t xml:space="preserve">0.542564451694489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535362303256989</t>
+    <t xml:space="preserve">0.535362243652344</t>
   </si>
   <si>
     <t xml:space="preserve">0.536162495613098</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">0.516956686973572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515356183052063</t>
+    <t xml:space="preserve">0.515356242656708</t>
   </si>
   <si>
     <t xml:space="preserve">0.508954226970673</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554790496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524158835411072</t>
+    <t xml:space="preserve">0.510554730892181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524158895015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.529760599136353</t>
@@ -3182,19 +3182,19 @@
     <t xml:space="preserve">0.531361043453217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550566852092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532161295413971</t>
+    <t xml:space="preserve">0.550566911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532161355018616</t>
   </si>
   <si>
     <t xml:space="preserve">0.530560791492462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527359843254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51215523481369</t>
+    <t xml:space="preserve">0.527359783649445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512155175209045</t>
   </si>
   <si>
     <t xml:space="preserve">0.534561991691589</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">0.520157635211945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540163695812225</t>
+    <t xml:space="preserve">0.54016375541687</t>
   </si>
   <si>
     <t xml:space="preserve">0.54736590385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552167356014252</t>
+    <t xml:space="preserve">0.552167296409607</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
@@ -3218,34 +3218,34 @@
     <t xml:space="preserve">0.557769060134888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548966348171234</t>
+    <t xml:space="preserve">0.548966407775879</t>
   </si>
   <si>
     <t xml:space="preserve">0.559369564056396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556968748569489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558569252490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584177076816559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587378084659576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573773860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600982129573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612185537815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616986989974976</t>
+    <t xml:space="preserve">0.556968808174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558569312095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584177136421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587378025054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573773920536041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600982189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612185478210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61698704957962</t>
   </si>
   <si>
     <t xml:space="preserve">0.621788501739502</t>
@@ -3257,16 +3257,16 @@
     <t xml:space="preserve">0.622588694095612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620187938213348</t>
+    <t xml:space="preserve">0.620187878608704</t>
   </si>
   <si>
     <t xml:space="preserve">0.599381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60418313741684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602582693099976</t>
+    <t xml:space="preserve">0.604183077812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602582633495331</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">0.624989449977875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628190398216248</t>
+    <t xml:space="preserve">0.628190338611603</t>
   </si>
   <si>
     <t xml:space="preserve">0.636192858219147</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">0.640194058418274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643394947052002</t>
+    <t xml:space="preserve">0.643395006656647</t>
   </si>
   <si>
     <t xml:space="preserve">0.637793302536011</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792042732239</t>
+    <t xml:space="preserve">0.633792102336884</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628990709781647</t>
+    <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.635921716690063</t>
@@ -3351,9 +3351,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.62119323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.640253603458405</t>
@@ -53723,7 +53720,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53749,7 +53746,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1898" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53775,7 +53772,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1899" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53801,7 +53798,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1900" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53827,7 +53824,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1901" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53879,7 +53876,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1903" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53905,7 +53902,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53931,7 +53928,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1905" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53957,7 +53954,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1906" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54009,7 +54006,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1908" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54061,7 +54058,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1910" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54087,7 +54084,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1911" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54113,7 +54110,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1912" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54139,7 +54136,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1913" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54217,7 +54214,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1916" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54269,7 +54266,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1918" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54295,7 +54292,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1919" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54347,7 +54344,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1921" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54399,7 +54396,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1923" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54425,7 +54422,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1924" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54503,7 +54500,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1927" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54529,7 +54526,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1928" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54555,7 +54552,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1929" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54581,7 +54578,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1930" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54685,7 +54682,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1934" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54737,7 +54734,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1936" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54763,7 +54760,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1937" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54789,7 +54786,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1938" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54867,7 +54864,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1941" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54893,7 +54890,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1942" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54919,7 +54916,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1943" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54997,7 +54994,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G1946" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55049,7 +55046,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1948" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55075,7 +55072,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1949" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55101,7 +55098,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1950" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55127,7 +55124,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1951" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55153,7 +55150,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55179,7 +55176,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1953" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55205,7 +55202,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1954" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55231,7 +55228,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1955" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55283,7 +55280,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1957" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55309,7 +55306,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1958" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55335,7 +55332,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1959" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55361,7 +55358,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1960" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55517,7 +55514,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1966" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55543,7 +55540,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55569,7 +55566,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55595,7 +55592,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1969" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55621,7 +55618,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1970" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55673,7 +55670,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1972" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55699,7 +55696,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1973" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55725,7 +55722,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1974" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55751,7 +55748,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1975" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55777,7 +55774,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1976" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55803,7 +55800,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1977" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55829,7 +55826,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1978" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55855,7 +55852,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55881,7 +55878,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1980" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55907,7 +55904,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1981" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55933,7 +55930,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1982" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55959,7 +55956,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55985,7 +55982,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1984" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56011,7 +56008,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1985" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56063,7 +56060,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1987" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56089,7 +56086,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56115,7 +56112,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1989" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56141,7 +56138,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1990" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56167,7 +56164,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1991" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56193,7 +56190,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1992" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56219,7 +56216,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1993" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56245,7 +56242,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1994" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56297,7 +56294,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1996" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56323,7 +56320,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1997" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56375,7 +56372,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1999" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56427,7 +56424,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2001" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56453,7 +56450,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2002" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56609,7 +56606,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2008" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56635,7 +56632,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2009" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56661,7 +56658,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G2010" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56713,7 +56710,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56739,7 +56736,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2013" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56765,7 +56762,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2014" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56791,7 +56788,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2015" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56817,7 +56814,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G2016" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56843,7 +56840,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2017" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56921,7 +56918,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2020" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56947,7 +56944,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G2021" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56973,7 +56970,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G2022" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56999,7 +56996,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2023" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57025,7 +57022,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2024" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57051,7 +57048,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G2025" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57077,7 +57074,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2026" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57103,7 +57100,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G2027" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57129,7 +57126,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2028" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57155,7 +57152,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2029" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57181,7 +57178,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2030" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57259,7 +57256,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2033" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57285,7 +57282,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2034" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57363,7 +57360,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2037" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57389,7 +57386,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2038" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57415,7 +57412,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2039" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57441,7 +57438,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2040" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57467,7 +57464,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2041" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57493,7 +57490,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2042" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57519,7 +57516,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G2043" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57545,7 +57542,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2044" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57571,7 +57568,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2045" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57597,7 +57594,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2046" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57623,7 +57620,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2047" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57649,7 +57646,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57675,7 +57672,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57701,7 +57698,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2050" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57727,7 +57724,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2051" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57753,7 +57750,7 @@
         <v>0.75</v>
       </c>
       <c r="G2052" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57779,7 +57776,7 @@
         <v>0.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57805,7 +57802,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G2054" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57831,7 +57828,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2055" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57857,7 +57854,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2056" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57883,7 +57880,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2057" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57909,7 +57906,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2058" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57935,7 +57932,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2059" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57961,7 +57958,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G2060" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57987,7 +57984,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58013,7 +58010,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2062" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58039,7 +58036,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2063" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58065,7 +58062,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G2064" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58091,7 +58088,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2065" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58117,7 +58114,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2066" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58169,7 +58166,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2068" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58195,7 +58192,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2069" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58221,7 +58218,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2070" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58247,7 +58244,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2071" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58273,7 +58270,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2072" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58325,7 +58322,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2074" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58351,7 +58348,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2075" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58403,7 +58400,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2077" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58429,7 +58426,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2078" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58455,7 +58452,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2079" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58507,7 +58504,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2081" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58533,7 +58530,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2082" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58585,7 +58582,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2084" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58611,7 +58608,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2085" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58637,7 +58634,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2086" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58663,7 +58660,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2087" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58689,7 +58686,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2088" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58715,7 +58712,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2089" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58741,7 +58738,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2090" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58767,7 +58764,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2091" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58793,7 +58790,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2092" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58819,7 +58816,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G2093" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58845,7 +58842,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G2094" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58871,7 +58868,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G2095" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58897,7 +58894,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2096" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58923,7 +58920,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2097" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58949,7 +58946,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G2098" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58975,7 +58972,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2099" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59001,7 +58998,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2100" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59027,7 +59024,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G2101" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59053,7 +59050,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2102" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59079,7 +59076,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2103" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59105,7 +59102,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2104" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59131,7 +59128,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59157,7 +59154,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2106" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59183,7 +59180,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2107" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59209,7 +59206,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2108" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59235,7 +59232,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2109" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59261,7 +59258,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59287,7 +59284,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2111" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59313,7 +59310,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2112" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59339,7 +59336,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2113" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59365,7 +59362,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2114" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59391,7 +59388,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2115" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59417,7 +59414,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2116" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59443,7 +59440,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2117" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59469,7 +59466,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2118" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59495,7 +59492,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2119" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59521,7 +59518,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2120" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59547,7 +59544,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G2121" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59573,7 +59570,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2122" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59599,7 +59596,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2123" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59625,7 +59622,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2124" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59651,7 +59648,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2125" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59677,7 +59674,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2126" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59703,7 +59700,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2127" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59729,7 +59726,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2128" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59755,7 +59752,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2129" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59781,7 +59778,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2130" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59807,7 +59804,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2131" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59833,7 +59830,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2132" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59859,7 +59856,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2133" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59885,7 +59882,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G2134" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59911,7 +59908,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2135" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59937,7 +59934,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2136" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59963,7 +59960,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2137" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59989,7 +59986,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2138" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60015,7 +60012,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2139" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60041,7 +60038,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2140" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60067,7 +60064,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60093,7 +60090,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2142" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60119,7 +60116,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2143" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60145,7 +60142,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2144" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60171,7 +60168,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2145" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60197,7 +60194,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2146" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60223,7 +60220,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2147" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60249,7 +60246,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2148" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60275,7 +60272,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2149" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60301,7 +60298,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2150" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60327,7 +60324,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2151" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60353,7 +60350,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2152" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60379,7 +60376,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60405,7 +60402,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2154" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60431,7 +60428,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2155" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60457,7 +60454,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2156" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60483,7 +60480,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2157" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60509,7 +60506,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2158" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60535,7 +60532,7 @@
         <v>0.75</v>
       </c>
       <c r="G2159" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60561,7 +60558,7 @@
         <v>0.75</v>
       </c>
       <c r="G2160" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60587,7 +60584,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2161" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60613,7 +60610,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2162" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60639,7 +60636,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2163" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60665,7 +60662,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2164" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60691,7 +60688,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2165" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60717,7 +60714,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2166" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60743,7 +60740,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2167" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60769,7 +60766,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2168" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60795,7 +60792,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2169" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60821,7 +60818,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2170" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60847,7 +60844,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2171" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60873,7 +60870,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2172" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60899,7 +60896,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2173" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60925,7 +60922,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2174" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60951,7 +60948,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2175" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60977,7 +60974,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2176" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61003,7 +61000,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2177" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61029,7 +61026,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2178" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61055,7 +61052,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2179" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61081,7 +61078,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2180" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61107,7 +61104,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2181" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61133,7 +61130,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2182" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61159,7 +61156,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2183" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61185,7 +61182,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61211,7 +61208,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2185" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61237,7 +61234,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2186" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61263,7 +61260,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2187" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61289,7 +61286,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61315,7 +61312,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2189" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61341,7 +61338,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2190" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61367,7 +61364,7 @@
         <v>0.75</v>
       </c>
       <c r="G2191" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61393,7 +61390,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2192" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61419,7 +61416,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2193" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61445,7 +61442,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2194" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61471,7 +61468,7 @@
         <v>0.75</v>
       </c>
       <c r="G2195" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61497,7 +61494,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2196" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61523,7 +61520,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2197" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61549,7 +61546,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2198" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61575,7 +61572,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2199" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61601,7 +61598,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2200" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61627,7 +61624,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2201" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61653,7 +61650,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2202" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61679,7 +61676,7 @@
         <v>0.75</v>
       </c>
       <c r="G2203" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61705,7 +61702,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2204" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61731,7 +61728,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2205" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61757,7 +61754,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2206" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61783,7 +61780,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2207" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61809,7 +61806,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2208" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61835,7 +61832,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2209" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61861,7 +61858,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2210" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61887,7 +61884,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2211" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61913,7 +61910,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2212" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61939,7 +61936,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2213" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61965,7 +61962,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2214" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61991,7 +61988,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2215" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62017,7 +62014,7 @@
         <v>0.75</v>
       </c>
       <c r="G2216" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62043,7 +62040,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2217" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62069,7 +62066,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2218" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62095,7 +62092,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2219" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62121,7 +62118,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2220" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62147,7 +62144,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2221" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62173,7 +62170,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2222" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62199,7 +62196,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2223" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62225,7 +62222,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2224" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62251,7 +62248,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2225" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62277,7 +62274,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2226" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62303,7 +62300,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2227" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62329,7 +62326,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62355,7 +62352,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2229" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62381,7 +62378,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2230" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62407,7 +62404,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2231" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62433,7 +62430,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2232" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62459,7 +62456,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2233" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62485,7 +62482,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2234" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62511,7 +62508,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2235" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62537,7 +62534,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2236" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62563,7 +62560,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2237" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62589,7 +62586,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2238" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62615,7 +62612,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2239" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62641,7 +62638,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2240" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62667,7 +62664,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G2241" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62693,7 +62690,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2242" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62719,7 +62716,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2243" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62745,7 +62742,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2244" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62771,7 +62768,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2245" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62797,7 +62794,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2246" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62823,7 +62820,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2247" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62849,7 +62846,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62875,7 +62872,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2249" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62901,7 +62898,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2250" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62927,7 +62924,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2251" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62953,7 +62950,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2252" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62979,7 +62976,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2253" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63005,7 +63002,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2254" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63031,7 +63028,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2255" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63057,7 +63054,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2256" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63083,7 +63080,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2257" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63109,7 +63106,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2258" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63135,7 +63132,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2259" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63161,7 +63158,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2260" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63187,7 +63184,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2261" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63213,7 +63210,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G2262" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63239,7 +63236,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63265,7 +63262,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63291,7 +63288,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63317,7 +63314,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63343,7 +63340,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63369,7 +63366,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63395,7 +63392,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63421,7 +63418,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63447,7 +63444,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63473,7 +63470,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63499,7 +63496,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63525,7 +63522,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63551,7 +63548,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63577,7 +63574,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63603,7 +63600,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63629,7 +63626,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63655,7 +63652,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63681,7 +63678,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63707,7 +63704,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63733,7 +63730,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63759,7 +63756,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63785,7 +63782,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63811,7 +63808,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63837,7 +63834,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63863,7 +63860,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63889,7 +63886,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63915,7 +63912,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63941,7 +63938,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63967,7 +63964,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63993,7 +63990,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64019,7 +64016,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64045,7 +64042,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64071,7 +64068,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64097,7 +64094,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64123,7 +64120,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64149,7 +64146,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64175,7 +64172,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64201,7 +64198,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64227,7 +64224,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64253,7 +64250,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64279,7 +64276,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64305,7 +64302,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64331,7 +64328,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64357,7 +64354,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64383,7 +64380,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64409,7 +64406,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64435,7 +64432,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64461,7 +64458,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64487,7 +64484,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64513,7 +64510,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64539,7 +64536,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64565,7 +64562,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64591,7 +64588,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64617,7 +64614,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64643,7 +64640,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64669,7 +64666,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64695,7 +64692,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64721,7 +64718,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64747,7 +64744,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64773,7 +64770,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64799,7 +64796,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64825,7 +64822,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64851,7 +64848,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64877,7 +64874,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64903,7 +64900,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64929,7 +64926,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64955,7 +64952,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64981,7 +64978,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65007,7 +65004,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65033,7 +65030,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65059,7 +65056,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65085,7 +65082,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65111,7 +65108,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65137,7 +65134,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65163,7 +65160,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65189,7 +65186,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65215,7 +65212,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65241,7 +65238,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65267,7 +65264,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65293,7 +65290,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65319,7 +65316,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65345,7 +65342,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65371,7 +65368,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65397,7 +65394,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65423,7 +65420,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65449,7 +65446,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65475,7 +65472,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65501,7 +65498,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65527,7 +65524,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65553,7 +65550,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65579,7 +65576,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65605,7 +65602,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65631,7 +65628,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65657,7 +65654,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65683,7 +65680,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65709,7 +65706,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65735,7 +65732,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65761,7 +65758,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65787,7 +65784,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65813,7 +65810,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65839,7 +65836,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65865,7 +65862,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65891,7 +65888,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65917,7 +65914,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65943,7 +65940,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65969,7 +65966,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65995,7 +65992,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66021,7 +66018,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66047,7 +66044,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66073,7 +66070,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66099,7 +66096,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66125,7 +66122,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66151,7 +66148,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66177,7 +66174,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66203,7 +66200,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66229,7 +66226,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66255,7 +66252,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66281,7 +66278,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66307,7 +66304,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66333,7 +66330,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66359,7 +66356,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66385,7 +66382,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66411,7 +66408,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66437,7 +66434,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66463,7 +66460,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66489,7 +66486,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66515,7 +66512,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66541,7 +66538,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66567,7 +66564,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66593,7 +66590,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66619,7 +66616,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66645,7 +66642,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66671,7 +66668,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66697,7 +66694,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66723,7 +66720,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66749,7 +66746,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66775,7 +66772,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66801,7 +66798,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66827,7 +66824,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66853,7 +66850,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66879,7 +66876,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66905,7 +66902,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66931,7 +66928,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66957,7 +66954,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66983,7 +66980,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67009,7 +67006,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67035,7 +67032,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67061,7 +67058,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67087,7 +67084,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67113,7 +67110,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67139,7 +67136,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67165,7 +67162,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67191,7 +67188,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67217,7 +67214,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67243,7 +67240,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67269,7 +67266,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67295,7 +67292,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67321,7 +67318,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67347,7 +67344,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67373,7 +67370,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67399,7 +67396,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67425,7 +67422,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67451,7 +67448,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67477,7 +67474,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67503,7 +67500,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67529,7 +67526,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67555,7 +67552,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67581,7 +67578,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67607,7 +67604,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67633,7 +67630,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67659,7 +67656,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67685,7 +67682,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67711,7 +67708,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67737,7 +67734,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67763,7 +67760,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67789,7 +67786,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67815,7 +67812,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67841,7 +67838,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67867,7 +67864,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67893,7 +67890,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67919,7 +67916,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67945,7 +67942,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67971,7 +67968,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67997,7 +67994,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68023,7 +68020,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68049,7 +68046,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68075,7 +68072,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68101,7 +68098,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68127,7 +68124,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68153,7 +68150,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68179,7 +68176,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68205,7 +68202,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68231,7 +68228,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68257,7 +68254,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68283,7 +68280,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68309,7 +68306,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68335,7 +68332,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68361,7 +68358,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68387,7 +68384,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68413,7 +68410,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68439,7 +68436,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68465,7 +68462,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68491,7 +68488,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68517,7 +68514,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68543,7 +68540,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68569,7 +68566,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68595,7 +68592,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68621,7 +68618,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68647,7 +68644,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68673,7 +68670,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68699,7 +68696,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68725,7 +68722,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68751,7 +68748,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68777,7 +68774,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68803,7 +68800,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68829,7 +68826,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68855,7 +68852,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68881,7 +68878,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68907,7 +68904,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68933,7 +68930,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68959,7 +68956,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68985,7 +68982,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69011,7 +69008,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69037,7 +69034,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69063,7 +69060,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69089,7 +69086,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69097,7 +69094,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6493287037</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>168065</v>
@@ -69115,9 +69112,35 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6494907407</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>53694</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>1.04200005531311</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>1.02400004863739</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>1.02400004863739</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594666719437</t>
+    <t xml:space="preserve">0.378594636917114</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716745138168</t>
+    <t xml:space="preserve">0.382716715335846</t>
   </si>
   <si>
     <t xml:space="preserve">0.367179721593857</t>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">0.380497127771378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361789375543594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352276891469955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368131011724472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387155801057816</t>
+    <t xml:space="preserve">0.361789405345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352276921272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36813098192215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387155830860138</t>
   </si>
   <si>
     <t xml:space="preserve">0.410936921834946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390009522438049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373521357774734</t>
+    <t xml:space="preserve">0.390009582042694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373521387577057</t>
   </si>
   <si>
     <t xml:space="preserve">0.359886884689331</t>
@@ -80,43 +80,43 @@
     <t xml:space="preserve">0.335471630096436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34561824798584</t>
+    <t xml:space="preserve">0.345618218183517</t>
   </si>
   <si>
     <t xml:space="preserve">0.361472308635712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341496199369431</t>
+    <t xml:space="preserve">0.341496169567108</t>
   </si>
   <si>
     <t xml:space="preserve">0.355130642652512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352593988180161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342447459697723</t>
+    <t xml:space="preserve">0.352594017982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342447429895401</t>
   </si>
   <si>
     <t xml:space="preserve">0.360838145017624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357350200414658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357984364032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350691497325897</t>
+    <t xml:space="preserve">0.35735023021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357984393835068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35069152712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291714429855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297739028930664</t>
+    <t xml:space="preserve">0.291714459657669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297738999128342</t>
   </si>
   <si>
     <t xml:space="preserve">0.275860458612442</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">0.304461121559143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326593399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789095878601</t>
+    <t xml:space="preserve">0.326593369245529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789066076279</t>
   </si>
   <si>
     <t xml:space="preserve">0.32913002371788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348471909761429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327544629573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671158790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330081284046173</t>
+    <t xml:space="preserve">0.348471939563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327544659376144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671128988266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330081254243851</t>
   </si>
   <si>
     <t xml:space="preserve">0.334203332662582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838763952255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356399029493332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368765145540237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325325101613998</t>
+    <t xml:space="preserve">0.3868388235569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35639899969101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368765115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325325071811676</t>
   </si>
   <si>
     <t xml:space="preserve">0.318032205104828</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">0.308329522609711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331032514572144</t>
+    <t xml:space="preserve">0.331032544374466</t>
   </si>
   <si>
     <t xml:space="preserve">0.322788387537003</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">0.319934666156769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309153974056244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331666648387909</t>
+    <t xml:space="preserve">0.309153944253922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331666678190231</t>
   </si>
   <si>
     <t xml:space="preserve">0.320251762866974</t>
@@ -200,25 +200,25 @@
     <t xml:space="preserve">0.308836847543716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306300222873688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880517482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28588017821312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267743170261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260767340660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489492893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258738100528717</t>
+    <t xml:space="preserve">0.306300193071365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880487680435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.285880208015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267743140459061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260767370462418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489463090897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738040924072</t>
   </si>
   <si>
     <t xml:space="preserve">0.288543671369553</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643067121506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367496818304062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369716376066208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399309158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388741225004196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38779005408287</t>
+    <t xml:space="preserve">0.364643126726151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367496848106384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369716435670853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399279356003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388741254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387790024280548</t>
   </si>
   <si>
     <t xml:space="preserve">0.370033442974091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35703319311142</t>
+    <t xml:space="preserve">0.357033163309097</t>
   </si>
   <si>
     <t xml:space="preserve">0.3741554915905</t>
@@ -260,76 +260,76 @@
     <t xml:space="preserve">0.370984673500061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372253030538559</t>
+    <t xml:space="preserve">0.372253060340881</t>
   </si>
   <si>
     <t xml:space="preserve">0.387472897768021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377326309680939</t>
+    <t xml:space="preserve">0.377326369285583</t>
   </si>
   <si>
     <t xml:space="preserve">0.439791291952133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453425735235214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454059928655624</t>
+    <t xml:space="preserve">0.453425765037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45405986905098</t>
   </si>
   <si>
     <t xml:space="preserve">0.461669862270355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.459133237600327</t>
+    <t xml:space="preserve">0.459133207798004</t>
   </si>
   <si>
     <t xml:space="preserve">0.45564529299736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456279516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840620756149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792250156403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485767930746078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477841019630432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483231365680695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484816759824753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497817099094391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489255875349045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475621432065964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476889729499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488304644823074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493694990873337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489890038967133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548861265182</t>
+    <t xml:space="preserve">0.456279546022415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840680360794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47879222035408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485768049955368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477840930223465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483231395483017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484816789627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497817069292068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489255905151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475621402263641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476889699697495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493695020675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4898901283741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548771858215</t>
   </si>
   <si>
     <t xml:space="preserve">0.468645662069321</t>
@@ -338,46 +338,46 @@
     <t xml:space="preserve">0.473084777593613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495280504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486719280481339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48418265581131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497500032186508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507329523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50796365737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514939427375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183215141296</t>
+    <t xml:space="preserve">0.495280414819717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486719310283661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484182626008987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497500002384186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50732958316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507963716983795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514939367771149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183274745941</t>
   </si>
   <si>
     <t xml:space="preserve">0.515890657901764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526354372501373</t>
+    <t xml:space="preserve">0.526354432106018</t>
   </si>
   <si>
     <t xml:space="preserve">0.525720179080963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52952516078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535866737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540305912494659</t>
+    <t xml:space="preserve">0.529525220394135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535866796970367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540305972099304</t>
   </si>
   <si>
     <t xml:space="preserve">0.620844483375549</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">0.577087342739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561867415904999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583428859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569160223007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566940784454346</t>
+    <t xml:space="preserve">0.561867475509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428919315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569160342216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566940724849701</t>
   </si>
   <si>
     <t xml:space="preserve">0.559013724327087</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">0.551720917224884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529208064079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516841888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476201057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516207814216614</t>
+    <t xml:space="preserve">0.529208123683929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516841948032379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516207873821259</t>
   </si>
   <si>
     <t xml:space="preserve">0.465791910886765</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">0.483548402786255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549184143543243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547281682491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558379530906677</t>
+    <t xml:space="preserve">0.549184203147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558379590511322</t>
   </si>
   <si>
     <t xml:space="preserve">0.585965633392334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586599826812744</t>
+    <t xml:space="preserve">0.586599767208099</t>
   </si>
   <si>
     <t xml:space="preserve">0.613868713378906</t>
@@ -458,22 +458,22 @@
     <t xml:space="preserve">0.665869951248169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655089259147644</t>
+    <t xml:space="preserve">0.655089318752289</t>
   </si>
   <si>
     <t xml:space="preserve">0.62306410074234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633844792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62211287021637</t>
+    <t xml:space="preserve">0.63384485244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622112929821014</t>
   </si>
   <si>
     <t xml:space="preserve">0.618942022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615137040615082</t>
+    <t xml:space="preserve">0.615137100219727</t>
   </si>
   <si>
     <t xml:space="preserve">0.631625294685364</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">0.629088580608368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643674314022064</t>
+    <t xml:space="preserve">0.643674254417419</t>
   </si>
   <si>
     <t xml:space="preserve">0.644308507442474</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">0.636064410209656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634796023368835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628454446792603</t>
+    <t xml:space="preserve">0.634796142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628454506397247</t>
   </si>
   <si>
     <t xml:space="preserve">0.632259368896484</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234889030457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602453708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588185131549835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590087652206421</t>
+    <t xml:space="preserve">0.626234829425812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602453768253326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58818519115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590087592601776</t>
   </si>
   <si>
     <t xml:space="preserve">0.589136362075806</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">0.592941343784332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600551307201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595795035362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594526767730713</t>
+    <t xml:space="preserve">0.60055136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595795094966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594526827335358</t>
   </si>
   <si>
     <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601185500621796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603088021278381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609746634960175</t>
+    <t xml:space="preserve">0.60118556022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603087961673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609746694564819</t>
   </si>
   <si>
     <t xml:space="preserve">0.611332058906555</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">0.605941712856293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5986487865448</t>
+    <t xml:space="preserve">0.598648846149445</t>
   </si>
   <si>
     <t xml:space="preserve">0.593258500099182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58850222826004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380578517914</t>
+    <t xml:space="preserve">0.588502287864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380518913269</t>
   </si>
   <si>
     <t xml:space="preserve">0.617673695087433</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">0.611015021800995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604039251804352</t>
+    <t xml:space="preserve">0.604039192199707</t>
   </si>
   <si>
     <t xml:space="preserve">0.605307519435883</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">0.61006373167038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624649465084076</t>
+    <t xml:space="preserve">0.624649524688721</t>
   </si>
   <si>
     <t xml:space="preserve">0.617039501667023</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">0.610380828380585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596429347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591355979442596</t>
+    <t xml:space="preserve">0.596429288387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591356039047241</t>
   </si>
   <si>
     <t xml:space="preserve">0.589770615100861</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">0.56535530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523183584213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481963008642197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493377983570099</t>
+    <t xml:space="preserve">0.523183524608612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481963038444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493378013372421</t>
   </si>
   <si>
     <t xml:space="preserve">0.492109626531601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508280754089355</t>
+    <t xml:space="preserve">0.508280694484711</t>
   </si>
   <si>
     <t xml:space="preserve">0.513988196849823</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">0.548550009727478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544110894203186</t>
+    <t xml:space="preserve">0.544110953807831</t>
   </si>
   <si>
     <t xml:space="preserve">0.521598100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53047639131546</t>
+    <t xml:space="preserve">0.530476450920105</t>
   </si>
   <si>
     <t xml:space="preserve">0.546013414859772</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.54094010591507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532696068286896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538720488548279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539037585258484</t>
+    <t xml:space="preserve">0.532696008682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538720548152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539037644863129</t>
   </si>
   <si>
     <t xml:space="preserve">0.533330142498016</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">0.532061815261841</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568843305110931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570428669452667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566306531429291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549501240253448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560599088668823</t>
+    <t xml:space="preserve">0.568843185901642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570428609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566306591033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549501299858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560599148273468</t>
   </si>
   <si>
     <t xml:space="preserve">0.56440407037735</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.54284256696701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545062184333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521281182765961</t>
+    <t xml:space="preserve">0.545062124729156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521281123161316</t>
   </si>
   <si>
     <t xml:space="preserve">0.516524910926819</t>
@@ -710,37 +710,37 @@
     <t xml:space="preserve">0.50669538974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528256833553314</t>
+    <t xml:space="preserve">0.528256893157959</t>
   </si>
   <si>
     <t xml:space="preserve">0.519695639610291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526037275791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518744468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511451601982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514305293560028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523817718029022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508597850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522549390792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513671159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511134505271912</t>
+    <t xml:space="preserve">0.526037335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51874440908432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511451542377472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514305353164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523817777633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508597791194916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522549450397491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513671219348907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511134445667267</t>
   </si>
   <si>
     <t xml:space="preserve">0.504158735275269</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.510500311851501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499719560146332</t>
+    <t xml:space="preserve">0.499719530344009</t>
   </si>
   <si>
     <t xml:space="preserve">0.512085735797882</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">0.560282051563263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569794535636902</t>
+    <t xml:space="preserve">0.569794416427612</t>
   </si>
   <si>
     <t xml:space="preserve">0.575501978397369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627820253372192</t>
+    <t xml:space="preserve">0.627820312976837</t>
   </si>
   <si>
     <t xml:space="preserve">0.658894240856171</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">0.655723392963409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358205318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262523174286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73689603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707724630832672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696943819522858</t>
+    <t xml:space="preserve">0.682358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736896097660065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707724690437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696943879127502</t>
   </si>
   <si>
     <t xml:space="preserve">0.733091175556183</t>
@@ -809,34 +809,34 @@
     <t xml:space="preserve">0.74894517660141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747676908969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.754652619361877</t>
+    <t xml:space="preserve">0.747676849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.754652738571167</t>
   </si>
   <si>
     <t xml:space="preserve">0.755286872386932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760360240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818068861961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799678146839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771140873432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768604278564453</t>
+    <t xml:space="preserve">0.76036012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81806880235672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799678206443787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771140813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768604159355164</t>
   </si>
   <si>
     <t xml:space="preserve">0.720407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727383613586426</t>
+    <t xml:space="preserve">0.727383673191071</t>
   </si>
   <si>
     <t xml:space="preserve">0.740701138973236</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">0.774945795536041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78382408618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801580727100372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849776923656464</t>
+    <t xml:space="preserve">0.78382396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801580607891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849777042865753</t>
   </si>
   <si>
     <t xml:space="preserve">0.884021759033203</t>
@@ -863,88 +863,88 @@
     <t xml:space="preserve">0.851045310497284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878314197063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894168138504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876498222351</t>
+    <t xml:space="preserve">0.878314256668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894168198108673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876379013062</t>
   </si>
   <si>
     <t xml:space="preserve">0.924608051776886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887826681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901778221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881485044956207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412354946136</t>
+    <t xml:space="preserve">0.88782662153244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901778101921082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881484925746918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412295341492</t>
   </si>
   <si>
     <t xml:space="preserve">0.87514340877533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896070718765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910656571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827300071716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91002231836319</t>
+    <t xml:space="preserve">0.896070659160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9106565117836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827240467072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910022377967834</t>
   </si>
   <si>
     <t xml:space="preserve">0.889729142189026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892899990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436644554138</t>
+    <t xml:space="preserve">0.892899870872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436584949493</t>
   </si>
   <si>
     <t xml:space="preserve">0.863094329833984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860557734966278</t>
+    <t xml:space="preserve">0.860557615756989</t>
   </si>
   <si>
     <t xml:space="preserve">0.867533504962921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87577760219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868167638778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756555140018463</t>
+    <t xml:space="preserve">0.875777542591095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868167519569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.756555199623108</t>
   </si>
   <si>
     <t xml:space="preserve">0.788897395133972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812995553016663</t>
+    <t xml:space="preserve">0.812995433807373</t>
   </si>
   <si>
     <t xml:space="preserve">0.807288110256195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838362097740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790165722370148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786360800266266</t>
+    <t xml:space="preserve">0.838362157344818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790165781974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786360740661621</t>
   </si>
   <si>
     <t xml:space="preserve">0.811727225780487</t>
@@ -956,70 +956,70 @@
     <t xml:space="preserve">0.814898014068604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.792702317237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803483068943024</t>
+    <t xml:space="preserve">0.792702376842499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803483128547668</t>
   </si>
   <si>
     <t xml:space="preserve">0.804117321968079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.776848316192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780019044876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781921684741974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791434049606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785092413425446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970704078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531528949738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77367752790451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775580108165741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769872486591339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767335832118988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771775007247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628389358521</t>
+    <t xml:space="preserve">0.776848375797272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780019164085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781921625137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791433990001678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785092532634735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786994993686676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793970763683319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531409740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7736776471138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775580048561096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769872605800629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767336010932922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771775126457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76162850856781</t>
   </si>
   <si>
     <t xml:space="preserve">0.795873165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811093032360077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843435406684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654654979706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606694698334</t>
+    <t xml:space="preserve">0.811093091964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435347080231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606813907623</t>
   </si>
   <si>
     <t xml:space="preserve">0.862460196018219</t>
@@ -1028,55 +1028,55 @@
     <t xml:space="preserve">0.866899251937866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840264678001404</t>
+    <t xml:space="preserve">0.840264558792114</t>
   </si>
   <si>
     <t xml:space="preserve">0.830752074718475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855484306812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84280127286911</t>
+    <t xml:space="preserve">0.855484426021576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801094055176</t>
   </si>
   <si>
     <t xml:space="preserve">0.849142730236053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820605576038361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824410378932953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826947093009949</t>
+    <t xml:space="preserve">0.820605516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824410438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826947152614594</t>
   </si>
   <si>
     <t xml:space="preserve">0.80601978302002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799044013023376</t>
+    <t xml:space="preserve">0.799043953418732</t>
   </si>
   <si>
     <t xml:space="preserve">0.804751455783844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785726606845856</t>
+    <t xml:space="preserve">0.785726487636566</t>
   </si>
   <si>
     <t xml:space="preserve">0.778750836849213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777482450008392</t>
+    <t xml:space="preserve">0.777482509613037</t>
   </si>
   <si>
     <t xml:space="preserve">0.802214741706848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80665385723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807922303676605</t>
+    <t xml:space="preserve">0.806653916835785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80792224407196</t>
   </si>
   <si>
     <t xml:space="preserve">0.854850292205811</t>
@@ -1088,106 +1088,106 @@
     <t xml:space="preserve">0.852313458919525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863728523254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864996790885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850411117076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84089869260788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834556996822357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996052742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581226825714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826312959194183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805385589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814263880252838</t>
+    <t xml:space="preserve">0.86372846364975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864996910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850410997867584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840898633003235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834557116031647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996112346649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826312899589539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805385649204254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814263939857483</t>
   </si>
   <si>
     <t xml:space="preserve">0.81870299577713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819337129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79650741815567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809190690517426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809824764728546</t>
+    <t xml:space="preserve">0.81933718919754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796507298946381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809190630912781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809824645519257</t>
   </si>
   <si>
     <t xml:space="preserve">0.797775685787201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798409759998322</t>
+    <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
     <t xml:space="preserve">0.817434787750244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823142170906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812361359596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819971323013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797141492366791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716602921485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704553782939911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736262023448944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759725987911224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240914106369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776214122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784458220005035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783189952373505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752116024494171</t>
+    <t xml:space="preserve">0.823142230510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812361419200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819971203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797141551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716602981090546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704553842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736261963844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75972592830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772409081459045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776214182376862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78445827960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783190011978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752115964889526</t>
   </si>
   <si>
     <t xml:space="preserve">0.760994255542755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757823586463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701698303223</t>
+    <t xml:space="preserve">0.757823467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701638698578</t>
   </si>
   <si>
     <t xml:space="preserve">0.790799915790558</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">0.810458898544312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774311602115631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781287491321564</t>
+    <t xml:space="preserve">0.774311661720276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781287431716919</t>
   </si>
   <si>
     <t xml:space="preserve">0.795238971710205</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">0.800312340259552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815532267093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764799118041992</t>
+    <t xml:space="preserve">0.815532207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764799237251282</t>
   </si>
   <si>
     <t xml:space="preserve">0.731822848320007</t>
@@ -1220,34 +1220,34 @@
     <t xml:space="preserve">0.711529612541199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.693773150444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739432752132416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70391970872879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695041418075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683626472949982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660796701908112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684894919395447</t>
+    <t xml:space="preserve">0.693773090839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739432871341705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703919649124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695041477680206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683626532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660796761512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684894859790802</t>
   </si>
   <si>
     <t xml:space="preserve">0.670943260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69123649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678553342819214</t>
+    <t xml:space="preserve">0.691236436367035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678553283214569</t>
   </si>
   <si>
     <t xml:space="preserve">0.687431514263153</t>
@@ -1256,46 +1256,46 @@
     <t xml:space="preserve">0.717871248722076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.730554521083832</t>
+    <t xml:space="preserve">0.730554401874542</t>
   </si>
   <si>
     <t xml:space="preserve">0.710261285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697578191757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714066386222839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729286134243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753384292125702</t>
+    <t xml:space="preserve">0.697578132152557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714066326618195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729286253452301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753384351730347</t>
   </si>
   <si>
     <t xml:space="preserve">0.748310983181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757189333438873</t>
+    <t xml:space="preserve">0.757189273834229</t>
   </si>
   <si>
     <t xml:space="preserve">0.758457660675049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763530910015106</t>
+    <t xml:space="preserve">0.763530969619751</t>
   </si>
   <si>
     <t xml:space="preserve">0.749579429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747042715549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735627770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745774388313293</t>
+    <t xml:space="preserve">0.747042775154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735627830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745774328708649</t>
   </si>
   <si>
     <t xml:space="preserve">0.743237793445587</t>
@@ -1304,55 +1304,55 @@
     <t xml:space="preserve">0.741969347000122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744506061077118</t>
+    <t xml:space="preserve">0.744506120681763</t>
   </si>
   <si>
     <t xml:space="preserve">0.722944617271423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700114727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456363201141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846399784088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725481271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715334713459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712798058986664</t>
+    <t xml:space="preserve">0.700114667415619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456303596497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846518993378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72548121213913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715334594249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712797999382019</t>
   </si>
   <si>
     <t xml:space="preserve">0.69250476360321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705187976360321</t>
+    <t xml:space="preserve">0.705188035964966</t>
   </si>
   <si>
     <t xml:space="preserve">0.681089878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701382994651794</t>
+    <t xml:space="preserve">0.701383054256439</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699781894684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686163187026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679821610450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672211587429047</t>
+    <t xml:space="preserve">0.688699841499329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686163246631622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6798215508461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672211647033691</t>
   </si>
   <si>
     <t xml:space="preserve">0.646845161914825</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">0.65826004743576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659528374671936</t>
+    <t xml:space="preserve">0.659528315067291</t>
   </si>
   <si>
     <t xml:space="preserve">0.651918411254883</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">0.641771852970123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63543027639389</t>
+    <t xml:space="preserve">0.635430216789246</t>
   </si>
   <si>
     <t xml:space="preserve">0.643040239810944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639235258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637966930866241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594209671020508</t>
+    <t xml:space="preserve">0.639235138893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637966871261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594209730625153</t>
   </si>
   <si>
     <t xml:space="preserve">0.596746325492859</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">0.609429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598014652729034</t>
+    <t xml:space="preserve">0.598014712333679</t>
   </si>
   <si>
     <t xml:space="preserve">0.599917113780975</t>
@@ -1409,25 +1409,25 @@
     <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478617191315</t>
+    <t xml:space="preserve">0.621478676795959</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622747004032135</t>
+    <t xml:space="preserve">0.62274694442749</t>
   </si>
   <si>
     <t xml:space="preserve">0.615771174430847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6233811378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612600445747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591038882732391</t>
+    <t xml:space="preserve">0.623381078243256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612600386142731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591038942337036</t>
   </si>
   <si>
     <t xml:space="preserve">0.584063172340393</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">0.580892324447632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565672397613525</t>
+    <t xml:space="preserve">0.56567245721817</t>
   </si>
   <si>
     <t xml:space="preserve">0.570745706558228</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">0.559965014457703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528891086578369</t>
+    <t xml:space="preserve">0.537135183811188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528891026973724</t>
   </si>
   <si>
     <t xml:space="preserve">0.573282361030579</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">0.569477379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608795464038849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307948112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630356907844543</t>
+    <t xml:space="preserve">0.608795404434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307888507843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356967449188</t>
   </si>
   <si>
     <t xml:space="preserve">0.604990482330322</t>
@@ -1478,25 +1478,25 @@
     <t xml:space="preserve">0.580258190631866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572013974189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568208992481232</t>
+    <t xml:space="preserve">0.572014033794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568209111690521</t>
   </si>
   <si>
     <t xml:space="preserve">0.554891645908356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629722833633423</t>
+    <t xml:space="preserve">0.629722774028778</t>
   </si>
   <si>
     <t xml:space="preserve">0.721676290035248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766067564487457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78255569934845</t>
+    <t xml:space="preserve">0.766067504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782555758953094</t>
   </si>
   <si>
     <t xml:space="preserve">0.828215420246124</t>
@@ -1511,22 +1511,22 @@
     <t xml:space="preserve">0.871338427066803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882753372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880216777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903046548366547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922071278095245</t>
+    <t xml:space="preserve">0.882753312587738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880216717720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903046607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92207133769989</t>
   </si>
   <si>
     <t xml:space="preserve">0.937291324138641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918266475200653</t>
+    <t xml:space="preserve">0.918266415596008</t>
   </si>
   <si>
     <t xml:space="preserve">0.866265177726746</t>
@@ -1535,79 +1535,79 @@
     <t xml:space="preserve">0.839630365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896704912185669</t>
+    <t xml:space="preserve">0.896704971790314</t>
   </si>
   <si>
     <t xml:space="preserve">0.87641179561615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868801832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070159435272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559591770172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934754610061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314875602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583143234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929681241512299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144646644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906851470470428</t>
+    <t xml:space="preserve">0.868801772594452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070099830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559651374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934754490852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314815998077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583202838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929681360721588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144765853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906851530075073</t>
   </si>
   <si>
     <t xml:space="preserve">0.930949687957764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891631603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833288729190826</t>
+    <t xml:space="preserve">0.891631722450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833288669586182</t>
   </si>
   <si>
     <t xml:space="preserve">0.821873843669891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802849054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755921065807343</t>
+    <t xml:space="preserve">0.802848994731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755920946598053</t>
   </si>
   <si>
     <t xml:space="preserve">0.640503525733948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636698484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627019226551056</t>
+    <t xml:space="preserve">0.636698544025421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627019166946411</t>
   </si>
   <si>
     <t xml:space="preserve">0.641851961612701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625670790672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534986972809</t>
+    <t xml:space="preserve">0.625670731067657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534927368164</t>
   </si>
   <si>
     <t xml:space="preserve">0.616906046867371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618928611278534</t>
+    <t xml:space="preserve">0.618928670883179</t>
   </si>
   <si>
     <t xml:space="preserve">0.595331132411957</t>
@@ -1625,28 +1625,28 @@
     <t xml:space="preserve">0.602073311805725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598028123378754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594657003879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593982696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631064474582672</t>
+    <t xml:space="preserve">0.598028004169464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838115215302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593982756137848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631064534187317</t>
   </si>
   <si>
     <t xml:space="preserve">0.623648107051849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65398782491684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656684696674347</t>
+    <t xml:space="preserve">0.653987765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656684577465057</t>
   </si>
   <si>
     <t xml:space="preserve">0.637132525444031</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624322354793549</t>
+    <t xml:space="preserve">0.624322295188904</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716098308563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62769341468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614883363246918</t>
+    <t xml:space="preserve">0.627693474292755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614883422851562</t>
   </si>
   <si>
     <t xml:space="preserve">0.608815491199493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61758029460907</t>
+    <t xml:space="preserve">0.617580235004425</t>
   </si>
   <si>
     <t xml:space="preserve">0.635784029960632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624996542930603</t>
+    <t xml:space="preserve">0.624996602535248</t>
   </si>
   <si>
     <t xml:space="preserve">0.614209175109863</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">0.656010389328003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633761405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612186431884766</t>
+    <t xml:space="preserve">0.633761346340179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612186551094055</t>
   </si>
   <si>
     <t xml:space="preserve">0.621625483036041</t>
@@ -1715,31 +1715,31 @@
     <t xml:space="preserve">0.610163867473602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549484610557556</t>
+    <t xml:space="preserve">0.549484550952911</t>
   </si>
   <si>
     <t xml:space="preserve">0.561620473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552855610847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578475832939148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558923602104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563643097877502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569711089134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249413967133</t>
+    <t xml:space="preserve">0.552855730056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565665662288666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578475773334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558923542499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563643157482147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569711029529572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249354362488</t>
   </si>
   <si>
     <t xml:space="preserve">0.562294661998749</t>
@@ -1748,28 +1748,28 @@
     <t xml:space="preserve">0.573082149028778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583869576454163</t>
+    <t xml:space="preserve">0.583869516849518</t>
   </si>
   <si>
     <t xml:space="preserve">0.584543704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567014217376709</t>
+    <t xml:space="preserve">0.567014157772064</t>
   </si>
   <si>
     <t xml:space="preserve">0.566339910030365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593308568000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599376320838928</t>
+    <t xml:space="preserve">0.593308508396149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599376380443573</t>
   </si>
   <si>
     <t xml:space="preserve">0.586566388607025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591285884380341</t>
+    <t xml:space="preserve">0.591285824775696</t>
   </si>
   <si>
     <t xml:space="preserve">0.600050628185272</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">0.60274749994278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607466995716095</t>
+    <t xml:space="preserve">0.60746705532074</t>
   </si>
   <si>
     <t xml:space="preserve">0.590611636638641</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914764881134</t>
+    <t xml:space="preserve">0.587914824485779</t>
   </si>
   <si>
     <t xml:space="preserve">0.618254423141479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639829218387604</t>
+    <t xml:space="preserve">0.639829277992249</t>
   </si>
   <si>
     <t xml:space="preserve">0.641177713871002</t>
@@ -1802,40 +1802,40 @@
     <t xml:space="preserve">0.588589012622833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598702251911163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620277047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62297397851944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609489679336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615557610988617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620951354503632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64859414100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604770123958588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604095935821533</t>
+    <t xml:space="preserve">0.598702192306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620277166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622973918914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609489619731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615557551383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620951294898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648594081401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604770243167877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604095995426178</t>
   </si>
   <si>
     <t xml:space="preserve">0.603421747684479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639155089855194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638480842113495</t>
+    <t xml:space="preserve">0.639155149459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63848090171814</t>
   </si>
   <si>
     <t xml:space="preserve">0.655336201190948</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">0.695789098739624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714667081832886</t>
+    <t xml:space="preserve">0.714667022228241</t>
   </si>
   <si>
     <t xml:space="preserve">0.702531278133392</t>
@@ -1859,82 +1859,82 @@
     <t xml:space="preserve">0.728151440620422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717363953590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.726802825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722757637500763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711970210075378</t>
+    <t xml:space="preserve">0.717363893985748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.726803004741669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722757697105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409261226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711970150470734</t>
   </si>
   <si>
     <t xml:space="preserve">0.701182782649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694440603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6890469789505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683653295040131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679607927799225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.680956363677979</t>
+    <t xml:space="preserve">0.69444066286087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689046919345856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683653235435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67960798740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.680956304073334</t>
   </si>
   <si>
     <t xml:space="preserve">0.672191560268402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68500167131424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675562560558319</t>
+    <t xml:space="preserve">0.685001611709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675562620162964</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146312236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631738662719727</t>
+    <t xml:space="preserve">0.631738722324371</t>
   </si>
   <si>
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919833660126</t>
+    <t xml:space="preserve">0.647919893264771</t>
   </si>
   <si>
     <t xml:space="preserve">0.645897209644318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636458218097687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633087158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611512243747711</t>
+    <t xml:space="preserve">0.636458277702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63308721780777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611512303352356</t>
   </si>
   <si>
     <t xml:space="preserve">0.574430525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589263319969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560271978378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553529858589172</t>
+    <t xml:space="preserve">0.589263200759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560271918773651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553529918193817</t>
   </si>
   <si>
     <t xml:space="preserve">0.538697123527527</t>
@@ -1943,19 +1943,19 @@
     <t xml:space="preserve">0.527235507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478692084550858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463859438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458465695381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391044229269028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419361293315887</t>
+    <t xml:space="preserve">0.478692144155502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46385931968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45846563577652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39104425907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41936120390892</t>
   </si>
   <si>
     <t xml:space="preserve">0.394415289163589</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">0.387673169374466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38834735751152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380256772041321</t>
+    <t xml:space="preserve">0.388347387313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380256831645966</t>
   </si>
   <si>
     <t xml:space="preserve">0.403180092573166</t>
@@ -1976,37 +1976,37 @@
     <t xml:space="preserve">0.412619084119797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431497097015381</t>
+    <t xml:space="preserve">0.431497067213058</t>
   </si>
   <si>
     <t xml:space="preserve">0.465207874774933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469927340745926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479366362094879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489479571580887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474646836519241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473298400640488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411610126495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498918622732162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49689593911171</t>
+    <t xml:space="preserve">0.469927370548248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479366332292557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489479511976242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474646806716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473298370838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533627033234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411639928818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918473720551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496895849704742</t>
   </si>
   <si>
     <t xml:space="preserve">0.495547473430634</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">0.482063144445419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490827977657318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484760046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480714708566666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482737362384796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485434263944626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488131105899811</t>
+    <t xml:space="preserve">0.490827947854996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484760016202927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48071476817131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482737392187119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485434204339981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488131016492844</t>
   </si>
   <si>
     <t xml:space="preserve">0.481388956308365</t>
@@ -2042,31 +2042,31 @@
     <t xml:space="preserve">0.472624182701111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427451819181442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434868156909943</t>
+    <t xml:space="preserve">0.427451848983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434868216514587</t>
   </si>
   <si>
     <t xml:space="preserve">0.438239216804504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443632930517197</t>
+    <t xml:space="preserve">0.443632990121841</t>
   </si>
   <si>
     <t xml:space="preserve">0.43014869093895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409248024225235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434212207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410049825906754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892371416092</t>
+    <t xml:space="preserve">0.409248054027557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434212177991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410049796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892401218414</t>
   </si>
   <si>
     <t xml:space="preserve">0.449136018753052</t>
@@ -2078,25 +2078,25 @@
     <t xml:space="preserve">0.456953227519989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486800938844681</t>
+    <t xml:space="preserve">0.486800909042358</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446293383836746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453399956226349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466191828250885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46690246462822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48040497303009</t>
+    <t xml:space="preserve">0.446293413639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453399986028671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466191858053207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466902494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480404943227768</t>
   </si>
   <si>
     <t xml:space="preserve">0.498882085084915</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">0.445582717657089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442740082740784</t>
+    <t xml:space="preserve">0.442740052938461</t>
   </si>
   <si>
     <t xml:space="preserve">0.452689319849014</t>
@@ -2120,31 +2120,31 @@
     <t xml:space="preserve">0.447004020214081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450557321310043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448425322771072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442029446363449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429948210716248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438476085662842</t>
+    <t xml:space="preserve">0.450557351112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44842529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442029386758804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429948270320892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438476115465164</t>
   </si>
   <si>
     <t xml:space="preserve">0.429237544536591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44771471619606</t>
+    <t xml:space="preserve">0.447714686393738</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463349133729935</t>
+    <t xml:space="preserve">0.463349103927612</t>
   </si>
   <si>
     <t xml:space="preserve">0.458374559879303</t>
@@ -2153,37 +2153,37 @@
     <t xml:space="preserve">0.444161385297775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456242620944977</t>
+    <t xml:space="preserve">0.456242561340332</t>
   </si>
   <si>
     <t xml:space="preserve">0.449846655130386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455531895160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450748920441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430658906698227</t>
+    <t xml:space="preserve">0.455531924962997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450778722763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430658876895905</t>
   </si>
   <si>
     <t xml:space="preserve">0.420709699392319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427816271781921</t>
+    <t xml:space="preserve">0.427816241979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.413603127002716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417156398296356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416445761919022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427105665206909</t>
+    <t xml:space="preserve">0.417156338691711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416445732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427105575799942</t>
   </si>
   <si>
     <t xml:space="preserve">0.437054842710495</t>
@@ -2192,64 +2192,64 @@
     <t xml:space="preserve">0.432080179452896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434922844171524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422841638326645</t>
+    <t xml:space="preserve">0.434922784566879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422841668128967</t>
   </si>
   <si>
     <t xml:space="preserve">0.417867034673691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.406496554613113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407917827367783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397968620061874</t>
+    <t xml:space="preserve">0.406496495008469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40791779756546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397968590259552</t>
   </si>
   <si>
     <t xml:space="preserve">0.403653889894485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401521891355515</t>
+    <t xml:space="preserve">0.401521921157837</t>
   </si>
   <si>
     <t xml:space="preserve">0.405075192451477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400811225175858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387308716773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385176748037338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400100618600845</t>
+    <t xml:space="preserve">0.40081125497818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387308746576309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385176777839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400100558996201</t>
   </si>
   <si>
     <t xml:space="preserve">0.415735006332397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398679286241531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409339100122452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395836651325226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382334113121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370963633060455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383755475282669</t>
+    <t xml:space="preserve">0.398679226636887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409339129924774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395836621522903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382334142923355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370963603258133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383755505084991</t>
   </si>
   <si>
     <t xml:space="preserve">0.366699635982513</t>
@@ -2258,28 +2258,28 @@
     <t xml:space="preserve">0.363146364688873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3539077937603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356750398874283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359593063592911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358882397413254</t>
+    <t xml:space="preserve">0.353907823562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356750428676605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359593033790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358882367610931</t>
   </si>
   <si>
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151381492615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.376648873090744</t>
+    <t xml:space="preserve">0.388730019330978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151351690292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
     <t xml:space="preserve">0.372384935617447</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">0.361725032329559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355329155921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353552490472794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354618459939957</t>
+    <t xml:space="preserve">0.355329126119614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353552460670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354618489742279</t>
   </si>
   <si>
     <t xml:space="preserve">0.351775825023651</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">0.351065158843994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334009379148483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323349475860596</t>
+    <t xml:space="preserve">0.334009349346161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32334953546524</t>
   </si>
   <si>
     <t xml:space="preserve">0.342181950807571</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">0.337207317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337562680244446</t>
+    <t xml:space="preserve">0.337562650442123</t>
   </si>
   <si>
     <t xml:space="preserve">0.343958586454391</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">0.361014395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36030375957489</t>
+    <t xml:space="preserve">0.360303729772568</t>
   </si>
   <si>
     <t xml:space="preserve">0.389440685510635</t>
@@ -2339,127 +2339,127 @@
     <t xml:space="preserve">0.412181794643402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421420335769653</t>
+    <t xml:space="preserve">0.421420365571976</t>
   </si>
   <si>
     <t xml:space="preserve">0.415024399757385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419999063014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313763380051</t>
+    <t xml:space="preserve">0.419999033212662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313733577728</t>
   </si>
   <si>
     <t xml:space="preserve">0.405785828828812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402232527732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418577671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419288337230682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399389952421188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393704652786255</t>
+    <t xml:space="preserve">0.402232557535172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418577700853348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419288367033005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399389863014221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3937047123909</t>
   </si>
   <si>
     <t xml:space="preserve">0.392993986606598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391572684049606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397257953882217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40436452627182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395125925540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386598080396652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380202144384384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806208372116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369542241096497</t>
+    <t xml:space="preserve">0.391572713851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39725798368454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404364556074142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395125985145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386598110198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380202174186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806238174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369542270898819</t>
   </si>
   <si>
     <t xml:space="preserve">0.368831604719162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364567667245865</t>
+    <t xml:space="preserve">0.364567697048187</t>
   </si>
   <si>
     <t xml:space="preserve">0.428526908159256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423552334308624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436344146728516</t>
+    <t xml:space="preserve">0.423552274703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436344176530838</t>
   </si>
   <si>
     <t xml:space="preserve">0.426394909620285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440608143806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897477626801</t>
+    <t xml:space="preserve">0.440608114004135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897418022156</t>
   </si>
   <si>
     <t xml:space="preserve">0.464770466089249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471877038478851</t>
+    <t xml:space="preserve">0.471877068281174</t>
   </si>
   <si>
     <t xml:space="preserve">0.478983670473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492486149072647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515227198600769</t>
+    <t xml:space="preserve">0.492486208677292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515227258205414</t>
   </si>
   <si>
     <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50669926404953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51735919713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120596408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5138059258461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510963261127472</t>
+    <t xml:space="preserve">0.506699323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517359137535095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120656013489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513805866241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510963201522827</t>
   </si>
   <si>
     <t xml:space="preserve">0.507409989833832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513095200061798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522333800792694</t>
+    <t xml:space="preserve">0.513095259666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522333860397339</t>
   </si>
   <si>
     <t xml:space="preserve">0.537257611751556</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">0.523755133152008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525887191295624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526597678661346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525176465511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530151009559631</t>
+    <t xml:space="preserve">0.525887131690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526597738265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525176405906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530151069164276</t>
   </si>
   <si>
     <t xml:space="preserve">0.52446573972702</t>
@@ -2486,46 +2486,46 @@
     <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544364154338837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.541521608829498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536546945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528729677200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518780529499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515937924385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523044466972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542232155799866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531572461128235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542942941188812</t>
+    <t xml:space="preserve">0.544364213943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.541521549224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536547005176544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528729796409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518780469894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515937864780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523044407367706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54223221540451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53157240152359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542942881584167</t>
   </si>
   <si>
     <t xml:space="preserve">0.549338817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5649733543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550941228866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549464225769043</t>
+    <t xml:space="preserve">0.564973294734955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550941288471222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549464285373688</t>
   </si>
   <si>
     <t xml:space="preserve">0.539124846458435</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.537647783756256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531739592552185</t>
+    <t xml:space="preserve">0.53173953294754</t>
   </si>
   <si>
     <t xml:space="preserve">0.526569843292236</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753401279449</t>
+    <t xml:space="preserve">0.514753460884094</t>
   </si>
   <si>
     <t xml:space="preserve">0.518446087837219</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">0.52435427904129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533955156803131</t>
+    <t xml:space="preserve">0.533955097198486</t>
   </si>
   <si>
     <t xml:space="preserve">0.544294476509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556849479675293</t>
+    <t xml:space="preserve">0.556849539279938</t>
   </si>
   <si>
     <t xml:space="preserve">0.546510100364685</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">0.563496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566450417041779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572358548641205</t>
+    <t xml:space="preserve">0.566450357437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57235848903656</t>
   </si>
   <si>
     <t xml:space="preserve">0.581220865249634</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">0.575312674045563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56866592168808</t>
+    <t xml:space="preserve">0.568665862083435</t>
   </si>
   <si>
     <t xml:space="preserve">0.54281747341156</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">0.548725664615631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536170721054077</t>
+    <t xml:space="preserve">0.536170661449432</t>
   </si>
   <si>
     <t xml:space="preserve">0.527308404445648</t>
@@ -2624,40 +2624,40 @@
     <t xml:space="preserve">0.511799335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50958377122879</t>
+    <t xml:space="preserve">0.509583711624146</t>
   </si>
   <si>
     <t xml:space="preserve">0.506629586219788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487427949905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488166451454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735263347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48890495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480781197547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48151969909668</t>
+    <t xml:space="preserve">0.487427920103073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48816642165184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735293149948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488904982805252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480781227350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481519669294357</t>
   </si>
   <si>
     <t xml:space="preserve">0.492597639560699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522138774394989</t>
+    <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534693658351898</t>
+    <t xml:space="preserve">0.534693598747253</t>
   </si>
   <si>
     <t xml:space="preserve">0.532478094100952</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">0.512537837028503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514014899730682</t>
+    <t xml:space="preserve">0.514014840126038</t>
   </si>
   <si>
     <t xml:space="preserve">0.525092840194702</t>
@@ -2708,22 +2708,22 @@
     <t xml:space="preserve">0.498505830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502936959266663</t>
+    <t xml:space="preserve">0.502937018871307</t>
   </si>
   <si>
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721395015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771539211273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540601909160614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553895354270935</t>
+    <t xml:space="preserve">0.500721454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540601849555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55389541387558</t>
   </si>
   <si>
     <t xml:space="preserve">0.55020272731781</t>
@@ -2741,19 +2741,19 @@
     <t xml:space="preserve">0.539863348007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613716125488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641780078411102</t>
+    <t xml:space="preserve">0.613716065883636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641780138015747</t>
   </si>
   <si>
     <t xml:space="preserve">0.62257844209671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627009570598602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612977623939514</t>
+    <t xml:space="preserve">0.627009510993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612977564334869</t>
   </si>
   <si>
     <t xml:space="preserve">0.616670191287994</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">0.620362818241119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61519318819046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601161122322083</t>
+    <t xml:space="preserve">0.615193128585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601161062717438</t>
   </si>
   <si>
     <t xml:space="preserve">0.5945143699646</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">0.589344680309296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600422561168671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607069373130798</t>
+    <t xml:space="preserve">0.600422620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607069313526154</t>
   </si>
   <si>
     <t xml:space="preserve">0.593037247657776</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">0.597468495368958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592298746109009</t>
+    <t xml:space="preserve">0.592298805713654</t>
   </si>
   <si>
     <t xml:space="preserve">0.603376686573029</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">0.664674401283264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66688996553421</t>
+    <t xml:space="preserve">0.666890025138855</t>
   </si>
   <si>
     <t xml:space="preserve">0.658766210079193</t>
@@ -2813,40 +2813,40 @@
     <t xml:space="preserve">0.653596520423889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667628526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.648426830768585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647688329219818</t>
+    <t xml:space="preserve">0.667628467082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64842689037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647688269615173</t>
   </si>
   <si>
     <t xml:space="preserve">0.639564514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629225134849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642518639564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640303075313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633656322956085</t>
+    <t xml:space="preserve">0.629225075244904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642518699169159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640303015708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63365626335144</t>
   </si>
   <si>
     <t xml:space="preserve">0.675752341747284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649165332317352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65581214427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655073583126068</t>
+    <t xml:space="preserve">0.649165391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655812084674835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655073642730713</t>
   </si>
   <si>
     <t xml:space="preserve">0.635871887207031</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">0.618147253990173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625532567501068</t>
+    <t xml:space="preserve">0.625532507896423</t>
   </si>
   <si>
     <t xml:space="preserve">0.638087451457977</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638826012611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626271069049835</t>
+    <t xml:space="preserve">0.638825953006744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62627100944519</t>
   </si>
   <si>
     <t xml:space="preserve">0.630702137947083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649903893470764</t>
+    <t xml:space="preserve">0.649903953075409</t>
   </si>
   <si>
     <t xml:space="preserve">0.657289147377014</t>
@@ -2882,49 +2882,49 @@
     <t xml:space="preserve">0.662458896636963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678706467151642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676490843296051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673536717891693</t>
+    <t xml:space="preserve">0.678706526756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676490902900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.673536777496338</t>
   </si>
   <si>
     <t xml:space="preserve">0.661720335483551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635133385658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576789796352386</t>
+    <t xml:space="preserve">0.635133326053619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576789677143097</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587867617607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507368087768555</t>
+    <t xml:space="preserve">0.587867677211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507368147373199</t>
   </si>
   <si>
     <t xml:space="preserve">0.529524028301239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565711855888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564234793186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582697927951813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570881545543671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559803605079651</t>
+    <t xml:space="preserve">0.565711796283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582697868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570881485939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559803664684296</t>
   </si>
   <si>
     <t xml:space="preserve">0.547248661518097</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">0.536909222602844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542078971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567188918590546</t>
+    <t xml:space="preserve">0.542078912258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567188858985901</t>
   </si>
   <si>
     <t xml:space="preserve">0.5797438621521</t>
@@ -2945,294 +2945,294 @@
     <t xml:space="preserve">0.562019169330597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55758798122406</t>
+    <t xml:space="preserve">0.557588040828705</t>
   </si>
   <si>
     <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555372357368469</t>
+    <t xml:space="preserve">0.555372416973114</t>
   </si>
   <si>
     <t xml:space="preserve">0.569404482841492</t>
   </si>
   <si>
+    <t xml:space="preserve">0.574574053287506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58257657289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576174676418304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570572912693024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568172216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169756412506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562570571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569772660732269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578575372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566571712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571373164653778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564971208572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552967607975006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54656571149826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537762939929962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755738735199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516156375408173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525759398937225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521758079528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536962747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54816609621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52655953168869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522558391094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532961547374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524959146976471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508153975009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504152834415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484146773815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480945736169815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5057532787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493749648332596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487347722053528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488147974014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561770260334015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56097000837326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58897852897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568972408771515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572173416614532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575374364852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577775120735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565771520137787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580976068973541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581776320934296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583376824855804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576974868774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579375565052032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584977269172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586577773094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585777521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591379225254059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564170956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555368363857269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567371964454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563370764255524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544164955615997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54096394777298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543364703655243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542564392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535362303256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536162555217743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520957887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528960287570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528160095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523358643054962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516956686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515356242656708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508954226970673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506553530693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502552330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517756938934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510554730892181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524158835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529760539531708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531361043453217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550566852092743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532161295413971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530560791492462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527359783649445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51215523481369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534561991691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520157635211945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540163695812225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547365963459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552167415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556168556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557769119739532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548966348171234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559369504451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556968808174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558569252490997</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.574574112892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58257657289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576174676418304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570572912693024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56817215681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169756412506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562570512294769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569772660732269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566571712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571373164653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564971268177032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552967607975006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54656571149826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537762939929962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516156435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525759398937225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521758139133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536962747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548166155815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526559591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522558391094208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53296160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524959087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508153975009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484146744012833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480945765972137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5057532787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493749648332596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48734775185585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48814794421196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561770260334015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56097000837326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588978469371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56897246837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572173416614532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575374364852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577775061130524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565771520137787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580976068973541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581776320934296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58337676525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576974868774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579375565052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584977269172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586577773094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585777580738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591379225254059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564170956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555368363857269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567371964454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563370764255524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544164955615997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54096394777298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543364703655243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542564451694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535362303256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536162495613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520957887172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528960287570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528160095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523358643054962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516956686973572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515356183052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508954226970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506553590297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502552330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517756938934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510554730892181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524158835411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529760539531708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531360983848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550566852092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532161295413971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530560731887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527359843254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51215523481369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534561991691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520157635211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540163695812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54736590385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552167415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556168556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557769060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548966348171234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559369564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556968748569489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558569312095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574172496796</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.584177076816559</t>
   </si>
   <si>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">0.600982129573822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612185537815094</t>
+    <t xml:space="preserve">0.612185478210449</t>
   </si>
   <si>
     <t xml:space="preserve">0.616986989974976</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">0.621788442134857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624189138412476</t>
+    <t xml:space="preserve">0.62418919801712</t>
   </si>
   <si>
     <t xml:space="preserve">0.622588634490967</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">0.640194058418274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643394947052002</t>
+    <t xml:space="preserve">0.643395006656647</t>
   </si>
   <si>
     <t xml:space="preserve">0.637793302536011</t>
@@ -69178,7 +69178,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494328704</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>236385</v>
@@ -69199,6 +69199,32 @@
         <v>1344</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494444444</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>198510</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>1.05599999427795</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>1.02799999713898</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>1.02799999713898</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>1.05599999427795</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594696521759</t>
+    <t xml:space="preserve">0.378594666719437</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716715335846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367179751396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380497127771378</t>
+    <t xml:space="preserve">0.382716685533524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367179721593857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3804971575737</t>
   </si>
   <si>
     <t xml:space="preserve">0.361789345741272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352276921272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368131011724472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387155830860138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936951637268</t>
+    <t xml:space="preserve">0.3522769510746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36813098192215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387155801057816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936921834946</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009582042694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521387577057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886884689331</t>
+    <t xml:space="preserve">0.373521357774734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886914491653</t>
   </si>
   <si>
     <t xml:space="preserve">0.335471630096436</t>
@@ -83,37 +83,37 @@
     <t xml:space="preserve">0.34561824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361472249031067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341496199369431</t>
+    <t xml:space="preserve">0.361472308635712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341496229171753</t>
   </si>
   <si>
     <t xml:space="preserve">0.355130672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352593988180161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342447459697723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360838174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35735023021698</t>
+    <t xml:space="preserve">0.352594017982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342447429895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360838145017624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357350260019302</t>
   </si>
   <si>
     <t xml:space="preserve">0.357984393835068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350691497325897</t>
+    <t xml:space="preserve">0.35069152712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291714519262314</t>
+    <t xml:space="preserve">0.291714459657669</t>
   </si>
   <si>
     <t xml:space="preserve">0.297739028930664</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">0.27586042881012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.276240944862366</t>
+    <t xml:space="preserve">0.276240974664688</t>
   </si>
   <si>
     <t xml:space="preserve">0.304461121559143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326593369245529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789095878601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32913002371788</t>
+    <t xml:space="preserve">0.326593399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789036273956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329129993915558</t>
   </si>
   <si>
     <t xml:space="preserve">0.348471939563751</t>
@@ -149,28 +149,28 @@
     <t xml:space="preserve">0.330081254243851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334203362464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838793754578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356398940086365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368765145540237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325325042009354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318032205104828</t>
+    <t xml:space="preserve">0.33420330286026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386838763952255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356398969888687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368765115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325325012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31803223490715</t>
   </si>
   <si>
     <t xml:space="preserve">0.306236773729324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308329522609711</t>
+    <t xml:space="preserve">0.308329552412033</t>
   </si>
   <si>
     <t xml:space="preserve">0.331032514572144</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">0.322788417339325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319934695959091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153914451599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331666707992554</t>
+    <t xml:space="preserve">0.319934666156769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153944253922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331666678190231</t>
   </si>
   <si>
     <t xml:space="preserve">0.320251762866974</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">0.323422580957413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308836847543716</t>
+    <t xml:space="preserve">0.308836817741394</t>
   </si>
   <si>
     <t xml:space="preserve">0.306300222873688</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">0.298880487680435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28588017821312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267743140459061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260767340660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489463090897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258738040924072</t>
+    <t xml:space="preserve">0.285880148410797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267743200063705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260767370462418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738070726395</t>
   </si>
   <si>
     <t xml:space="preserve">0.288543671369553</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643096923828</t>
+    <t xml:space="preserve">0.364643067121506</t>
   </si>
   <si>
     <t xml:space="preserve">0.367496818304062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369716376066208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399309158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388741225004196</t>
+    <t xml:space="preserve">0.36971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399279356003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388741195201874</t>
   </si>
   <si>
     <t xml:space="preserve">0.387790024280548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033532381058</t>
+    <t xml:space="preserve">0.370033472776413</t>
   </si>
   <si>
     <t xml:space="preserve">0.357033163309097</t>
@@ -254,52 +254,52 @@
     <t xml:space="preserve">0.3741554915905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377643436193466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370984643697739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372253060340881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387472897768021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377326309680939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439791232347488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453425765037537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454059898853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46166980266571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133177995682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455645322799683</t>
+    <t xml:space="preserve">0.377643406391144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370984703302383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372253090143204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387472957372665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377326339483261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439791262149811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453425735235214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454059928655624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461669862270355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133207798004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455645382404327</t>
   </si>
   <si>
     <t xml:space="preserve">0.45627948641777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464840620756149</t>
+    <t xml:space="preserve">0.464840680360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.478792250156403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485767930746078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477841049432755</t>
+    <t xml:space="preserve">0.485767990350723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477841019630432</t>
   </si>
   <si>
     <t xml:space="preserve">0.483231365680695</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">0.48925593495369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475621432065964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476889759302139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488304644823074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493695050477982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489890098571777</t>
+    <t xml:space="preserve">0.475621491670609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476889729499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304704427719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493694990873337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489890038967133</t>
   </si>
   <si>
     <t xml:space="preserve">0.496548742055893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.468645721673965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084837198257</t>
+    <t xml:space="preserve">0.468645662069321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084777593613</t>
   </si>
   <si>
     <t xml:space="preserve">0.49528044462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486719280481339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48418253660202</t>
+    <t xml:space="preserve">0.486719220876694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484182596206665</t>
   </si>
   <si>
     <t xml:space="preserve">0.497499972581863</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">0.510183215141296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515890777111053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354432106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525720238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52952516078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535866856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540305912494659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620844483375549</t>
+    <t xml:space="preserve">0.515890717506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354312896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525720179080963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529525220394135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535866796970367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540305852890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620844542980194</t>
   </si>
   <si>
     <t xml:space="preserve">0.625917792320251</t>
@@ -392,19 +392,19 @@
     <t xml:space="preserve">0.597697615623474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596112191677094</t>
+    <t xml:space="preserve">0.596112132072449</t>
   </si>
   <si>
     <t xml:space="preserve">0.577087342739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561867415904999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583429038524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569160342216492</t>
+    <t xml:space="preserve">0.561867475509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428919315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569160223007202</t>
   </si>
   <si>
     <t xml:space="preserve">0.566940724849701</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">0.551720857620239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529208123683929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516842007637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476081848145</t>
+    <t xml:space="preserve">0.529208064079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516841948032379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476141452789</t>
   </si>
   <si>
     <t xml:space="preserve">0.516207754611969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465791910886765</t>
+    <t xml:space="preserve">0.465791970491409</t>
   </si>
   <si>
     <t xml:space="preserve">0.4835484623909</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">0.549184203147888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547281682491302</t>
+    <t xml:space="preserve">0.547281742095947</t>
   </si>
   <si>
     <t xml:space="preserve">0.558379590511322</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">0.585965633392334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586599826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613868653774261</t>
+    <t xml:space="preserve">0.586599767208099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613868713378906</t>
   </si>
   <si>
     <t xml:space="preserve">0.654455065727234</t>
@@ -461,22 +461,22 @@
     <t xml:space="preserve">0.655089259147644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623064041137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63384473323822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622112810611725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618941962718964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615137100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631625294685364</t>
+    <t xml:space="preserve">0.62306410074234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63384485244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62211287021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618942022323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615137040615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631625235080719</t>
   </si>
   <si>
     <t xml:space="preserve">0.628771543502808</t>
@@ -491,31 +491,31 @@
     <t xml:space="preserve">0.643674314022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644308626651764</t>
+    <t xml:space="preserve">0.644308507442474</t>
   </si>
   <si>
     <t xml:space="preserve">0.64557683467865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636064410209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63479608297348</t>
+    <t xml:space="preserve">0.636064469814301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634796142578125</t>
   </si>
   <si>
     <t xml:space="preserve">0.628454446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632259368896484</t>
+    <t xml:space="preserve">0.632259428501129</t>
   </si>
   <si>
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234889030457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602453887462616</t>
+    <t xml:space="preserve">0.626234948635101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602453827857971</t>
   </si>
   <si>
     <t xml:space="preserve">0.588185131549835</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">0.589136362075806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.619893252849579</t>
+    <t xml:space="preserve">0.619893312454224</t>
   </si>
   <si>
     <t xml:space="preserve">0.592941403388977</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">0.594526767730713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591673076152802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60118556022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603087902069092</t>
+    <t xml:space="preserve">0.591673016548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601185500621796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603087961673737</t>
   </si>
   <si>
     <t xml:space="preserve">0.609746634960175</t>
@@ -560,25 +560,25 @@
     <t xml:space="preserve">0.614185810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611966192722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605941712856293</t>
+    <t xml:space="preserve">0.611966252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605941653251648</t>
   </si>
   <si>
     <t xml:space="preserve">0.598648846149445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593258500099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588502287864685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380518913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617673695087433</t>
+    <t xml:space="preserve">0.593258559703827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58850222826004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380459308624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617673635482788</t>
   </si>
   <si>
     <t xml:space="preserve">0.611015021800995</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">0.604039132595062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605307579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610063791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649524688721</t>
+    <t xml:space="preserve">0.605307519435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61006373167038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649465084076</t>
   </si>
   <si>
     <t xml:space="preserve">0.617039501667023</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">0.610380828380585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596429347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591355979442596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589770555496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56535530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523183524608612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481963127851486</t>
+    <t xml:space="preserve">0.596429288387299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591355919837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589770615100861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565355360507965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523183584213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481963008642197</t>
   </si>
   <si>
     <t xml:space="preserve">0.493377923965454</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">0.492109626531601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508280754089355</t>
+    <t xml:space="preserve">0.508280873298645</t>
   </si>
   <si>
     <t xml:space="preserve">0.513988256454468</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">0.509231984615326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509549081325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51779317855835</t>
+    <t xml:space="preserve">0.509549140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517793238162994</t>
   </si>
   <si>
     <t xml:space="preserve">0.548550069332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544110894203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521598100662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53047639131546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546013355255127</t>
+    <t xml:space="preserve">0.544110834598541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521598219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530476450920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546013414859772</t>
   </si>
   <si>
     <t xml:space="preserve">0.54094010591507</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">0.538720548152924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539037585258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533330202102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532061755657196</t>
+    <t xml:space="preserve">0.539037644863129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533330142498016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532061815261841</t>
   </si>
   <si>
     <t xml:space="preserve">0.568843245506287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570428609848022</t>
+    <t xml:space="preserve">0.570428669452667</t>
   </si>
   <si>
     <t xml:space="preserve">0.566306591033936</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">0.549501299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560599088668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564404129981995</t>
+    <t xml:space="preserve">0.560599207878113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56440407037735</t>
   </si>
   <si>
     <t xml:space="preserve">0.550452530384064</t>
@@ -701,19 +701,19 @@
     <t xml:space="preserve">0.545062184333801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521281123161316</t>
+    <t xml:space="preserve">0.521281182765961</t>
   </si>
   <si>
     <t xml:space="preserve">0.516524910926819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506695449352264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528256833553314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519695699214935</t>
+    <t xml:space="preserve">0.506695330142975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528256952762604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519695639610291</t>
   </si>
   <si>
     <t xml:space="preserve">0.526037335395813</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">0.518744468688965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511451601982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514305233955383</t>
+    <t xml:space="preserve">0.511451542377472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514305293560028</t>
   </si>
   <si>
     <t xml:space="preserve">0.523817777633667</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">0.522549390792847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513671159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511134564876556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504158675670624</t>
+    <t xml:space="preserve">0.513671100139618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511134505271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504158735275269</t>
   </si>
   <si>
     <t xml:space="preserve">0.506061196327209</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541574239730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550769567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553623378276825</t>
+    <t xml:space="preserve">0.54157429933548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550769627094269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55362331867218</t>
   </si>
   <si>
     <t xml:space="preserve">0.560281991958618</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.569794535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575501918792725</t>
+    <t xml:space="preserve">0.575501978397369</t>
   </si>
   <si>
     <t xml:space="preserve">0.627820253372192</t>
@@ -785,19 +785,19 @@
     <t xml:space="preserve">0.658894240856171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655723392963409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682358264923096</t>
+    <t xml:space="preserve">0.655723452568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682358205318451</t>
   </si>
   <si>
     <t xml:space="preserve">0.762262642383575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736896097660065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707724690437317</t>
+    <t xml:space="preserve">0.736896157264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707724750041962</t>
   </si>
   <si>
     <t xml:space="preserve">0.696943879127502</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">0.733091175556183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748945295810699</t>
+    <t xml:space="preserve">0.748945236206055</t>
   </si>
   <si>
     <t xml:space="preserve">0.747676849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754652619361877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755286872386932</t>
+    <t xml:space="preserve">0.754652678966522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755286812782288</t>
   </si>
   <si>
     <t xml:space="preserve">0.76036012172699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.818068861961365</t>
+    <t xml:space="preserve">0.81806880235672</t>
   </si>
   <si>
     <t xml:space="preserve">0.799678206443787</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.768604218959808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720407962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727383673191071</t>
+    <t xml:space="preserve">0.720407903194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727383732795715</t>
   </si>
   <si>
     <t xml:space="preserve">0.740701138973236</t>
@@ -845,25 +845,25 @@
     <t xml:space="preserve">0.738164484500885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774945795536041</t>
+    <t xml:space="preserve">0.774945914745331</t>
   </si>
   <si>
     <t xml:space="preserve">0.783824145793915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801580607891083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849776864051819</t>
+    <t xml:space="preserve">0.801580667495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849776983261108</t>
   </si>
   <si>
     <t xml:space="preserve">0.884021699428558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.851045250892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878314197063446</t>
+    <t xml:space="preserve">0.851045310497284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878314256668091</t>
   </si>
   <si>
     <t xml:space="preserve">0.894168138504028</t>
@@ -872,19 +872,19 @@
     <t xml:space="preserve">0.925876498222351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.924607932567596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88782674074173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901778340339661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881485044956207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412354946136</t>
+    <t xml:space="preserve">0.924608170986176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887826800346375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901778221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881484985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412474155426</t>
   </si>
   <si>
     <t xml:space="preserve">0.87514340877533</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">0.896070718765259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9106565117836</t>
+    <t xml:space="preserve">0.910656571388245</t>
   </si>
   <si>
     <t xml:space="preserve">0.913827240467072</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">0.889729142189026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892899990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436584949493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863094329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860557675361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533564567566</t>
+    <t xml:space="preserve">0.892899930477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86309427022934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860557734966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533504962921</t>
   </si>
   <si>
     <t xml:space="preserve">0.875777661800385</t>
@@ -926,31 +926,31 @@
     <t xml:space="preserve">0.868167638778687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756555080413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788897335529327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812995433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807288110256195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838361978530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790165722370148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786360740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811727166175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830117881298065</t>
+    <t xml:space="preserve">0.756555140018463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788897395133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812995553016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807288229465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838362038135529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790165781974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786360800266266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811727285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83011794090271</t>
   </si>
   <si>
     <t xml:space="preserve">0.814898014068604</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">0.792702436447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803483128547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804117321968079</t>
+    <t xml:space="preserve">0.803483068943024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804117202758789</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848316192627</t>
@@ -974,55 +974,55 @@
     <t xml:space="preserve">0.781921744346619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791434109210968</t>
+    <t xml:space="preserve">0.791433990001678</t>
   </si>
   <si>
     <t xml:space="preserve">0.78509247303009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786995112895966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970763683319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531588554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773677587509155</t>
+    <t xml:space="preserve">0.786994934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793970704078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531528949738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77367752790451</t>
   </si>
   <si>
     <t xml:space="preserve">0.775580048561096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769872486591339</t>
+    <t xml:space="preserve">0.769872546195984</t>
   </si>
   <si>
     <t xml:space="preserve">0.767335951328278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77177494764328</t>
+    <t xml:space="preserve">0.77177506685257</t>
   </si>
   <si>
     <t xml:space="preserve">0.761628389358521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79587322473526</t>
+    <t xml:space="preserve">0.795873165130615</t>
   </si>
   <si>
     <t xml:space="preserve">0.811093151569366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843435406684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606813907623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460136413574</t>
+    <t xml:space="preserve">0.843435347080231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654654979706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606873512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460315227509</t>
   </si>
   <si>
     <t xml:space="preserve">0.866899371147156</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">0.840264558792114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830752074718475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855484366416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801153659821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142849445343</t>
+    <t xml:space="preserve">0.830751955509186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855484306812286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142789840698</t>
   </si>
   <si>
     <t xml:space="preserve">0.820605576038361</t>
@@ -1049,61 +1049,61 @@
     <t xml:space="preserve">0.824410438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826947152614594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806019723415375</t>
+    <t xml:space="preserve">0.826947033405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80601978302002</t>
   </si>
   <si>
     <t xml:space="preserve">0.799044013023376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804751515388489</t>
+    <t xml:space="preserve">0.804751455783844</t>
   </si>
   <si>
     <t xml:space="preserve">0.785726606845856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778750836849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777482450008392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802214801311493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80665385723114</t>
+    <t xml:space="preserve">0.778750777244568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777482390403748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802214860916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665397644043</t>
   </si>
   <si>
     <t xml:space="preserve">0.807922303676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.854850292205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857386946678162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852313697338104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863728523254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86499685049057</t>
+    <t xml:space="preserve">0.854850232601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857386887073517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852313578128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863728582859039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.864996790885925</t>
   </si>
   <si>
     <t xml:space="preserve">0.850411176681519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840898752212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996231555939</t>
+    <t xml:space="preserve">0.840898633003235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834557116031647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996171951294</t>
   </si>
   <si>
     <t xml:space="preserve">0.827581226825714</t>
@@ -1112,55 +1112,55 @@
     <t xml:space="preserve">0.826312899589539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805385708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814263880252838</t>
+    <t xml:space="preserve">0.805385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814263939857483</t>
   </si>
   <si>
     <t xml:space="preserve">0.81870299577713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819337248802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796507298946381</t>
+    <t xml:space="preserve">0.819337129592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796507358551025</t>
   </si>
   <si>
     <t xml:space="preserve">0.809190630912781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809824764728546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797775685787201</t>
+    <t xml:space="preserve">0.809824705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797775745391846</t>
   </si>
   <si>
     <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817434668540955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823142111301422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812361419200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819971323013306</t>
+    <t xml:space="preserve">0.817434728145599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823142170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812361359596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81997138261795</t>
   </si>
   <si>
     <t xml:space="preserve">0.797141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.716602921485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704553842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736262023448944</t>
+    <t xml:space="preserve">0.716602861881256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7045539021492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736261963844299</t>
   </si>
   <si>
     <t xml:space="preserve">0.75972592830658</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">0.784458220005035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783189952373505</t>
+    <t xml:space="preserve">0.783190011978149</t>
   </si>
   <si>
     <t xml:space="preserve">0.752116024494171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760994255542755</t>
+    <t xml:space="preserve">0.7609943151474</t>
   </si>
   <si>
     <t xml:space="preserve">0.757823526859283</t>
@@ -1196,49 +1196,49 @@
     <t xml:space="preserve">0.810458958148956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774311661720276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781287431716919</t>
+    <t xml:space="preserve">0.774311602115631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781287550926208</t>
   </si>
   <si>
     <t xml:space="preserve">0.79523903131485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800312340259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815532267093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764799237251282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.731822848320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711529672145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.693773031234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739432752132416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.703919649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695041477680206</t>
+    <t xml:space="preserve">0.800312280654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815532088279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764799296855927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.731822907924652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711529612541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.693773150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739432811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70391970872879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695041418075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.683626472949982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660796701908112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684894919395447</t>
+    <t xml:space="preserve">0.660796761512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684894859790802</t>
   </si>
   <si>
     <t xml:space="preserve">0.670943260192871</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">0.687431573867798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717871189117432</t>
+    <t xml:space="preserve">0.717871248722076</t>
   </si>
   <si>
     <t xml:space="preserve">0.730554521083832</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">0.710261344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697578191757202</t>
+    <t xml:space="preserve">0.697578072547913</t>
   </si>
   <si>
     <t xml:space="preserve">0.714066326618195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729286193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753384292125702</t>
+    <t xml:space="preserve">0.729286134243011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753384351730347</t>
   </si>
   <si>
     <t xml:space="preserve">0.748310983181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757189393043518</t>
+    <t xml:space="preserve">0.757189333438873</t>
   </si>
   <si>
     <t xml:space="preserve">0.758457660675049</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">0.749579429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747042775154114</t>
+    <t xml:space="preserve">0.747042715549469</t>
   </si>
   <si>
     <t xml:space="preserve">0.735627770423889</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">0.743237793445587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.741969287395477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.744506120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722944498062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.700114786624908</t>
+    <t xml:space="preserve">0.741969406604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744506180286407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722944617271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700114727020264</t>
   </si>
   <si>
     <t xml:space="preserve">0.706456363201141</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">0.698846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72548121213913</t>
+    <t xml:space="preserve">0.725481271743774</t>
   </si>
   <si>
     <t xml:space="preserve">0.71533465385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.712797880172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69250476360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705187976360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68108993768692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701382994651794</t>
+    <t xml:space="preserve">0.712797939777374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692504823207855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705188035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.681089878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701383054256439</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699781894684</t>
+    <t xml:space="preserve">0.688699841499329</t>
   </si>
   <si>
     <t xml:space="preserve">0.686163187026978</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">0.6798215508461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672211527824402</t>
+    <t xml:space="preserve">0.672211587429047</t>
   </si>
   <si>
     <t xml:space="preserve">0.646845161914825</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">0.677284836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65826004743576</t>
+    <t xml:space="preserve">0.658259987831116</t>
   </si>
   <si>
     <t xml:space="preserve">0.659528374671936</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">0.651918411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648113369941711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641771793365479</t>
+    <t xml:space="preserve">0.648113429546356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641771852970123</t>
   </si>
   <si>
     <t xml:space="preserve">0.635430216789246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643040120601654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639235258102417</t>
+    <t xml:space="preserve">0.643040239810944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639235198497772</t>
   </si>
   <si>
     <t xml:space="preserve">0.637966930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594209611415863</t>
+    <t xml:space="preserve">0.594209730625153</t>
   </si>
   <si>
     <t xml:space="preserve">0.596746385097504</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">0.598014652729034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599917113780975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603722155094147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573916494846344</t>
+    <t xml:space="preserve">0.59991717338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603722214698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573916554450989</t>
   </si>
   <si>
     <t xml:space="preserve">0.621478676795959</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274694442749</t>
+    <t xml:space="preserve">0.622747004032135</t>
   </si>
   <si>
     <t xml:space="preserve">0.615771234035492</t>
@@ -1433,25 +1433,25 @@
     <t xml:space="preserve">0.584063112735748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580892264842987</t>
+    <t xml:space="preserve">0.580892324447632</t>
   </si>
   <si>
     <t xml:space="preserve">0.565672397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570745706558228</t>
+    <t xml:space="preserve">0.570745646953583</t>
   </si>
   <si>
     <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572648227214813</t>
+    <t xml:space="preserve">0.572648167610168</t>
   </si>
   <si>
     <t xml:space="preserve">0.559964954853058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135124206543</t>
+    <t xml:space="preserve">0.537135183811188</t>
   </si>
   <si>
     <t xml:space="preserve">0.528891086578369</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">0.569477438926697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608795344829559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307828903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630356907844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604990422725677</t>
+    <t xml:space="preserve">0.608795404434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307888507843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356967449188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604990482330322</t>
   </si>
   <si>
     <t xml:space="preserve">0.580258190631866</t>
@@ -1481,109 +1481,109 @@
     <t xml:space="preserve">0.572014033794403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568209052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554891645908356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629722714424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721676349639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766067504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782555818557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215420246124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825678765773773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873875141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871338307857513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880216777324677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903046429157257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922071278095245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937291443347931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918266355991364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86626523733139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896704971790314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876411736011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070040225983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559710979462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934754550457001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314875602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583262443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929681241512299</t>
+    <t xml:space="preserve">0.568209111690521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554891705513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629722833633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721676290035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766067445278168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78255569934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825678944587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873875200748444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871338486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753312587738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880216717720032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903046488761902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922071397304535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937291324138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918266415596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866265058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630305767059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896705031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876411855220795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801653385162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070099830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559770584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934754610061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314815998077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583143234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929681360721588</t>
   </si>
   <si>
     <t xml:space="preserve">0.927144765853882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906851530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930949687957764</t>
+    <t xml:space="preserve">0.906851470470428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930949568748474</t>
   </si>
   <si>
     <t xml:space="preserve">0.891631662845612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833288729190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802848994731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755921125411987</t>
+    <t xml:space="preserve">0.833288848400116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873843669891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802848935127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755921065807343</t>
   </si>
   <si>
     <t xml:space="preserve">0.640503525733948</t>
@@ -1607,46 +1607,46 @@
     <t xml:space="preserve">0.616906046867371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618928551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595331132411957</t>
+    <t xml:space="preserve">0.618928611278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59735381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596005320549011</t>
+    <t xml:space="preserve">0.597353875637054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596005439758301</t>
   </si>
   <si>
     <t xml:space="preserve">0.602073311805725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598028004169464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594657003879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838115215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593982756137848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631064474582672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623648166656494</t>
+    <t xml:space="preserve">0.598028063774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594656884670258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593982696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631064534187317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623648107051849</t>
   </si>
   <si>
     <t xml:space="preserve">0.65398782491684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656684696674347</t>
+    <t xml:space="preserve">0.656684637069702</t>
   </si>
   <si>
     <t xml:space="preserve">0.637132465839386</t>
@@ -1658,31 +1658,31 @@
     <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624322354793549</t>
+    <t xml:space="preserve">0.624322414398193</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716098308563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62769341468811</t>
+    <t xml:space="preserve">0.627693355083466</t>
   </si>
   <si>
     <t xml:space="preserve">0.614883363246918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608815491199493</t>
+    <t xml:space="preserve">0.608815431594849</t>
   </si>
   <si>
     <t xml:space="preserve">0.61758029460907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635783970355988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624996542930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614209234714508</t>
+    <t xml:space="preserve">0.635784029960632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624996602535248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614209175109863</t>
   </si>
   <si>
     <t xml:space="preserve">0.605444371700287</t>
@@ -1691,28 +1691,28 @@
     <t xml:space="preserve">0.606118619441986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630390286445618</t>
+    <t xml:space="preserve">0.630390346050262</t>
   </si>
   <si>
     <t xml:space="preserve">0.643200397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656010448932648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633761405944824</t>
+    <t xml:space="preserve">0.656010389328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633761346340179</t>
   </si>
   <si>
     <t xml:space="preserve">0.61218649148941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621625542640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608141243457794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610163867473602</t>
+    <t xml:space="preserve">0.621625483036041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608141183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610163927078247</t>
   </si>
   <si>
     <t xml:space="preserve">0.549484610557556</t>
@@ -1733,16 +1733,16 @@
     <t xml:space="preserve">0.558923542499542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563643157482147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569711029529572</t>
+    <t xml:space="preserve">0.563643097877502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569711089134216</t>
   </si>
   <si>
     <t xml:space="preserve">0.558249473571777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.562294661998749</t>
+    <t xml:space="preserve">0.562294721603394</t>
   </si>
   <si>
     <t xml:space="preserve">0.573082149028778</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">0.567014157772064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566339910030365</t>
+    <t xml:space="preserve">0.56633996963501</t>
   </si>
   <si>
     <t xml:space="preserve">0.593308508396149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599376380443573</t>
+    <t xml:space="preserve">0.599376440048218</t>
   </si>
   <si>
     <t xml:space="preserve">0.58656632900238</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">0.600050628185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60274749994278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60746705532074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590611696243286</t>
+    <t xml:space="preserve">0.602747559547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607466995716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590611636638641</t>
   </si>
   <si>
     <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914824485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618254363536835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639829337596893</t>
+    <t xml:space="preserve">0.587914764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618254482746124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639829277992249</t>
   </si>
   <si>
     <t xml:space="preserve">0.641177713871002</t>
@@ -1802,64 +1802,64 @@
     <t xml:space="preserve">0.588589012622833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598702192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620277106761932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62297397851944</t>
+    <t xml:space="preserve">0.598702251911163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620277047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622973918914795</t>
   </si>
   <si>
     <t xml:space="preserve">0.609489619731903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615557551383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620951294898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64859414100647</t>
+    <t xml:space="preserve">0.615557491779327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620951354503632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648594081401825</t>
   </si>
   <si>
     <t xml:space="preserve">0.604770183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604095935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603421688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639155149459839</t>
+    <t xml:space="preserve">0.604095995426178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603421747684479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
     <t xml:space="preserve">0.638480842113495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655336201190948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695789039134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714666962623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702531278133392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.699834406375885</t>
+    <t xml:space="preserve">0.655336260795593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695789098739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714667022228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702531218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69983434677124</t>
   </si>
   <si>
     <t xml:space="preserve">0.716015577316284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728151440620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717363893985748</t>
+    <t xml:space="preserve">0.728151381015778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717363953590393</t>
   </si>
   <si>
     <t xml:space="preserve">0.726802825927734</t>
@@ -1868,16 +1868,16 @@
     <t xml:space="preserve">0.722757637500763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721409201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711970269680023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701182723045349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694440603256226</t>
+    <t xml:space="preserve">0.721409261226654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711970210075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701182782649994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69444066286087</t>
   </si>
   <si>
     <t xml:space="preserve">0.689046919345856</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">0.683653235435486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67960798740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.680956363677979</t>
+    <t xml:space="preserve">0.67960786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.680956423282623</t>
   </si>
   <si>
     <t xml:space="preserve">0.672191619873047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.685001730918884</t>
+    <t xml:space="preserve">0.68500167131424</t>
   </si>
   <si>
     <t xml:space="preserve">0.675562620162964</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">0.631738662719727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632412910461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647919833660126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645897269248962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636458218097687</t>
+    <t xml:space="preserve">0.632412970066071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647919893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645897209644318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636458277702332</t>
   </si>
   <si>
     <t xml:space="preserve">0.63308721780777</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">0.611512243747711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574430525302887</t>
+    <t xml:space="preserve">0.574430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">0.589263319969177</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">0.560271978378296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553529858589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538697242736816</t>
+    <t xml:space="preserve">0.553529798984528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538697123527527</t>
   </si>
   <si>
     <t xml:space="preserve">0.527235567569733</t>
@@ -1946,46 +1946,46 @@
     <t xml:space="preserve">0.478692084550858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463859379291534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458465665578842</t>
+    <t xml:space="preserve">0.463859438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458465695381165</t>
   </si>
   <si>
     <t xml:space="preserve">0.391044229269028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419361233711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394415289163589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387673199176788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388347387313843</t>
+    <t xml:space="preserve">0.419361263513565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394415318965912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387673169374466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388347417116165</t>
   </si>
   <si>
     <t xml:space="preserve">0.380256831645966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403180062770844</t>
+    <t xml:space="preserve">0.403180122375488</t>
   </si>
   <si>
     <t xml:space="preserve">0.412619084119797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431497067213058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465207785367966</t>
+    <t xml:space="preserve">0.431497126817703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46520784497261</t>
   </si>
   <si>
     <t xml:space="preserve">0.469927340745926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479366362094879</t>
+    <t xml:space="preserve">0.479366302490234</t>
   </si>
   <si>
     <t xml:space="preserve">0.489479511976242</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">0.474646776914597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473298460245132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533567428589</t>
+    <t xml:space="preserve">0.473298400640488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533627033234</t>
   </si>
   <si>
     <t xml:space="preserve">0.483411550521851</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">0.49891859292984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49689581990242</t>
+    <t xml:space="preserve">0.496895879507065</t>
   </si>
   <si>
     <t xml:space="preserve">0.495547473430634</t>
@@ -2030,88 +2030,88 @@
     <t xml:space="preserve">0.482737362384796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485434263944626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488131046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481388956308365</t>
+    <t xml:space="preserve">0.485434323549271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488131105899811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48138889670372</t>
   </si>
   <si>
     <t xml:space="preserve">0.472624182701111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427451848983765</t>
+    <t xml:space="preserve">0.427451819181442</t>
   </si>
   <si>
     <t xml:space="preserve">0.434868156909943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438239246606827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443632900714874</t>
+    <t xml:space="preserve">0.438239216804504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443632990121841</t>
   </si>
   <si>
     <t xml:space="preserve">0.43014869093895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409248024225235</t>
+    <t xml:space="preserve">0.409248054027557</t>
   </si>
   <si>
     <t xml:space="preserve">0.434212177991867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410049855709076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892401218414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449135959148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4512679874897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456953287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486800938844681</t>
+    <t xml:space="preserve">0.410049796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892371416092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449136078357697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451267957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456953227519989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486800879240036</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446293383836746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453399956226349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46619188785553</t>
+    <t xml:space="preserve">0.446293354034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453399986028671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466191828250885</t>
   </si>
   <si>
     <t xml:space="preserve">0.46690246462822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.480405002832413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49888214468956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488222122192383</t>
+    <t xml:space="preserve">0.48040497303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498882085084915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488222241401672</t>
   </si>
   <si>
     <t xml:space="preserve">0.477562308311462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445582687854767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442740052938461</t>
+    <t xml:space="preserve">0.445582717657089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442740112543106</t>
   </si>
   <si>
     <t xml:space="preserve">0.452689319849014</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">0.447004020214081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450557351112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448425352573395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442029416561127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429948270320892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438476145267487</t>
+    <t xml:space="preserve">0.450557321310043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448425322771072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442029446363449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429948180913925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438476115465164</t>
   </si>
   <si>
     <t xml:space="preserve">0.429237544536591</t>
@@ -2147,61 +2147,61 @@
     <t xml:space="preserve">0.463349193334579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458374559879303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444161385297775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456242591142654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449846684932709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455531865358353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450778722763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430658876895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420709669589996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427816271781921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413603067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417156428098679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.416445732116699</t>
+    <t xml:space="preserve">0.458374530076981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444161355495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456242620944977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449846655130386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455531924962997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450719118118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430658906698227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420709699392319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427816241979599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413603127002716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417156368494034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.416445761919022</t>
   </si>
   <si>
     <t xml:space="preserve">0.427105635404587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437054812908173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.432080209255219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434922814369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422841668128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417867064476013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406496524810791</t>
+    <t xml:space="preserve">0.437054842710495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432080179452896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434922844171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422841638326645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417867004871368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406496584415436</t>
   </si>
   <si>
     <t xml:space="preserve">0.40791779756546</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">0.397968620061874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403653919696808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401521921157837</t>
+    <t xml:space="preserve">0.403653889894485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401521891355515</t>
   </si>
   <si>
     <t xml:space="preserve">0.405075192451477</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">0.400811225175858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387308716773987</t>
+    <t xml:space="preserve">0.387308746576309</t>
   </si>
   <si>
     <t xml:space="preserve">0.385176748037338</t>
@@ -2231,40 +2231,40 @@
     <t xml:space="preserve">0.400100618600845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.41573503613472</t>
+    <t xml:space="preserve">0.415735006332397</t>
   </si>
   <si>
     <t xml:space="preserve">0.398679286241531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409339129924774</t>
+    <t xml:space="preserve">0.409339100122452</t>
   </si>
   <si>
     <t xml:space="preserve">0.395836651325226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382334142923355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370963603258133</t>
+    <t xml:space="preserve">0.382334113121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370963633060455</t>
   </si>
   <si>
     <t xml:space="preserve">0.383755475282669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366699606180191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363146334886551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353907823562622</t>
+    <t xml:space="preserve">0.366699635982513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363146364688873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3539077937603</t>
   </si>
   <si>
     <t xml:space="preserve">0.356750398874283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359593033790588</t>
+    <t xml:space="preserve">0.359593063592911</t>
   </si>
   <si>
     <t xml:space="preserve">0.358882397413254</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730019330978</t>
+    <t xml:space="preserve">0.388730049133301</t>
   </si>
   <si>
     <t xml:space="preserve">0.390151381492615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376648813486099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372384905815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363857001066208</t>
+    <t xml:space="preserve">0.376648843288422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372384935617447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363857060670853</t>
   </si>
   <si>
     <t xml:space="preserve">0.361725032329559</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">0.355329126119614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353552460670471</t>
+    <t xml:space="preserve">0.353552490472794</t>
   </si>
   <si>
     <t xml:space="preserve">0.354618459939957</t>
@@ -2309,64 +2309,64 @@
     <t xml:space="preserve">0.334009379148483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323349505662918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342181921005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337207347154617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337562680244446</t>
+    <t xml:space="preserve">0.323349475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342181950807571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337207317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.337562650442123</t>
   </si>
   <si>
     <t xml:space="preserve">0.343958586454391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361014425754547</t>
+    <t xml:space="preserve">0.361014395952225</t>
   </si>
   <si>
     <t xml:space="preserve">0.36030375957489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38944074511528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396547347307205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41218176484108</t>
+    <t xml:space="preserve">0.389440715312958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396547317504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412181794643402</t>
   </si>
   <si>
     <t xml:space="preserve">0.421420335769653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415024399757385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419999033212662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313733577728</t>
+    <t xml:space="preserve">0.415024369955063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419999063014984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313793182373</t>
   </si>
   <si>
     <t xml:space="preserve">0.405785828828812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402232497930527</t>
+    <t xml:space="preserve">0.402232527732849</t>
   </si>
   <si>
     <t xml:space="preserve">0.418577700853348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419288337230682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399389892816544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393704682588577</t>
+    <t xml:space="preserve">0.419288367033005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399389952421188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393704652786255</t>
   </si>
   <si>
     <t xml:space="preserve">0.392993986606598</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">0.397257953882217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404364556074142</t>
+    <t xml:space="preserve">0.40436452627182</t>
   </si>
   <si>
     <t xml:space="preserve">0.395125955343246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386598110198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380202144384384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806238174438</t>
+    <t xml:space="preserve">0.386598080396652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380202174186707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806208372116</t>
   </si>
   <si>
     <t xml:space="preserve">0.369542241096497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368831634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.364567667245865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428526848554611</t>
+    <t xml:space="preserve">0.368831604719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.364567637443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428526967763901</t>
   </si>
   <si>
     <t xml:space="preserve">0.423552334308624</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">0.436344176530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426394939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440608084201813</t>
+    <t xml:space="preserve">0.42639496922493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44060817360878</t>
   </si>
   <si>
     <t xml:space="preserve">0.439897447824478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464770466089249</t>
+    <t xml:space="preserve">0.464770436286926</t>
   </si>
   <si>
     <t xml:space="preserve">0.471877038478851</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">0.478983670473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492486208677292</t>
+    <t xml:space="preserve">0.492486149072647</t>
   </si>
   <si>
     <t xml:space="preserve">0.515227258205414</t>
@@ -2438,19 +2438,19 @@
     <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506699323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517359137535095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120656013489</t>
+    <t xml:space="preserve">0.50669926404953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517359256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120596408844</t>
   </si>
   <si>
     <t xml:space="preserve">0.5138059258461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510963320732117</t>
+    <t xml:space="preserve">0.510963261127472</t>
   </si>
   <si>
     <t xml:space="preserve">0.507409989833832</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">0.513095259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522333800792694</t>
+    <t xml:space="preserve">0.522333741188049</t>
   </si>
   <si>
     <t xml:space="preserve">0.537257611751556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523755073547363</t>
+    <t xml:space="preserve">0.523755133152008</t>
   </si>
   <si>
     <t xml:space="preserve">0.525887191295624</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">0.526597678661346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525176525115967</t>
+    <t xml:space="preserve">0.525176465511322</t>
   </si>
   <si>
     <t xml:space="preserve">0.530151009559631</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544364094734192</t>
+    <t xml:space="preserve">0.544364154338837</t>
   </si>
   <si>
     <t xml:space="preserve">0.541521608829498</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">0.536546945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528729736804962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518780529499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515937864780426</t>
+    <t xml:space="preserve">0.528729677200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518780469894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515937924385071</t>
   </si>
   <si>
     <t xml:space="preserve">0.523044466972351</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">0.542942881584167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54933887720108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56497323513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550941228866577</t>
+    <t xml:space="preserve">0.549338817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564973294734955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550941288471222</t>
   </si>
   <si>
     <t xml:space="preserve">0.549464225769043</t>
@@ -2531,22 +2531,22 @@
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647724151611</t>
+    <t xml:space="preserve">0.537647783756256</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569902896881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516230463981628</t>
+    <t xml:space="preserve">0.526569843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
     <t xml:space="preserve">0.514753460884094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518446147441864</t>
+    <t xml:space="preserve">0.518446087837219</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">0.533955156803131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544294476509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556849479675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54651015996933</t>
+    <t xml:space="preserve">0.544294536113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556849539279938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546510100364685</t>
   </si>
   <si>
     <t xml:space="preserve">0.553156852722168</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">0.563496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566450357437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57235848903656</t>
+    <t xml:space="preserve">0.566450417041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572358548641205</t>
   </si>
   <si>
     <t xml:space="preserve">0.581220865249634</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">0.583436489105225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575312674045563</t>
+    <t xml:space="preserve">0.575312733650208</t>
   </si>
   <si>
     <t xml:space="preserve">0.56866592168808</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">0.527308404445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522877216339111</t>
+    <t xml:space="preserve">0.522877275943756</t>
   </si>
   <si>
     <t xml:space="preserve">0.53543221950531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531001091003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51696902513504</t>
+    <t xml:space="preserve">0.531001031398773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516968965530396</t>
   </si>
   <si>
     <t xml:space="preserve">0.511060774326324</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">0.511799395084381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509583711624146</t>
+    <t xml:space="preserve">0.50958377122879</t>
   </si>
   <si>
     <t xml:space="preserve">0.506629586219788</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">0.487427949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488166391849518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735263347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488905012607574</t>
+    <t xml:space="preserve">0.488166451454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735322952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48890495300293</t>
   </si>
   <si>
     <t xml:space="preserve">0.480781197547913</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">0.48151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492597579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522138655185699</t>
+    <t xml:space="preserve">0.492597639560699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">0.532478094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519923090934753</t>
+    <t xml:space="preserve">0.519923150539398</t>
   </si>
   <si>
     <t xml:space="preserve">0.517707526683807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512537896633148</t>
+    <t xml:space="preserve">0.512537837028503</t>
   </si>
   <si>
     <t xml:space="preserve">0.514014899730682</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">0.545033037662506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528785467147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533216655254364</t>
+    <t xml:space="preserve">0.528785526752472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533216595649719</t>
   </si>
   <si>
     <t xml:space="preserve">0.520661652088165</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">0.515491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508106708526611</t>
+    <t xml:space="preserve">0.508106648921967</t>
   </si>
   <si>
     <t xml:space="preserve">0.505152583122253</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721335411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771658420563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540601849555969</t>
+    <t xml:space="preserve">0.500721454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540601909160614</t>
   </si>
   <si>
     <t xml:space="preserve">0.553895354270935</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">0.547987163066864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538386285305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530262470245361</t>
+    <t xml:space="preserve">0.538386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530262529850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.539863407611847</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">0.594514429569244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599684000015259</t>
+    <t xml:space="preserve">0.599684059619904</t>
   </si>
   <si>
     <t xml:space="preserve">0.589344680309296</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">0.592298805713654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603376686573029</t>
+    <t xml:space="preserve">0.603376746177673</t>
   </si>
   <si>
     <t xml:space="preserve">0.641041576862335</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">0.666890025138855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658766210079193</t>
+    <t xml:space="preserve">0.658766150474548</t>
   </si>
   <si>
     <t xml:space="preserve">0.653596520423889</t>
@@ -2831,10 +2831,10 @@
     <t xml:space="preserve">0.642518639564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640303015708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63365626335144</t>
+    <t xml:space="preserve">0.640303075313568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633656322956085</t>
   </si>
   <si>
     <t xml:space="preserve">0.675752341747284</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">0.618147253990173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625532507896423</t>
+    <t xml:space="preserve">0.625532567501068</t>
   </si>
   <si>
     <t xml:space="preserve">0.638087451457977</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">0.638826012611389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626271069049835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702197551727</t>
+    <t xml:space="preserve">0.62627100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702137947083</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2879,13 +2879,13 @@
     <t xml:space="preserve">0.657289147377014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662458837032318</t>
+    <t xml:space="preserve">0.662458896636963</t>
   </si>
   <si>
     <t xml:space="preserve">0.678706467151642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.676490902900696</t>
+    <t xml:space="preserve">0.676490843296051</t>
   </si>
   <si>
     <t xml:space="preserve">0.673536777496338</t>
@@ -2906,25 +2906,25 @@
     <t xml:space="preserve">0.587867677211761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507368087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529523968696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711736679077</t>
+    <t xml:space="preserve">0.507368147373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711796283722</t>
   </si>
   <si>
     <t xml:space="preserve">0.564234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582697927951813</t>
+    <t xml:space="preserve">0.582697868347168</t>
   </si>
   <si>
     <t xml:space="preserve">0.570881545543671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559803605079651</t>
+    <t xml:space="preserve">0.559803664684296</t>
   </si>
   <si>
     <t xml:space="preserve">0.547248601913452</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">0.542078971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567188918590546</t>
+    <t xml:space="preserve">0.567188858985901</t>
   </si>
   <si>
     <t xml:space="preserve">0.5797438621521</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">0.562019169330597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55758798122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543556034564972</t>
+    <t xml:space="preserve">0.557588040828705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
     <t xml:space="preserve">0.555372416973114</t>
@@ -2957,289 +2957,289 @@
     <t xml:space="preserve">0.569404482841492</t>
   </si>
   <si>
+    <t xml:space="preserve">0.574574112892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58257657289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576174676418304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570572912693024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56817215681076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169756412506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562570512294769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569772660732269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578575372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566571712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.571373164653778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564971268177032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552967607975006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54656571149826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537762939929962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755738735199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516156435012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525759398937225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521758139133453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536962747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548166155815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526559591293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522558391094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53296160697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524959087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508153975009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484146744012833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480945765972137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5057532787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493749648332596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48734775185585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48814794421196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561770260334015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56097000837326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588978469371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56897246837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572173416614532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575374364852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577775061130524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565771520137787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580976068973541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581776320934296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58337676525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576974868774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579375565052032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584977269172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586577773094177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585777580738068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591379225254059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564170956611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555368363857269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567371964454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.563370764255524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544164955615997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54096394777298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543364703655243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542564451694489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535362303256989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536162495613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520957887172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528960287570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528160095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523358643054962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516956686973572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515356183052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508954226970673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506553590297699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502552330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517756938934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510554730892181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524158835411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529760539531708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531360983848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550566852092743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532161295413971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530560731887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527359843254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51215523481369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.534561991691589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520157635211945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540163695812225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54736590385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552167415618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556168556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557769060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548966348171234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556968748569489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558569312095642</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.574574172496796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582576513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973668575287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576174676418304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570572972297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568172216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169816017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562570512294769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569772720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566571712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571373164653778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564971208572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552967607975006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54656571149826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537762999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755679130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516156435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525759339332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521758139133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536962747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548166155815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526559591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522558391094208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532961547374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524959087371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508153975009918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484146744012833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480945765972137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5057532787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493749648332596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48734775185585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48814794421196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56177031993866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56097000837326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588978469371796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568972527980804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572173416614532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575374364852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577775120735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565771460533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580976068973541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581776320934296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58337676525116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576974928379059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579375565052032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584977269172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586577773094177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585777580738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591379284858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564170956611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555368363857269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567371904850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.563370764255524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544164955615997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54096394777298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543364703655243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542564451694489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535362303256989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536162495613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520957887172699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528960287570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528160095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523358643054962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516956686973572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515356183052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508954226970673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506553530693054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502552330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517756938934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510554790496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524158835411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529760599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531361043453217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550566852092743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532161295413971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530560791492462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527359843254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51215523481369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.534561991691589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520157635211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540163695812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54736590385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552167356014252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556168556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557769060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548966348171234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559369564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556968748569489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558569252490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574112892151</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.584177076816559</t>
   </si>
   <si>
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773860931396</t>
+    <t xml:space="preserve">0.573773920536041</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788501739502</t>
+    <t xml:space="preserve">0.621788442134857</t>
   </si>
   <si>
     <t xml:space="preserve">0.624189138412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622588694095612</t>
+    <t xml:space="preserve">0.622588634490967</t>
   </si>
   <si>
     <t xml:space="preserve">0.620187938213348</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602582693099976</t>
+    <t xml:space="preserve">0.602582633495331</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3311,22 +3311,22 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792042732239</t>
+    <t xml:space="preserve">0.633792102336884</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628990709781647</t>
+    <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.635921716690063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651516497135162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641986310482025</t>
+    <t xml:space="preserve">0.651516437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64198637008667</t>
   </si>
   <si>
     <t xml:space="preserve">0.631589770317078</t>
@@ -3335,34 +3335,31 @@
     <t xml:space="preserve">0.627257883548737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615128636360168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262163639069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663043498993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197629451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615995049476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62119323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628990650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640253603458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723357200623</t>
+    <t xml:space="preserve">0.615128576755524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197569847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464803218842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615994989871979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621193289756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64025354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723416805267</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3371,22 +3368,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732036590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619460463523865</t>
+    <t xml:space="preserve">0.604732096195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61946052312851</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395810127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331216335297</t>
+    <t xml:space="preserve">0.612529516220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395869731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331156730652</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3395,13 +3392,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62032687664032</t>
+    <t xml:space="preserve">0.620326936244965</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801029682159</t>
+    <t xml:space="preserve">0.597801089286804</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3416,7 +3413,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658823013306</t>
+    <t xml:space="preserve">0.624658763408661</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3431,10 +3428,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861402988434</t>
+    <t xml:space="preserve">0.617727696895599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861343383789</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3455,7 +3452,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387190341949</t>
+    <t xml:space="preserve">0.639387130737305</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3482,13 +3479,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382910251617</t>
+    <t xml:space="preserve">0.652382850646973</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848383903503</t>
+    <t xml:space="preserve">0.655848443508148</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3521,10 +3518,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042344093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687037944793701</t>
+    <t xml:space="preserve">0.674042284488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687038004398346</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3539,13 +3536,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682706117630005</t>
+    <t xml:space="preserve">0.68270605802536</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637184143066</t>
+    <t xml:space="preserve">0.689637124538422</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3569,13 +3566,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739887058734894</t>
+    <t xml:space="preserve">0.739886999130249</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412905693054</t>
+    <t xml:space="preserve">0.762412965297699</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3590,118 +3587,121 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
+    <t xml:space="preserve">0.779740452766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76846718788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757193803787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745920479297638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751557111740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753435969352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742162644863129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7346470952034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.732768177986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727131485939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723373711109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73088926076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725252628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729010403156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712100386619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713979244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719615936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717737019062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704584777355194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708342611789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691432535648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702705919742584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69894814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697069227695465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70082700252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706463634967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710221469402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715858161449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721494853496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69519031047821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676401436328888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740283727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73652595281601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749678194522858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760951578617096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787256062030792</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.779740512371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76846718788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76658821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757193803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745920479297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751557111740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753435969352722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742162644863129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7346470952034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.732768177986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727131485939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723373711109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73088926076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725252628326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729010403156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712100386619568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713979244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719615936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717737019062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704584777355194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708342611789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691432535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702705919742584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697069227695465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70082700252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706463634967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710221469402313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715858161449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721494853496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69519031047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676401436328888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740283727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73652595281601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738404870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749678194522858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760951578617096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787256062030792</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -53726,7 +53726,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53752,7 +53752,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1898" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53778,7 +53778,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1899" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53804,7 +53804,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1900" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53830,7 +53830,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1901" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53882,7 +53882,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1903" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53908,7 +53908,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53934,7 +53934,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1905" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53960,7 +53960,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1906" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54012,7 +54012,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1908" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54064,7 +54064,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1910" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54090,7 +54090,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1911" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54116,7 +54116,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1912" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54142,7 +54142,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1913" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54220,7 +54220,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1916" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54272,7 +54272,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1918" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54298,7 +54298,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1919" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54350,7 +54350,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1921" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54402,7 +54402,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1923" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54428,7 +54428,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1924" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54506,7 +54506,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1927" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54532,7 +54532,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1928" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54558,7 +54558,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1929" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54584,7 +54584,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1930" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54688,7 +54688,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1934" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54740,7 +54740,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1936" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54766,7 +54766,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1937" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54792,7 +54792,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1938" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54870,7 +54870,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1941" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54896,7 +54896,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1942" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54922,7 +54922,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1943" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -55000,7 +55000,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G1946" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55052,7 +55052,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1948" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55078,7 +55078,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1949" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55104,7 +55104,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1950" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55130,7 +55130,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1951" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55156,7 +55156,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55182,7 +55182,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1953" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55208,7 +55208,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1954" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55234,7 +55234,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1955" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55286,7 +55286,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1957" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55312,7 +55312,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1958" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55338,7 +55338,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1959" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55364,7 +55364,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1960" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55520,7 +55520,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1966" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55546,7 +55546,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55572,7 +55572,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55598,7 +55598,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1969" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55624,7 +55624,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1970" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55676,7 +55676,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1972" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55702,7 +55702,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1973" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55728,7 +55728,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1974" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55754,7 +55754,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1975" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55780,7 +55780,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1976" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55806,7 +55806,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1977" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55832,7 +55832,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1978" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55858,7 +55858,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55884,7 +55884,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1980" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55910,7 +55910,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1981" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55936,7 +55936,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1982" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55962,7 +55962,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55988,7 +55988,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1984" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56014,7 +56014,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1985" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56066,7 +56066,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1987" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56092,7 +56092,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56118,7 +56118,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1989" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56144,7 +56144,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1990" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56170,7 +56170,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1991" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56196,7 +56196,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1992" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56222,7 +56222,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1993" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56248,7 +56248,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1994" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56300,7 +56300,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1996" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56326,7 +56326,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1997" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56378,7 +56378,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1999" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56430,7 +56430,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2001" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56456,7 +56456,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2002" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56612,7 +56612,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2008" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56638,7 +56638,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2009" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56664,7 +56664,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G2010" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56716,7 +56716,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56742,7 +56742,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2013" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56768,7 +56768,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2014" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56794,7 +56794,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2015" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56820,7 +56820,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G2016" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56846,7 +56846,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2017" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56924,7 +56924,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2020" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56950,7 +56950,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G2021" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56976,7 +56976,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G2022" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57002,7 +57002,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2023" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57028,7 +57028,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2024" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57054,7 +57054,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G2025" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57080,7 +57080,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2026" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57106,7 +57106,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G2027" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57132,7 +57132,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2028" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57158,7 +57158,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2029" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57184,7 +57184,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2030" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57262,7 +57262,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2033" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57288,7 +57288,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2034" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57366,7 +57366,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2037" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57392,7 +57392,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2038" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57418,7 +57418,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2039" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57444,7 +57444,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2040" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57470,7 +57470,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2041" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57496,7 +57496,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2042" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57522,7 +57522,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G2043" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57548,7 +57548,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2044" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57574,7 +57574,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2045" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57600,7 +57600,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2046" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57626,7 +57626,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2047" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57652,7 +57652,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57678,7 +57678,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57704,7 +57704,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2050" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57730,7 +57730,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2051" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57756,7 +57756,7 @@
         <v>0.75</v>
       </c>
       <c r="G2052" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57782,7 +57782,7 @@
         <v>0.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57808,7 +57808,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G2054" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57834,7 +57834,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2055" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57860,7 +57860,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2056" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57886,7 +57886,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2057" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57912,7 +57912,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2058" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57938,7 +57938,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2059" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57964,7 +57964,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G2060" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57990,7 +57990,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58016,7 +58016,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2062" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58042,7 +58042,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2063" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58068,7 +58068,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G2064" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58094,7 +58094,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2065" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58120,7 +58120,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2066" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58172,7 +58172,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2068" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58198,7 +58198,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2069" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58224,7 +58224,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2070" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58250,7 +58250,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2071" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58276,7 +58276,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2072" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58328,7 +58328,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2074" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58354,7 +58354,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2075" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58406,7 +58406,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2077" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58432,7 +58432,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2078" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58458,7 +58458,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2079" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58510,7 +58510,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2081" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58536,7 +58536,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2082" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58588,7 +58588,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2084" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58614,7 +58614,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2085" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58640,7 +58640,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2086" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58666,7 +58666,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2087" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58692,7 +58692,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2088" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58718,7 +58718,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2089" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58744,7 +58744,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2090" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58770,7 +58770,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2091" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58796,7 +58796,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2092" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58822,7 +58822,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G2093" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58848,7 +58848,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G2094" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58874,7 +58874,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G2095" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58900,7 +58900,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2096" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58926,7 +58926,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2097" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58952,7 +58952,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G2098" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58978,7 +58978,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2099" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59004,7 +59004,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2100" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59030,7 +59030,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G2101" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59056,7 +59056,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2102" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59082,7 +59082,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2103" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59108,7 +59108,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2104" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59134,7 +59134,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59160,7 +59160,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2106" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59186,7 +59186,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2107" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59212,7 +59212,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2108" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59238,7 +59238,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2109" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59264,7 +59264,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59290,7 +59290,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2111" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59316,7 +59316,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2112" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59342,7 +59342,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2113" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59368,7 +59368,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2114" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59394,7 +59394,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2115" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59420,7 +59420,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2116" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59446,7 +59446,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2117" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59472,7 +59472,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2118" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59498,7 +59498,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2119" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59524,7 +59524,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2120" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59550,7 +59550,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G2121" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59576,7 +59576,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2122" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59602,7 +59602,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2123" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59628,7 +59628,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2124" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59654,7 +59654,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2125" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59680,7 +59680,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2126" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59706,7 +59706,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2127" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59732,7 +59732,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2128" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59758,7 +59758,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2129" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59784,7 +59784,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2130" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59810,7 +59810,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2131" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59836,7 +59836,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2132" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59862,7 +59862,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2133" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59888,7 +59888,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G2134" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59914,7 +59914,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2135" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59940,7 +59940,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2136" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59966,7 +59966,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2137" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59992,7 +59992,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2138" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60018,7 +60018,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2139" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60044,7 +60044,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2140" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60070,7 +60070,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60096,7 +60096,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2142" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60122,7 +60122,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2143" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60148,7 +60148,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2144" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60174,7 +60174,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2145" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60200,7 +60200,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2146" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60226,7 +60226,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2147" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60252,7 +60252,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2148" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60278,7 +60278,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2149" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60304,7 +60304,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2150" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60330,7 +60330,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2151" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60356,7 +60356,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2152" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60382,7 +60382,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60408,7 +60408,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2154" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60434,7 +60434,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2155" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60460,7 +60460,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2156" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60486,7 +60486,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2157" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60512,7 +60512,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2158" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60538,7 +60538,7 @@
         <v>0.75</v>
       </c>
       <c r="G2159" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60564,7 +60564,7 @@
         <v>0.75</v>
       </c>
       <c r="G2160" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60590,7 +60590,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2161" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60616,7 +60616,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2162" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60642,7 +60642,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2163" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60668,7 +60668,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2164" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60694,7 +60694,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2165" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60720,7 +60720,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2166" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60746,7 +60746,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2167" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60772,7 +60772,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2168" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60798,7 +60798,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2169" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60824,7 +60824,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2170" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60850,7 +60850,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2171" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60876,7 +60876,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2172" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60902,7 +60902,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2173" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60928,7 +60928,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2174" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60954,7 +60954,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2175" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60980,7 +60980,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2176" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61006,7 +61006,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2177" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61032,7 +61032,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2178" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61058,7 +61058,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2179" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61084,7 +61084,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2180" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61110,7 +61110,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2181" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61136,7 +61136,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2182" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61162,7 +61162,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2183" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61188,7 +61188,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61214,7 +61214,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2185" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61240,7 +61240,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2186" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61266,7 +61266,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2187" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61292,7 +61292,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61318,7 +61318,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2189" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61344,7 +61344,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2190" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61370,7 +61370,7 @@
         <v>0.75</v>
       </c>
       <c r="G2191" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61396,7 +61396,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2192" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61422,7 +61422,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2193" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61448,7 +61448,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2194" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61474,7 +61474,7 @@
         <v>0.75</v>
       </c>
       <c r="G2195" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61500,7 +61500,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2196" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61526,7 +61526,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2197" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61552,7 +61552,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2198" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61578,7 +61578,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2199" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61604,7 +61604,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2200" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61630,7 +61630,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2201" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61656,7 +61656,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2202" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61682,7 +61682,7 @@
         <v>0.75</v>
       </c>
       <c r="G2203" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61708,7 +61708,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2204" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61734,7 +61734,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2205" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61760,7 +61760,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2206" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61786,7 +61786,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2207" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61812,7 +61812,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2208" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61838,7 +61838,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2209" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61864,7 +61864,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2210" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61890,7 +61890,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2211" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61916,7 +61916,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2212" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61942,7 +61942,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2213" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61968,7 +61968,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2214" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61994,7 +61994,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2215" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62020,7 +62020,7 @@
         <v>0.75</v>
       </c>
       <c r="G2216" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62046,7 +62046,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2217" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62072,7 +62072,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2218" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62098,7 +62098,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2219" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62124,7 +62124,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2220" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62150,7 +62150,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2221" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62176,7 +62176,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2222" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62202,7 +62202,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2223" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62228,7 +62228,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2224" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62254,7 +62254,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2225" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62280,7 +62280,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2226" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62306,7 +62306,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2227" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62332,7 +62332,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62358,7 +62358,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2229" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62384,7 +62384,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2230" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62410,7 +62410,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2231" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62436,7 +62436,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2232" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62462,7 +62462,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2233" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62488,7 +62488,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2234" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62514,7 +62514,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2235" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62540,7 +62540,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2236" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62566,7 +62566,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2237" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62592,7 +62592,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2238" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62618,7 +62618,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2239" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62644,7 +62644,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2240" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62670,7 +62670,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G2241" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62696,7 +62696,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2242" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62722,7 +62722,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2243" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62748,7 +62748,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2244" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62774,7 +62774,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2245" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62800,7 +62800,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2246" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62826,7 +62826,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2247" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62852,7 +62852,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62878,7 +62878,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2249" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62904,7 +62904,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2250" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62930,7 +62930,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2251" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62956,7 +62956,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2252" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62982,7 +62982,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2253" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63008,7 +63008,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2254" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63034,7 +63034,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2255" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63060,7 +63060,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2256" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63086,7 +63086,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2257" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63112,7 +63112,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2258" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63138,7 +63138,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2259" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63164,7 +63164,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2260" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63190,7 +63190,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2261" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63216,7 +63216,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G2262" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63242,7 +63242,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1192</v>
+        <v>1229</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -69256,7 +69256,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.649537037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>102302</v>
@@ -69265,7 +69265,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="D2495" t="n">
-        <v>1.03999996185303</v>
+        <v>1.03799998760223</v>
       </c>
       <c r="E2495" t="n">
         <v>1.04999995231628</v>
@@ -69277,6 +69277,32 @@
         <v>1344</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6494328704</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>149676</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>1.0460000038147</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1353">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594666719437</t>
+    <t xml:space="preserve">0.378594636917114</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
@@ -47,97 +47,97 @@
     <t xml:space="preserve">0.382716685533524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367179721593857</t>
+    <t xml:space="preserve">0.367179781198502</t>
   </si>
   <si>
     <t xml:space="preserve">0.3804971575737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361789345741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3522769510746</t>
+    <t xml:space="preserve">0.361789405345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352276921272278</t>
   </si>
   <si>
     <t xml:space="preserve">0.36813098192215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387155801057816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936921834946</t>
+    <t xml:space="preserve">0.387155830860138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936892032623</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009582042694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521357774734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886914491653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335471630096436</t>
+    <t xml:space="preserve">0.373521327972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886884689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335471600294113</t>
   </si>
   <si>
     <t xml:space="preserve">0.34561824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361472308635712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341496229171753</t>
+    <t xml:space="preserve">0.361472249031067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341496199369431</t>
   </si>
   <si>
     <t xml:space="preserve">0.355130672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352594017982483</t>
+    <t xml:space="preserve">0.352593988180161</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447429895401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360838145017624</t>
+    <t xml:space="preserve">0.360838115215302</t>
   </si>
   <si>
     <t xml:space="preserve">0.357350260019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357984393835068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35069152712822</t>
+    <t xml:space="preserve">0.357984364032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350691467523575</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291714459657669</t>
+    <t xml:space="preserve">0.291714489459991</t>
   </si>
   <si>
     <t xml:space="preserve">0.297739028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27586042881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276240974664688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304461121559143</t>
+    <t xml:space="preserve">0.275860399007797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276240944862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304461151361465</t>
   </si>
   <si>
     <t xml:space="preserve">0.326593399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348789036273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329129993915558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348471939563751</t>
+    <t xml:space="preserve">0.348789006471634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329130053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348471999168396</t>
   </si>
   <si>
     <t xml:space="preserve">0.327544629573822</t>
@@ -149,49 +149,49 @@
     <t xml:space="preserve">0.330081254243851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33420330286026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838763952255</t>
+    <t xml:space="preserve">0.334203332662582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386838734149933</t>
   </si>
   <si>
     <t xml:space="preserve">0.356398969888687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368765115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325325012207031</t>
+    <t xml:space="preserve">0.368765145540237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325325071811676</t>
   </si>
   <si>
     <t xml:space="preserve">0.31803223490715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306236773729324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308329552412033</t>
+    <t xml:space="preserve">0.306236803531647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308329522609711</t>
   </si>
   <si>
     <t xml:space="preserve">0.331032514572144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322788417339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319934666156769</t>
+    <t xml:space="preserve">0.322788387537003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319934695959091</t>
   </si>
   <si>
     <t xml:space="preserve">0.309153944253922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331666678190231</t>
+    <t xml:space="preserve">0.331666707992554</t>
   </si>
   <si>
     <t xml:space="preserve">0.320251762866974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310802727937698</t>
+    <t xml:space="preserve">0.310802757740021</t>
   </si>
   <si>
     <t xml:space="preserve">0.323422580957413</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">0.306300222873688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298880487680435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285880148410797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267743200063705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260767370462418</t>
+    <t xml:space="preserve">0.298880517482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28588017821312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267743140459061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260767340660095</t>
   </si>
   <si>
     <t xml:space="preserve">0.267489492893219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258738070726395</t>
+    <t xml:space="preserve">0.258738040924072</t>
   </si>
   <si>
     <t xml:space="preserve">0.288543671369553</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643067121506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367496818304062</t>
+    <t xml:space="preserve">0.364643096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367496848106384</t>
   </si>
   <si>
     <t xml:space="preserve">0.36971640586853</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">0.369399279356003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388741195201874</t>
+    <t xml:space="preserve">0.388741254806519</t>
   </si>
   <si>
     <t xml:space="preserve">0.387790024280548</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">0.370033472776413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357033163309097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3741554915905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377643406391144</t>
+    <t xml:space="preserve">0.35703319311142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374155521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377643436193466</t>
   </si>
   <si>
     <t xml:space="preserve">0.370984703302383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372253090143204</t>
+    <t xml:space="preserve">0.372253060340881</t>
   </si>
   <si>
     <t xml:space="preserve">0.387472957372665</t>
@@ -269,25 +269,25 @@
     <t xml:space="preserve">0.377326339483261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439791262149811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453425735235214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454059928655624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461669862270355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133207798004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455645382404327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45627948641777</t>
+    <t xml:space="preserve">0.439791291952133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453425705432892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454059898853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461669832468033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133177995682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45564529299736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456279516220093</t>
   </si>
   <si>
     <t xml:space="preserve">0.464840680360794</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">0.478792250156403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485767990350723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477841019630432</t>
+    <t xml:space="preserve">0.485767930746078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477840960025787</t>
   </si>
   <si>
     <t xml:space="preserve">0.483231365680695</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">0.48925593495369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475621491670609</t>
+    <t xml:space="preserve">0.475621372461319</t>
   </si>
   <si>
     <t xml:space="preserve">0.476889729499817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488304704427719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493694990873337</t>
+    <t xml:space="preserve">0.48830458521843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493695110082626</t>
   </si>
   <si>
     <t xml:space="preserve">0.489890038967133</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">0.484182596206665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497499972581863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507329523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50796365737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514939427375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183215141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515890717506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354312896729</t>
+    <t xml:space="preserve">0.497500032186508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50732958316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507963716983795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514939486980438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183274745941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515890657901764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354372501373</t>
   </si>
   <si>
     <t xml:space="preserve">0.525720179080963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529525220394135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535866796970367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540305852890015</t>
+    <t xml:space="preserve">0.529525101184845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535866856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540305912494659</t>
   </si>
   <si>
     <t xml:space="preserve">0.620844542980194</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">0.627503216266632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597697615623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596112132072449</t>
+    <t xml:space="preserve">0.597697556018829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596112191677094</t>
   </si>
   <si>
     <t xml:space="preserve">0.577087342739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561867475509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583428919315338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569160223007202</t>
+    <t xml:space="preserve">0.561867356300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428978919983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569160282611847</t>
   </si>
   <si>
     <t xml:space="preserve">0.566940724849701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559013724327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551720857620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529208064079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516841948032379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476141452789</t>
+    <t xml:space="preserve">0.559013783931732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551720798015594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529208123683929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516841888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476081848145</t>
   </si>
   <si>
     <t xml:space="preserve">0.516207754611969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465791970491409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4835484623909</t>
+    <t xml:space="preserve">0.465791910886765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483548521995544</t>
   </si>
   <si>
     <t xml:space="preserve">0.549184203147888</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">0.547281742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558379590511322</t>
+    <t xml:space="preserve">0.558379530906677</t>
   </si>
   <si>
     <t xml:space="preserve">0.585965633392334</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">0.654455065727234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665869951248169</t>
+    <t xml:space="preserve">0.665870010852814</t>
   </si>
   <si>
     <t xml:space="preserve">0.655089259147644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62306410074234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63384485244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62211287021637</t>
+    <t xml:space="preserve">0.623063981533051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63384473323822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622112810611725</t>
   </si>
   <si>
     <t xml:space="preserve">0.618942022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615137040615082</t>
+    <t xml:space="preserve">0.615136981010437</t>
   </si>
   <si>
     <t xml:space="preserve">0.631625235080719</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">0.63416188955307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629088640213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643674314022064</t>
+    <t xml:space="preserve">0.629088580608368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643674373626709</t>
   </si>
   <si>
     <t xml:space="preserve">0.644308507442474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64557683467865</t>
+    <t xml:space="preserve">0.645576775074005</t>
   </si>
   <si>
     <t xml:space="preserve">0.636064469814301</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">0.628454446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632259428501129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626551985740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626234948635101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602453827857971</t>
+    <t xml:space="preserve">0.632259368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626551926136017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626234889030457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602453768253326</t>
   </si>
   <si>
     <t xml:space="preserve">0.588185131549835</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">0.592941403388977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600551307201385</t>
+    <t xml:space="preserve">0.60055136680603</t>
   </si>
   <si>
     <t xml:space="preserve">0.595795094966888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594526767730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591673016548157</t>
+    <t xml:space="preserve">0.594526827335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
     <t xml:space="preserve">0.601185500621796</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.609746634960175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611332058906555</t>
+    <t xml:space="preserve">0.61133199930191</t>
   </si>
   <si>
     <t xml:space="preserve">0.614185810089111</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">0.605941653251648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598648846149445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593258559703827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58850222826004</t>
+    <t xml:space="preserve">0.598648905754089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593258500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588502287864685</t>
   </si>
   <si>
     <t xml:space="preserve">0.597380459308624</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">0.611015021800995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604039132595062</t>
+    <t xml:space="preserve">0.604039192199707</t>
   </si>
   <si>
     <t xml:space="preserve">0.605307519435883</t>
@@ -593,25 +593,25 @@
     <t xml:space="preserve">0.61006373167038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624649465084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039501667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610380828380585</t>
+    <t xml:space="preserve">0.624649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039561271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61038076877594</t>
   </si>
   <si>
     <t xml:space="preserve">0.596429288387299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591355919837952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589770615100861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565355360507965</t>
+    <t xml:space="preserve">0.591355979442596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589770555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56535530090332</t>
   </si>
   <si>
     <t xml:space="preserve">0.523183584213257</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">0.492109626531601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508280873298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513988256454468</t>
+    <t xml:space="preserve">0.508280694484711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513988316059113</t>
   </si>
   <si>
     <t xml:space="preserve">0.509231984615326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509549140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517793238162994</t>
+    <t xml:space="preserve">0.509549081325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51779317855835</t>
   </si>
   <si>
     <t xml:space="preserve">0.548550069332123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544110834598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521598219871521</t>
+    <t xml:space="preserve">0.544110894203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521598160266876</t>
   </si>
   <si>
     <t xml:space="preserve">0.530476450920105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546013414859772</t>
+    <t xml:space="preserve">0.546013474464417</t>
   </si>
   <si>
     <t xml:space="preserve">0.54094010591507</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">0.568843245506287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570428669452667</t>
+    <t xml:space="preserve">0.570428609848022</t>
   </si>
   <si>
     <t xml:space="preserve">0.566306591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549501299858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560599207878113</t>
+    <t xml:space="preserve">0.549501240253448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560599148273468</t>
   </si>
   <si>
     <t xml:space="preserve">0.56440407037735</t>
@@ -695,40 +695,40 @@
     <t xml:space="preserve">0.550452530384064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542842626571655</t>
+    <t xml:space="preserve">0.54284256696701</t>
   </si>
   <si>
     <t xml:space="preserve">0.545062184333801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521281182765961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516524910926819</t>
+    <t xml:space="preserve">0.521281063556671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516524970531464</t>
   </si>
   <si>
     <t xml:space="preserve">0.506695330142975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528256952762604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519695639610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526037335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518744468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511451542377472</t>
+    <t xml:space="preserve">0.528256893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519695699214935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526037275791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51874440908432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511451661586761</t>
   </si>
   <si>
     <t xml:space="preserve">0.514305293560028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523817777633667</t>
+    <t xml:space="preserve">0.523817658424377</t>
   </si>
   <si>
     <t xml:space="preserve">0.508597850799561</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">0.505109965801239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510500371456146</t>
+    <t xml:space="preserve">0.510500311851501</t>
   </si>
   <si>
     <t xml:space="preserve">0.499719560146332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512085735797882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54157429933548</t>
+    <t xml:space="preserve">0.512085676193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54157418012619</t>
   </si>
   <si>
     <t xml:space="preserve">0.550769627094269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55362331867218</t>
+    <t xml:space="preserve">0.55362343788147</t>
   </si>
   <si>
     <t xml:space="preserve">0.560281991958618</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">0.569794535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575501978397369</t>
+    <t xml:space="preserve">0.575501918792725</t>
   </si>
   <si>
     <t xml:space="preserve">0.627820253372192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658894240856171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655723452568054</t>
+    <t xml:space="preserve">0.658894300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655723392963409</t>
   </si>
   <si>
     <t xml:space="preserve">0.682358205318451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762262642383575</t>
+    <t xml:space="preserve">0.76226270198822</t>
   </si>
   <si>
     <t xml:space="preserve">0.736896157264709</t>
@@ -800,127 +800,127 @@
     <t xml:space="preserve">0.707724750041962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696943879127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733091175556183</t>
+    <t xml:space="preserve">0.696943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733091115951538</t>
   </si>
   <si>
     <t xml:space="preserve">0.748945236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.747676849365234</t>
+    <t xml:space="preserve">0.747676908969879</t>
   </si>
   <si>
     <t xml:space="preserve">0.754652678966522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755286812782288</t>
+    <t xml:space="preserve">0.755286872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.76036012172699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.81806880235672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799678206443787</t>
+    <t xml:space="preserve">0.818068861961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799678087234497</t>
   </si>
   <si>
     <t xml:space="preserve">0.771140873432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768604218959808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720407903194427</t>
+    <t xml:space="preserve">0.768604278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720407962799072</t>
   </si>
   <si>
     <t xml:space="preserve">0.727383732795715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740701138973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738164484500885</t>
+    <t xml:space="preserve">0.740701079368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73816454410553</t>
   </si>
   <si>
     <t xml:space="preserve">0.774945914745331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783824145793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801580667495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849776983261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884021699428558</t>
+    <t xml:space="preserve">0.783824026584625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801580607891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849777042865753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884021759033203</t>
   </si>
   <si>
     <t xml:space="preserve">0.851045310497284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.878314256668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.894168138504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876498222351</t>
+    <t xml:space="preserve">0.878314197063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.894168198108673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876438617706</t>
   </si>
   <si>
     <t xml:space="preserve">0.924608170986176</t>
   </si>
   <si>
-    <t xml:space="preserve">0.887826800346375</t>
+    <t xml:space="preserve">0.88782662153244</t>
   </si>
   <si>
     <t xml:space="preserve">0.901778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881484985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412474155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87514340877533</t>
+    <t xml:space="preserve">0.881484925746918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875143468379974</t>
   </si>
   <si>
     <t xml:space="preserve">0.896070718765259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.910656571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827240467072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910022258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729142189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892899930477142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436525344849</t>
+    <t xml:space="preserve">0.9106565117836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827180862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.91002231836319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889729082584381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892900049686432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436644554138</t>
   </si>
   <si>
     <t xml:space="preserve">0.86309427022934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860557734966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533504962921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875777661800385</t>
+    <t xml:space="preserve">0.860557615756989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533564567566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87577748298645</t>
   </si>
   <si>
     <t xml:space="preserve">0.868167638778687</t>
@@ -929,40 +929,40 @@
     <t xml:space="preserve">0.756555140018463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788897395133972</t>
+    <t xml:space="preserve">0.788897335529327</t>
   </si>
   <si>
     <t xml:space="preserve">0.812995553016663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807288229465485</t>
+    <t xml:space="preserve">0.807288110256195</t>
   </si>
   <si>
     <t xml:space="preserve">0.838362038135529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790165781974792</t>
+    <t xml:space="preserve">0.790165841579437</t>
   </si>
   <si>
     <t xml:space="preserve">0.786360800266266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811727285385132</t>
+    <t xml:space="preserve">0.811727166175842</t>
   </si>
   <si>
     <t xml:space="preserve">0.83011794090271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814898014068604</t>
+    <t xml:space="preserve">0.814897954463959</t>
   </si>
   <si>
     <t xml:space="preserve">0.792702436447144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803483068943024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804117202758789</t>
+    <t xml:space="preserve">0.803483128547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804117262363434</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848316192627</t>
@@ -971,40 +971,40 @@
     <t xml:space="preserve">0.780019164085388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781921744346619</t>
+    <t xml:space="preserve">0.781921684741974</t>
   </si>
   <si>
     <t xml:space="preserve">0.791433990001678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78509247303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970704078674</t>
+    <t xml:space="preserve">0.785092532634735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786994874477386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79397064447403</t>
   </si>
   <si>
     <t xml:space="preserve">0.789531528949738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77367752790451</t>
+    <t xml:space="preserve">0.773677468299866</t>
   </si>
   <si>
     <t xml:space="preserve">0.775580048561096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769872546195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767335951328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77177506685257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628389358521</t>
+    <t xml:space="preserve">0.769872486591339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767335891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771775007247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761628448963165</t>
   </si>
   <si>
     <t xml:space="preserve">0.795873165130615</t>
@@ -1013,49 +1013,49 @@
     <t xml:space="preserve">0.811093151569366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843435347080231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654654979706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606873512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460315227509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866899371147156</t>
+    <t xml:space="preserve">0.84343546628952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866899311542511</t>
   </si>
   <si>
     <t xml:space="preserve">0.840264558792114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830751955509186</t>
+    <t xml:space="preserve">0.830752074718475</t>
   </si>
   <si>
     <t xml:space="preserve">0.855484306812286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.842801094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142789840698</t>
+    <t xml:space="preserve">0.842801213264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142670631409</t>
   </si>
   <si>
     <t xml:space="preserve">0.820605576038361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824410438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826947033405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80601978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799044013023376</t>
+    <t xml:space="preserve">0.824410498142242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826947152614594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806019842624664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799043953418732</t>
   </si>
   <si>
     <t xml:space="preserve">0.804751455783844</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">0.778750777244568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777482390403748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802214860916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80665397644043</t>
+    <t xml:space="preserve">0.777482509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802214801311493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665385723114</t>
   </si>
   <si>
     <t xml:space="preserve">0.807922303676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.854850232601166</t>
+    <t xml:space="preserve">0.854850351810455</t>
   </si>
   <si>
     <t xml:space="preserve">0.857386887073517</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">0.863728582859039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.864996790885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850411176681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840898633003235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834557116031647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581226825714</t>
+    <t xml:space="preserve">0.864996910095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850410997867584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84089869260788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834556996822357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996112346649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581286430359</t>
   </si>
   <si>
     <t xml:space="preserve">0.826312899589539</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">0.81870299577713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819337129592896</t>
+    <t xml:space="preserve">0.819337248802185</t>
   </si>
   <si>
     <t xml:space="preserve">0.796507358551025</t>
@@ -1139,34 +1139,34 @@
     <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817434728145599</t>
+    <t xml:space="preserve">0.817434787750244</t>
   </si>
   <si>
     <t xml:space="preserve">0.823142170906067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812361359596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81997138261795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797141551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716602861881256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7045539021492</t>
+    <t xml:space="preserve">0.812361419200897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819971323013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797141492366791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716602981090546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704553842544556</t>
   </si>
   <si>
     <t xml:space="preserve">0.736261963844299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240926027298</t>
+    <t xml:space="preserve">0.759725868701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772409319877625</t>
   </si>
   <si>
     <t xml:space="preserve">0.776214122772217</t>
@@ -1184,34 +1184,34 @@
     <t xml:space="preserve">0.7609943151474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757823526859283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701698303223</t>
+    <t xml:space="preserve">0.757823467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701757907867</t>
   </si>
   <si>
     <t xml:space="preserve">0.790799915790558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810458958148956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311602115631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781287550926208</t>
+    <t xml:space="preserve">0.810458898544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311661720276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781287372112274</t>
   </si>
   <si>
     <t xml:space="preserve">0.79523903131485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800312280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815532088279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764799296855927</t>
+    <t xml:space="preserve">0.800312399864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815532207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764799237251282</t>
   </si>
   <si>
     <t xml:space="preserve">0.731822907924652</t>
@@ -1226,31 +1226,31 @@
     <t xml:space="preserve">0.739432811737061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.70391970872879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695041418075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683626472949982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660796761512756</t>
+    <t xml:space="preserve">0.703919768333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695041358470917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683626532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660796701908112</t>
   </si>
   <si>
     <t xml:space="preserve">0.684894859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670943260192871</t>
+    <t xml:space="preserve">0.670943200588226</t>
   </si>
   <si>
     <t xml:space="preserve">0.69123649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678553283214569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687431573867798</t>
+    <t xml:space="preserve">0.678553342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687431454658508</t>
   </si>
   <si>
     <t xml:space="preserve">0.717871248722076</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">0.710261344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697578072547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714066326618195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729286134243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753384351730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748310983181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757189333438873</t>
+    <t xml:space="preserve">0.697578012943268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714066386222839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753384292125702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748311042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757189273834229</t>
   </si>
   <si>
     <t xml:space="preserve">0.758457660675049</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">0.763530910015106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749579429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042715549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735627770423889</t>
+    <t xml:space="preserve">0.74957937002182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735627710819244</t>
   </si>
   <si>
     <t xml:space="preserve">0.745774388313293</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">0.741969406604767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744506180286407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722944617271423</t>
+    <t xml:space="preserve">0.744506120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722944498062134</t>
   </si>
   <si>
     <t xml:space="preserve">0.700114727020264</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">0.698846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725481271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71533465385437</t>
+    <t xml:space="preserve">0.72548121213913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715334594249725</t>
   </si>
   <si>
     <t xml:space="preserve">0.712797939777374</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">0.692504823207855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705188035964966</t>
+    <t xml:space="preserve">0.705187976360321</t>
   </si>
   <si>
     <t xml:space="preserve">0.681089878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701383054256439</t>
+    <t xml:space="preserve">0.70138293504715</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">0.688699841499329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.686163187026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6798215508461</t>
+    <t xml:space="preserve">0.686163246631622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679821610450745</t>
   </si>
   <si>
     <t xml:space="preserve">0.672211587429047</t>
@@ -1361,64 +1361,64 @@
     <t xml:space="preserve">0.677284836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658259987831116</t>
+    <t xml:space="preserve">0.658260107040405</t>
   </si>
   <si>
     <t xml:space="preserve">0.659528374671936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651918411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.648113429546356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641771852970123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635430216789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643040239810944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639235198497772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637966930866241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594209730625153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596746385097504</t>
+    <t xml:space="preserve">0.651918470859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648113489151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641771793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635430157184601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643040120601654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639235138893127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637966871261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594209671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596746325492859</t>
   </si>
   <si>
     <t xml:space="preserve">0.609429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598014652729034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59991717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603722214698792</t>
+    <t xml:space="preserve">0.598014712333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599917113780975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603722155094147</t>
   </si>
   <si>
     <t xml:space="preserve">0.573916554450989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478676795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649381816387177</t>
+    <t xml:space="preserve">0.621478617191315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649381756782532</t>
   </si>
   <si>
     <t xml:space="preserve">0.622747004032135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615771234035492</t>
+    <t xml:space="preserve">0.615771293640137</t>
   </si>
   <si>
     <t xml:space="preserve">0.6233811378479</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">0.591038942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584063112735748</t>
+    <t xml:space="preserve">0.584063172340393</t>
   </si>
   <si>
     <t xml:space="preserve">0.580892324447632</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">0.565672397613525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570745646953583</t>
+    <t xml:space="preserve">0.570745706558228</t>
   </si>
   <si>
     <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572648167610168</t>
+    <t xml:space="preserve">0.572648227214813</t>
   </si>
   <si>
     <t xml:space="preserve">0.559964954853058</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">0.537135183811188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528891086578369</t>
+    <t xml:space="preserve">0.528891026973724</t>
   </si>
   <si>
     <t xml:space="preserve">0.573282361030579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569477438926697</t>
+    <t xml:space="preserve">0.569477379322052</t>
   </si>
   <si>
     <t xml:space="preserve">0.608795404434204</t>
@@ -1469,94 +1469,94 @@
     <t xml:space="preserve">0.618307888507843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630356967449188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604990482330322</t>
+    <t xml:space="preserve">0.630356907844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604990422725677</t>
   </si>
   <si>
     <t xml:space="preserve">0.580258190631866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572014033794403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568209111690521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554891705513</t>
+    <t xml:space="preserve">0.572013974189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568209052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554891645908356</t>
   </si>
   <si>
     <t xml:space="preserve">0.629722833633423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721676290035248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766067445278168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78255569934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825678944587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873875200748444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753312587738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880216717720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903046488761902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922071397304535</t>
+    <t xml:space="preserve">0.721676230430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766067624092102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782555818557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215479850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825678825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873875081539154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871338367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880216777324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903046607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92207145690918</t>
   </si>
   <si>
     <t xml:space="preserve">0.937291324138641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.918266415596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866265058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630305767059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896705031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876411855220795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801653385162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070099830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559770584106</t>
+    <t xml:space="preserve">0.918266355991364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866265118122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630424976349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896704912185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87641167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801891803741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070159435272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559591770172</t>
   </si>
   <si>
     <t xml:space="preserve">0.934754610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904314815998077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583143234253</t>
+    <t xml:space="preserve">0.904314935207367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583202838898</t>
   </si>
   <si>
     <t xml:space="preserve">0.929681360721588</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">0.927144765853882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906851470470428</t>
+    <t xml:space="preserve">0.906851410865784</t>
   </si>
   <si>
     <t xml:space="preserve">0.930949568748474</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">0.833288848400116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.821873843669891</t>
+    <t xml:space="preserve">0.821873784065247</t>
   </si>
   <si>
     <t xml:space="preserve">0.802848935127258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755921065807343</t>
+    <t xml:space="preserve">0.755921006202698</t>
   </si>
   <si>
     <t xml:space="preserve">0.640503525733948</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">0.641851961612701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625670790672302</t>
+    <t xml:space="preserve">0.625670850276947</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534986972809</t>
@@ -1610,28 +1610,28 @@
     <t xml:space="preserve">0.618928611278534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595331192016602</t>
+    <t xml:space="preserve">0.595331132411957</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597353875637054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596005439758301</t>
+    <t xml:space="preserve">0.597353756427765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596005380153656</t>
   </si>
   <si>
     <t xml:space="preserve">0.602073311805725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598028063774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594656884670258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838174819946</t>
+    <t xml:space="preserve">0.598028004169464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838115215302</t>
   </si>
   <si>
     <t xml:space="preserve">0.593982696533203</t>
@@ -1643,34 +1643,34 @@
     <t xml:space="preserve">0.623648107051849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65398782491684</t>
+    <t xml:space="preserve">0.653987765312195</t>
   </si>
   <si>
     <t xml:space="preserve">0.656684637069702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637132465839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626345038414001</t>
+    <t xml:space="preserve">0.637132406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626344978809357</t>
   </si>
   <si>
     <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624322414398193</t>
+    <t xml:space="preserve">0.624322354793549</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716098308563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627693355083466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614883363246918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608815431594849</t>
+    <t xml:space="preserve">0.62769341468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614883422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608815491199493</t>
   </si>
   <si>
     <t xml:space="preserve">0.61758029460907</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">0.624996602535248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614209175109863</t>
+    <t xml:space="preserve">0.614209234714508</t>
   </si>
   <si>
     <t xml:space="preserve">0.605444371700287</t>
@@ -1691,49 +1691,49 @@
     <t xml:space="preserve">0.606118619441986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630390346050262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643200397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656010389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633761346340179</t>
+    <t xml:space="preserve">0.630390286445618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64320033788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656010448932648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633761405944824</t>
   </si>
   <si>
     <t xml:space="preserve">0.61218649148941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621625483036041</t>
+    <t xml:space="preserve">0.621625542640686</t>
   </si>
   <si>
     <t xml:space="preserve">0.608141183853149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610163927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549484610557556</t>
+    <t xml:space="preserve">0.610163867473602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549484550952911</t>
   </si>
   <si>
     <t xml:space="preserve">0.561620473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552855610847473</t>
+    <t xml:space="preserve">0.552855670452118</t>
   </si>
   <si>
     <t xml:space="preserve">0.565665721893311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578475713729858</t>
+    <t xml:space="preserve">0.578475773334503</t>
   </si>
   <si>
     <t xml:space="preserve">0.558923542499542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563643097877502</t>
+    <t xml:space="preserve">0.563643157482147</t>
   </si>
   <si>
     <t xml:space="preserve">0.569711089134216</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">0.558249473571777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.562294721603394</t>
+    <t xml:space="preserve">0.562294661998749</t>
   </si>
   <si>
     <t xml:space="preserve">0.573082149028778</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">0.600050628185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602747559547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607466995716095</t>
+    <t xml:space="preserve">0.60274749994278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60746705532074</t>
   </si>
   <si>
     <t xml:space="preserve">0.590611636638641</t>
@@ -1799,22 +1799,22 @@
     <t xml:space="preserve">0.641177713871002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588589012622833</t>
+    <t xml:space="preserve">0.588589072227478</t>
   </si>
   <si>
     <t xml:space="preserve">0.598702251911163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620277047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622973918914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609489619731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615557491779327</t>
+    <t xml:space="preserve">0.620277106761932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62297397851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609489679336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615557551383972</t>
   </si>
   <si>
     <t xml:space="preserve">0.620951354503632</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">0.604770183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604095995426178</t>
+    <t xml:space="preserve">0.604095935821533</t>
   </si>
   <si>
     <t xml:space="preserve">0.603421747684479</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638480842113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655336260795593</t>
+    <t xml:space="preserve">0.63848090171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
     <t xml:space="preserve">0.695789098739624</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">0.702531218528748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69983434677124</t>
+    <t xml:space="preserve">0.699834406375885</t>
   </si>
   <si>
     <t xml:space="preserve">0.716015577316284</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">0.717363953590393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726802825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722757637500763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409261226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711970210075378</t>
+    <t xml:space="preserve">0.726802945137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722757697105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711970269680023</t>
   </si>
   <si>
     <t xml:space="preserve">0.701182782649994</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">0.69444066286087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689046919345856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683653235435486</t>
+    <t xml:space="preserve">0.6890469789505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683653175830841</t>
   </si>
   <si>
     <t xml:space="preserve">0.67960786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680956423282623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672191619873047</t>
+    <t xml:space="preserve">0.680956363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672191560268402</t>
   </si>
   <si>
     <t xml:space="preserve">0.68500167131424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675562620162964</t>
+    <t xml:space="preserve">0.675562560558319</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146312236786</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919893264771</t>
+    <t xml:space="preserve">0.647919833660126</t>
   </si>
   <si>
     <t xml:space="preserve">0.645897209644318</t>
@@ -1922,52 +1922,52 @@
     <t xml:space="preserve">0.63308721780777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611512243747711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589263319969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560271978378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.553529798984528</t>
+    <t xml:space="preserve">0.611512303352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574430525302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589263260364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560271918773651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553529858589172</t>
   </si>
   <si>
     <t xml:space="preserve">0.538697123527527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527235567569733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478692084550858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463859438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458465695381165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391044229269028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419361263513565</t>
+    <t xml:space="preserve">0.527235507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478692054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463859379291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45846563577652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391044199466705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41936120390892</t>
   </si>
   <si>
     <t xml:space="preserve">0.394415318965912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387673169374466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388347417116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380256831645966</t>
+    <t xml:space="preserve">0.387673199176788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388347387313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380256801843643</t>
   </si>
   <si>
     <t xml:space="preserve">0.403180122375488</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">0.412619084119797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431497126817703</t>
+    <t xml:space="preserve">0.431497067213058</t>
   </si>
   <si>
     <t xml:space="preserve">0.46520784497261</t>
@@ -1991,19 +1991,19 @@
     <t xml:space="preserve">0.489479511976242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474646776914597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473298400640488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533627033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411550521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49891859292984</t>
+    <t xml:space="preserve">0.474646836519241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473298460245132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533567428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411610126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918533325195</t>
   </si>
   <si>
     <t xml:space="preserve">0.496895879507065</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482063144445419</t>
+    <t xml:space="preserve">0.482063084840775</t>
   </si>
   <si>
     <t xml:space="preserve">0.490827918052673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484760046005249</t>
+    <t xml:space="preserve">0.484760016202927</t>
   </si>
   <si>
     <t xml:space="preserve">0.480714738368988</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">0.482737362384796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485434323549271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488131105899811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48138889670372</t>
+    <t xml:space="preserve">0.485434263944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488131046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481388956308365</t>
   </si>
   <si>
     <t xml:space="preserve">0.472624182701111</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">0.434868156909943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438239216804504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443632990121841</t>
+    <t xml:space="preserve">0.438239246606827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443632930517197</t>
   </si>
   <si>
     <t xml:space="preserve">0.43014869093895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409248054027557</t>
+    <t xml:space="preserve">0.409248024225235</t>
   </si>
   <si>
     <t xml:space="preserve">0.434212177991867</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">0.410049796104431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412892371416092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449136078357697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451267957687378</t>
+    <t xml:space="preserve">0.412892431020737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449135959148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451268017292023</t>
   </si>
   <si>
     <t xml:space="preserve">0.456953227519989</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">0.469034463167191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446293354034424</t>
+    <t xml:space="preserve">0.446293413639069</t>
   </si>
   <si>
     <t xml:space="preserve">0.453399986028671</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">0.498882085084915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488222241401672</t>
+    <t xml:space="preserve">0.488222181797028</t>
   </si>
   <si>
     <t xml:space="preserve">0.477562308311462</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">0.445582717657089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442740112543106</t>
+    <t xml:space="preserve">0.442740052938461</t>
   </si>
   <si>
     <t xml:space="preserve">0.452689319849014</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">0.447004020214081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450557321310043</t>
+    <t xml:space="preserve">0.450557380914688</t>
   </si>
   <si>
     <t xml:space="preserve">0.448425322771072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442029446363449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429948180913925</t>
+    <t xml:space="preserve">0.442029386758804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429948300123215</t>
   </si>
   <si>
     <t xml:space="preserve">0.438476115465164</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">0.429237544536591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44771471619606</t>
+    <t xml:space="preserve">0.447714656591415</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">0.463349193334579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458374530076981</t>
+    <t xml:space="preserve">0.458374559879303</t>
   </si>
   <si>
     <t xml:space="preserve">0.444161355495453</t>
@@ -2159,31 +2159,31 @@
     <t xml:space="preserve">0.449846655130386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455531924962997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450719118118</t>
+    <t xml:space="preserve">0.455531865358353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450778722763</t>
   </si>
   <si>
     <t xml:space="preserve">0.430658906698227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420709699392319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427816241979599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413603127002716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417156368494034</t>
+    <t xml:space="preserve">0.420709639787674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427816182374954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413603097200394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417156398296356</t>
   </si>
   <si>
     <t xml:space="preserve">0.416445761919022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427105635404587</t>
+    <t xml:space="preserve">0.427105575799942</t>
   </si>
   <si>
     <t xml:space="preserve">0.437054842710495</t>
@@ -2195,64 +2195,64 @@
     <t xml:space="preserve">0.434922844171524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422841638326645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417867004871368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406496584415436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40791779756546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397968620061874</t>
+    <t xml:space="preserve">0.422841668128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417867034673691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406496554613113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.407917827367783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397968590259552</t>
   </si>
   <si>
     <t xml:space="preserve">0.403653889894485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401521891355515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405075192451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400811225175858</t>
+    <t xml:space="preserve">0.401521921157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405075162649155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40081125497818</t>
   </si>
   <si>
     <t xml:space="preserve">0.387308746576309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385176748037338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400100618600845</t>
+    <t xml:space="preserve">0.385176777839661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400100558996201</t>
   </si>
   <si>
     <t xml:space="preserve">0.415735006332397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398679286241531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409339100122452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395836651325226</t>
+    <t xml:space="preserve">0.398679256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409339129924774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395836621522903</t>
   </si>
   <si>
     <t xml:space="preserve">0.382334113121033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370963633060455</t>
+    <t xml:space="preserve">0.370963603258133</t>
   </si>
   <si>
     <t xml:space="preserve">0.383755475282669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366699635982513</t>
+    <t xml:space="preserve">0.366699606180191</t>
   </si>
   <si>
     <t xml:space="preserve">0.363146364688873</t>
@@ -2267,13 +2267,13 @@
     <t xml:space="preserve">0.359593063592911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358882397413254</t>
+    <t xml:space="preserve">0.358882367610931</t>
   </si>
   <si>
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730049133301</t>
+    <t xml:space="preserve">0.388730019330978</t>
   </si>
   <si>
     <t xml:space="preserve">0.390151381492615</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372384935617447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363857060670853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361725032329559</t>
+    <t xml:space="preserve">0.372384876012802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36385703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361725002527237</t>
   </si>
   <si>
     <t xml:space="preserve">0.355329126119614</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">0.351775795221329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065158843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334009379148483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323349475860596</t>
+    <t xml:space="preserve">0.351065188646317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334009349346161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323349505662918</t>
   </si>
   <si>
     <t xml:space="preserve">0.342181950807571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337207317352295</t>
+    <t xml:space="preserve">0.337207347154617</t>
   </si>
   <si>
     <t xml:space="preserve">0.337562650442123</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">0.361014395952225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36030375957489</t>
+    <t xml:space="preserve">0.360303789377213</t>
   </si>
   <si>
     <t xml:space="preserve">0.389440715312958</t>
@@ -2342,67 +2342,67 @@
     <t xml:space="preserve">0.421420335769653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415024369955063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419999063014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313793182373</t>
+    <t xml:space="preserve">0.415024399757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419999033212662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313763380051</t>
   </si>
   <si>
     <t xml:space="preserve">0.405785828828812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402232527732849</t>
+    <t xml:space="preserve">0.402232557535172</t>
   </si>
   <si>
     <t xml:space="preserve">0.418577700853348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419288367033005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399389952421188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393704652786255</t>
+    <t xml:space="preserve">0.419288337230682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399389892816544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393704682588577</t>
   </si>
   <si>
     <t xml:space="preserve">0.392993986606598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391572713851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397257953882217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40436452627182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395125955343246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386598080396652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380202174186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806208372116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369542241096497</t>
+    <t xml:space="preserve">0.391572684049606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39725798368454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404364556074142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395125985145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386598110198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380202203989029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806267976761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369542270898819</t>
   </si>
   <si>
     <t xml:space="preserve">0.368831604719162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364567637443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428526967763901</t>
+    <t xml:space="preserve">0.364567667245865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428526908159256</t>
   </si>
   <si>
     <t xml:space="preserve">0.423552334308624</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">0.42639496922493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44060817360878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897447824478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464770436286926</t>
+    <t xml:space="preserve">0.440608114004135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897507429123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464770466089249</t>
   </si>
   <si>
     <t xml:space="preserve">0.471877038478851</t>
@@ -2438,19 +2438,19 @@
     <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50669926404953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517359256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120596408844</t>
+    <t xml:space="preserve">0.506699323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517359137535095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120656013489</t>
   </si>
   <si>
     <t xml:space="preserve">0.5138059258461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510963261127472</t>
+    <t xml:space="preserve">0.510963201522827</t>
   </si>
   <si>
     <t xml:space="preserve">0.507409989833832</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">0.523755133152008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525887191295624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526597678661346</t>
+    <t xml:space="preserve">0.525887131690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526597738265991</t>
   </si>
   <si>
     <t xml:space="preserve">0.525176465511322</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">0.52446573972702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53867894411087</t>
+    <t xml:space="preserve">0.538678884506226</t>
   </si>
   <si>
     <t xml:space="preserve">0.544364154338837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541521608829498</t>
+    <t xml:space="preserve">0.541521668434143</t>
   </si>
   <si>
     <t xml:space="preserve">0.536546945571899</t>
@@ -2501,22 +2501,22 @@
     <t xml:space="preserve">0.518780469894409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515937924385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523044466972351</t>
+    <t xml:space="preserve">0.515937864780426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523044407367706</t>
   </si>
   <si>
     <t xml:space="preserve">0.54223221540451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531572461128235</t>
+    <t xml:space="preserve">0.53157240152359</t>
   </si>
   <si>
     <t xml:space="preserve">0.542942881584167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549338817596436</t>
+    <t xml:space="preserve">0.54933887720108</t>
   </si>
   <si>
     <t xml:space="preserve">0.564973294734955</t>
@@ -2525,25 +2525,25 @@
     <t xml:space="preserve">0.550941288471222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549464225769043</t>
+    <t xml:space="preserve">0.549464166164398</t>
   </si>
   <si>
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647783756256</t>
+    <t xml:space="preserve">0.537647724151611</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569843292236</t>
+    <t xml:space="preserve">0.526569902896881</t>
   </si>
   <si>
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753460884094</t>
+    <t xml:space="preserve">0.514753401279449</t>
   </si>
   <si>
     <t xml:space="preserve">0.518446087837219</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">0.544294536113739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556849539279938</t>
+    <t xml:space="preserve">0.556849479675293</t>
   </si>
   <si>
     <t xml:space="preserve">0.546510100364685</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">0.563496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566450417041779</t>
+    <t xml:space="preserve">0.566450357437134</t>
   </si>
   <si>
     <t xml:space="preserve">0.572358548641205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581220865249634</t>
+    <t xml:space="preserve">0.581220924854279</t>
   </si>
   <si>
     <t xml:space="preserve">0.584174990653992</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">0.583436489105225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575312733650208</t>
+    <t xml:space="preserve">0.575312674045563</t>
   </si>
   <si>
     <t xml:space="preserve">0.56866592168808</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511799395084381</t>
+    <t xml:space="preserve">0.511799335479736</t>
   </si>
   <si>
     <t xml:space="preserve">0.50958377122879</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">0.488166451454163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483735322952271</t>
+    <t xml:space="preserve">0.483735263347626</t>
   </si>
   <si>
     <t xml:space="preserve">0.48890495300293</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">0.480781197547913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48151969909668</t>
+    <t xml:space="preserve">0.481519758701324</t>
   </si>
   <si>
     <t xml:space="preserve">0.492597639560699</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">0.525831341743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534693598747253</t>
+    <t xml:space="preserve">0.534693658351898</t>
   </si>
   <si>
     <t xml:space="preserve">0.532478094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519923150539398</t>
+    <t xml:space="preserve">0.519923090934753</t>
   </si>
   <si>
     <t xml:space="preserve">0.517707526683807</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">0.545033037662506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528785526752472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533216595649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520661652088165</t>
+    <t xml:space="preserve">0.528785467147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533216655254364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52066171169281</t>
   </si>
   <si>
     <t xml:space="preserve">0.515491962432861</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">0.508106648921967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505152583122253</t>
+    <t xml:space="preserve">0.505152642726898</t>
   </si>
   <si>
     <t xml:space="preserve">0.502198457717896</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">0.495551705360413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498505830764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502937018871307</t>
+    <t xml:space="preserve">0.498505890369415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502936959266663</t>
   </si>
   <si>
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721454620361</t>
+    <t xml:space="preserve">0.500721395015717</t>
   </si>
   <si>
     <t xml:space="preserve">0.545771598815918</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">0.553895354270935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55020272731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547987163066864</t>
+    <t xml:space="preserve">0.550202786922455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547987103462219</t>
   </si>
   <si>
     <t xml:space="preserve">0.538386344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530262529850006</t>
+    <t xml:space="preserve">0.530262470245361</t>
   </si>
   <si>
     <t xml:space="preserve">0.539863407611847</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612977564334869</t>
+    <t xml:space="preserve">0.612977504730225</t>
   </si>
   <si>
     <t xml:space="preserve">0.616670191287994</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">0.601161122322083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594514429569244</t>
+    <t xml:space="preserve">0.5945143699646</t>
   </si>
   <si>
     <t xml:space="preserve">0.599684059619904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589344680309296</t>
+    <t xml:space="preserve">0.589344620704651</t>
   </si>
   <si>
     <t xml:space="preserve">0.600422620773315</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">0.592298805713654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603376746177673</t>
+    <t xml:space="preserve">0.603376686573029</t>
   </si>
   <si>
     <t xml:space="preserve">0.641041576862335</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">0.653596520423889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667628467082977</t>
+    <t xml:space="preserve">0.667628526687622</t>
   </si>
   <si>
     <t xml:space="preserve">0.648426830768585</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">0.675752341747284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649165332317352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655812084674835</t>
+    <t xml:space="preserve">0.649165391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65581214427948</t>
   </si>
   <si>
     <t xml:space="preserve">0.655073583126068</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">0.638826012611389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62627100944519</t>
+    <t xml:space="preserve">0.626271069049835</t>
   </si>
   <si>
     <t xml:space="preserve">0.630702137947083</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587867677211761</t>
+    <t xml:space="preserve">0.587867617607117</t>
   </si>
   <si>
     <t xml:space="preserve">0.507368147373199</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">0.565711796283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564234733581543</t>
+    <t xml:space="preserve">0.564234793186188</t>
   </si>
   <si>
     <t xml:space="preserve">0.582697868347168</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">0.570881545543671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559803664684296</t>
+    <t xml:space="preserve">0.559803605079651</t>
   </si>
   <si>
     <t xml:space="preserve">0.547248601913452</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">0.567188858985901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5797438621521</t>
+    <t xml:space="preserve">0.579743921756744</t>
   </si>
   <si>
     <t xml:space="preserve">0.562019169330597</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555372416973114</t>
+    <t xml:space="preserve">0.555372476577759</t>
   </si>
   <si>
     <t xml:space="preserve">0.569404482841492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574574112892151</t>
+    <t xml:space="preserve">0.574574172496796</t>
   </si>
   <si>
     <t xml:space="preserve">0.58257657289505</t>
@@ -3228,9 +3228,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.558569312095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574172496796</t>
   </si>
   <si>
     <t xml:space="preserve">0.584177076816559</t>
@@ -51360,7 +51357,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51594,7 +51591,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1815" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51620,7 +51617,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51698,7 +51695,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1819" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51802,7 +51799,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51828,7 +51825,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51906,7 +51903,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52244,7 +52241,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G1840" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52270,7 +52267,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1841" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52296,7 +52293,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1842" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52322,7 +52319,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1843" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52348,7 +52345,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1844" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52374,7 +52371,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1845" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52400,7 +52397,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52426,7 +52423,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1847" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52452,7 +52449,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52478,7 +52475,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52504,7 +52501,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52530,7 +52527,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1851" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52556,7 +52553,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1852" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52582,7 +52579,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1853" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52608,7 +52605,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1854" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52634,7 +52631,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52660,7 +52657,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1856" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52686,7 +52683,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1857" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52712,7 +52709,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1858" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52738,7 +52735,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1859" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52764,7 +52761,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52790,7 +52787,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1861" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52816,7 +52813,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1862" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52842,7 +52839,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1863" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52868,7 +52865,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1864" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52894,7 +52891,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1865" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52920,7 +52917,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1866" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52946,7 +52943,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1867" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52972,7 +52969,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52998,7 +52995,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53024,7 +53021,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1870" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53050,7 +53047,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1871" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53076,7 +53073,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1872" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53102,7 +53099,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53128,7 +53125,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1874" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53154,7 +53151,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1875" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53180,7 +53177,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53206,7 +53203,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1877" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53232,7 +53229,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53258,7 +53255,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1879" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53284,7 +53281,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1880" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53310,7 +53307,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1881" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53336,7 +53333,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53362,7 +53359,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53388,7 +53385,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53414,7 +53411,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1885" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53440,7 +53437,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1886" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53466,7 +53463,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53492,7 +53489,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1888" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53518,7 +53515,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1889" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53544,7 +53541,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1890" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53570,7 +53567,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1891" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53596,7 +53593,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1892" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53622,7 +53619,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1893" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53648,7 +53645,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53674,7 +53671,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1895" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53700,7 +53697,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53726,7 +53723,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53752,7 +53749,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1898" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53778,7 +53775,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1899" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53804,7 +53801,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1900" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53830,7 +53827,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1901" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53856,7 +53853,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53882,7 +53879,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1903" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53908,7 +53905,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53934,7 +53931,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1905" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53960,7 +53957,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1906" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53986,7 +53983,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54012,7 +54009,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1908" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54038,7 +54035,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54064,7 +54061,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1910" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54090,7 +54087,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1911" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54116,7 +54113,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1912" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54142,7 +54139,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1913" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54168,7 +54165,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1914" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54194,7 +54191,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54220,7 +54217,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1916" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54246,7 +54243,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1917" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54272,7 +54269,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1918" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54298,7 +54295,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1919" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54324,7 +54321,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1920" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54350,7 +54347,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1921" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54376,7 +54373,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1922" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54402,7 +54399,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1923" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54428,7 +54425,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1924" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54454,7 +54451,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1925" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54480,7 +54477,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54506,7 +54503,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1927" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54532,7 +54529,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1928" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54558,7 +54555,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1929" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54584,7 +54581,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1930" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54610,7 +54607,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1931" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54636,7 +54633,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1932" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54662,7 +54659,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1933" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54688,7 +54685,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1934" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54714,7 +54711,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54740,7 +54737,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1936" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54766,7 +54763,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1937" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54792,7 +54789,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1938" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54818,7 +54815,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54844,7 +54841,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1940" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54870,7 +54867,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1941" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54896,7 +54893,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1942" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54922,7 +54919,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1943" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54948,7 +54945,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54974,7 +54971,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1945" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55000,7 +54997,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G1946" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55026,7 +55023,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1947" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55052,7 +55049,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1948" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55078,7 +55075,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1949" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55104,7 +55101,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1950" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55130,7 +55127,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1951" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55156,7 +55153,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55182,7 +55179,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1953" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55208,7 +55205,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1954" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55234,7 +55231,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1955" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55260,7 +55257,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1956" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55286,7 +55283,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1957" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55312,7 +55309,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1958" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55338,7 +55335,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1959" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55364,7 +55361,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1960" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55390,7 +55387,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1961" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55416,7 +55413,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1962" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55442,7 +55439,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1963" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55468,7 +55465,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1964" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55494,7 +55491,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1965" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55520,7 +55517,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1966" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55546,7 +55543,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55572,7 +55569,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55598,7 +55595,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1969" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55624,7 +55621,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1970" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55650,7 +55647,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1971" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55676,7 +55673,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1972" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55702,7 +55699,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1973" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55728,7 +55725,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1974" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55754,7 +55751,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1975" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55780,7 +55777,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1976" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55806,7 +55803,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1977" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55832,7 +55829,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1978" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55858,7 +55855,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55884,7 +55881,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1980" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55910,7 +55907,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1981" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55936,7 +55933,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1982" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55962,7 +55959,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55988,7 +55985,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1984" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56014,7 +56011,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1985" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56040,7 +56037,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1986" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56066,7 +56063,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1987" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56092,7 +56089,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56118,7 +56115,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1989" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56144,7 +56141,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1990" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56170,7 +56167,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1991" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56196,7 +56193,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1992" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56222,7 +56219,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1993" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56248,7 +56245,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1994" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56274,7 +56271,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1995" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56300,7 +56297,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1996" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56326,7 +56323,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1997" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56352,7 +56349,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1998" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56378,7 +56375,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1999" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56404,7 +56401,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2000" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56430,7 +56427,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2001" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56456,7 +56453,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2002" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56482,7 +56479,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2003" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56508,7 +56505,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2004" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56534,7 +56531,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2005" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56560,7 +56557,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2006" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56586,7 +56583,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2007" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56612,7 +56609,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2008" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56638,7 +56635,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2009" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56664,7 +56661,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G2010" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56690,7 +56687,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2011" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56716,7 +56713,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56742,7 +56739,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2013" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56768,7 +56765,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2014" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56794,7 +56791,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2015" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56820,7 +56817,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G2016" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56846,7 +56843,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2017" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56872,7 +56869,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2018" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56898,7 +56895,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56924,7 +56921,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2020" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56950,7 +56947,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G2021" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56976,7 +56973,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G2022" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57002,7 +56999,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2023" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57028,7 +57025,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2024" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57054,7 +57051,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G2025" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57080,7 +57077,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2026" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57106,7 +57103,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G2027" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57132,7 +57129,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2028" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57158,7 +57155,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2029" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57184,7 +57181,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2030" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57210,7 +57207,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57236,7 +57233,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57262,7 +57259,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2033" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57288,7 +57285,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2034" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57314,7 +57311,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57340,7 +57337,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -57366,7 +57363,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2037" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57392,7 +57389,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2038" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57418,7 +57415,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2039" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57444,7 +57441,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2040" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57470,7 +57467,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2041" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57496,7 +57493,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2042" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57522,7 +57519,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G2043" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57548,7 +57545,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2044" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57574,7 +57571,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2045" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57600,7 +57597,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2046" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57626,7 +57623,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2047" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57652,7 +57649,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57678,7 +57675,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57704,7 +57701,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2050" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57730,7 +57727,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2051" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57756,7 +57753,7 @@
         <v>0.75</v>
       </c>
       <c r="G2052" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57782,7 +57779,7 @@
         <v>0.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57808,7 +57805,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G2054" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57834,7 +57831,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2055" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57860,7 +57857,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2056" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57886,7 +57883,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2057" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57912,7 +57909,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2058" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57938,7 +57935,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2059" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57964,7 +57961,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G2060" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57990,7 +57987,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58016,7 +58013,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2062" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58042,7 +58039,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2063" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58068,7 +58065,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G2064" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58094,7 +58091,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2065" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58120,7 +58117,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2066" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58146,7 +58143,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G2067" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58172,7 +58169,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2068" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58198,7 +58195,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2069" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58224,7 +58221,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2070" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58250,7 +58247,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2071" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58276,7 +58273,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2072" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58302,7 +58299,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58328,7 +58325,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2074" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58354,7 +58351,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2075" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58380,7 +58377,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58406,7 +58403,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2077" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58432,7 +58429,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2078" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58458,7 +58455,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2079" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58484,7 +58481,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58510,7 +58507,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2081" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58536,7 +58533,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2082" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58562,7 +58559,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -58588,7 +58585,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2084" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58614,7 +58611,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2085" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58640,7 +58637,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2086" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58666,7 +58663,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2087" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58692,7 +58689,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2088" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58718,7 +58715,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2089" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58744,7 +58741,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2090" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58770,7 +58767,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2091" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58796,7 +58793,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2092" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58822,7 +58819,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G2093" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58848,7 +58845,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G2094" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58874,7 +58871,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G2095" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58900,7 +58897,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2096" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58926,7 +58923,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2097" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58952,7 +58949,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G2098" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58978,7 +58975,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2099" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59004,7 +59001,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2100" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59030,7 +59027,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G2101" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59056,7 +59053,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2102" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59082,7 +59079,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2103" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59108,7 +59105,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2104" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59134,7 +59131,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59160,7 +59157,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2106" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59186,7 +59183,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2107" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59212,7 +59209,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2108" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59238,7 +59235,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2109" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59264,7 +59261,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59290,7 +59287,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2111" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59316,7 +59313,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2112" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59342,7 +59339,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2113" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59368,7 +59365,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2114" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59394,7 +59391,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2115" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59420,7 +59417,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2116" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59446,7 +59443,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2117" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59472,7 +59469,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2118" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59498,7 +59495,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2119" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59524,7 +59521,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2120" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59550,7 +59547,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G2121" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59576,7 +59573,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2122" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59602,7 +59599,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2123" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59628,7 +59625,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2124" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59654,7 +59651,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2125" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59680,7 +59677,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2126" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59706,7 +59703,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2127" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59732,7 +59729,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2128" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59758,7 +59755,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2129" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59784,7 +59781,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2130" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59810,7 +59807,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2131" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59836,7 +59833,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2132" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59862,7 +59859,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2133" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59888,7 +59885,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G2134" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59914,7 +59911,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2135" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59940,7 +59937,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2136" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59966,7 +59963,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2137" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59992,7 +59989,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2138" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60018,7 +60015,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2139" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60044,7 +60041,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2140" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60070,7 +60067,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60096,7 +60093,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2142" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60122,7 +60119,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2143" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60148,7 +60145,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2144" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60174,7 +60171,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2145" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60200,7 +60197,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2146" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60226,7 +60223,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2147" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60252,7 +60249,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2148" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60278,7 +60275,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2149" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60304,7 +60301,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2150" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60330,7 +60327,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2151" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60356,7 +60353,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2152" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60382,7 +60379,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60408,7 +60405,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2154" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60434,7 +60431,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2155" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60460,7 +60457,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2156" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60486,7 +60483,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2157" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60512,7 +60509,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2158" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60538,7 +60535,7 @@
         <v>0.75</v>
       </c>
       <c r="G2159" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60564,7 +60561,7 @@
         <v>0.75</v>
       </c>
       <c r="G2160" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60590,7 +60587,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2161" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60616,7 +60613,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2162" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60642,7 +60639,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2163" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60668,7 +60665,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2164" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60694,7 +60691,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2165" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60720,7 +60717,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2166" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60746,7 +60743,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2167" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60772,7 +60769,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2168" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60798,7 +60795,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2169" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60824,7 +60821,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2170" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60850,7 +60847,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2171" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60876,7 +60873,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2172" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60902,7 +60899,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2173" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60928,7 +60925,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2174" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60954,7 +60951,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2175" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60980,7 +60977,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2176" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61006,7 +61003,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2177" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61032,7 +61029,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2178" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61058,7 +61055,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2179" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61084,7 +61081,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2180" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61110,7 +61107,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2181" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61136,7 +61133,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2182" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61162,7 +61159,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2183" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61188,7 +61185,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61214,7 +61211,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2185" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61240,7 +61237,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2186" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61266,7 +61263,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2187" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61292,7 +61289,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61318,7 +61315,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2189" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61344,7 +61341,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2190" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61370,7 +61367,7 @@
         <v>0.75</v>
       </c>
       <c r="G2191" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61396,7 +61393,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2192" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61422,7 +61419,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2193" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61448,7 +61445,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2194" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61474,7 +61471,7 @@
         <v>0.75</v>
       </c>
       <c r="G2195" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61500,7 +61497,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2196" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61526,7 +61523,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2197" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61552,7 +61549,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2198" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61578,7 +61575,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2199" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61604,7 +61601,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2200" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61630,7 +61627,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2201" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61656,7 +61653,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2202" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61682,7 +61679,7 @@
         <v>0.75</v>
       </c>
       <c r="G2203" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61708,7 +61705,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2204" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61734,7 +61731,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2205" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61760,7 +61757,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2206" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61786,7 +61783,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2207" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61812,7 +61809,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2208" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61838,7 +61835,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2209" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61864,7 +61861,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2210" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61890,7 +61887,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2211" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61916,7 +61913,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2212" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61942,7 +61939,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2213" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61968,7 +61965,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2214" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61994,7 +61991,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2215" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62020,7 +62017,7 @@
         <v>0.75</v>
       </c>
       <c r="G2216" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62046,7 +62043,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2217" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62072,7 +62069,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2218" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62098,7 +62095,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2219" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62124,7 +62121,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2220" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62150,7 +62147,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2221" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62176,7 +62173,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2222" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62202,7 +62199,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2223" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62228,7 +62225,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2224" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62254,7 +62251,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2225" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62280,7 +62277,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2226" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62306,7 +62303,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2227" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62332,7 +62329,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62358,7 +62355,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2229" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62384,7 +62381,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2230" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62410,7 +62407,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2231" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62436,7 +62433,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2232" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62462,7 +62459,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2233" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62488,7 +62485,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2234" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62514,7 +62511,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2235" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62540,7 +62537,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2236" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62566,7 +62563,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2237" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62592,7 +62589,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2238" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62618,7 +62615,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2239" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62644,7 +62641,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2240" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62670,7 +62667,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G2241" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62696,7 +62693,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2242" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62722,7 +62719,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2243" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62748,7 +62745,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2244" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62774,7 +62771,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2245" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62800,7 +62797,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2246" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62826,7 +62823,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2247" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62852,7 +62849,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62878,7 +62875,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2249" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62904,7 +62901,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2250" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62930,7 +62927,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2251" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62956,7 +62953,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2252" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62982,7 +62979,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2253" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63008,7 +63005,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2254" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63034,7 +63031,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2255" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63060,7 +63057,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2256" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63086,7 +63083,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2257" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63112,7 +63109,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2258" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63138,7 +63135,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2259" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63164,7 +63161,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2260" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63190,7 +63187,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2261" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63216,7 +63213,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G2262" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63242,7 +63239,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63268,7 +63265,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63294,7 +63291,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63320,7 +63317,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63346,7 +63343,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63372,7 +63369,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63398,7 +63395,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63424,7 +63421,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63450,7 +63447,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63476,7 +63473,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63502,7 +63499,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63528,7 +63525,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63554,7 +63551,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63580,7 +63577,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63606,7 +63603,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63632,7 +63629,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63658,7 +63655,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63684,7 +63681,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63710,7 +63707,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63736,7 +63733,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63762,7 +63759,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63788,7 +63785,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63814,7 +63811,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63840,7 +63837,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63866,7 +63863,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63892,7 +63889,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63918,7 +63915,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63944,7 +63941,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63970,7 +63967,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63996,7 +63993,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64022,7 +64019,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64048,7 +64045,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64074,7 +64071,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64100,7 +64097,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64126,7 +64123,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64152,7 +64149,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64178,7 +64175,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64204,7 +64201,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64230,7 +64227,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64256,7 +64253,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64282,7 +64279,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64308,7 +64305,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64334,7 +64331,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64360,7 +64357,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64386,7 +64383,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64412,7 +64409,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64438,7 +64435,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64464,7 +64461,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64490,7 +64487,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64516,7 +64513,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64542,7 +64539,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64568,7 +64565,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64594,7 +64591,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64620,7 +64617,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64646,7 +64643,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64672,7 +64669,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64698,7 +64695,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64724,7 +64721,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64750,7 +64747,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64776,7 +64773,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64802,7 +64799,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64828,7 +64825,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64854,7 +64851,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64880,7 +64877,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64906,7 +64903,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64932,7 +64929,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64958,7 +64955,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64984,7 +64981,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65010,7 +65007,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65036,7 +65033,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65062,7 +65059,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65088,7 +65085,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65114,7 +65111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65140,7 +65137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65166,7 +65163,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65192,7 +65189,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65218,7 +65215,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65244,7 +65241,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65270,7 +65267,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65296,7 +65293,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65322,7 +65319,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65348,7 +65345,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65374,7 +65371,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65400,7 +65397,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65426,7 +65423,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65452,7 +65449,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65478,7 +65475,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65504,7 +65501,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65530,7 +65527,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65556,7 +65553,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65582,7 +65579,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65608,7 +65605,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65634,7 +65631,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65660,7 +65657,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65686,7 +65683,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65712,7 +65709,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65738,7 +65735,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65764,7 +65761,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65790,7 +65787,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65816,7 +65813,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65842,7 +65839,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65868,7 +65865,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65894,7 +65891,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65920,7 +65917,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65946,7 +65943,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65972,7 +65969,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65998,7 +65995,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66024,7 +66021,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66050,7 +66047,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66076,7 +66073,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66102,7 +66099,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66128,7 +66125,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66154,7 +66151,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66180,7 +66177,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66206,7 +66203,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66232,7 +66229,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66258,7 +66255,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66284,7 +66281,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66310,7 +66307,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66336,7 +66333,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66362,7 +66359,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66388,7 +66385,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66414,7 +66411,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66440,7 +66437,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66466,7 +66463,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66492,7 +66489,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66518,7 +66515,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66544,7 +66541,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66570,7 +66567,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66596,7 +66593,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66622,7 +66619,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66648,7 +66645,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66674,7 +66671,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66700,7 +66697,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66726,7 +66723,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66752,7 +66749,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66778,7 +66775,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66804,7 +66801,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66830,7 +66827,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66856,7 +66853,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66882,7 +66879,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66908,7 +66905,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66934,7 +66931,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66960,7 +66957,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66986,7 +66983,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67012,7 +67009,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67038,7 +67035,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67064,7 +67061,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67090,7 +67087,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67116,7 +67113,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67142,7 +67139,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67168,7 +67165,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67194,7 +67191,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67220,7 +67217,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67246,7 +67243,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67272,7 +67269,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67298,7 +67295,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67324,7 +67321,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67350,7 +67347,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67376,7 +67373,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67402,7 +67399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67428,7 +67425,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67454,7 +67451,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67480,7 +67477,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67506,7 +67503,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67532,7 +67529,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67558,7 +67555,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67584,7 +67581,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67610,7 +67607,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67636,7 +67633,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67662,7 +67659,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67688,7 +67685,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67714,7 +67711,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67740,7 +67737,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67766,7 +67763,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67792,7 +67789,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67818,7 +67815,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67844,7 +67841,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67870,7 +67867,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67896,7 +67893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67922,7 +67919,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67948,7 +67945,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67974,7 +67971,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68000,7 +67997,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68026,7 +68023,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68052,7 +68049,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68078,7 +68075,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68104,7 +68101,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68130,7 +68127,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68156,7 +68153,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68182,7 +68179,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68208,7 +68205,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68234,7 +68231,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68260,7 +68257,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68286,7 +68283,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68312,7 +68309,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68338,7 +68335,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68364,7 +68361,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68390,7 +68387,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68416,7 +68413,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68442,7 +68439,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68468,7 +68465,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68494,7 +68491,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68520,7 +68517,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68546,7 +68543,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68572,7 +68569,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68598,7 +68595,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68624,7 +68621,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68650,7 +68647,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68676,7 +68673,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68702,7 +68699,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68728,7 +68725,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68754,7 +68751,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68780,7 +68777,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68806,7 +68803,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68832,7 +68829,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68858,7 +68855,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68884,7 +68881,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68910,7 +68907,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68936,7 +68933,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68962,7 +68959,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68988,7 +68985,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69014,7 +69011,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69040,7 +69037,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69066,7 +69063,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69092,7 +69089,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69118,7 +69115,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69144,7 +69141,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69170,7 +69167,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2491" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69196,7 +69193,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2492" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69222,7 +69219,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2493" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69248,7 +69245,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2494" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69274,7 +69271,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2495" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69282,7 +69279,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6494328704</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>149676</v>
@@ -69300,9 +69297,35 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6496296296</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>90018</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>1.03199994564056</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>1.03600001335144</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -47,67 +47,67 @@
     <t xml:space="preserve">0.382716715335846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367179781198502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3804971575737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789375543594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352276891469955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36813098192215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387155830860138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936951637268</t>
+    <t xml:space="preserve">0.367179751396179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380497187376022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789405345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3522769510746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368131011724472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387155890464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936921834946</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009611845016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521357774734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886884689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335471570491791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345618218183517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361472308635712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341496169567108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355130672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352594017982483</t>
+    <t xml:space="preserve">0.373521327972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886854887009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335471600294113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34561824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361472249031067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341496229171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355130612850189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352594047784805</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447429895401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360838115215302</t>
+    <t xml:space="preserve">0.360838085412979</t>
   </si>
   <si>
     <t xml:space="preserve">0.35735023021698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357984364032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350691497325897</t>
+    <t xml:space="preserve">0.357984393835068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35069152712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
@@ -125,55 +125,55 @@
     <t xml:space="preserve">0.276240944862366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304461181163788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326593369245529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789036273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329130053520203</t>
+    <t xml:space="preserve">0.304461151361465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326593399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789066076279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329129993915558</t>
   </si>
   <si>
     <t xml:space="preserve">0.348471969366074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.327544629573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671128988266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330081254243851</t>
+    <t xml:space="preserve">0.3275445997715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671099185944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330081284046173</t>
   </si>
   <si>
     <t xml:space="preserve">0.334203332662582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838734149933</t>
+    <t xml:space="preserve">0.386838763952255</t>
   </si>
   <si>
     <t xml:space="preserve">0.356398969888687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368765145540237</t>
+    <t xml:space="preserve">0.368765115737915</t>
   </si>
   <si>
     <t xml:space="preserve">0.325325071811676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318032205104828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306236803531647</t>
+    <t xml:space="preserve">0.318032175302505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306236773729324</t>
   </si>
   <si>
     <t xml:space="preserve">0.308329522609711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331032484769821</t>
+    <t xml:space="preserve">0.331032544374466</t>
   </si>
   <si>
     <t xml:space="preserve">0.322788387537003</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">0.319934666156769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309153914451599</t>
+    <t xml:space="preserve">0.309153944253922</t>
   </si>
   <si>
     <t xml:space="preserve">0.331666678190231</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.310802757740021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323422580957413</t>
+    <t xml:space="preserve">0.323422610759735</t>
   </si>
   <si>
     <t xml:space="preserve">0.308836847543716</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.306300193071365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298880517482758</t>
+    <t xml:space="preserve">0.298880487680435</t>
   </si>
   <si>
     <t xml:space="preserve">0.285880208015442</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">0.267743170261383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260767340660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489492893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25873801112175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28854364156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371618866920471</t>
+    <t xml:space="preserve">0.260767370462418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489463090897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738070726395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288543671369553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
     <t xml:space="preserve">0.364643067121506</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.367496877908707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36971640586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399279356003</t>
+    <t xml:space="preserve">0.369716376066208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399309158325</t>
   </si>
   <si>
     <t xml:space="preserve">0.388741225004196</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.38779005408287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35703319311142</t>
+    <t xml:space="preserve">0.370033472776413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357033163309097</t>
   </si>
   <si>
     <t xml:space="preserve">0.374155551195145</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">0.377643436193466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370984703302383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372253030538559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387472927570343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377326369285583</t>
+    <t xml:space="preserve">0.370984673500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372253090143204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387472957372665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377326428890228</t>
   </si>
   <si>
     <t xml:space="preserve">0.439791262149811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453425705432892</t>
+    <t xml:space="preserve">0.453425735235214</t>
   </si>
   <si>
     <t xml:space="preserve">0.454059958457947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133177995682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455645322799683</t>
+    <t xml:space="preserve">0.46166980266571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133237600327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455645352602005</t>
   </si>
   <si>
     <t xml:space="preserve">0.456279516220093</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">0.47879222035408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485768049955368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477840930223465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483231335878372</t>
+    <t xml:space="preserve">0.485767990350723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47784098982811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483231395483017</t>
   </si>
   <si>
     <t xml:space="preserve">0.484816789627075</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.475621402263641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476889699697495</t>
+    <t xml:space="preserve">0.476889759302139</t>
   </si>
   <si>
     <t xml:space="preserve">0.488304615020752</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.493695080280304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489890038967133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548712253571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645662069321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084777593613</t>
+    <t xml:space="preserve">0.489890098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548771858215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468645721673965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084717988968</t>
   </si>
   <si>
     <t xml:space="preserve">0.495280474424362</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">0.486719280481339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484182626008987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497500061988831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50732958316803</t>
+    <t xml:space="preserve">0.484182566404343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497500002384186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507329523563385</t>
   </si>
   <si>
     <t xml:space="preserve">0.507963716983795</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">0.515890717506409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526354432106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525720179080963</t>
+    <t xml:space="preserve">0.526354372501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525720238685608</t>
   </si>
   <si>
     <t xml:space="preserve">0.529525101184845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535866737365723</t>
+    <t xml:space="preserve">0.535866856575012</t>
   </si>
   <si>
     <t xml:space="preserve">0.540305912494659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620844483375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625917792320251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627503216266632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597697556018829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596112132072449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57708728313446</t>
+    <t xml:space="preserve">0.620844423770905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625917732715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627503275871277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597697615623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596112191677094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577087342739105</t>
   </si>
   <si>
     <t xml:space="preserve">0.561867475509644</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">0.569160282611847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566940724849701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559013783931732</t>
+    <t xml:space="preserve">0.566940784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559013724327087</t>
   </si>
   <si>
     <t xml:space="preserve">0.551720917224884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529208183288574</t>
+    <t xml:space="preserve">0.529208123683929</t>
   </si>
   <si>
     <t xml:space="preserve">0.516841948032379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5174760222435</t>
+    <t xml:space="preserve">0.517476141452789</t>
   </si>
   <si>
     <t xml:space="preserve">0.516207814216614</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">0.549184203147888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547281742095947</t>
+    <t xml:space="preserve">0.547281801700592</t>
   </si>
   <si>
     <t xml:space="preserve">0.558379590511322</t>
@@ -449,37 +449,37 @@
     <t xml:space="preserve">0.586599767208099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613868713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654455065727234</t>
+    <t xml:space="preserve">0.613868772983551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654455006122589</t>
   </si>
   <si>
     <t xml:space="preserve">0.665870010852814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655089259147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62306410074234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633844792842865</t>
+    <t xml:space="preserve">0.655089199542999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623064160346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63384485244751</t>
   </si>
   <si>
     <t xml:space="preserve">0.62211287021637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618942081928253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615137040615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631625175476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628771483898163</t>
+    <t xml:space="preserve">0.618942022323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615137100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631625294685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628771543502808</t>
   </si>
   <si>
     <t xml:space="preserve">0.63416188955307</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">0.629088580608368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643674254417419</t>
+    <t xml:space="preserve">0.643674314022064</t>
   </si>
   <si>
     <t xml:space="preserve">0.644308507442474</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">0.645576775074005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636064410209656</t>
+    <t xml:space="preserve">0.636064350605011</t>
   </si>
   <si>
     <t xml:space="preserve">0.634796142578125</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">0.628454446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632259368896484</t>
+    <t xml:space="preserve">0.632259428501129</t>
   </si>
   <si>
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234948635101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602453768253326</t>
+    <t xml:space="preserve">0.626234829425812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602453827857971</t>
   </si>
   <si>
     <t xml:space="preserve">0.58818519115448</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.619893252849579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592941403388977</t>
+    <t xml:space="preserve">0.592941462993622</t>
   </si>
   <si>
     <t xml:space="preserve">0.600551307201385</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">0.594526767730713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591673076152802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60118556022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603087902069092</t>
+    <t xml:space="preserve">0.591673016548157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601185500621796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603087961673737</t>
   </si>
   <si>
     <t xml:space="preserve">0.609746634960175</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.611332058906555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614185869693756</t>
+    <t xml:space="preserve">0.614185750484467</t>
   </si>
   <si>
     <t xml:space="preserve">0.611966252326965</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">0.605941712856293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598648846149445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593258440494537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58850222826004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380459308624</t>
+    <t xml:space="preserve">0.598648905754089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593258500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588502287864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380518913269</t>
   </si>
   <si>
     <t xml:space="preserve">0.617673695087433</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">0.611015021800995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604039251804352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605307579040527</t>
+    <t xml:space="preserve">0.604039192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605307519435883</t>
   </si>
   <si>
     <t xml:space="preserve">0.61006373167038</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">0.624649524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617039561271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610380828380585</t>
+    <t xml:space="preserve">0.617039501667023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61038076877594</t>
   </si>
   <si>
     <t xml:space="preserve">0.596429288387299</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">0.591355979442596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589770615100861</t>
+    <t xml:space="preserve">0.589770555496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.56535530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523183643817902</t>
+    <t xml:space="preserve">0.523183524608612</t>
   </si>
   <si>
     <t xml:space="preserve">0.481963038444519</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">0.493377953767776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492109626531601</t>
+    <t xml:space="preserve">0.492109656333923</t>
   </si>
   <si>
     <t xml:space="preserve">0.508280813694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513988256454468</t>
+    <t xml:space="preserve">0.513988196849823</t>
   </si>
   <si>
     <t xml:space="preserve">0.509231984615326</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">0.51779317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548550128936768</t>
+    <t xml:space="preserve">0.548550069332123</t>
   </si>
   <si>
     <t xml:space="preserve">0.544110894203186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521598219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530476450920105</t>
+    <t xml:space="preserve">0.521598160266876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53047639131546</t>
   </si>
   <si>
     <t xml:space="preserve">0.546013355255127</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">0.54094010591507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532695949077606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538720488548279</t>
+    <t xml:space="preserve">0.532696008682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538720548152924</t>
   </si>
   <si>
     <t xml:space="preserve">0.539037644863129</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">0.533330142498016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532061815261841</t>
+    <t xml:space="preserve">0.532061874866486</t>
   </si>
   <si>
     <t xml:space="preserve">0.568843185901642</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">0.566306591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549501299858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560599148273468</t>
+    <t xml:space="preserve">0.549501240253448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560599088668823</t>
   </si>
   <si>
     <t xml:space="preserve">0.56440407037735</t>
@@ -701,34 +701,34 @@
     <t xml:space="preserve">0.545062124729156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521281063556671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516524851322174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506695330142975</t>
+    <t xml:space="preserve">0.521281123161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516524791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50669538974762</t>
   </si>
   <si>
     <t xml:space="preserve">0.528256893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519695699214935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526037335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518744468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511451601982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514305353164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523817658424377</t>
+    <t xml:space="preserve">0.519695639610291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526037275791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51874440908432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511451542377472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514305293560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523817718029022</t>
   </si>
   <si>
     <t xml:space="preserve">0.508597791194916</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">0.510500311851501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499719530344009</t>
+    <t xml:space="preserve">0.499719649553299</t>
   </si>
   <si>
     <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54157418012619</t>
+    <t xml:space="preserve">0.541574239730835</t>
   </si>
   <si>
     <t xml:space="preserve">0.550769627094269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553623378276825</t>
+    <t xml:space="preserve">0.55362343788147</t>
   </si>
   <si>
     <t xml:space="preserve">0.560282051563263</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">0.575501918792725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627820312976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658894181251526</t>
+    <t xml:space="preserve">0.627820372581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658894240856171</t>
   </si>
   <si>
     <t xml:space="preserve">0.655723392963409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358205318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262582778931</t>
+    <t xml:space="preserve">0.682358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262523174286</t>
   </si>
   <si>
     <t xml:space="preserve">0.736896097660065</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">0.696943938732147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.733091175556183</t>
+    <t xml:space="preserve">0.733091115951538</t>
   </si>
   <si>
     <t xml:space="preserve">0.748945295810699</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">0.747676908969879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754652738571167</t>
+    <t xml:space="preserve">0.754652857780457</t>
   </si>
   <si>
     <t xml:space="preserve">0.755286872386932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760360062122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81806880235672</t>
+    <t xml:space="preserve">0.760360181331635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81806892156601</t>
   </si>
   <si>
     <t xml:space="preserve">0.799678206443787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771140873432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768604278564453</t>
+    <t xml:space="preserve">0.771140813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768604159355164</t>
   </si>
   <si>
     <t xml:space="preserve">0.720407962799072</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">0.727383732795715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740701138973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738164484500885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774945855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783824026584625</t>
+    <t xml:space="preserve">0.740701019763947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73816454410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774945914745331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78382408618927</t>
   </si>
   <si>
     <t xml:space="preserve">0.801580667495728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849776983261108</t>
+    <t xml:space="preserve">0.849776864051819</t>
   </si>
   <si>
     <t xml:space="preserve">0.884021699428558</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">0.894168198108673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925876498222351</t>
+    <t xml:space="preserve">0.925876319408417</t>
   </si>
   <si>
     <t xml:space="preserve">0.924608051776886</t>
@@ -878,37 +878,37 @@
     <t xml:space="preserve">0.887826681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.901778221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881485044956207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412414550781</t>
+    <t xml:space="preserve">0.901778280735016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881484925746918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412474155426</t>
   </si>
   <si>
     <t xml:space="preserve">0.87514340877533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896070778369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910656452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827240467072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91002231836319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729082584381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892900049686432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436584949493</t>
+    <t xml:space="preserve">0.896070837974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9106565117836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827300071716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9100221991539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889729201793671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892899870872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436525344849</t>
   </si>
   <si>
     <t xml:space="preserve">0.863094329833984</t>
@@ -920,46 +920,46 @@
     <t xml:space="preserve">0.867533564567566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87577748298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868167638778687</t>
+    <t xml:space="preserve">0.875777542591095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868167698383331</t>
   </si>
   <si>
     <t xml:space="preserve">0.756555140018463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788897395133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812995553016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807288110256195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838362097740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790165781974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786360859870911</t>
+    <t xml:space="preserve">0.788897335529327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812995493412018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80728816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838362157344818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790165841579437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786360800266266</t>
   </si>
   <si>
     <t xml:space="preserve">0.811727225780487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830118000507355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814897954463959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792702436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803483128547668</t>
+    <t xml:space="preserve">0.830117881298065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814898014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792702376842499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803483009338379</t>
   </si>
   <si>
     <t xml:space="preserve">0.804117262363434</t>
@@ -971,49 +971,49 @@
     <t xml:space="preserve">0.780019223690033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781921744346619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791433930397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78509247303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994874477386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531528949738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773677468299866</t>
+    <t xml:space="preserve">0.781921625137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791433990001678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785092413425446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786995053291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793970704078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531588554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77367752790451</t>
   </si>
   <si>
     <t xml:space="preserve">0.775580108165741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769872486591339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767335891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771775126457214</t>
+    <t xml:space="preserve">0.769872605800629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767335951328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77177494764328</t>
   </si>
   <si>
     <t xml:space="preserve">0.761628448963165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79587322473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811093151569366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843435347080231</t>
+    <t xml:space="preserve">0.795873165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811093032360077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435168266296</t>
   </si>
   <si>
     <t xml:space="preserve">0.832654535770416</t>
@@ -1022,25 +1022,25 @@
     <t xml:space="preserve">0.872606754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.862460196018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866899430751801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840264618396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830752015113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855484306812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801213264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142730236053</t>
+    <t xml:space="preserve">0.862460076808929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866899311542511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840264558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.830752074718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855484366416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801153659821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142789840698</t>
   </si>
   <si>
     <t xml:space="preserve">0.820605516433716</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">0.826947093009949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80601978302002</t>
+    <t xml:space="preserve">0.806019842624664</t>
   </si>
   <si>
     <t xml:space="preserve">0.799044013023376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804751515388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785726606845856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778750777244568</t>
+    <t xml:space="preserve">0.804751455783844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785726547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778750836849213</t>
   </si>
   <si>
     <t xml:space="preserve">0.777482450008392</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">0.806654036045074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.807922184467316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854850351810455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857386946678162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.852313578128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863728582859039</t>
+    <t xml:space="preserve">0.807922303676605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854850292205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857386887073517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852313637733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86372846364975</t>
   </si>
   <si>
     <t xml:space="preserve">0.864996910095215</t>
@@ -1097,49 +1097,49 @@
     <t xml:space="preserve">0.850411117076874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84089869260788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834556996822357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996112346649</t>
+    <t xml:space="preserve">0.840898633003235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996231555939</t>
   </si>
   <si>
     <t xml:space="preserve">0.827581346035004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826312899589539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.805385589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814263939857483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81870299577713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81933718919754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79650741815567</t>
+    <t xml:space="preserve">0.826312959194183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805385649204254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814263880252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818703055381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819337248802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796507358551025</t>
   </si>
   <si>
     <t xml:space="preserve">0.809190630912781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809824705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797775745391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798409759998322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817434787750244</t>
+    <t xml:space="preserve">0.809824645519257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797775685787201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798409819602966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817434728145599</t>
   </si>
   <si>
     <t xml:space="preserve">0.823142051696777</t>
@@ -1151,40 +1151,40 @@
     <t xml:space="preserve">0.819971323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797141432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716602981090546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704553782939911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736261963844299</t>
+    <t xml:space="preserve">0.797141492366791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716602861881256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7045539021492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736262023448944</t>
   </si>
   <si>
     <t xml:space="preserve">0.75972592830658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77240926027298</t>
+    <t xml:space="preserve">0.77240914106369</t>
   </si>
   <si>
     <t xml:space="preserve">0.776214182376862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784458339214325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.783190011978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752116024494171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7609943151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823407649994</t>
+    <t xml:space="preserve">0.78445827960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783189833164215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752115905284882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760994374752045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823467254639</t>
   </si>
   <si>
     <t xml:space="preserve">0.766701757907867</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">0.790799856185913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.810458958148956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311661720276</t>
+    <t xml:space="preserve">0.810458898544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311780929565</t>
   </si>
   <si>
     <t xml:space="preserve">0.781287431716919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795238971710205</t>
+    <t xml:space="preserve">0.79523903131485</t>
   </si>
   <si>
     <t xml:space="preserve">0.800312340259552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.815532207489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.764799237251282</t>
+    <t xml:space="preserve">0.815532267093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.764799296855927</t>
   </si>
   <si>
     <t xml:space="preserve">0.731822848320007</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">0.711529612541199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.693773090839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739432811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70391970872879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695041418075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683626592159271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660796701908112</t>
+    <t xml:space="preserve">0.693773031234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739432752132416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703919649124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695041477680206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683626472949982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660796761512756</t>
   </si>
   <si>
     <t xml:space="preserve">0.684894859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670943140983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691236436367035</t>
+    <t xml:space="preserve">0.670943200588226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69123649597168</t>
   </si>
   <si>
     <t xml:space="preserve">0.678553283214569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.687431454658508</t>
+    <t xml:space="preserve">0.687431514263153</t>
   </si>
   <si>
     <t xml:space="preserve">0.717871308326721</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">0.730554521083832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.710261344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697578072547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714066386222839</t>
+    <t xml:space="preserve">0.710261225700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697578132152557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714066326618195</t>
   </si>
   <si>
     <t xml:space="preserve">0.729286134243011</t>
@@ -1286,40 +1286,40 @@
     <t xml:space="preserve">0.763530969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749579310417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042715549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735627710819244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745774328708649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.743237733840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.741969406604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.744506061077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722944617271423</t>
+    <t xml:space="preserve">0.749579429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735627830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745774388313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.743237793445587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.741969347000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.744506180286407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722944498062134</t>
   </si>
   <si>
     <t xml:space="preserve">0.700114667415619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706456363201141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846399784088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72548121213913</t>
+    <t xml:space="preserve">0.706456303596497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846459388733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725481331348419</t>
   </si>
   <si>
     <t xml:space="preserve">0.71533465385437</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">0.692504823207855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705188035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.681089878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701382994651794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696309745311737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.688699781894684</t>
+    <t xml:space="preserve">0.705188095569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.681089818477631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701383054256439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696309804916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.688699841499329</t>
   </si>
   <si>
     <t xml:space="preserve">0.686163246631622</t>
@@ -1352,43 +1352,43 @@
     <t xml:space="preserve">0.679821610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672211587429047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.646845161914825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.677284836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658260107040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659528434276581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651918470859528</t>
+    <t xml:space="preserve">0.672211647033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64684522151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.677284896373749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658259987831116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659528374671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651918411254883</t>
   </si>
   <si>
     <t xml:space="preserve">0.648113429546356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641771793365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635430097579956</t>
+    <t xml:space="preserve">0.641771852970123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635430157184601</t>
   </si>
   <si>
     <t xml:space="preserve">0.643040239810944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639235138893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637966871261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594209611415863</t>
+    <t xml:space="preserve">0.639235198497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637966930866241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594209671020508</t>
   </si>
   <si>
     <t xml:space="preserve">0.596746325492859</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">0.598014652729034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599917113780975</t>
+    <t xml:space="preserve">0.599917054176331</t>
   </si>
   <si>
     <t xml:space="preserve">0.603722155094147</t>
@@ -1409,16 +1409,16 @@
     <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478676795959</t>
+    <t xml:space="preserve">0.621478736400604</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622747004032135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615771293640137</t>
+    <t xml:space="preserve">0.62274694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">0.6233811378479</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">0.591038882732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584063172340393</t>
+    <t xml:space="preserve">0.584063112735748</t>
   </si>
   <si>
     <t xml:space="preserve">0.580892324447632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56567245721817</t>
+    <t xml:space="preserve">0.565672397613525</t>
   </si>
   <si>
     <t xml:space="preserve">0.570745646953583</t>
@@ -1445,37 +1445,37 @@
     <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572648167610168</t>
+    <t xml:space="preserve">0.572648286819458</t>
   </si>
   <si>
     <t xml:space="preserve">0.559965014457703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135124206543</t>
+    <t xml:space="preserve">0.537135183811188</t>
   </si>
   <si>
     <t xml:space="preserve">0.528891026973724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573282301425934</t>
+    <t xml:space="preserve">0.573282361030579</t>
   </si>
   <si>
     <t xml:space="preserve">0.569477438926697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608795404434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307828903198</t>
+    <t xml:space="preserve">0.608795464038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307888507843</t>
   </si>
   <si>
     <t xml:space="preserve">0.630356967449188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604990422725677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580258190631866</t>
+    <t xml:space="preserve">0.604990482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580258131027222</t>
   </si>
   <si>
     <t xml:space="preserve">0.572014033794403</t>
@@ -1484,67 +1484,67 @@
     <t xml:space="preserve">0.568209111690521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554891705513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629722714424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721676230430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766067624092102</t>
+    <t xml:space="preserve">0.554891645908356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629722774028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721676170825958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766067504882812</t>
   </si>
   <si>
     <t xml:space="preserve">0.782555758953094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828215420246124</t>
+    <t xml:space="preserve">0.828215479850769</t>
   </si>
   <si>
     <t xml:space="preserve">0.825678825378418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873875021934509</t>
+    <t xml:space="preserve">0.873875081539154</t>
   </si>
   <si>
     <t xml:space="preserve">0.871338486671448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882753252983093</t>
+    <t xml:space="preserve">0.882753312587738</t>
   </si>
   <si>
     <t xml:space="preserve">0.880216717720032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903046607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92207145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937291324138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918266355991364</t>
+    <t xml:space="preserve">0.903046548366547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92207133769989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937291443347931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918266475200653</t>
   </si>
   <si>
     <t xml:space="preserve">0.866265118122101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.839630305767059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896704971790314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.876411616802216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070099830627</t>
+    <t xml:space="preserve">0.839630365371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896705031394958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87641179561615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801772594452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070159435272</t>
   </si>
   <si>
     <t xml:space="preserve">0.938559651374817</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">0.934754610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904314935207367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583083629608</t>
+    <t xml:space="preserve">0.904314875602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583143234253</t>
   </si>
   <si>
     <t xml:space="preserve">0.929681360721588</t>
@@ -1565,22 +1565,22 @@
     <t xml:space="preserve">0.927144765853882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906851410865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930949687957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891631662845612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833288788795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802848994731903</t>
+    <t xml:space="preserve">0.906851470470428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930949807167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891631603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833288669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873843669891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802848935127258</t>
   </si>
   <si>
     <t xml:space="preserve">0.755921006202698</t>
@@ -1589,31 +1589,31 @@
     <t xml:space="preserve">0.640503525733948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636698544025421</t>
+    <t xml:space="preserve">0.636698603630066</t>
   </si>
   <si>
     <t xml:space="preserve">0.627019226551056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641852021217346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625670731067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534927368164</t>
+    <t xml:space="preserve">0.641851961612701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625670790672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534986972809</t>
   </si>
   <si>
     <t xml:space="preserve">0.616905987262726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618928611278534</t>
+    <t xml:space="preserve">0.618928670883179</t>
   </si>
   <si>
     <t xml:space="preserve">0.595331132411957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59667956829071</t>
+    <t xml:space="preserve">0.596679508686066</t>
   </si>
   <si>
     <t xml:space="preserve">0.597353756427765</t>
@@ -1625,13 +1625,13 @@
     <t xml:space="preserve">0.602073311805725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598027944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594656944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838055610657</t>
+    <t xml:space="preserve">0.598028004169464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594656884670258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838115215302</t>
   </si>
   <si>
     <t xml:space="preserve">0.593982696533203</t>
@@ -1640,40 +1640,40 @@
     <t xml:space="preserve">0.631064534187317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623648107051849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65398782491684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656684637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637132465839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626344919204712</t>
+    <t xml:space="preserve">0.623648166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.653987765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656684696674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637132406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626344978809357</t>
   </si>
   <si>
     <t xml:space="preserve">0.628367602825165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624322295188904</t>
+    <t xml:space="preserve">0.624322354793549</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716098308563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627693355083466</t>
+    <t xml:space="preserve">0.62769341468811</t>
   </si>
   <si>
     <t xml:space="preserve">0.614883363246918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608815431594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61758017539978</t>
+    <t xml:space="preserve">0.608815491199493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617580235004425</t>
   </si>
   <si>
     <t xml:space="preserve">0.635784029960632</t>
@@ -1682,25 +1682,25 @@
     <t xml:space="preserve">0.624996542930603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614209175109863</t>
+    <t xml:space="preserve">0.614209234714508</t>
   </si>
   <si>
     <t xml:space="preserve">0.605444431304932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606118559837341</t>
+    <t xml:space="preserve">0.606118619441986</t>
   </si>
   <si>
     <t xml:space="preserve">0.630390286445618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643200397491455</t>
+    <t xml:space="preserve">0.64320033788681</t>
   </si>
   <si>
     <t xml:space="preserve">0.656010448932648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633761405944824</t>
+    <t xml:space="preserve">0.633761346340179</t>
   </si>
   <si>
     <t xml:space="preserve">0.61218649148941</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">0.621625483036041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608141183853149</t>
+    <t xml:space="preserve">0.608141303062439</t>
   </si>
   <si>
     <t xml:space="preserve">0.610163867473602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549484610557556</t>
+    <t xml:space="preserve">0.549484670162201</t>
   </si>
   <si>
     <t xml:space="preserve">0.56162041425705</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">0.578475773334503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558923542499542</t>
+    <t xml:space="preserve">0.558923602104187</t>
   </si>
   <si>
     <t xml:space="preserve">0.563643097877502</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">0.569710969924927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558249413967133</t>
+    <t xml:space="preserve">0.558249354362488</t>
   </si>
   <si>
     <t xml:space="preserve">0.562294661998749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573082089424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583869516849518</t>
+    <t xml:space="preserve">0.573082149028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583869457244873</t>
   </si>
   <si>
     <t xml:space="preserve">0.584543704986572</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">0.593308448791504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599376380443573</t>
+    <t xml:space="preserve">0.599376440048218</t>
   </si>
   <si>
     <t xml:space="preserve">0.58656632900238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591285824775696</t>
+    <t xml:space="preserve">0.591285765171051</t>
   </si>
   <si>
     <t xml:space="preserve">0.600050628185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60274749994278</t>
+    <t xml:space="preserve">0.602747559547424</t>
   </si>
   <si>
     <t xml:space="preserve">0.60746705532074</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914705276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618254482746124</t>
+    <t xml:space="preserve">0.587914764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618254423141479</t>
   </si>
   <si>
     <t xml:space="preserve">0.639829337596893</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">0.641177713871002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588589072227478</t>
+    <t xml:space="preserve">0.588589012622833</t>
   </si>
   <si>
     <t xml:space="preserve">0.598702192306519</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">0.622973918914795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609489619731903</t>
+    <t xml:space="preserve">0.609489679336548</t>
   </si>
   <si>
     <t xml:space="preserve">0.615557551383972</t>
@@ -1820,28 +1820,28 @@
     <t xml:space="preserve">0.620951294898987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648594081401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604770123958588</t>
+    <t xml:space="preserve">0.64859402179718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604770243167877</t>
   </si>
   <si>
     <t xml:space="preserve">0.604095995426178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603421747684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639155149459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638480961322784</t>
+    <t xml:space="preserve">0.603421807289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639155030250549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63848090171814</t>
   </si>
   <si>
     <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695789098739624</t>
+    <t xml:space="preserve">0.695789039134979</t>
   </si>
   <si>
     <t xml:space="preserve">0.714667022228241</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">0.699834406375885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.716015577316284</t>
+    <t xml:space="preserve">0.716015517711639</t>
   </si>
   <si>
     <t xml:space="preserve">0.728151381015778</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">0.717363893985748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726802945137024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722757756710052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409261226654</t>
+    <t xml:space="preserve">0.726802885532379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722757637500763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409320831299</t>
   </si>
   <si>
     <t xml:space="preserve">0.711970210075378</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">0.689046919345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683653235435486</t>
+    <t xml:space="preserve">0.683653295040131</t>
   </si>
   <si>
     <t xml:space="preserve">0.679607927799225</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">0.680956363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672191560268402</t>
+    <t xml:space="preserve">0.672191619873047</t>
   </si>
   <si>
     <t xml:space="preserve">0.68500167131424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675562560558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.668146312236786</t>
+    <t xml:space="preserve">0.675562679767609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.668146371841431</t>
   </si>
   <si>
     <t xml:space="preserve">0.631738722324371</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">0.63308721780777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611512243747711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574430525302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589263260364532</t>
+    <t xml:space="preserve">0.611512303352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589263200759888</t>
   </si>
   <si>
     <t xml:space="preserve">0.560271978378296</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">0.553529858589172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538697123527527</t>
+    <t xml:space="preserve">0.538697183132172</t>
   </si>
   <si>
     <t xml:space="preserve">0.527235507965088</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">0.478692084550858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463859438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45846563577652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391044199466705</t>
+    <t xml:space="preserve">0.463859379291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458465665578842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39104425907135</t>
   </si>
   <si>
     <t xml:space="preserve">0.419361233711243</t>
@@ -1970,46 +1970,46 @@
     <t xml:space="preserve">0.380256831645966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403180092573166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412619113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431497067213058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465207874774933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927370548248</t>
+    <t xml:space="preserve">0.403180122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412619143724442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431497097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465207815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927310943604</t>
   </si>
   <si>
     <t xml:space="preserve">0.479366332292557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489479571580887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474646866321564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47329843044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533567428589</t>
+    <t xml:space="preserve">0.48947948217392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474646776914597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473298370838165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533627033234</t>
   </si>
   <si>
     <t xml:space="preserve">0.483411639928818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498918533325195</t>
+    <t xml:space="preserve">0.498918473720551</t>
   </si>
   <si>
     <t xml:space="preserve">0.496895849704742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495547473430634</t>
+    <t xml:space="preserve">0.495547413825989</t>
   </si>
   <si>
     <t xml:space="preserve">0.511054396629333</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">0.482063144445419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490827947854996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484760075807571</t>
+    <t xml:space="preserve">0.490827918052673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484760016202927</t>
   </si>
   <si>
     <t xml:space="preserve">0.48071476817131</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">0.482737392187119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485434263944626</t>
+    <t xml:space="preserve">0.485434204339981</t>
   </si>
   <si>
     <t xml:space="preserve">0.488131076097488</t>
@@ -2039,28 +2039,28 @@
     <t xml:space="preserve">0.481388956308365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472624182701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42745178937912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434868156909943</t>
+    <t xml:space="preserve">0.472624123096466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427451848983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434868186712265</t>
   </si>
   <si>
     <t xml:space="preserve">0.438239276409149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443632930517197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43014869093895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409248024225235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434212237596512</t>
+    <t xml:space="preserve">0.443632960319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430148661136627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409248054027557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434212177991867</t>
   </si>
   <si>
     <t xml:space="preserve">0.410049825906754</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">0.456953287124634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486800938844681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469034522771835</t>
+    <t xml:space="preserve">0.486800909042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469034463167191</t>
   </si>
   <si>
     <t xml:space="preserve">0.446293413639069</t>
@@ -2093,22 +2093,22 @@
     <t xml:space="preserve">0.466191858053207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466902494430542</t>
+    <t xml:space="preserve">0.466902434825897</t>
   </si>
   <si>
     <t xml:space="preserve">0.480405002832413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49888214468956</t>
+    <t xml:space="preserve">0.498882085084915</t>
   </si>
   <si>
     <t xml:space="preserve">0.48822221159935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477562367916107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445582747459412</t>
+    <t xml:space="preserve">0.477562308311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445582687854767</t>
   </si>
   <si>
     <t xml:space="preserve">0.442740082740784</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">0.429237574338913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.447714686393738</t>
+    <t xml:space="preserve">0.447714656591415</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">0.458374559879303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444161415100098</t>
+    <t xml:space="preserve">0.444161355495453</t>
   </si>
   <si>
     <t xml:space="preserve">0.456242650747299</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">0.449846655130386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455531924962997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450778722763</t>
+    <t xml:space="preserve">0.455531865358353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450748920441</t>
   </si>
   <si>
     <t xml:space="preserve">0.430658876895905</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">0.420709669589996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427816241979599</t>
+    <t xml:space="preserve">0.427816212177277</t>
   </si>
   <si>
     <t xml:space="preserve">0.413603127002716</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">0.417156428098679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416445732116699</t>
+    <t xml:space="preserve">0.416445761919022</t>
   </si>
   <si>
     <t xml:space="preserve">0.427105605602264</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">0.437054842710495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432080209255219</t>
+    <t xml:space="preserve">0.432080179452896</t>
   </si>
   <si>
     <t xml:space="preserve">0.434922873973846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.422841727733612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417867064476013</t>
+    <t xml:space="preserve">0.422841668128967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417867034673691</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496524810791</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">0.387308746576309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385176748037338</t>
+    <t xml:space="preserve">0.385176777839661</t>
   </si>
   <si>
     <t xml:space="preserve">0.400100558996201</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">0.382334113121033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370963633060455</t>
+    <t xml:space="preserve">0.370963603258133</t>
   </si>
   <si>
     <t xml:space="preserve">0.383755445480347</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">0.388730019330978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390151381492615</t>
+    <t xml:space="preserve">0.390151411294937</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">0.372384905815125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36385703086853</t>
+    <t xml:space="preserve">0.363857060670853</t>
   </si>
   <si>
     <t xml:space="preserve">0.361725032329559</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">0.351775825023651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065158843994</t>
+    <t xml:space="preserve">0.351065188646317</t>
   </si>
   <si>
     <t xml:space="preserve">0.334009349346161</t>
@@ -2345,16 +2345,16 @@
     <t xml:space="preserve">0.415024399757385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419999033212662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313763380051</t>
+    <t xml:space="preserve">0.419999063014984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313733577728</t>
   </si>
   <si>
     <t xml:space="preserve">0.405785858631134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402232557535172</t>
+    <t xml:space="preserve">0.402232527732849</t>
   </si>
   <si>
     <t xml:space="preserve">0.418577700853348</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">0.392993956804276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391572684049606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39725798368454</t>
+    <t xml:space="preserve">0.391572654247284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397257953882217</t>
   </si>
   <si>
     <t xml:space="preserve">0.40436452627182</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">0.395125985145569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386598110198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380202174186707</t>
+    <t xml:space="preserve">0.386598080396652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380202203989029</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806238174438</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">0.369542270898819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368831604719162</t>
+    <t xml:space="preserve">0.368831634521484</t>
   </si>
   <si>
     <t xml:space="preserve">0.364567697048187</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">0.428526937961578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423552364110947</t>
+    <t xml:space="preserve">0.423552334308624</t>
   </si>
   <si>
     <t xml:space="preserve">0.43634420633316</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">0.471877068281174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478983730077744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492486208677292</t>
+    <t xml:space="preserve">0.478983670473099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492486149072647</t>
   </si>
   <si>
     <t xml:space="preserve">0.515227258205414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512384653091431</t>
+    <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
     <t xml:space="preserve">0.50669938325882</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">0.508120656013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5138059258461</t>
+    <t xml:space="preserve">0.513805866241455</t>
   </si>
   <si>
     <t xml:space="preserve">0.510963261127472</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">0.513095319271088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522333860397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537257611751556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523755192756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525887131690979</t>
+    <t xml:space="preserve">0.522333800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537257552146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523755133152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525887072086334</t>
   </si>
   <si>
     <t xml:space="preserve">0.526597738265991</t>
@@ -2501,19 +2501,19 @@
     <t xml:space="preserve">0.518780529499054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515937924385071</t>
+    <t xml:space="preserve">0.515937864780426</t>
   </si>
   <si>
     <t xml:space="preserve">0.523044466972351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542232275009155</t>
+    <t xml:space="preserve">0.54223221540451</t>
   </si>
   <si>
     <t xml:space="preserve">0.53157240152359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542942941188812</t>
+    <t xml:space="preserve">0.542942881584167</t>
   </si>
   <si>
     <t xml:space="preserve">0.549338817596436</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.537647724151611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531739592552185</t>
+    <t xml:space="preserve">0.53173953294754</t>
   </si>
   <si>
     <t xml:space="preserve">0.526569902896881</t>
@@ -2546,34 +2546,34 @@
     <t xml:space="preserve">0.514753401279449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518446147441864</t>
+    <t xml:space="preserve">0.518446087837219</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533955156803131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544294536113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556849539279938</t>
+    <t xml:space="preserve">0.533955097198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544294476509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556849479675293</t>
   </si>
   <si>
     <t xml:space="preserve">0.546510100364685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553156912326813</t>
+    <t xml:space="preserve">0.553156852722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.56128066778183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.563496291637421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566450357437134</t>
+    <t xml:space="preserve">0.563496232032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566450297832489</t>
   </si>
   <si>
     <t xml:space="preserve">0.57235848903656</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">0.583436489105225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575312674045563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56866592168808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54281747341156</t>
+    <t xml:space="preserve">0.575312614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568665862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542817413806915</t>
   </si>
   <si>
     <t xml:space="preserve">0.548725664615631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536170721054077</t>
+    <t xml:space="preserve">0.536170661449432</t>
   </si>
   <si>
     <t xml:space="preserve">0.527308404445648</t>
@@ -2621,22 +2621,22 @@
     <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511799335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50958377122879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506629645824432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.487427979707718</t>
+    <t xml:space="preserve">0.511799275875092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509583711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506629586219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.487427920103073</t>
   </si>
   <si>
     <t xml:space="preserve">0.488166481256485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483735293149948</t>
+    <t xml:space="preserve">0.483735233545303</t>
   </si>
   <si>
     <t xml:space="preserve">0.488904982805252</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">0.492597639560699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522138774394989</t>
+    <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">0.534693658351898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532478153705597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519923150539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517707586288452</t>
+    <t xml:space="preserve">0.532478094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519923090934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517707526683807</t>
   </si>
   <si>
     <t xml:space="preserve">0.512537837028503</t>
@@ -2693,16 +2693,16 @@
     <t xml:space="preserve">0.515491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508106708526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505152583122253</t>
+    <t xml:space="preserve">0.508106648921967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505152642726898</t>
   </si>
   <si>
     <t xml:space="preserve">0.502198457717896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495551764965057</t>
+    <t xml:space="preserve">0.495551705360413</t>
   </si>
   <si>
     <t xml:space="preserve">0.498505890369415</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">0.545771598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540601909160614</t>
+    <t xml:space="preserve">0.540601849555969</t>
   </si>
   <si>
     <t xml:space="preserve">0.55389541387558</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">0.538386285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530262529850006</t>
+    <t xml:space="preserve">0.530262470245361</t>
   </si>
   <si>
     <t xml:space="preserve">0.539863348007202</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">0.613716065883636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641780078411102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622578382492065</t>
+    <t xml:space="preserve">0.641780138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62257844209671</t>
   </si>
   <si>
     <t xml:space="preserve">0.627009510993958</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">0.612977504730225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61667013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629963576793671</t>
+    <t xml:space="preserve">0.616670191287994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629963636398315</t>
   </si>
   <si>
     <t xml:space="preserve">0.620362818241119</t>
@@ -2777,28 +2777,28 @@
     <t xml:space="preserve">0.599684000015259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589344680309296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600422561168671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607069253921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593037307262421</t>
+    <t xml:space="preserve">0.589344620704651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600422620773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607069313526154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593037247657776</t>
   </si>
   <si>
     <t xml:space="preserve">0.597468495368958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592298746109009</t>
+    <t xml:space="preserve">0.592298805713654</t>
   </si>
   <si>
     <t xml:space="preserve">0.603376626968384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64104151725769</t>
+    <t xml:space="preserve">0.641041576862335</t>
   </si>
   <si>
     <t xml:space="preserve">0.664674401283264</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.667628526687622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648426830768585</t>
+    <t xml:space="preserve">0.64842689037323</t>
   </si>
   <si>
     <t xml:space="preserve">0.647688269615173</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">0.635871827602386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618147194385529</t>
+    <t xml:space="preserve">0.618147253990173</t>
   </si>
   <si>
     <t xml:space="preserve">0.625532507896423</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638825953006744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62627100944519</t>
+    <t xml:space="preserve">0.638826012611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626271069049835</t>
   </si>
   <si>
     <t xml:space="preserve">0.630702137947083</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">0.649903893470764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657289147377014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662458837032318</t>
+    <t xml:space="preserve">0.657289206981659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662458896636963</t>
   </si>
   <si>
     <t xml:space="preserve">0.678706526756287</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">0.635133326053619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576789736747742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604115188121796</t>
+    <t xml:space="preserve">0.576789677143097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
     <t xml:space="preserve">0.587867617607117</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">0.565711796283722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564234793186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.582697927951813</t>
+    <t xml:space="preserve">0.564234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582697868347168</t>
   </si>
   <si>
     <t xml:space="preserve">0.570881485939026</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">0.536909222602844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542078971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567188918590546</t>
+    <t xml:space="preserve">0.542078912258148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567188858985901</t>
   </si>
   <si>
     <t xml:space="preserve">0.5797438621521</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">0.58257657289505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572973668575287</t>
+    <t xml:space="preserve">0.572973728179932</t>
   </si>
   <si>
     <t xml:space="preserve">0.576174676418304</t>
@@ -2978,10 +2978,10 @@
     <t xml:space="preserve">0.560169756412506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.562570512294769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569772720336914</t>
+    <t xml:space="preserve">0.562570571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569772660732269</t>
   </si>
   <si>
     <t xml:space="preserve">0.578575372695923</t>
@@ -2999,31 +2999,31 @@
     <t xml:space="preserve">0.552967607975006</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546565651893616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537762999534607</t>
+    <t xml:space="preserve">0.54656571149826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537762939929962</t>
   </si>
   <si>
     <t xml:space="preserve">0.513755738735199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516156435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525759339332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521758139133453</t>
+    <t xml:space="preserve">0.516156375408173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525759398937225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521758079528809</t>
   </si>
   <si>
     <t xml:space="preserve">0.536962747573853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548166155815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526559591293335</t>
+    <t xml:space="preserve">0.54816609621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52655953168869</t>
   </si>
   <si>
     <t xml:space="preserve">0.522558391094208</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">0.532961547374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524959087371826</t>
+    <t xml:space="preserve">0.524959146976471</t>
   </si>
   <si>
     <t xml:space="preserve">0.508153975009918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484146744012833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48094579577446</t>
+    <t xml:space="preserve">0.504152834415436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484146773815155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480945736169815</t>
   </si>
   <si>
     <t xml:space="preserve">0.5057532787323</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">0.565771520137787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580976128578186</t>
+    <t xml:space="preserve">0.580976068973541</t>
   </si>
   <si>
     <t xml:space="preserve">0.581776320934296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58337676525116</t>
+    <t xml:space="preserve">0.583376824855804</t>
   </si>
   <si>
     <t xml:space="preserve">0.576974868774414</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">0.585777521133423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591379284858704</t>
+    <t xml:space="preserve">0.591379225254059</t>
   </si>
   <si>
     <t xml:space="preserve">0.564170956611633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555368304252625</t>
+    <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
     <t xml:space="preserve">0.567371964454651</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">0.535362303256989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536162495613098</t>
+    <t xml:space="preserve">0.536162555217743</t>
   </si>
   <si>
     <t xml:space="preserve">0.520957887172699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528960347175598</t>
+    <t xml:space="preserve">0.528960287570953</t>
   </si>
   <si>
     <t xml:space="preserve">0.528160095214844</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">0.531361043453217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550566911697388</t>
+    <t xml:space="preserve">0.550566852092743</t>
   </si>
   <si>
     <t xml:space="preserve">0.532161295413971</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">0.527359783649445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512155175209045</t>
+    <t xml:space="preserve">0.51215523481369</t>
   </si>
   <si>
     <t xml:space="preserve">0.534561991691589</t>
@@ -3206,28 +3206,28 @@
     <t xml:space="preserve">0.540163695812225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54736590385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552167356014252</t>
+    <t xml:space="preserve">0.547365963459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557769060134888</t>
+    <t xml:space="preserve">0.557769119739532</t>
   </si>
   <si>
     <t xml:space="preserve">0.548966348171234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559369564056396</t>
+    <t xml:space="preserve">0.559369504451752</t>
   </si>
   <si>
     <t xml:space="preserve">0.556968808174133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558569312095642</t>
+    <t xml:space="preserve">0.558569252490997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584177076816559</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788501739502</t>
+    <t xml:space="preserve">0.621788442134857</t>
   </si>
   <si>
     <t xml:space="preserve">0.62418919801712</t>
@@ -3257,16 +3257,16 @@
     <t xml:space="preserve">0.622588634490967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620187878608704</t>
+    <t xml:space="preserve">0.620187938213348</t>
   </si>
   <si>
     <t xml:space="preserve">0.599381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604183077812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602582693099976</t>
+    <t xml:space="preserve">0.60418313741684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602582633495331</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3281,13 +3281,13 @@
     <t xml:space="preserve">0.616186738014221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62498939037323</t>
+    <t xml:space="preserve">0.624989449977875</t>
   </si>
   <si>
     <t xml:space="preserve">0.628190398216248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636192798614502</t>
+    <t xml:space="preserve">0.636192858219147</t>
   </si>
   <si>
     <t xml:space="preserve">0.640194058418274</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">0.637793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641794443130493</t>
+    <t xml:space="preserve">0.641794502735138</t>
   </si>
   <si>
     <t xml:space="preserve">0.647396206855774</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792042732239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620988249778748</t>
+    <t xml:space="preserve">0.633792102336884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
     <t xml:space="preserve">0.628990650177002</t>
@@ -69357,7 +69357,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909722222</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>34075</v>
@@ -69378,6 +69378,32 @@
         <v>1304</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911574074</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>52671</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>1.0440000295639</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>1.03199994564056</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>1.0440000295639</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -44,61 +44,61 @@
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716715335846</t>
+    <t xml:space="preserve">0.382716774940491</t>
   </si>
   <si>
     <t xml:space="preserve">0.367179751396179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380497187376022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789405345917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3522769510746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368131011724472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387155890464783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936921834946</t>
+    <t xml:space="preserve">0.3804971575737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789345741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352276921272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36813098192215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387155830860138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936951637268</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009611845016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521327972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886854887009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335471600294113</t>
+    <t xml:space="preserve">0.373521387577057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886884689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335471630096436</t>
   </si>
   <si>
     <t xml:space="preserve">0.34561824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361472249031067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341496229171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.355130612850189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352594047784805</t>
+    <t xml:space="preserve">0.361472278833389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341496169567108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.355130642652512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352593988180161</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447429895401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360838085412979</t>
+    <t xml:space="preserve">0.360838145017624</t>
   </si>
   <si>
     <t xml:space="preserve">0.35735023021698</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">0.357984393835068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35069152712822</t>
+    <t xml:space="preserve">0.350691556930542</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">0.291714489459991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297738999128342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275860458612442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276240944862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304461151361465</t>
+    <t xml:space="preserve">0.297739028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27586042881012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276240915060043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304461121559143</t>
   </si>
   <si>
     <t xml:space="preserve">0.326593399047852</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">0.348789066076279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329129993915558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348471969366074</t>
+    <t xml:space="preserve">0.32913002371788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348471939563751</t>
   </si>
   <si>
     <t xml:space="preserve">0.3275445997715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671099185944</t>
+    <t xml:space="preserve">0.314671128988266</t>
   </si>
   <si>
     <t xml:space="preserve">0.330081284046173</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">0.334203332662582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838763952255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356398969888687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368765115737915</t>
+    <t xml:space="preserve">0.386838734149933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35639899969101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368765145540237</t>
   </si>
   <si>
     <t xml:space="preserve">0.325325071811676</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">0.308329522609711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331032544374466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322788387537003</t>
+    <t xml:space="preserve">0.331032514572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322788417339325</t>
   </si>
   <si>
     <t xml:space="preserve">0.319934666156769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309153944253922</t>
+    <t xml:space="preserve">0.309153914451599</t>
   </si>
   <si>
     <t xml:space="preserve">0.331666678190231</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.310802757740021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323422610759735</t>
+    <t xml:space="preserve">0.323422580957413</t>
   </si>
   <si>
     <t xml:space="preserve">0.308836847543716</t>
@@ -206,31 +206,31 @@
     <t xml:space="preserve">0.298880487680435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285880208015442</t>
+    <t xml:space="preserve">0.285880148410797</t>
   </si>
   <si>
     <t xml:space="preserve">0.267743170261383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260767370462418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489463090897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258738070726395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288543671369553</t>
+    <t xml:space="preserve">0.260767340660095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489492893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288543701171875</t>
   </si>
   <si>
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643067121506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367496877908707</t>
+    <t xml:space="preserve">0.364643096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36749678850174</t>
   </si>
   <si>
     <t xml:space="preserve">0.369716376066208</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">0.38779005408287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033472776413</t>
+    <t xml:space="preserve">0.370033532381058</t>
   </si>
   <si>
     <t xml:space="preserve">0.357033163309097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374155551195145</t>
+    <t xml:space="preserve">0.3741554915905</t>
   </si>
   <si>
     <t xml:space="preserve">0.377643436193466</t>
@@ -260,91 +260,91 @@
     <t xml:space="preserve">0.370984673500061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372253090143204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387472957372665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377326428890228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439791262149811</t>
+    <t xml:space="preserve">0.372253030538559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387472927570343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377326339483261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439791291952133</t>
   </si>
   <si>
     <t xml:space="preserve">0.453425735235214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454059958457947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46166980266571</t>
+    <t xml:space="preserve">0.454059928655624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461669832468033</t>
   </si>
   <si>
     <t xml:space="preserve">0.459133237600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455645352602005</t>
+    <t xml:space="preserve">0.455645322799683</t>
   </si>
   <si>
     <t xml:space="preserve">0.456279516220093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464840680360794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47879222035408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485767990350723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47784098982811</t>
+    <t xml:space="preserve">0.464840650558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792250156403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485767960548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477841019630432</t>
   </si>
   <si>
     <t xml:space="preserve">0.483231395483017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484816789627075</t>
+    <t xml:space="preserve">0.484816819429398</t>
   </si>
   <si>
     <t xml:space="preserve">0.497817128896713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489255905151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475621402263641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476889759302139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488304615020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493695080280304</t>
+    <t xml:space="preserve">0.489255964756012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475621432065964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476889699697495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304704427719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493695050477982</t>
   </si>
   <si>
     <t xml:space="preserve">0.489890098571777</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496548771858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645721673965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084717988968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495280474424362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486719280481339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484182566404343</t>
+    <t xml:space="preserve">0.496548742055893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46864578127861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084807395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49528044462204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486719220876694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48418265581131</t>
   </si>
   <si>
     <t xml:space="preserve">0.497500002384186</t>
@@ -353,52 +353,52 @@
     <t xml:space="preserve">0.507329523563385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507963716983795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514939427375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183215141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515890717506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354372501373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525720238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529525101184845</t>
+    <t xml:space="preserve">0.50796365737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514939486980438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183274745941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515890777111053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354312896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525720179080963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52952516078949</t>
   </si>
   <si>
     <t xml:space="preserve">0.535866856575012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540305912494659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620844423770905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625917732715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627503275871277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597697615623474</t>
+    <t xml:space="preserve">0.540305972099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620844483375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625917911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627503216266632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597697556018829</t>
   </si>
   <si>
     <t xml:space="preserve">0.596112191677094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577087342739105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561867475509644</t>
+    <t xml:space="preserve">0.57708740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561867415904999</t>
   </si>
   <si>
     <t xml:space="preserve">0.583428978919983</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">0.569160282611847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566940784454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559013724327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551720917224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529208123683929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516841948032379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476141452789</t>
+    <t xml:space="preserve">0.566940665245056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559013783931732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551720857620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529208064079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516842007637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476081848145</t>
   </si>
   <si>
     <t xml:space="preserve">0.516207814216614</t>
@@ -437,34 +437,34 @@
     <t xml:space="preserve">0.549184203147888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547281801700592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558379590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585965633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586599767208099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613868772983551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654455006122589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.665870010852814</t>
+    <t xml:space="preserve">0.547281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585965573787689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586599707603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613868713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654455065727234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.665869951248169</t>
   </si>
   <si>
     <t xml:space="preserve">0.655089199542999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623064160346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63384485244751</t>
+    <t xml:space="preserve">0.62306410074234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633844792842865</t>
   </si>
   <si>
     <t xml:space="preserve">0.62211287021637</t>
@@ -473,34 +473,34 @@
     <t xml:space="preserve">0.618942022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615137100219727</t>
+    <t xml:space="preserve">0.615137040615082</t>
   </si>
   <si>
     <t xml:space="preserve">0.631625294685364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628771543502808</t>
+    <t xml:space="preserve">0.628771603107452</t>
   </si>
   <si>
     <t xml:space="preserve">0.63416188955307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629088580608368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643674314022064</t>
+    <t xml:space="preserve">0.629088521003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643674373626709</t>
   </si>
   <si>
     <t xml:space="preserve">0.644308507442474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645576775074005</t>
+    <t xml:space="preserve">0.64557683467865</t>
   </si>
   <si>
     <t xml:space="preserve">0.636064350605011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634796142578125</t>
+    <t xml:space="preserve">0.634796023368835</t>
   </si>
   <si>
     <t xml:space="preserve">0.628454446792603</t>
@@ -515,34 +515,34 @@
     <t xml:space="preserve">0.626234829425812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602453827857971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58818519115448</t>
+    <t xml:space="preserve">0.602453768253326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588185250759125</t>
   </si>
   <si>
     <t xml:space="preserve">0.590087652206421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58913642168045</t>
+    <t xml:space="preserve">0.589136481285095</t>
   </si>
   <si>
     <t xml:space="preserve">0.619893252849579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592941462993622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600551307201385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595795094966888</t>
+    <t xml:space="preserve">0.592941343784332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60055136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595795154571533</t>
   </si>
   <si>
     <t xml:space="preserve">0.594526767730713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591673016548157</t>
+    <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
     <t xml:space="preserve">0.601185500621796</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">0.603087961673737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609746634960175</t>
+    <t xml:space="preserve">0.609746694564819</t>
   </si>
   <si>
     <t xml:space="preserve">0.611332058906555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614185750484467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611966252326965</t>
+    <t xml:space="preserve">0.614185810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61196631193161</t>
   </si>
   <si>
     <t xml:space="preserve">0.605941712856293</t>
@@ -569,58 +569,58 @@
     <t xml:space="preserve">0.598648905754089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593258500099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588502287864685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380518913269</t>
+    <t xml:space="preserve">0.593258440494537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588502168655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380459308624</t>
   </si>
   <si>
     <t xml:space="preserve">0.617673695087433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611015021800995</t>
+    <t xml:space="preserve">0.61101508140564</t>
   </si>
   <si>
     <t xml:space="preserve">0.604039192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605307519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61006373167038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649524688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039501667023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61038076877594</t>
+    <t xml:space="preserve">0.605307638645172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610063791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649405479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039561271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610380828380585</t>
   </si>
   <si>
     <t xml:space="preserve">0.596429288387299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591355979442596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589770555496216</t>
+    <t xml:space="preserve">0.591355919837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589770615100861</t>
   </si>
   <si>
     <t xml:space="preserve">0.56535530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523183524608612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481963038444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493377953767776</t>
+    <t xml:space="preserve">0.523183643817902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481963068246841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493377923965454</t>
   </si>
   <si>
     <t xml:space="preserve">0.492109656333923</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">0.508280813694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513988196849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509231984615326</t>
+    <t xml:space="preserve">0.513988256454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509232044219971</t>
   </si>
   <si>
     <t xml:space="preserve">0.509549081325531</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">0.53047639131546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546013355255127</t>
+    <t xml:space="preserve">0.546013414859772</t>
   </si>
   <si>
     <t xml:space="preserve">0.54094010591507</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">0.538720548152924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539037644863129</t>
+    <t xml:space="preserve">0.539037585258484</t>
   </si>
   <si>
     <t xml:space="preserve">0.533330142498016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532061874866486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568843185901642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570428609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566306591033936</t>
+    <t xml:space="preserve">0.532061815261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568843245506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570428669452667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566306531429291</t>
   </si>
   <si>
     <t xml:space="preserve">0.549501240253448</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">0.56440407037735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550452530384064</t>
+    <t xml:space="preserve">0.550452470779419</t>
   </si>
   <si>
     <t xml:space="preserve">0.542842626571655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545062124729156</t>
+    <t xml:space="preserve">0.545062184333801</t>
   </si>
   <si>
     <t xml:space="preserve">0.521281123161316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516524791717529</t>
+    <t xml:space="preserve">0.516524851322174</t>
   </si>
   <si>
     <t xml:space="preserve">0.50669538974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528256893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519695639610291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526037275791168</t>
+    <t xml:space="preserve">0.528256773948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519695699214935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526037395000458</t>
   </si>
   <si>
     <t xml:space="preserve">0.51874440908432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511451542377472</t>
+    <t xml:space="preserve">0.511451661586761</t>
   </si>
   <si>
     <t xml:space="preserve">0.514305293560028</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">0.523817718029022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508597791194916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522549450397491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513671100139618</t>
+    <t xml:space="preserve">0.508597850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522549390792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513671159744263</t>
   </si>
   <si>
     <t xml:space="preserve">0.511134505271912</t>
@@ -752,46 +752,46 @@
     <t xml:space="preserve">0.505109965801239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510500311851501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499719649553299</t>
+    <t xml:space="preserve">0.510500371456146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499719619750977</t>
   </si>
   <si>
     <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541574239730835</t>
+    <t xml:space="preserve">0.54157429933548</t>
   </si>
   <si>
     <t xml:space="preserve">0.550769627094269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55362343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560282051563263</t>
+    <t xml:space="preserve">0.553623378276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560281991958618</t>
   </si>
   <si>
     <t xml:space="preserve">0.569794476032257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575501918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627820372581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658894240856171</t>
+    <t xml:space="preserve">0.575501978397369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627820312976837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658894300460815</t>
   </si>
   <si>
     <t xml:space="preserve">0.655723392963409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262523174286</t>
+    <t xml:space="preserve">0.682358145713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262582778931</t>
   </si>
   <si>
     <t xml:space="preserve">0.736896097660065</t>
@@ -800,43 +800,43 @@
     <t xml:space="preserve">0.707724750041962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696943938732147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733091115951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748945295810699</t>
+    <t xml:space="preserve">0.696943879127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733091235160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748945236206055</t>
   </si>
   <si>
     <t xml:space="preserve">0.747676908969879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754652857780457</t>
+    <t xml:space="preserve">0.754652678966522</t>
   </si>
   <si>
     <t xml:space="preserve">0.755286872386932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760360181331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81806892156601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799678206443787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771140813827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.768604159355164</t>
+    <t xml:space="preserve">0.760360062122345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818068861961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799678146839142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771140873432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.768604278564453</t>
   </si>
   <si>
     <t xml:space="preserve">0.720407962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727383732795715</t>
+    <t xml:space="preserve">0.727383673191071</t>
   </si>
   <si>
     <t xml:space="preserve">0.740701019763947</t>
@@ -845,19 +845,19 @@
     <t xml:space="preserve">0.73816454410553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774945914745331</t>
+    <t xml:space="preserve">0.774945855140686</t>
   </si>
   <si>
     <t xml:space="preserve">0.78382408618927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801580667495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849776864051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884021699428558</t>
+    <t xml:space="preserve">0.801580607891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849776983261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884021759033203</t>
   </si>
   <si>
     <t xml:space="preserve">0.851045310497284</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">0.878314197063446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894168198108673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876319408417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924608051776886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887826681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.901778280735016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.881484925746918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412474155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87514340877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896070837974548</t>
+    <t xml:space="preserve">0.894168317317963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876557826996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924607932567596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88782662153244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.901778221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.881485044956207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412354946136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875143468379974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896070778369904</t>
   </si>
   <si>
     <t xml:space="preserve">0.9106565117836</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">0.913827300071716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9100221991539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729201793671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892899870872498</t>
+    <t xml:space="preserve">0.910022258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889729082584381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892900109291077</t>
   </si>
   <si>
     <t xml:space="preserve">0.895436525344849</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">0.867533564567566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.875777542591095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868167698383331</t>
+    <t xml:space="preserve">0.87577760219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868167459964752</t>
   </si>
   <si>
     <t xml:space="preserve">0.756555140018463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788897335529327</t>
+    <t xml:space="preserve">0.788897395133972</t>
   </si>
   <si>
     <t xml:space="preserve">0.812995493412018</t>
@@ -938,85 +938,85 @@
     <t xml:space="preserve">0.80728816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838362157344818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790165841579437</t>
+    <t xml:space="preserve">0.838362097740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790165722370148</t>
   </si>
   <si>
     <t xml:space="preserve">0.786360800266266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811727225780487</t>
+    <t xml:space="preserve">0.811727285385132</t>
   </si>
   <si>
     <t xml:space="preserve">0.830117881298065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814898014068604</t>
+    <t xml:space="preserve">0.814897954463959</t>
   </si>
   <si>
     <t xml:space="preserve">0.792702376842499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803483009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804117262363434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776848316192627</t>
+    <t xml:space="preserve">0.803483128547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804117381572723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776848375797272</t>
   </si>
   <si>
     <t xml:space="preserve">0.780019223690033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781921625137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.791433990001678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785092413425446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786995053291321</t>
+    <t xml:space="preserve">0.781921684741974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.791434109210968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78509247303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786994993686676</t>
   </si>
   <si>
     <t xml:space="preserve">0.793970704078674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789531588554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77367752790451</t>
+    <t xml:space="preserve">0.789531648159027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.773677468299866</t>
   </si>
   <si>
     <t xml:space="preserve">0.775580108165741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769872605800629</t>
+    <t xml:space="preserve">0.769872546195984</t>
   </si>
   <si>
     <t xml:space="preserve">0.767335951328278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77177494764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628448963165</t>
+    <t xml:space="preserve">0.771775007247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76162850856781</t>
   </si>
   <si>
     <t xml:space="preserve">0.795873165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811093032360077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843435168266296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654535770416</t>
+    <t xml:space="preserve">0.811093151569366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654595375061</t>
   </si>
   <si>
     <t xml:space="preserve">0.872606754302979</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">0.862460076808929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866899311542511</t>
+    <t xml:space="preserve">0.866899251937866</t>
   </si>
   <si>
     <t xml:space="preserve">0.840264558792114</t>
@@ -1034,52 +1034,52 @@
     <t xml:space="preserve">0.830752074718475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855484366416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801153659821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142789840698</t>
+    <t xml:space="preserve">0.855484306812286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801213264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142730236053</t>
   </si>
   <si>
     <t xml:space="preserve">0.820605516433716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.824410498142242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826947093009949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806019842624664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799044013023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804751455783844</t>
+    <t xml:space="preserve">0.824410438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826947033405304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806019723415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799043953418732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804751396179199</t>
   </si>
   <si>
     <t xml:space="preserve">0.785726547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.778750836849213</t>
+    <t xml:space="preserve">0.778750777244568</t>
   </si>
   <si>
     <t xml:space="preserve">0.777482450008392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802214741706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806654036045074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807922303676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854850292205811</t>
+    <t xml:space="preserve">0.802214801311493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665385723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80792236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854850232601166</t>
   </si>
   <si>
     <t xml:space="preserve">0.857386887073517</t>
@@ -1088,25 +1088,25 @@
     <t xml:space="preserve">0.852313637733459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86372846364975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.864996910095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.850411117076874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840898633003235</t>
+    <t xml:space="preserve">0.863728523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86499685049057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.850411057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84089869260788</t>
   </si>
   <si>
     <t xml:space="preserve">0.834557056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.838996231555939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581346035004</t>
+    <t xml:space="preserve">0.838996171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581226825714</t>
   </si>
   <si>
     <t xml:space="preserve">0.826312959194183</t>
@@ -1121,52 +1121,52 @@
     <t xml:space="preserve">0.818703055381775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819337248802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796507358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809190630912781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809824645519257</t>
+    <t xml:space="preserve">0.81933718919754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796507477760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809190511703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809824824333191</t>
   </si>
   <si>
     <t xml:space="preserve">0.797775685787201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798409819602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817434728145599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823142051696777</t>
+    <t xml:space="preserve">0.798409879207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817434787750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823142111301422</t>
   </si>
   <si>
     <t xml:space="preserve">0.812361419200897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819971323013306</t>
+    <t xml:space="preserve">0.819971263408661</t>
   </si>
   <si>
     <t xml:space="preserve">0.797141492366791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.716602861881256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7045539021492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736262023448944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240914106369</t>
+    <t xml:space="preserve">0.716602921485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704553842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736261963844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759725987911224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77240926027298</t>
   </si>
   <si>
     <t xml:space="preserve">0.776214182376862</t>
@@ -1175,52 +1175,52 @@
     <t xml:space="preserve">0.78445827960968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783189833164215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752115905284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760994374752045</t>
+    <t xml:space="preserve">0.78318989276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752116024494171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7609943151474</t>
   </si>
   <si>
     <t xml:space="preserve">0.757823467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766701757907867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790799856185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810458898544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311780929565</t>
+    <t xml:space="preserve">0.766701698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790799915790558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810458838939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311661720276</t>
   </si>
   <si>
     <t xml:space="preserve">0.781287431716919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.79523903131485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800312340259552</t>
+    <t xml:space="preserve">0.795238971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800312280654907</t>
   </si>
   <si>
     <t xml:space="preserve">0.815532267093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.764799296855927</t>
+    <t xml:space="preserve">0.764799177646637</t>
   </si>
   <si>
     <t xml:space="preserve">0.731822848320007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711529612541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.693773031234741</t>
+    <t xml:space="preserve">0.711529672145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.693773090839386</t>
   </si>
   <si>
     <t xml:space="preserve">0.739432752132416</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">0.703919649124146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695041477680206</t>
+    <t xml:space="preserve">0.695041418075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.683626472949982</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">0.684894859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670943200588226</t>
+    <t xml:space="preserve">0.670943260192871</t>
   </si>
   <si>
     <t xml:space="preserve">0.69123649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678553283214569</t>
+    <t xml:space="preserve">0.678553223609924</t>
   </si>
   <si>
     <t xml:space="preserve">0.687431514263153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717871308326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730554521083832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710261225700378</t>
+    <t xml:space="preserve">0.717871189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730554461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710261285305023</t>
   </si>
   <si>
     <t xml:space="preserve">0.697578132152557</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">0.714066326618195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.729286134243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753384292125702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748311102390289</t>
+    <t xml:space="preserve">0.729286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753384232521057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748310983181</t>
   </si>
   <si>
     <t xml:space="preserve">0.757189333438873</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">0.763530969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">0.749579429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042655944824</t>
+    <t xml:space="preserve">0.74957948923111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042775154114</t>
   </si>
   <si>
     <t xml:space="preserve">0.735627830028534</t>
@@ -1304,40 +1304,40 @@
     <t xml:space="preserve">0.741969347000122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744506180286407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722944498062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.700114667415619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456303596497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846459388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725481331348419</t>
+    <t xml:space="preserve">0.744506061077118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722944557666779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700114727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456422805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846399784088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72548121213913</t>
   </si>
   <si>
     <t xml:space="preserve">0.71533465385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.712797939777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.692504823207855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705188095569611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.681089818477631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701383054256439</t>
+    <t xml:space="preserve">0.712797999382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69250476360321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705187976360321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68108993768692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701383113861084</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">0.686163246631622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.679821610450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672211647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64684522151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.677284896373749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658259987831116</t>
+    <t xml:space="preserve">0.679821670055389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672211587429047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.646845161914825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.677284836769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65826004743576</t>
   </si>
   <si>
     <t xml:space="preserve">0.659528374671936</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">0.648113429546356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641771852970123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635430157184601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643040239810944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639235198497772</t>
+    <t xml:space="preserve">0.641771733760834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635430216789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643040180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639235258102417</t>
   </si>
   <si>
     <t xml:space="preserve">0.637966930866241</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">0.609429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598014652729034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599917054176331</t>
+    <t xml:space="preserve">0.59801459312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599917113780975</t>
   </si>
   <si>
     <t xml:space="preserve">0.603722155094147</t>
@@ -1409,25 +1409,25 @@
     <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478736400604</t>
+    <t xml:space="preserve">0.621478676795959</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615771174430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6233811378479</t>
+    <t xml:space="preserve">0.622747004032135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615771234035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623381078243256</t>
   </si>
   <si>
     <t xml:space="preserve">0.612600386142731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591038882732391</t>
+    <t xml:space="preserve">0.591038942337036</t>
   </si>
   <si>
     <t xml:space="preserve">0.584063112735748</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">0.580892324447632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565672397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570745646953583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561233282089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572648286819458</t>
+    <t xml:space="preserve">0.56567245721817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570745706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561233222484589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572648227214813</t>
   </si>
   <si>
     <t xml:space="preserve">0.559965014457703</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">0.537135183811188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528891026973724</t>
+    <t xml:space="preserve">0.528891086578369</t>
   </si>
   <si>
     <t xml:space="preserve">0.573282361030579</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">0.569477438926697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608795464038849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307888507843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630356967449188</t>
+    <t xml:space="preserve">0.608795404434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307828903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356907844543</t>
   </si>
   <si>
     <t xml:space="preserve">0.604990482330322</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">0.580258131027222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572014033794403</t>
+    <t xml:space="preserve">0.572014093399048</t>
   </si>
   <si>
     <t xml:space="preserve">0.568209111690521</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">0.629722774028778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721676170825958</t>
+    <t xml:space="preserve">0.721676290035248</t>
   </si>
   <si>
     <t xml:space="preserve">0.766067504882812</t>
@@ -1508,88 +1508,88 @@
     <t xml:space="preserve">0.873875081539154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753312587738</t>
+    <t xml:space="preserve">0.871338427066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753372192383</t>
   </si>
   <si>
     <t xml:space="preserve">0.880216717720032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903046548366547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92207133769989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937291443347931</t>
+    <t xml:space="preserve">0.903046607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922071397304535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93729156255722</t>
   </si>
   <si>
     <t xml:space="preserve">0.918266475200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866265118122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896705031394958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87641179561615</t>
+    <t xml:space="preserve">0.86626523733139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630424976349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896704912185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876411736011505</t>
   </si>
   <si>
     <t xml:space="preserve">0.868801772594452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.870070159435272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559651374817</t>
+    <t xml:space="preserve">0.870070040225983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559591770172</t>
   </si>
   <si>
     <t xml:space="preserve">0.934754610061646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.904314875602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583143234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929681360721588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144765853882</t>
+    <t xml:space="preserve">0.904314815998077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583202838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929681301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144706249237</t>
   </si>
   <si>
     <t xml:space="preserve">0.906851470470428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930949807167053</t>
+    <t xml:space="preserve">0.930949687957764</t>
   </si>
   <si>
     <t xml:space="preserve">0.891631603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873843669891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802848935127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755921006202698</t>
+    <t xml:space="preserve">0.833288788795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802849054336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755921065807343</t>
   </si>
   <si>
     <t xml:space="preserve">0.640503525733948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636698603630066</t>
+    <t xml:space="preserve">0.636698484420776</t>
   </si>
   <si>
     <t xml:space="preserve">0.627019226551056</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">0.641851961612701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625670790672302</t>
+    <t xml:space="preserve">0.625670731067657</t>
   </si>
   <si>
     <t xml:space="preserve">0.613534986972809</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">0.616905987262726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618928670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595331132411957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596679508686066</t>
+    <t xml:space="preserve">0.618928611278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595331251621246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59667956829071</t>
   </si>
   <si>
     <t xml:space="preserve">0.597353756427765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596005320549011</t>
+    <t xml:space="preserve">0.596005380153656</t>
   </si>
   <si>
     <t xml:space="preserve">0.602073311805725</t>
@@ -1628,34 +1628,34 @@
     <t xml:space="preserve">0.598028004169464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594656884670258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838115215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593982696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631064534187317</t>
+    <t xml:space="preserve">0.594656944274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838055610657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593982756137848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631064474582672</t>
   </si>
   <si>
     <t xml:space="preserve">0.623648166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653987765312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656684696674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637132406234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626344978809357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628367602825165</t>
+    <t xml:space="preserve">0.65398782491684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656684637069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637132465839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626345098018646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
     <t xml:space="preserve">0.624322354793549</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">0.608815491199493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617580235004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635784029960632</t>
+    <t xml:space="preserve">0.61758029460907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635783910751343</t>
   </si>
   <si>
     <t xml:space="preserve">0.624996542930603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614209234714508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605444431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606118619441986</t>
+    <t xml:space="preserve">0.614209175109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605444371700287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606118500232697</t>
   </si>
   <si>
     <t xml:space="preserve">0.630390286445618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64320033788681</t>
+    <t xml:space="preserve">0.643200397491455</t>
   </si>
   <si>
     <t xml:space="preserve">0.656010448932648</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">0.621625483036041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608141303062439</t>
+    <t xml:space="preserve">0.608141243457794</t>
   </si>
   <si>
     <t xml:space="preserve">0.610163867473602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549484670162201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56162041425705</t>
+    <t xml:space="preserve">0.549484610557556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561620354652405</t>
   </si>
   <si>
     <t xml:space="preserve">0.552855670452118</t>
@@ -1730,70 +1730,70 @@
     <t xml:space="preserve">0.578475773334503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558923602104187</t>
+    <t xml:space="preserve">0.558923542499542</t>
   </si>
   <si>
     <t xml:space="preserve">0.563643097877502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569710969924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249354362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562294661998749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573082149028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583869457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584543704986572</t>
+    <t xml:space="preserve">0.569711029529572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249413967133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562294721603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583869516849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584543764591217</t>
   </si>
   <si>
     <t xml:space="preserve">0.567014157772064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566339910030365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593308448791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599376440048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58656632900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591285765171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600050628185272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602747559547424</t>
+    <t xml:space="preserve">0.56633996963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593308568000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599376499652863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586566388607025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591285884380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600050568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602747440338135</t>
   </si>
   <si>
     <t xml:space="preserve">0.60746705532074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590611636638641</t>
+    <t xml:space="preserve">0.590611696243286</t>
   </si>
   <si>
     <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914764881134</t>
+    <t xml:space="preserve">0.587914824485779</t>
   </si>
   <si>
     <t xml:space="preserve">0.618254423141479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639829337596893</t>
+    <t xml:space="preserve">0.639829277992249</t>
   </si>
   <si>
     <t xml:space="preserve">0.641177713871002</t>
@@ -1808,31 +1808,31 @@
     <t xml:space="preserve">0.620277106761932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622973918914795</t>
+    <t xml:space="preserve">0.62297397851944</t>
   </si>
   <si>
     <t xml:space="preserve">0.609489679336548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615557551383972</t>
+    <t xml:space="preserve">0.615557610988617</t>
   </si>
   <si>
     <t xml:space="preserve">0.620951294898987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64859402179718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604770243167877</t>
+    <t xml:space="preserve">0.64859414100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604770183563232</t>
   </si>
   <si>
     <t xml:space="preserve">0.604095995426178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603421807289124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639155030250549</t>
+    <t xml:space="preserve">0.603421747684479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
     <t xml:space="preserve">0.63848090171814</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">0.695789039134979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714667022228241</t>
+    <t xml:space="preserve">0.714667081832886</t>
   </si>
   <si>
     <t xml:space="preserve">0.702531278133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.699834406375885</t>
+    <t xml:space="preserve">0.69983434677124</t>
   </si>
   <si>
     <t xml:space="preserve">0.716015517711639</t>
@@ -1859,16 +1859,16 @@
     <t xml:space="preserve">0.728151381015778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717363893985748</t>
+    <t xml:space="preserve">0.717363953590393</t>
   </si>
   <si>
     <t xml:space="preserve">0.726802885532379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722757637500763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409320831299</t>
+    <t xml:space="preserve">0.722757697105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409201622009</t>
   </si>
   <si>
     <t xml:space="preserve">0.711970210075378</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">0.689046919345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683653295040131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679607927799225</t>
+    <t xml:space="preserve">0.683653235435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67960798740387</t>
   </si>
   <si>
     <t xml:space="preserve">0.680956363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672191619873047</t>
+    <t xml:space="preserve">0.672191560268402</t>
   </si>
   <si>
     <t xml:space="preserve">0.68500167131424</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">0.675562679767609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.668146371841431</t>
+    <t xml:space="preserve">0.668146312236786</t>
   </si>
   <si>
     <t xml:space="preserve">0.631738722324371</t>
@@ -1919,28 +1919,28 @@
     <t xml:space="preserve">0.636458277702332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63308721780777</t>
+    <t xml:space="preserve">0.633087158203125</t>
   </si>
   <si>
     <t xml:space="preserve">0.611512303352356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589263200759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560271978378296</t>
+    <t xml:space="preserve">0.574430584907532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589263260364532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560272037982941</t>
   </si>
   <si>
     <t xml:space="preserve">0.553529858589172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538697183132172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527235507965088</t>
+    <t xml:space="preserve">0.538697242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527235567569733</t>
   </si>
   <si>
     <t xml:space="preserve">0.478692084550858</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">0.463859379291534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458465665578842</t>
+    <t xml:space="preserve">0.458465605974197</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104425907135</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">0.394415289163589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387673169374466</t>
+    <t xml:space="preserve">0.387673139572144</t>
   </si>
   <si>
     <t xml:space="preserve">0.388347387313843</t>
@@ -1973,43 +1973,43 @@
     <t xml:space="preserve">0.403180122375488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412619143724442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431497097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465207815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927310943604</t>
+    <t xml:space="preserve">0.412619084119797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431497126817703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46520784497261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927340745926</t>
   </si>
   <si>
     <t xml:space="preserve">0.479366332292557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48947948217392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474646776914597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473298370838165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533627033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411639928818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498918473720551</t>
+    <t xml:space="preserve">0.489479511976242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474646866321564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473298400640488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533597230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411610126495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918533325195</t>
   </si>
   <si>
     <t xml:space="preserve">0.496895849704742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495547413825989</t>
+    <t xml:space="preserve">0.495547443628311</t>
   </si>
   <si>
     <t xml:space="preserve">0.511054396629333</t>
@@ -2021,34 +2021,34 @@
     <t xml:space="preserve">0.490827918052673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484760016202927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48071476817131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482737392187119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485434204339981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488131076097488</t>
+    <t xml:space="preserve">0.484760075807571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480714738368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482737362384796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485434234142303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488131105899811</t>
   </si>
   <si>
     <t xml:space="preserve">0.481388956308365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472624123096466</t>
+    <t xml:space="preserve">0.472624182701111</t>
   </si>
   <si>
     <t xml:space="preserve">0.427451848983765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434868186712265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438239276409149</t>
+    <t xml:space="preserve">0.434868156909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438239216804504</t>
   </si>
   <si>
     <t xml:space="preserve">0.443632960319519</t>
@@ -2057,22 +2057,22 @@
     <t xml:space="preserve">0.430148661136627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409248054027557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434212177991867</t>
+    <t xml:space="preserve">0.409248024225235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434212148189545</t>
   </si>
   <si>
     <t xml:space="preserve">0.410049825906754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412892460823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449136018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4512679874897</t>
+    <t xml:space="preserve">0.412892401218414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449135988950729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451267927885056</t>
   </si>
   <si>
     <t xml:space="preserve">0.456953287124634</t>
@@ -2084,37 +2084,37 @@
     <t xml:space="preserve">0.469034463167191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446293413639069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453399956226349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466191858053207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466902434825897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480405002832413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498882085084915</t>
+    <t xml:space="preserve">0.446293383836746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453399986028671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46619176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46690246462822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48040497303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498882114887238</t>
   </si>
   <si>
     <t xml:space="preserve">0.48822221159935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.477562308311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445582687854767</t>
+    <t xml:space="preserve">0.477562338113785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445582717657089</t>
   </si>
   <si>
     <t xml:space="preserve">0.442740082740784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452689319849014</t>
+    <t xml:space="preserve">0.452689349651337</t>
   </si>
   <si>
     <t xml:space="preserve">0.447004050016403</t>
@@ -2129,16 +2129,16 @@
     <t xml:space="preserve">0.442029386758804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429948270320892</t>
+    <t xml:space="preserve">0.42994824051857</t>
   </si>
   <si>
     <t xml:space="preserve">0.438476115465164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429237574338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447714656591415</t>
+    <t xml:space="preserve">0.429237514734268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447714686393738</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
@@ -2150,37 +2150,37 @@
     <t xml:space="preserve">0.458374559879303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444161355495453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456242650747299</t>
+    <t xml:space="preserve">0.444161385297775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456242561340332</t>
   </si>
   <si>
     <t xml:space="preserve">0.449846655130386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455531865358353</t>
+    <t xml:space="preserve">0.455531895160675</t>
   </si>
   <si>
     <t xml:space="preserve">0.443450748920441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430658876895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420709669589996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427816212177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413603127002716</t>
+    <t xml:space="preserve">0.430658936500549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420709639787674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427816241979599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413603097200394</t>
   </si>
   <si>
     <t xml:space="preserve">0.417156428098679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.416445761919022</t>
+    <t xml:space="preserve">0.416445732116699</t>
   </si>
   <si>
     <t xml:space="preserve">0.427105605602264</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">0.437054842710495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432080179452896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434922873973846</t>
+    <t xml:space="preserve">0.432080209255219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434922814369202</t>
   </si>
   <si>
     <t xml:space="preserve">0.422841668128967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417867034673691</t>
+    <t xml:space="preserve">0.417867064476013</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496524810791</t>
@@ -2207,37 +2207,37 @@
     <t xml:space="preserve">0.407917827367783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397968590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403653889894485</t>
+    <t xml:space="preserve">0.397968620061874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403653919696808</t>
   </si>
   <si>
     <t xml:space="preserve">0.401521891355515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405075192451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40081125497818</t>
+    <t xml:space="preserve">0.405075162649155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400811225175858</t>
   </si>
   <si>
     <t xml:space="preserve">0.387308746576309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385176777839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400100558996201</t>
+    <t xml:space="preserve">0.385176748037338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400100588798523</t>
   </si>
   <si>
     <t xml:space="preserve">0.41573503613472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398679226636887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409339129924774</t>
+    <t xml:space="preserve">0.398679256439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409339159727097</t>
   </si>
   <si>
     <t xml:space="preserve">0.395836621522903</t>
@@ -2246,28 +2246,28 @@
     <t xml:space="preserve">0.382334113121033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370963603258133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383755445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366699606180191</t>
+    <t xml:space="preserve">0.370963633060455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383755475282669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366699635982513</t>
   </si>
   <si>
     <t xml:space="preserve">0.363146334886551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353907823562622</t>
+    <t xml:space="preserve">0.3539077937603</t>
   </si>
   <si>
     <t xml:space="preserve">0.356750428676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359593063592911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358882397413254</t>
+    <t xml:space="preserve">0.359593033790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358882427215576</t>
   </si>
   <si>
     <t xml:space="preserve">0.370252966880798</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">0.372384905815125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363857060670853</t>
+    <t xml:space="preserve">0.36385703086853</t>
   </si>
   <si>
     <t xml:space="preserve">0.361725032329559</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">0.355329126119614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353552460670471</t>
+    <t xml:space="preserve">0.353552490472794</t>
   </si>
   <si>
     <t xml:space="preserve">0.354618489742279</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">0.351775825023651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065188646317</t>
+    <t xml:space="preserve">0.351065158843994</t>
   </si>
   <si>
     <t xml:space="preserve">0.334009349346161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32334953546524</t>
+    <t xml:space="preserve">0.323349505662918</t>
   </si>
   <si>
     <t xml:space="preserve">0.342181950807571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337207347154617</t>
+    <t xml:space="preserve">0.337207317352295</t>
   </si>
   <si>
     <t xml:space="preserve">0.337562680244446</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">0.343958586454391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361014395952225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36030375957489</t>
+    <t xml:space="preserve">0.361014425754547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360303729772568</t>
   </si>
   <si>
     <t xml:space="preserve">0.389440715312958</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">0.396547317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412181794643402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.421420365571976</t>
+    <t xml:space="preserve">0.41218176484108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421420305967331</t>
   </si>
   <si>
     <t xml:space="preserve">0.415024399757385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419999063014984</t>
+    <t xml:space="preserve">0.419999003410339</t>
   </si>
   <si>
     <t xml:space="preserve">0.414313733577728</t>
@@ -2360,25 +2360,25 @@
     <t xml:space="preserve">0.418577700853348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419288337230682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399389863014221</t>
+    <t xml:space="preserve">0.419288367033005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399389922618866</t>
   </si>
   <si>
     <t xml:space="preserve">0.393704652786255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392993956804276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391572654247284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397257953882217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.40436452627182</t>
+    <t xml:space="preserve">0.392993986606598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391572684049606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39725798368454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404364556074142</t>
   </si>
   <si>
     <t xml:space="preserve">0.395125985145569</t>
@@ -2387,13 +2387,13 @@
     <t xml:space="preserve">0.386598080396652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380202203989029</t>
+    <t xml:space="preserve">0.380202174186707</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806238174438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369542270898819</t>
+    <t xml:space="preserve">0.369542241096497</t>
   </si>
   <si>
     <t xml:space="preserve">0.368831634521484</t>
@@ -2402,19 +2402,19 @@
     <t xml:space="preserve">0.364567697048187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428526937961578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423552334308624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43634420633316</t>
+    <t xml:space="preserve">0.428526878356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423552364110947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436344116926193</t>
   </si>
   <si>
     <t xml:space="preserve">0.42639496922493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440608114004135</t>
+    <t xml:space="preserve">0.440608084201813</t>
   </si>
   <si>
     <t xml:space="preserve">0.439897477626801</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">0.464770525693893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471877068281174</t>
+    <t xml:space="preserve">0.471877038478851</t>
   </si>
   <si>
     <t xml:space="preserve">0.478983670473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492486149072647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515227258205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512384593486786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50669938325882</t>
+    <t xml:space="preserve">0.492486208677292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515227198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512384653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506699323654175</t>
   </si>
   <si>
     <t xml:space="preserve">0.517359137535095</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">0.508120656013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513805866241455</t>
+    <t xml:space="preserve">0.5138059258461</t>
   </si>
   <si>
     <t xml:space="preserve">0.510963261127472</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">0.507409989833832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513095319271088</t>
+    <t xml:space="preserve">0.513095200061798</t>
   </si>
   <si>
     <t xml:space="preserve">0.522333800792694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537257552146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523755133152008</t>
+    <t xml:space="preserve">0.537257611751556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523755073547363</t>
   </si>
   <si>
     <t xml:space="preserve">0.525887072086334</t>
@@ -2474,25 +2474,25 @@
     <t xml:space="preserve">0.526597738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525176465511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.530151069164276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524465799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53867894411087</t>
+    <t xml:space="preserve">0.525176525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.530151009559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52446573972702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538679003715515</t>
   </si>
   <si>
     <t xml:space="preserve">0.544364213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541521608829498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536547005176544</t>
+    <t xml:space="preserve">0.541521549224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536546945571899</t>
   </si>
   <si>
     <t xml:space="preserve">0.528729736804962</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">0.549338817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564973294734955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550941288471222</t>
+    <t xml:space="preserve">0.5649733543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550941228866577</t>
   </si>
   <si>
     <t xml:space="preserve">0.549464225769043</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.537647724151611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53173953294754</t>
+    <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
     <t xml:space="preserve">0.526569902896881</t>
@@ -2543,16 +2543,16 @@
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753401279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518446087837219</t>
+    <t xml:space="preserve">0.514753460884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533955097198486</t>
+    <t xml:space="preserve">0.533955156803131</t>
   </si>
   <si>
     <t xml:space="preserve">0.544294476509094</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">0.563496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566450297832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57235848903656</t>
+    <t xml:space="preserve">0.566450417041779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572358548641205</t>
   </si>
   <si>
     <t xml:space="preserve">0.581220924854279</t>
@@ -2585,28 +2585,28 @@
     <t xml:space="preserve">0.584174990653992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583436489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575312614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568665862083435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542817413806915</t>
+    <t xml:space="preserve">0.58343642950058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575312674045563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56866592168808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54281747341156</t>
   </si>
   <si>
     <t xml:space="preserve">0.548725664615631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536170661449432</t>
+    <t xml:space="preserve">0.536170721054077</t>
   </si>
   <si>
     <t xml:space="preserve">0.527308404445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522877275943756</t>
+    <t xml:space="preserve">0.522877216339111</t>
   </si>
   <si>
     <t xml:space="preserve">0.53543221950531</t>
@@ -2618,37 +2618,37 @@
     <t xml:space="preserve">0.51696902513504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511060774326324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511799275875092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509583711624146</t>
+    <t xml:space="preserve">0.511060833930969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511799335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50958377122879</t>
   </si>
   <si>
     <t xml:space="preserve">0.506629586219788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487427920103073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488166481256485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735233545303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488904982805252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480781227350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481519728899002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492597639560699</t>
+    <t xml:space="preserve">0.487427949905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48816642165184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735263347626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488905012607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48078116774559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48151969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492597579956055</t>
   </si>
   <si>
     <t xml:space="preserve">0.522138714790344</t>
@@ -2660,22 +2660,22 @@
     <t xml:space="preserve">0.534693658351898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532478094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519923090934753</t>
+    <t xml:space="preserve">0.532478153705597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519923150539398</t>
   </si>
   <si>
     <t xml:space="preserve">0.517707526683807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512537837028503</t>
+    <t xml:space="preserve">0.512537896633148</t>
   </si>
   <si>
     <t xml:space="preserve">0.514014840126038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525092840194702</t>
+    <t xml:space="preserve">0.525092899799347</t>
   </si>
   <si>
     <t xml:space="preserve">0.545033037662506</t>
@@ -2684,49 +2684,49 @@
     <t xml:space="preserve">0.528785467147827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533216655254364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52066171169281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515491962432861</t>
+    <t xml:space="preserve">0.533216595649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520661592483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515491902828217</t>
   </si>
   <si>
     <t xml:space="preserve">0.508106648921967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505152642726898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502198457717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495551705360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498505890369415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502936959266663</t>
+    <t xml:space="preserve">0.505152583122253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50219851732254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495551735162735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498505830764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502937018871307</t>
   </si>
   <si>
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721395015717</t>
+    <t xml:space="preserve">0.500721454620361</t>
   </si>
   <si>
     <t xml:space="preserve">0.545771598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540601849555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55389541387558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550202786922455</t>
+    <t xml:space="preserve">0.540601909160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.553895354270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55020272731781</t>
   </si>
   <si>
     <t xml:space="preserve">0.547987163066864</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">0.539863348007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613716065883636</t>
+    <t xml:space="preserve">0.613716006278992</t>
   </si>
   <si>
     <t xml:space="preserve">0.641780138015747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62257844209671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627009510993958</t>
+    <t xml:space="preserve">0.622578382492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
     <t xml:space="preserve">0.612977504730225</t>
@@ -2771,16 +2771,16 @@
     <t xml:space="preserve">0.601161062717438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5945143699646</t>
+    <t xml:space="preserve">0.594514429569244</t>
   </si>
   <si>
     <t xml:space="preserve">0.599684000015259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589344620704651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600422620773315</t>
+    <t xml:space="preserve">0.589344680309296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600422561168671</t>
   </si>
   <si>
     <t xml:space="preserve">0.607069313526154</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">0.597468495368958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592298805713654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603376626968384</t>
+    <t xml:space="preserve">0.592298746109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603376686573029</t>
   </si>
   <si>
     <t xml:space="preserve">0.641041576862335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.666890025138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658766210079193</t>
+    <t xml:space="preserve">0.664674460887909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6668900847435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658766269683838</t>
   </si>
   <si>
     <t xml:space="preserve">0.653596520423889</t>
@@ -2816,19 +2816,19 @@
     <t xml:space="preserve">0.667628526687622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64842689037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647688269615173</t>
+    <t xml:space="preserve">0.648426830768585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647688329219818</t>
   </si>
   <si>
     <t xml:space="preserve">0.639564514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629225075244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642518639564514</t>
+    <t xml:space="preserve">0.629225134849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642518579959869</t>
   </si>
   <si>
     <t xml:space="preserve">0.640303015708923</t>
@@ -2837,88 +2837,88 @@
     <t xml:space="preserve">0.63365626335144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675752341747284</t>
+    <t xml:space="preserve">0.675752401351929</t>
   </si>
   <si>
     <t xml:space="preserve">0.649165391921997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65581214427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655073642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635871827602386</t>
+    <t xml:space="preserve">0.655812084674835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655073583126068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635871887207031</t>
   </si>
   <si>
     <t xml:space="preserve">0.618147253990173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625532507896423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.638087451457977</t>
+    <t xml:space="preserve">0.625532567501068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638087511062622</t>
   </si>
   <si>
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638826012611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626271069049835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702137947083</t>
+    <t xml:space="preserve">0.638825953006744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62627100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702197551727</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657289206981659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.662458896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678706526756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676490902900696</t>
+    <t xml:space="preserve">0.657289147377014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.662458837032318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678706407546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676490843296051</t>
   </si>
   <si>
     <t xml:space="preserve">0.673536777496338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661720335483551</t>
+    <t xml:space="preserve">0.661720395088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.635133326053619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576789677143097</t>
+    <t xml:space="preserve">0.576789736747742</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587867617607117</t>
+    <t xml:space="preserve">0.587867677211761</t>
   </si>
   <si>
     <t xml:space="preserve">0.507368147373199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711796283722</t>
+    <t xml:space="preserve">0.529523909091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711736679077</t>
   </si>
   <si>
     <t xml:space="preserve">0.564234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582697868347168</t>
+    <t xml:space="preserve">0.582697927951813</t>
   </si>
   <si>
     <t xml:space="preserve">0.570881485939026</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">0.536909222602844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542078912258148</t>
+    <t xml:space="preserve">0.542078971862793</t>
   </si>
   <si>
     <t xml:space="preserve">0.567188858985901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5797438621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562019169330597</t>
+    <t xml:space="preserve">0.579743802547455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562019109725952</t>
   </si>
   <si>
     <t xml:space="preserve">0.557588040828705</t>
@@ -2951,37 +2951,37 @@
     <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555372476577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569404482841492</t>
+    <t xml:space="preserve">0.555372416973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569404423236847</t>
   </si>
   <si>
     <t xml:space="preserve">0.574574112892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58257657289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973728179932</t>
+    <t xml:space="preserve">0.582576513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973668575287</t>
   </si>
   <si>
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572912693024</t>
+    <t xml:space="preserve">0.570572972297668</t>
   </si>
   <si>
     <t xml:space="preserve">0.568172216415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560169756412506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562570571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569772660732269</t>
+    <t xml:space="preserve">0.560169816017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562570512294769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569772720336914</t>
   </si>
   <si>
     <t xml:space="preserve">0.578575372695923</t>
@@ -3002,28 +3002,28 @@
     <t xml:space="preserve">0.54656571149826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537762939929962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516156375408173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525759398937225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521758079528809</t>
+    <t xml:space="preserve">0.537762999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755679130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516156435012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525759339332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521758139133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.536962747573853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54816609621048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52655953168869</t>
+    <t xml:space="preserve">0.548166155815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526559591293335</t>
   </si>
   <si>
     <t xml:space="preserve">0.522558391094208</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">0.532961547374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524959146976471</t>
+    <t xml:space="preserve">0.524959087371826</t>
   </si>
   <si>
     <t xml:space="preserve">0.508153975009918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504152834415436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484146773815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480945736169815</t>
+    <t xml:space="preserve">0.504152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484146744012833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480945765972137</t>
   </si>
   <si>
     <t xml:space="preserve">0.5057532787323</t>
@@ -3053,22 +3053,22 @@
     <t xml:space="preserve">0.493749648332596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487347722053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488147974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561770260334015</t>
+    <t xml:space="preserve">0.48734775185585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48814794421196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56177031993866</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58897852897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568972408771515</t>
+    <t xml:space="preserve">0.588978469371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568972527980804</t>
   </si>
   <si>
     <t xml:space="preserve">0.572173416614532</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">0.577775120735168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565771520137787</t>
+    <t xml:space="preserve">0.565771460533142</t>
   </si>
   <si>
     <t xml:space="preserve">0.580976068973541</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">0.581776320934296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583376824855804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576974868774414</t>
+    <t xml:space="preserve">0.58337676525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576974928379059</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">0.586577773094177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585777521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591379225254059</t>
+    <t xml:space="preserve">0.585777580738068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591379284858704</t>
   </si>
   <si>
     <t xml:space="preserve">0.564170956611633</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567371964454651</t>
+    <t xml:space="preserve">0.567371904850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">0.543364703655243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542564392089844</t>
+    <t xml:space="preserve">0.542564451694489</t>
   </si>
   <si>
     <t xml:space="preserve">0.535362303256989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536162555217743</t>
+    <t xml:space="preserve">0.536162495613098</t>
   </si>
   <si>
     <t xml:space="preserve">0.520957887172699</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">0.516956686973572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515356242656708</t>
+    <t xml:space="preserve">0.515356183052063</t>
   </si>
   <si>
     <t xml:space="preserve">0.508954226970673</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554730892181</t>
+    <t xml:space="preserve">0.510554790496826</t>
   </si>
   <si>
     <t xml:space="preserve">0.524158835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529760539531708</t>
+    <t xml:space="preserve">0.529760599136353</t>
   </si>
   <si>
     <t xml:space="preserve">0.531361043453217</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">0.530560791492462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527359783649445</t>
+    <t xml:space="preserve">0.527359843254089</t>
   </si>
   <si>
     <t xml:space="preserve">0.51215523481369</t>
@@ -3206,25 +3206,25 @@
     <t xml:space="preserve">0.540163695812225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547365963459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552167415618896</t>
+    <t xml:space="preserve">0.54736590385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552167356014252</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557769119739532</t>
+    <t xml:space="preserve">0.557769060134888</t>
   </si>
   <si>
     <t xml:space="preserve">0.548966348171234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559369504451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556968808174133</t>
+    <t xml:space="preserve">0.559369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556968748569489</t>
   </si>
   <si>
     <t xml:space="preserve">0.558569252490997</t>
@@ -3236,25 +3236,25 @@
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773920536041</t>
+    <t xml:space="preserve">0.573773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612185478210449</t>
+    <t xml:space="preserve">0.612185537815094</t>
   </si>
   <si>
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788442134857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62418919801712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622588634490967</t>
+    <t xml:space="preserve">0.621788501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624189138412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622588694095612</t>
   </si>
   <si>
     <t xml:space="preserve">0.620187938213348</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602582633495331</t>
+    <t xml:space="preserve">0.602582693099976</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">0.640194058418274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643395006656647</t>
+    <t xml:space="preserve">0.643394947052002</t>
   </si>
   <si>
     <t xml:space="preserve">0.637793302536011</t>
@@ -3308,55 +3308,58 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792102336884</t>
+    <t xml:space="preserve">0.633792042732239</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
+    <t xml:space="preserve">0.628990709781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635921716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651516497135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641986310482025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631589770317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627257883548737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615128636360168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262163639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663043498993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197629451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615995049476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62119323015213</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635921716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651516437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64198637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631589770317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627257883548737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615128576755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663103103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197569847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464803218842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615994989871979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621193289756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64025354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723416805267</t>
+    <t xml:space="preserve">0.640253603458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723357200623</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3365,22 +3368,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732096195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61946052312851</t>
+    <t xml:space="preserve">0.604732036590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619460463523865</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395869731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331156730652</t>
+    <t xml:space="preserve">0.612529456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395810127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331216335297</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3389,13 +3392,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620326936244965</t>
+    <t xml:space="preserve">0.62032687664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801089286804</t>
+    <t xml:space="preserve">0.597801029682159</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3410,7 +3413,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658763408661</t>
+    <t xml:space="preserve">0.624658823013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3425,10 +3428,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727696895599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861343383789</t>
+    <t xml:space="preserve">0.617727756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861402988434</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3449,7 +3452,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387130737305</t>
+    <t xml:space="preserve">0.639387190341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3476,13 +3479,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382850646973</t>
+    <t xml:space="preserve">0.652382910251617</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848443508148</t>
+    <t xml:space="preserve">0.655848383903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3515,10 +3518,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042284488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687038004398346</t>
+    <t xml:space="preserve">0.674042344093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3533,13 +3536,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68270605802536</t>
+    <t xml:space="preserve">0.682706117630005</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637124538422</t>
+    <t xml:space="preserve">0.689637184143066</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3563,13 +3566,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739886999130249</t>
+    <t xml:space="preserve">0.739887058734894</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412965297699</t>
+    <t xml:space="preserve">0.762412905693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3584,7 +3587,7 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779740452766418</t>
+    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.76846718788147</t>
@@ -3696,9 +3699,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.787256062030792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -53723,7 +53723,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53749,7 +53749,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1898" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53775,7 +53775,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1899" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53801,7 +53801,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1900" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53827,7 +53827,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1901" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53879,7 +53879,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1903" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53905,7 +53905,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53931,7 +53931,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1905" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53957,7 +53957,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1906" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54009,7 +54009,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1908" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54061,7 +54061,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1910" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54087,7 +54087,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1911" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54113,7 +54113,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1912" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54139,7 +54139,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1913" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54217,7 +54217,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1916" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54269,7 +54269,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1918" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54295,7 +54295,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1919" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54347,7 +54347,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1921" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54399,7 +54399,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1923" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54425,7 +54425,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1924" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54503,7 +54503,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1927" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54529,7 +54529,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1928" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54555,7 +54555,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1929" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54581,7 +54581,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1930" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54685,7 +54685,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1934" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54737,7 +54737,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1936" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54763,7 +54763,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1937" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54789,7 +54789,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1938" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54867,7 +54867,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1941" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54893,7 +54893,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1942" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54919,7 +54919,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1943" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54997,7 +54997,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G1946" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55049,7 +55049,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1948" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55075,7 +55075,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1949" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55101,7 +55101,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1950" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55127,7 +55127,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1951" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55153,7 +55153,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1952" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55179,7 +55179,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1953" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55205,7 +55205,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1954" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55231,7 +55231,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1955" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55283,7 +55283,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1957" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55309,7 +55309,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1958" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55335,7 +55335,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1959" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -55361,7 +55361,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1960" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -55517,7 +55517,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1966" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -55543,7 +55543,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1967" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -55569,7 +55569,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1968" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -55595,7 +55595,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1969" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -55621,7 +55621,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1970" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -55673,7 +55673,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1972" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -55699,7 +55699,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1973" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55725,7 +55725,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1974" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55751,7 +55751,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1975" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55777,7 +55777,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1976" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55803,7 +55803,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1977" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55829,7 +55829,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1978" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55855,7 +55855,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1979" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55881,7 +55881,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1980" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55907,7 +55907,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1981" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55933,7 +55933,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1982" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55959,7 +55959,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1983" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55985,7 +55985,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1984" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56011,7 +56011,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1985" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56063,7 +56063,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1987" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56089,7 +56089,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56115,7 +56115,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1989" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56141,7 +56141,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1990" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56167,7 +56167,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1991" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56193,7 +56193,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1992" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56219,7 +56219,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1993" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56245,7 +56245,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1994" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56297,7 +56297,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1996" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56323,7 +56323,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1997" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -56375,7 +56375,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1999" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -56427,7 +56427,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2001" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -56453,7 +56453,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2002" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -56609,7 +56609,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2008" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -56635,7 +56635,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G2009" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -56661,7 +56661,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G2010" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -56713,7 +56713,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2012" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56739,7 +56739,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2013" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56765,7 +56765,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2014" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56791,7 +56791,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2015" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56817,7 +56817,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G2016" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56843,7 +56843,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G2017" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56921,7 +56921,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2020" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56947,7 +56947,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G2021" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56973,7 +56973,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G2022" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56999,7 +56999,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G2023" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57025,7 +57025,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2024" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57051,7 +57051,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G2025" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57077,7 +57077,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2026" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57103,7 +57103,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G2027" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57129,7 +57129,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2028" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57155,7 +57155,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2029" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57181,7 +57181,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2030" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57259,7 +57259,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2033" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57285,7 +57285,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2034" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57363,7 +57363,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2037" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -57389,7 +57389,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G2038" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -57415,7 +57415,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2039" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -57441,7 +57441,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2040" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -57467,7 +57467,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2041" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -57493,7 +57493,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2042" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -57519,7 +57519,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G2043" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -57545,7 +57545,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2044" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57571,7 +57571,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2045" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -57597,7 +57597,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2046" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -57623,7 +57623,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2047" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -57649,7 +57649,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2048" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -57675,7 +57675,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2049" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -57701,7 +57701,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2050" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57727,7 +57727,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2051" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57753,7 +57753,7 @@
         <v>0.75</v>
       </c>
       <c r="G2052" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57779,7 +57779,7 @@
         <v>0.75</v>
       </c>
       <c r="G2053" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57805,7 +57805,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G2054" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57831,7 +57831,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2055" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57857,7 +57857,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2056" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57883,7 +57883,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2057" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57909,7 +57909,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2058" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57935,7 +57935,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2059" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57961,7 +57961,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G2060" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57987,7 +57987,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2061" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58013,7 +58013,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2062" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58039,7 +58039,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2063" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58065,7 +58065,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G2064" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58091,7 +58091,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2065" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58117,7 +58117,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2066" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58169,7 +58169,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2068" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58195,7 +58195,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G2069" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58221,7 +58221,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2070" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58247,7 +58247,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G2071" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58273,7 +58273,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G2072" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58325,7 +58325,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2074" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -58351,7 +58351,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2075" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -58403,7 +58403,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2077" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -58429,7 +58429,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2078" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -58455,7 +58455,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2079" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -58507,7 +58507,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2081" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -58533,7 +58533,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2082" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -58585,7 +58585,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2084" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -58611,7 +58611,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2085" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -58637,7 +58637,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2086" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -58663,7 +58663,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G2087" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -58689,7 +58689,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2088" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58715,7 +58715,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G2089" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58741,7 +58741,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G2090" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58767,7 +58767,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2091" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58793,7 +58793,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2092" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58819,7 +58819,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G2093" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58845,7 +58845,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G2094" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58871,7 +58871,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G2095" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58897,7 +58897,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2096" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58923,7 +58923,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2097" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58949,7 +58949,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G2098" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58975,7 +58975,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2099" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59001,7 +59001,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2100" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59027,7 +59027,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G2101" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59053,7 +59053,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2102" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59079,7 +59079,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2103" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59105,7 +59105,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2104" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59131,7 +59131,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2105" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59157,7 +59157,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2106" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59183,7 +59183,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2107" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59209,7 +59209,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2108" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59235,7 +59235,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2109" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59261,7 +59261,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G2110" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59287,7 +59287,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2111" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59313,7 +59313,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2112" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -59339,7 +59339,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2113" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -59365,7 +59365,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2114" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -59391,7 +59391,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2115" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -59417,7 +59417,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2116" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -59443,7 +59443,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2117" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -59469,7 +59469,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G2118" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -59495,7 +59495,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2119" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -59521,7 +59521,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2120" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -59547,7 +59547,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G2121" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -59573,7 +59573,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2122" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -59599,7 +59599,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2123" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -59625,7 +59625,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2124" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -59651,7 +59651,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2125" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -59677,7 +59677,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2126" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -59703,7 +59703,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2127" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59729,7 +59729,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2128" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59755,7 +59755,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2129" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59781,7 +59781,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2130" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59807,7 +59807,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G2131" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59833,7 +59833,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2132" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59859,7 +59859,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2133" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59885,7 +59885,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G2134" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59911,7 +59911,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2135" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59937,7 +59937,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G2136" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59963,7 +59963,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2137" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59989,7 +59989,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2138" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60015,7 +60015,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G2139" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60041,7 +60041,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2140" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60067,7 +60067,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2141" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60093,7 +60093,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2142" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60119,7 +60119,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2143" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60145,7 +60145,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2144" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60171,7 +60171,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2145" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60197,7 +60197,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2146" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60223,7 +60223,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2147" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60249,7 +60249,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2148" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60275,7 +60275,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2149" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60301,7 +60301,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2150" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60327,7 +60327,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2151" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -60353,7 +60353,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2152" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -60379,7 +60379,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2153" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -60405,7 +60405,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2154" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -60431,7 +60431,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2155" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -60457,7 +60457,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2156" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -60483,7 +60483,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2157" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -60509,7 +60509,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2158" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -60535,7 +60535,7 @@
         <v>0.75</v>
       </c>
       <c r="G2159" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -60561,7 +60561,7 @@
         <v>0.75</v>
       </c>
       <c r="G2160" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -60587,7 +60587,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2161" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -60613,7 +60613,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2162" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -60639,7 +60639,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2163" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -60665,7 +60665,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2164" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -60691,7 +60691,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2165" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60717,7 +60717,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2166" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60743,7 +60743,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2167" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60769,7 +60769,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2168" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60795,7 +60795,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G2169" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60821,7 +60821,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2170" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60847,7 +60847,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2171" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60873,7 +60873,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2172" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60899,7 +60899,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2173" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60925,7 +60925,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2174" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60951,7 +60951,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2175" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60977,7 +60977,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2176" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61003,7 +61003,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2177" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61029,7 +61029,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2178" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61055,7 +61055,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2179" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61081,7 +61081,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G2180" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61107,7 +61107,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2181" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61133,7 +61133,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2182" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61159,7 +61159,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2183" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61185,7 +61185,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2184" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61211,7 +61211,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2185" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61237,7 +61237,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G2186" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61263,7 +61263,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2187" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61289,7 +61289,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G2188" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61315,7 +61315,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2189" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -61341,7 +61341,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2190" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -61367,7 +61367,7 @@
         <v>0.75</v>
       </c>
       <c r="G2191" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -61393,7 +61393,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G2192" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -61419,7 +61419,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2193" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -61445,7 +61445,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2194" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -61471,7 +61471,7 @@
         <v>0.75</v>
       </c>
       <c r="G2195" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -61497,7 +61497,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2196" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -61523,7 +61523,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G2197" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -61549,7 +61549,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2198" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -61575,7 +61575,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2199" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -61601,7 +61601,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2200" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -61627,7 +61627,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G2201" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -61653,7 +61653,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G2202" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -61679,7 +61679,7 @@
         <v>0.75</v>
       </c>
       <c r="G2203" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -61705,7 +61705,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2204" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61731,7 +61731,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2205" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61757,7 +61757,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2206" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61783,7 +61783,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G2207" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61809,7 +61809,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2208" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61835,7 +61835,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2209" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61861,7 +61861,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2210" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61887,7 +61887,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2211" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61913,7 +61913,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2212" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61939,7 +61939,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G2213" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61965,7 +61965,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2214" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61991,7 +61991,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G2215" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62017,7 +62017,7 @@
         <v>0.75</v>
       </c>
       <c r="G2216" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62043,7 +62043,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2217" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62069,7 +62069,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2218" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62095,7 +62095,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2219" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62121,7 +62121,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2220" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62147,7 +62147,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2221" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62173,7 +62173,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G2222" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62199,7 +62199,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G2223" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62225,7 +62225,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G2224" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62251,7 +62251,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2225" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62277,7 +62277,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G2226" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62303,7 +62303,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2227" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62329,7 +62329,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -62355,7 +62355,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2229" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -62381,7 +62381,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G2230" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -62407,7 +62407,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2231" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -62433,7 +62433,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G2232" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -62459,7 +62459,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2233" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -62485,7 +62485,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2234" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -62511,7 +62511,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2235" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -62537,7 +62537,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2236" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -62563,7 +62563,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2237" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -62589,7 +62589,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2238" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -62615,7 +62615,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2239" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -62641,7 +62641,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2240" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -62667,7 +62667,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G2241" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -62693,7 +62693,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2242" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62719,7 +62719,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2243" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62745,7 +62745,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2244" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62771,7 +62771,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G2245" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62797,7 +62797,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G2246" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62823,7 +62823,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G2247" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62849,7 +62849,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62875,7 +62875,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2249" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62901,7 +62901,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2250" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62927,7 +62927,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2251" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62953,7 +62953,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2252" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62979,7 +62979,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2253" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63005,7 +63005,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2254" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63031,7 +63031,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2255" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63057,7 +63057,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G2256" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63083,7 +63083,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2257" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63109,7 +63109,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2258" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63135,7 +63135,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2259" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63161,7 +63161,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2260" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63187,7 +63187,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G2261" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63213,7 +63213,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G2262" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63239,7 +63239,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1228</v>
+        <v>1191</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -69383,7 +69383,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6911574074</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>52671</v>
@@ -69404,6 +69404,32 @@
         <v>1351</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6911111111</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>107045</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>1.03799998760223</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>1.02799999713898</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>1.03799998760223</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>1.03400003910065</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="1354">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594666719437</t>
+    <t xml:space="preserve">0.378594636917114</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716774940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367179751396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3804971575737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789345741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352276921272278</t>
+    <t xml:space="preserve">0.382716715335846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367179721593857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380497127771378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789405345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3522769510746</t>
   </si>
   <si>
     <t xml:space="preserve">0.36813098192215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387155830860138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936951637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390009611845016</t>
+    <t xml:space="preserve">0.387155801057816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936862230301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390009582042694</t>
   </si>
   <si>
     <t xml:space="preserve">0.373521387577057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359886884689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335471630096436</t>
+    <t xml:space="preserve">0.359886854887009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335471600294113</t>
   </si>
   <si>
     <t xml:space="preserve">0.34561824798584</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">0.341496169567108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355130642652512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352593988180161</t>
+    <t xml:space="preserve">0.355130672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352594017982483</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447429895401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360838145017624</t>
+    <t xml:space="preserve">0.360838115215302</t>
   </si>
   <si>
     <t xml:space="preserve">0.35735023021698</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">0.357984393835068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350691556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317080944776535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291714489459991</t>
+    <t xml:space="preserve">0.350691497325897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317080974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291714459657669</t>
   </si>
   <si>
     <t xml:space="preserve">0.297739028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27586042881012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276240915060043</t>
+    <t xml:space="preserve">0.275860458612442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276240944862366</t>
   </si>
   <si>
     <t xml:space="preserve">0.304461121559143</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">0.348789066076279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32913002371788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348471939563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3275445997715</t>
+    <t xml:space="preserve">0.329130053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348471909761429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.327544629573822</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671128988266</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">0.334203332662582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386838734149933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35639899969101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368765145540237</t>
+    <t xml:space="preserve">0.386838763952255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356398969888687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368765115737915</t>
   </si>
   <si>
     <t xml:space="preserve">0.325325071811676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318032175302505</t>
+    <t xml:space="preserve">0.318032205104828</t>
   </si>
   <si>
     <t xml:space="preserve">0.306236773729324</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.331032514572144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322788417339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319934666156769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153914451599</t>
+    <t xml:space="preserve">0.322788387537003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319934695959091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153974056244</t>
   </si>
   <si>
     <t xml:space="preserve">0.331666678190231</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">0.308836847543716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.306300193071365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880487680435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285880148410797</t>
+    <t xml:space="preserve">0.306300222873688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880517482758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28588017821312</t>
   </si>
   <si>
     <t xml:space="preserve">0.267743170261383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.260767340660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489492893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.258738040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288543701171875</t>
+    <t xml:space="preserve">0.260767370462418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489463090897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258738070726395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288543671369553</t>
   </si>
   <si>
     <t xml:space="preserve">0.371618896722794</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">0.364643096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36749678850174</t>
+    <t xml:space="preserve">0.367496848106384</t>
   </si>
   <si>
     <t xml:space="preserve">0.369716376066208</t>
@@ -239,22 +239,22 @@
     <t xml:space="preserve">0.369399309158325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388741225004196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38779005408287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370033532381058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357033163309097</t>
+    <t xml:space="preserve">0.388741254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387790024280548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370033472776413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35703319311142</t>
   </si>
   <si>
     <t xml:space="preserve">0.3741554915905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377643436193466</t>
+    <t xml:space="preserve">0.377643406391144</t>
   </si>
   <si>
     <t xml:space="preserve">0.370984673500061</t>
@@ -269,85 +269,85 @@
     <t xml:space="preserve">0.377326339483261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439791291952133</t>
+    <t xml:space="preserve">0.439791262149811</t>
   </si>
   <si>
     <t xml:space="preserve">0.453425735235214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454059928655624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.461669832468033</t>
+    <t xml:space="preserve">0.454059958457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.461669862270355</t>
   </si>
   <si>
     <t xml:space="preserve">0.459133237600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455645322799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456279516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840650558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792250156403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485767960548401</t>
+    <t xml:space="preserve">0.455645263195038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45627948641777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840680360794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485768049955368</t>
   </si>
   <si>
     <t xml:space="preserve">0.477841019630432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483231395483017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484816819429398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497817128896713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489255964756012</t>
+    <t xml:space="preserve">0.483231365680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484816759824753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497817099094391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48925593495369</t>
   </si>
   <si>
     <t xml:space="preserve">0.475621432065964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476889699697495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488304704427719</t>
+    <t xml:space="preserve">0.476889729499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304644823074</t>
   </si>
   <si>
     <t xml:space="preserve">0.493695050477982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489890098571777</t>
+    <t xml:space="preserve">0.48989000916481</t>
   </si>
   <si>
     <t xml:space="preserve">0.496548742055893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46864578127861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084807395935</t>
+    <t xml:space="preserve">0.468645662069321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084717988968</t>
   </si>
   <si>
     <t xml:space="preserve">0.49528044462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486719220876694</t>
+    <t xml:space="preserve">0.486719280481339</t>
   </si>
   <si>
     <t xml:space="preserve">0.48418265581131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497500002384186</t>
+    <t xml:space="preserve">0.497500091791153</t>
   </si>
   <si>
     <t xml:space="preserve">0.507329523563385</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">0.510183274745941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515890777111053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354312896729</t>
+    <t xml:space="preserve">0.515890598297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354432106018</t>
   </si>
   <si>
     <t xml:space="preserve">0.525720179080963</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">0.52952516078949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535866856575012</t>
+    <t xml:space="preserve">0.535866796970367</t>
   </si>
   <si>
     <t xml:space="preserve">0.540305972099304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620844483375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625917911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627503216266632</t>
+    <t xml:space="preserve">0.620844542980194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625917732715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627503156661987</t>
   </si>
   <si>
     <t xml:space="preserve">0.597697556018829</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">0.596112191677094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57708740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561867415904999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583428978919983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569160282611847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566940665245056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559013783931732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551720857620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529208064079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516842007637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517476081848145</t>
+    <t xml:space="preserve">0.577087342739105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561867475509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428919315338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569160342216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566940784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559013724327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551720917224884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529208123683929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516841948032379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517476141452789</t>
   </si>
   <si>
     <t xml:space="preserve">0.516207814216614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465791910886765</t>
+    <t xml:space="preserve">0.465791970491409</t>
   </si>
   <si>
     <t xml:space="preserve">0.4835484623909</t>
@@ -440,34 +440,34 @@
     <t xml:space="preserve">0.547281742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585965573787689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586599707603455</t>
+    <t xml:space="preserve">0.558379590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585965633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586599826812744</t>
   </si>
   <si>
     <t xml:space="preserve">0.613868713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654455065727234</t>
+    <t xml:space="preserve">0.654455125331879</t>
   </si>
   <si>
     <t xml:space="preserve">0.665869951248169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655089199542999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62306410074234</t>
+    <t xml:space="preserve">0.655089259147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623064041137695</t>
   </si>
   <si>
     <t xml:space="preserve">0.633844792842865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62211287021637</t>
+    <t xml:space="preserve">0.622112929821014</t>
   </si>
   <si>
     <t xml:space="preserve">0.618942022323608</t>
@@ -479,64 +479,64 @@
     <t xml:space="preserve">0.631625294685364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628771603107452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63416188955307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629088521003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643674373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.644308507442474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64557683467865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636064350605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634796023368835</t>
+    <t xml:space="preserve">0.628771543502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634161949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629088580608368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643674314022064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.644308626651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645576775074005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636064410209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63479608297348</t>
   </si>
   <si>
     <t xml:space="preserve">0.628454446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632259428501129</t>
+    <t xml:space="preserve">0.632259368896484</t>
   </si>
   <si>
     <t xml:space="preserve">0.626551985740662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234829425812</t>
+    <t xml:space="preserve">0.626234889030457</t>
   </si>
   <si>
     <t xml:space="preserve">0.602453768253326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588185250759125</t>
+    <t xml:space="preserve">0.588185131549835</t>
   </si>
   <si>
     <t xml:space="preserve">0.590087652206421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589136481285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619893252849579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592941343784332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60055136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595795154571533</t>
+    <t xml:space="preserve">0.589136362075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619893312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592941462993622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600551307201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595795094966888</t>
   </si>
   <si>
     <t xml:space="preserve">0.594526767730713</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601185500621796</t>
+    <t xml:space="preserve">0.601185441017151</t>
   </si>
   <si>
     <t xml:space="preserve">0.603087961673737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609746694564819</t>
+    <t xml:space="preserve">0.609746634960175</t>
   </si>
   <si>
     <t xml:space="preserve">0.611332058906555</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">0.614185810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61196631193161</t>
+    <t xml:space="preserve">0.611966252326965</t>
   </si>
   <si>
     <t xml:space="preserve">0.605941712856293</t>
@@ -569,73 +569,73 @@
     <t xml:space="preserve">0.598648905754089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593258440494537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588502168655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597380459308624</t>
+    <t xml:space="preserve">0.593258500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588502287864685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597380578517914</t>
   </si>
   <si>
     <t xml:space="preserve">0.617673695087433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61101508140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604039192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605307638645172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610063791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649405479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039561271667</t>
+    <t xml:space="preserve">0.611015021800995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604039251804352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605307519435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61006373167038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039501667023</t>
   </si>
   <si>
     <t xml:space="preserve">0.610380828380585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596429288387299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591355919837952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589770615100861</t>
+    <t xml:space="preserve">0.596429347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591355979442596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589770555496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.56535530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523183643817902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481963068246841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493377923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492109656333923</t>
+    <t xml:space="preserve">0.523183524608612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.481963008642197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493377983570099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492109596729279</t>
   </si>
   <si>
     <t xml:space="preserve">0.508280813694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513988256454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509232044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509549081325531</t>
+    <t xml:space="preserve">0.513988196849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509231984615326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509549140930176</t>
   </si>
   <si>
     <t xml:space="preserve">0.51779317855835</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">0.53047639131546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546013414859772</t>
+    <t xml:space="preserve">0.546013474464417</t>
   </si>
   <si>
     <t xml:space="preserve">0.54094010591507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532696008682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538720548152924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539037585258484</t>
+    <t xml:space="preserve">0.532696068286896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538720488548279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539037644863129</t>
   </si>
   <si>
     <t xml:space="preserve">0.533330142498016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532061815261841</t>
+    <t xml:space="preserve">0.532061755657196</t>
   </si>
   <si>
     <t xml:space="preserve">0.568843245506287</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">0.570428669452667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566306531429291</t>
+    <t xml:space="preserve">0.566306591033936</t>
   </si>
   <si>
     <t xml:space="preserve">0.549501240253448</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560599088668823</t>
+    <t xml:space="preserve">0.560599148273468</t>
   </si>
   <si>
     <t xml:space="preserve">0.56440407037735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550452470779419</t>
+    <t xml:space="preserve">0.550452530384064</t>
   </si>
   <si>
     <t xml:space="preserve">0.542842626571655</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">0.50669538974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528256773948669</t>
+    <t xml:space="preserve">0.528256893157959</t>
   </si>
   <si>
     <t xml:space="preserve">0.519695699214935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526037395000458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51874440908432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511451661586761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514305293560028</t>
+    <t xml:space="preserve">0.526037275791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518744349479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511451601982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514305233955383</t>
   </si>
   <si>
     <t xml:space="preserve">0.523817718029022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508597850799561</t>
+    <t xml:space="preserve">0.508597791194916</t>
   </si>
   <si>
     <t xml:space="preserve">0.522549390792847</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">0.511134505271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504158675670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506061196327209</t>
+    <t xml:space="preserve">0.504158735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506061255931854</t>
   </si>
   <si>
     <t xml:space="preserve">0.505109965801239</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.510500371456146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499719619750977</t>
+    <t xml:space="preserve">0.499719560146332</t>
   </si>
   <si>
     <t xml:space="preserve">0.512085735797882</t>
@@ -767,28 +767,28 @@
     <t xml:space="preserve">0.550769627094269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553623378276825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560281991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569794476032257</t>
+    <t xml:space="preserve">0.55362331867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560282051563263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569794535636902</t>
   </si>
   <si>
     <t xml:space="preserve">0.575501978397369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627820312976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658894300460815</t>
+    <t xml:space="preserve">0.627820253372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658894181251526</t>
   </si>
   <si>
     <t xml:space="preserve">0.655723392963409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358145713806</t>
+    <t xml:space="preserve">0.682358205318451</t>
   </si>
   <si>
     <t xml:space="preserve">0.762262582778931</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.736896097660065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.707724750041962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696943879127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733091235160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748945236206055</t>
+    <t xml:space="preserve">0.707724690437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696943819522858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733091115951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74894517660141</t>
   </si>
   <si>
     <t xml:space="preserve">0.747676908969879</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">0.754652678966522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755286872386932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760360062122345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818068861961365</t>
+    <t xml:space="preserve">0.755286812782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760360181331635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81806880235672</t>
   </si>
   <si>
     <t xml:space="preserve">0.799678146839142</t>
@@ -830,85 +830,85 @@
     <t xml:space="preserve">0.771140873432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768604278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.720407962799072</t>
+    <t xml:space="preserve">0.768604159355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720408022403717</t>
   </si>
   <si>
     <t xml:space="preserve">0.727383673191071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740701019763947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73816454410553</t>
+    <t xml:space="preserve">0.740701138973236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738164484500885</t>
   </si>
   <si>
     <t xml:space="preserve">0.774945855140686</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78382408618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.801580607891083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849776983261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884021759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851045310497284</t>
+    <t xml:space="preserve">0.78382396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.801580667495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849777042865753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884021699428558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851045250892639</t>
   </si>
   <si>
     <t xml:space="preserve">0.878314197063446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894168317317963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876557826996</t>
+    <t xml:space="preserve">0.894168198108673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876319408417</t>
   </si>
   <si>
     <t xml:space="preserve">0.924607932567596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.88782662153244</t>
+    <t xml:space="preserve">0.88782674074173</t>
   </si>
   <si>
     <t xml:space="preserve">0.901778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881485044956207</t>
+    <t xml:space="preserve">0.881484985351562</t>
   </si>
   <si>
     <t xml:space="preserve">0.902412354946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.875143468379974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896070778369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9106565117836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827300071716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910022258758545</t>
+    <t xml:space="preserve">0.87514328956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896070718765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910656571388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827180862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9100221991539</t>
   </si>
   <si>
     <t xml:space="preserve">0.889729082584381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.892900109291077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436525344849</t>
+    <t xml:space="preserve">0.892899870872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436644554138</t>
   </si>
   <si>
     <t xml:space="preserve">0.863094329833984</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">0.87577760219574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868167459964752</t>
+    <t xml:space="preserve">0.868167579174042</t>
   </si>
   <si>
     <t xml:space="preserve">0.756555140018463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788897395133972</t>
+    <t xml:space="preserve">0.788897335529327</t>
   </si>
   <si>
     <t xml:space="preserve">0.812995493412018</t>
@@ -944,40 +944,40 @@
     <t xml:space="preserve">0.790165722370148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.786360800266266</t>
+    <t xml:space="preserve">0.786360740661621</t>
   </si>
   <si>
     <t xml:space="preserve">0.811727285385132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830117881298065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814897954463959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792702376842499</t>
+    <t xml:space="preserve">0.83011794090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814898073673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792702436447144</t>
   </si>
   <si>
     <t xml:space="preserve">0.803483128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804117381572723</t>
+    <t xml:space="preserve">0.804117202758789</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848375797272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780019223690033</t>
+    <t xml:space="preserve">0.780019164085388</t>
   </si>
   <si>
     <t xml:space="preserve">0.781921684741974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791434109210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78509247303009</t>
+    <t xml:space="preserve">0.791434049606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785092532634735</t>
   </si>
   <si>
     <t xml:space="preserve">0.786994993686676</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">0.793970704078674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.789531648159027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.773677468299866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775580108165741</t>
+    <t xml:space="preserve">0.789531588554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77367752790451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775580048561096</t>
   </si>
   <si>
     <t xml:space="preserve">0.769872546195984</t>
@@ -1001,58 +1001,58 @@
     <t xml:space="preserve">0.767335951328278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771775007247925</t>
+    <t xml:space="preserve">0.771775126457214</t>
   </si>
   <si>
     <t xml:space="preserve">0.76162850856781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.795873165130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811093151569366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843435287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460076808929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866899251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840264558792114</t>
+    <t xml:space="preserve">0.79587310552597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811093091964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435347080231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654654979706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606813907623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866899311542511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840264499187469</t>
   </si>
   <si>
     <t xml:space="preserve">0.830752074718475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855484306812286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801213264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142730236053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820605516433716</t>
+    <t xml:space="preserve">0.855484485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142670631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820605576038361</t>
   </si>
   <si>
     <t xml:space="preserve">0.824410438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.826947033405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806019723415375</t>
+    <t xml:space="preserve">0.826947152614594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806019842624664</t>
   </si>
   <si>
     <t xml:space="preserve">0.799043953418732</t>
@@ -1061,22 +1061,22 @@
     <t xml:space="preserve">0.804751396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785726547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778750777244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777482450008392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802214801311493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80665385723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80792236328125</t>
+    <t xml:space="preserve">0.785726606845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778750836849213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777482509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802214741706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.806653797626495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807922303676605</t>
   </si>
   <si>
     <t xml:space="preserve">0.854850232601166</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">0.857386887073517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.852313637733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863728523254395</t>
+    <t xml:space="preserve">0.85231351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863728404045105</t>
   </si>
   <si>
     <t xml:space="preserve">0.86499685049057</t>
@@ -1097,58 +1097,58 @@
     <t xml:space="preserve">0.850411057472229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.84089869260788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834557056427002</t>
+    <t xml:space="preserve">0.840898752212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834556996822357</t>
   </si>
   <si>
     <t xml:space="preserve">0.838996171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.827581226825714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826312959194183</t>
+    <t xml:space="preserve">0.827581167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826312899589539</t>
   </si>
   <si>
     <t xml:space="preserve">0.805385649204254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814263880252838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818703055381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81933718919754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796507477760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809190511703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.809824824333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.797775685787201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798409879207611</t>
+    <t xml:space="preserve">0.814263939857483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81870299577713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819337248802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79650741815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809190571308136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.809824764728546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.797775626182556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798409759998322</t>
   </si>
   <si>
     <t xml:space="preserve">0.817434787750244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823142111301422</t>
+    <t xml:space="preserve">0.823142230510712</t>
   </si>
   <si>
     <t xml:space="preserve">0.812361419200897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819971263408661</t>
+    <t xml:space="preserve">0.819971203804016</t>
   </si>
   <si>
     <t xml:space="preserve">0.797141492366791</t>
@@ -1157,46 +1157,46 @@
     <t xml:space="preserve">0.716602921485901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.704553842544556</t>
+    <t xml:space="preserve">0.7045539021492</t>
   </si>
   <si>
     <t xml:space="preserve">0.736261963844299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.759725987911224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240926027298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776214182376862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78445827960968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78318989276886</t>
+    <t xml:space="preserve">0.75972592830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772409200668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776214122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784458220005035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783190011978149</t>
   </si>
   <si>
     <t xml:space="preserve">0.752116024494171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7609943151474</t>
+    <t xml:space="preserve">0.760994255542755</t>
   </si>
   <si>
     <t xml:space="preserve">0.757823467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766701698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790799915790558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810458838939667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311661720276</t>
+    <t xml:space="preserve">0.766701638698578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790799975395203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810458779335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311602115631</t>
   </si>
   <si>
     <t xml:space="preserve">0.781287431716919</t>
@@ -1205,67 +1205,67 @@
     <t xml:space="preserve">0.795238971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800312280654907</t>
+    <t xml:space="preserve">0.800312340259552</t>
   </si>
   <si>
     <t xml:space="preserve">0.815532267093658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.764799177646637</t>
+    <t xml:space="preserve">0.764799237251282</t>
   </si>
   <si>
     <t xml:space="preserve">0.731822848320007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711529672145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.693773090839386</t>
+    <t xml:space="preserve">0.711529612541199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.693773150444031</t>
   </si>
   <si>
     <t xml:space="preserve">0.739432752132416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703919649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695041418075562</t>
+    <t xml:space="preserve">0.70391970872879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695041358470917</t>
   </si>
   <si>
     <t xml:space="preserve">0.683626472949982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.660796761512756</t>
+    <t xml:space="preserve">0.660796701908112</t>
   </si>
   <si>
     <t xml:space="preserve">0.684894859790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670943260192871</t>
+    <t xml:space="preserve">0.670943200588226</t>
   </si>
   <si>
     <t xml:space="preserve">0.69123649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678553223609924</t>
+    <t xml:space="preserve">0.678553342819214</t>
   </si>
   <si>
     <t xml:space="preserve">0.687431514263153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717871189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730554461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710261285305023</t>
+    <t xml:space="preserve">0.717871248722076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730554401874542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710261344909668</t>
   </si>
   <si>
     <t xml:space="preserve">0.697578132152557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714066326618195</t>
+    <t xml:space="preserve">0.714066386222839</t>
   </si>
   <si>
     <t xml:space="preserve">0.729286193847656</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">0.748310983181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.757189333438873</t>
+    <t xml:space="preserve">0.757189273834229</t>
   </si>
   <si>
     <t xml:space="preserve">0.758457660675049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763530969619751</t>
+    <t xml:space="preserve">0.763530910015106</t>
   </si>
   <si>
     <t xml:space="preserve">0.74957948923111</t>
@@ -1310,46 +1310,46 @@
     <t xml:space="preserve">0.722944557666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700114727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456422805786</t>
+    <t xml:space="preserve">0.700114786624908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456303596497</t>
   </si>
   <si>
     <t xml:space="preserve">0.698846399784088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72548121213913</t>
+    <t xml:space="preserve">0.725481271743774</t>
   </si>
   <si>
     <t xml:space="preserve">0.71533465385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.712797999382019</t>
+    <t xml:space="preserve">0.712797939777374</t>
   </si>
   <si>
     <t xml:space="preserve">0.69250476360321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.705187976360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68108993768692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701383113861084</t>
+    <t xml:space="preserve">0.705188035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.681089878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701382994651794</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699841499329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686163246631622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679821670055389</t>
+    <t xml:space="preserve">0.688699722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686163187026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679821610450745</t>
   </si>
   <si>
     <t xml:space="preserve">0.672211587429047</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">0.677284836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65826004743576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659528374671936</t>
+    <t xml:space="preserve">0.658260107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659528315067291</t>
   </si>
   <si>
     <t xml:space="preserve">0.651918411254883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648113429546356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641771733760834</t>
+    <t xml:space="preserve">0.648113369941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641771793365479</t>
   </si>
   <si>
     <t xml:space="preserve">0.635430216789246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643040180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639235258102417</t>
+    <t xml:space="preserve">0.643040239810944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639235198497772</t>
   </si>
   <si>
     <t xml:space="preserve">0.637966930866241</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">0.609429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59801459312439</t>
+    <t xml:space="preserve">0.598014712333679</t>
   </si>
   <si>
     <t xml:space="preserve">0.599917113780975</t>
@@ -1409,49 +1409,49 @@
     <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478676795959</t>
+    <t xml:space="preserve">0.621478617191315</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622747004032135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615771234035492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623381078243256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612600386142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591038942337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584063112735748</t>
+    <t xml:space="preserve">0.62274706363678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615771174430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6233811378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612600445747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591038882732391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584063172340393</t>
   </si>
   <si>
     <t xml:space="preserve">0.580892324447632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56567245721817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570745706558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561233222484589</t>
+    <t xml:space="preserve">0.565672338008881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570745766162872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
     <t xml:space="preserve">0.572648227214813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559965014457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537135183811188</t>
+    <t xml:space="preserve">0.559964954853058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537135243415833</t>
   </si>
   <si>
     <t xml:space="preserve">0.528891086578369</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">0.573282361030579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569477438926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608795404434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307828903198</t>
+    <t xml:space="preserve">0.569477379322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608795464038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307948112488</t>
   </si>
   <si>
     <t xml:space="preserve">0.630356907844543</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">0.604990482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580258131027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572014093399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568209111690521</t>
+    <t xml:space="preserve">0.580258190631866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572014033794403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568209052085876</t>
   </si>
   <si>
     <t xml:space="preserve">0.554891645908356</t>
@@ -1490,79 +1490,79 @@
     <t xml:space="preserve">0.629722774028778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721676290035248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766067504882812</t>
+    <t xml:space="preserve">0.721676230430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766067564487457</t>
   </si>
   <si>
     <t xml:space="preserve">0.782555758953094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.828215479850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825678825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873875081539154</t>
+    <t xml:space="preserve">0.828215360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825678765773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873875021934509</t>
   </si>
   <si>
     <t xml:space="preserve">0.871338427066803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.882753372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880216717720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903046607971191</t>
+    <t xml:space="preserve">0.882753252983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880216777324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903046548366547</t>
   </si>
   <si>
     <t xml:space="preserve">0.922071397304535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93729156255722</t>
+    <t xml:space="preserve">0.937291324138641</t>
   </si>
   <si>
     <t xml:space="preserve">0.918266475200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.86626523733139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630424976349</t>
+    <t xml:space="preserve">0.866265177726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630365371704</t>
   </si>
   <si>
     <t xml:space="preserve">0.896704912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.876411736011505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801772594452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070040225983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559591770172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934754610061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314815998077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583202838898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929681301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144706249237</t>
+    <t xml:space="preserve">0.87641179561615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801891803741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070159435272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559710979462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934754550457001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314875602722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583143234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929681360721588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144765853882</t>
   </si>
   <si>
     <t xml:space="preserve">0.906851470470428</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">0.930949687957764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.891631603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833288788795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873903274536</t>
+    <t xml:space="preserve">0.891631782054901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833288669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873724460602</t>
   </si>
   <si>
     <t xml:space="preserve">0.802849054336548</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">0.636698484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627019226551056</t>
+    <t xml:space="preserve">0.627019286155701</t>
   </si>
   <si>
     <t xml:space="preserve">0.641851961612701</t>
@@ -1601,37 +1601,37 @@
     <t xml:space="preserve">0.625670731067657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613534986972809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616905987262726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618928611278534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595331251621246</t>
+    <t xml:space="preserve">0.613535046577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616906046867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618928670883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597353756427765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596005380153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602073311805725</t>
+    <t xml:space="preserve">0.59735381603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596005320549011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60207337141037</t>
   </si>
   <si>
     <t xml:space="preserve">0.598028004169464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594656944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838055610657</t>
+    <t xml:space="preserve">0.594657003879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838115215302</t>
   </si>
   <si>
     <t xml:space="preserve">0.593982756137848</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">0.65398782491684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656684637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637132465839386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626345098018646</t>
+    <t xml:space="preserve">0.656684696674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637132406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626345038414001</t>
   </si>
   <si>
     <t xml:space="preserve">0.62836766242981</t>
@@ -1661,34 +1661,34 @@
     <t xml:space="preserve">0.624322354793549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629716098308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62769341468811</t>
+    <t xml:space="preserve">0.629716157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627693474292755</t>
   </si>
   <si>
     <t xml:space="preserve">0.614883363246918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608815491199493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61758029460907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635783910751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624996542930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614209175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605444371700287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606118500232697</t>
+    <t xml:space="preserve">0.608815431594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617580235004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635783970355988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624996602535248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614209115505219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605444431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606118559837341</t>
   </si>
   <si>
     <t xml:space="preserve">0.630390286445618</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">0.643200397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656010448932648</t>
+    <t xml:space="preserve">0.656010389328003</t>
   </si>
   <si>
     <t xml:space="preserve">0.633761346340179</t>
@@ -1706,22 +1706,22 @@
     <t xml:space="preserve">0.61218649148941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621625483036041</t>
+    <t xml:space="preserve">0.621625602245331</t>
   </si>
   <si>
     <t xml:space="preserve">0.608141243457794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610163867473602</t>
+    <t xml:space="preserve">0.610163927078247</t>
   </si>
   <si>
     <t xml:space="preserve">0.549484610557556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561620354652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552855670452118</t>
+    <t xml:space="preserve">0.561620533466339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552855610847473</t>
   </si>
   <si>
     <t xml:space="preserve">0.565665721893311</t>
@@ -1730,64 +1730,64 @@
     <t xml:space="preserve">0.578475773334503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558923542499542</t>
+    <t xml:space="preserve">0.558923602104187</t>
   </si>
   <si>
     <t xml:space="preserve">0.563643097877502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569711029529572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249413967133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562294721603394</t>
+    <t xml:space="preserve">0.569711089134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249354362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562294602394104</t>
   </si>
   <si>
     <t xml:space="preserve">0.573082089424133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583869516849518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584543764591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567014157772064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56633996963501</t>
+    <t xml:space="preserve">0.583869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584543704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567014217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566339910030365</t>
   </si>
   <si>
     <t xml:space="preserve">0.593308568000793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599376499652863</t>
+    <t xml:space="preserve">0.599376440048218</t>
   </si>
   <si>
     <t xml:space="preserve">0.586566388607025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591285884380341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600050568580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602747440338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60746705532074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590611696243286</t>
+    <t xml:space="preserve">0.591285824775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600050687789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602747559547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607466995716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590611636638641</t>
   </si>
   <si>
     <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587914824485779</t>
+    <t xml:space="preserve">0.587914764881134</t>
   </si>
   <si>
     <t xml:space="preserve">0.618254423141479</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">0.641177713871002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588589012622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598702192306519</t>
+    <t xml:space="preserve">0.588589072227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598702251911163</t>
   </si>
   <si>
     <t xml:space="preserve">0.620277106761932</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">0.609489679336548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615557610988617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620951294898987</t>
+    <t xml:space="preserve">0.615557551383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620951354503632</t>
   </si>
   <si>
     <t xml:space="preserve">0.64859414100647</t>
@@ -1826,37 +1826,37 @@
     <t xml:space="preserve">0.604770183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604095995426178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603421747684479</t>
+    <t xml:space="preserve">0.604095935821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603421688079834</t>
   </si>
   <si>
     <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63848090171814</t>
+    <t xml:space="preserve">0.638480961322784</t>
   </si>
   <si>
     <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695789039134979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714667081832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702531278133392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69983434677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716015517711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728151381015778</t>
+    <t xml:space="preserve">0.695789098739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714667022228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702531218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699834406375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716015577316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728151500225067</t>
   </si>
   <si>
     <t xml:space="preserve">0.717363953590393</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">0.726802885532379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722757697105408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409201622009</t>
+    <t xml:space="preserve">0.722757637500763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409261226654</t>
   </si>
   <si>
     <t xml:space="preserve">0.711970210075378</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">0.701182782649994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69444066286087</t>
+    <t xml:space="preserve">0.694440603256226</t>
   </si>
   <si>
     <t xml:space="preserve">0.689046919345856</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">0.672191560268402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68500167131424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675562679767609</t>
+    <t xml:space="preserve">0.685001730918884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675562560558319</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146312236786</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919893264771</t>
+    <t xml:space="preserve">0.647919833660126</t>
   </si>
   <si>
     <t xml:space="preserve">0.645897269248962</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">0.636458277702332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633087158203125</t>
+    <t xml:space="preserve">0.63308721780777</t>
   </si>
   <si>
     <t xml:space="preserve">0.611512303352356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574430584907532</t>
+    <t xml:space="preserve">0.574430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">0.589263260364532</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">0.560272037982941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553529858589172</t>
+    <t xml:space="preserve">0.553529918193817</t>
   </si>
   <si>
     <t xml:space="preserve">0.538697242736816</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">0.463859379291534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458465605974197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39104425907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419361233711243</t>
+    <t xml:space="preserve">0.458465665578842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391044199466705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419361263513565</t>
   </si>
   <si>
     <t xml:space="preserve">0.394415289163589</t>
@@ -1964,40 +1964,40 @@
     <t xml:space="preserve">0.387673139572144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388347387313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380256831645966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.403180122375488</t>
+    <t xml:space="preserve">0.38834735751152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380256861448288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403180062770844</t>
   </si>
   <si>
     <t xml:space="preserve">0.412619084119797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.431497126817703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46520784497261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927340745926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.479366332292557</t>
+    <t xml:space="preserve">0.431497097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465207874774933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927281141281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479366362094879</t>
   </si>
   <si>
     <t xml:space="preserve">0.489479511976242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474646866321564</t>
+    <t xml:space="preserve">0.474646776914597</t>
   </si>
   <si>
     <t xml:space="preserve">0.473298400640488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464533597230911</t>
+    <t xml:space="preserve">0.464533567428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.483411610126495</t>
@@ -2006,52 +2006,52 @@
     <t xml:space="preserve">0.498918533325195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496895849704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495547443628311</t>
+    <t xml:space="preserve">0.496895879507065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495547533035278</t>
   </si>
   <si>
     <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482063144445419</t>
+    <t xml:space="preserve">0.482063204050064</t>
   </si>
   <si>
     <t xml:space="preserve">0.490827918052673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484760075807571</t>
+    <t xml:space="preserve">0.484760046005249</t>
   </si>
   <si>
     <t xml:space="preserve">0.480714738368988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482737362384796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485434234142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488131105899811</t>
+    <t xml:space="preserve">0.482737392187119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485434263944626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488131046295166</t>
   </si>
   <si>
     <t xml:space="preserve">0.481388956308365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472624182701111</t>
+    <t xml:space="preserve">0.472624152898788</t>
   </si>
   <si>
     <t xml:space="preserve">0.427451848983765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434868156909943</t>
+    <t xml:space="preserve">0.43486812710762</t>
   </si>
   <si>
     <t xml:space="preserve">0.438239216804504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443632960319519</t>
+    <t xml:space="preserve">0.443632990121841</t>
   </si>
   <si>
     <t xml:space="preserve">0.430148661136627</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">0.409248024225235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434212148189545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410049825906754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892401218414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449135988950729</t>
+    <t xml:space="preserve">0.434212177991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410049855709076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892371416092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449135959148407</t>
   </si>
   <si>
     <t xml:space="preserve">0.451267927885056</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">0.456953287124634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486800909042358</t>
+    <t xml:space="preserve">0.486800879240036</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
@@ -2087,58 +2087,58 @@
     <t xml:space="preserve">0.446293383836746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.453399986028671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46619176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46690246462822</t>
+    <t xml:space="preserve">0.453399956226349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466191828250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466902524232864</t>
   </si>
   <si>
     <t xml:space="preserve">0.48040497303009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498882114887238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48822221159935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477562338113785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445582717657089</t>
+    <t xml:space="preserve">0.498882085084915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488222122192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.477562308311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445582687854767</t>
   </si>
   <si>
     <t xml:space="preserve">0.442740082740784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452689349651337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447004050016403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450557351112366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448425322771072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442029386758804</t>
+    <t xml:space="preserve">0.452689319849014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447004020214081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450557321310043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44842529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442029416561127</t>
   </si>
   <si>
     <t xml:space="preserve">0.42994824051857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438476115465164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429237514734268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447714686393738</t>
+    <t xml:space="preserve">0.438476145267487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429237574338913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447714656591415</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
@@ -2153,31 +2153,31 @@
     <t xml:space="preserve">0.444161385297775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456242561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449846655130386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455531895160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450748920441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430658936500549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420709639787674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427816241979599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413603097200394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417156428098679</t>
+    <t xml:space="preserve">0.456242650747299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449846684932709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455531984567642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450778722763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430658876895905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420709699392319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427816301584244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413603067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417156368494034</t>
   </si>
   <si>
     <t xml:space="preserve">0.416445732116699</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">0.427105605602264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437054842710495</t>
+    <t xml:space="preserve">0.437054812908173</t>
   </si>
   <si>
     <t xml:space="preserve">0.432080209255219</t>
@@ -2198,28 +2198,28 @@
     <t xml:space="preserve">0.422841668128967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417867064476013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.406496524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407917827367783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397968620061874</t>
+    <t xml:space="preserve">0.417866975069046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.406496554613113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40791779756546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397968590259552</t>
   </si>
   <si>
     <t xml:space="preserve">0.403653919696808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401521891355515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405075162649155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400811225175858</t>
+    <t xml:space="preserve">0.401521950960159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405075192451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40081125497818</t>
   </si>
   <si>
     <t xml:space="preserve">0.387308746576309</t>
@@ -2237,25 +2237,25 @@
     <t xml:space="preserve">0.398679256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409339159727097</t>
+    <t xml:space="preserve">0.409339129924774</t>
   </si>
   <si>
     <t xml:space="preserve">0.395836621522903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382334113121033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370963633060455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383755475282669</t>
+    <t xml:space="preserve">0.382334142923355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370963573455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383755505084991</t>
   </si>
   <si>
     <t xml:space="preserve">0.366699635982513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363146334886551</t>
+    <t xml:space="preserve">0.363146364688873</t>
   </si>
   <si>
     <t xml:space="preserve">0.3539077937603</t>
@@ -2264,19 +2264,19 @@
     <t xml:space="preserve">0.356750428676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359593033790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358882427215576</t>
+    <t xml:space="preserve">0.359593063592911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358882397413254</t>
   </si>
   <si>
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730019330978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151411294937</t>
+    <t xml:space="preserve">0.388730049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151351690292</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">0.355329126119614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353552490472794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354618489742279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351775825023651</t>
+    <t xml:space="preserve">0.353552460670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354618459939957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351775795221329</t>
   </si>
   <si>
     <t xml:space="preserve">0.351065158843994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334009349346161</t>
+    <t xml:space="preserve">0.334009379148483</t>
   </si>
   <si>
     <t xml:space="preserve">0.323349505662918</t>
@@ -2315,22 +2315,22 @@
     <t xml:space="preserve">0.342181950807571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337207317352295</t>
+    <t xml:space="preserve">0.337207347154617</t>
   </si>
   <si>
     <t xml:space="preserve">0.337562680244446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343958586454391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361014425754547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360303729772568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.389440715312958</t>
+    <t xml:space="preserve">0.343958556652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361014395952225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36030375957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389440685510635</t>
   </si>
   <si>
     <t xml:space="preserve">0.396547317504883</t>
@@ -2339,52 +2339,52 @@
     <t xml:space="preserve">0.41218176484108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421420305967331</t>
+    <t xml:space="preserve">0.421420335769653</t>
   </si>
   <si>
     <t xml:space="preserve">0.415024399757385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419999003410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313733577728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405785858631134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402232527732849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418577700853348</t>
+    <t xml:space="preserve">0.419999063014984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313763380051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405785828828812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402232557535172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418577671051025</t>
   </si>
   <si>
     <t xml:space="preserve">0.419288367033005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.399389922618866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.393704652786255</t>
+    <t xml:space="preserve">0.399389892816544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393704682588577</t>
   </si>
   <si>
     <t xml:space="preserve">0.392993986606598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391572684049606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39725798368454</t>
+    <t xml:space="preserve">0.391572713851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.397257924079895</t>
   </si>
   <si>
     <t xml:space="preserve">0.404364556074142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395125985145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386598080396652</t>
+    <t xml:space="preserve">0.395125955343246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386598110198975</t>
   </si>
   <si>
     <t xml:space="preserve">0.380202174186707</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">0.368831634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364567697048187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428526878356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.423552364110947</t>
+    <t xml:space="preserve">0.364567667245865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428526908159256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.423552304506302</t>
   </si>
   <si>
     <t xml:space="preserve">0.436344116926193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42639496922493</t>
+    <t xml:space="preserve">0.426394939422607</t>
   </si>
   <si>
     <t xml:space="preserve">0.440608084201813</t>
@@ -2420,31 +2420,31 @@
     <t xml:space="preserve">0.439897477626801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464770525693893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471877038478851</t>
+    <t xml:space="preserve">0.464770466089249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471876978874207</t>
   </si>
   <si>
     <t xml:space="preserve">0.478983670473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492486208677292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515227198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512384653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.506699323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517359137535095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120656013489</t>
+    <t xml:space="preserve">0.492486149072647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515227258205414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512384593486786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50669926404953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51735919713974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120715618134</t>
   </si>
   <si>
     <t xml:space="preserve">0.5138059258461</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">0.523755073547363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525887072086334</t>
+    <t xml:space="preserve">0.525887131690979</t>
   </si>
   <si>
     <t xml:space="preserve">0.526597738265991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525176525115967</t>
+    <t xml:space="preserve">0.525176405906677</t>
   </si>
   <si>
     <t xml:space="preserve">0.530151009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52446573972702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538679003715515</t>
+    <t xml:space="preserve">0.524465680122375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
     <t xml:space="preserve">0.544364213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541521549224854</t>
+    <t xml:space="preserve">0.541521608829498</t>
   </si>
   <si>
     <t xml:space="preserve">0.536546945571899</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">0.515937864780426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523044466972351</t>
+    <t xml:space="preserve">0.523044407367706</t>
   </si>
   <si>
     <t xml:space="preserve">0.54223221540451</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">0.53157240152359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542942881584167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549338817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5649733543396</t>
+    <t xml:space="preserve">0.542942941188812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54933887720108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564973294734955</t>
   </si>
   <si>
     <t xml:space="preserve">0.550941228866577</t>
@@ -2531,22 +2531,22 @@
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647724151611</t>
+    <t xml:space="preserve">0.537647783756256</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569902896881</t>
+    <t xml:space="preserve">0.526569843292236</t>
   </si>
   <si>
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753460884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518446147441864</t>
+    <t xml:space="preserve">0.514753401279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518446087837219</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">0.572358548641205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581220924854279</t>
+    <t xml:space="preserve">0.581220865249634</t>
   </si>
   <si>
     <t xml:space="preserve">0.584174990653992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58343642950058</t>
+    <t xml:space="preserve">0.583436489105225</t>
   </si>
   <si>
     <t xml:space="preserve">0.575312674045563</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">0.527308404445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522877216339111</t>
+    <t xml:space="preserve">0.522877275943756</t>
   </si>
   <si>
     <t xml:space="preserve">0.53543221950531</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">0.51696902513504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511060833930969</t>
+    <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
     <t xml:space="preserve">0.511799335479736</t>
@@ -2633,25 +2633,25 @@
     <t xml:space="preserve">0.487427949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48816642165184</t>
+    <t xml:space="preserve">0.488166451454163</t>
   </si>
   <si>
     <t xml:space="preserve">0.483735263347626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488905012607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48078116774559</t>
+    <t xml:space="preserve">0.48890495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480781197547913</t>
   </si>
   <si>
     <t xml:space="preserve">0.48151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492597579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522138714790344</t>
+    <t xml:space="preserve">0.492597639560699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522138774394989</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">0.534693658351898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532478153705597</t>
+    <t xml:space="preserve">0.532478094100952</t>
   </si>
   <si>
     <t xml:space="preserve">0.519923150539398</t>
@@ -2669,28 +2669,28 @@
     <t xml:space="preserve">0.517707526683807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512537896633148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514014840126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525092899799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545033037662506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528785467147827</t>
+    <t xml:space="preserve">0.512537837028503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514014899730682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525092840194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545032978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528785526752472</t>
   </si>
   <si>
     <t xml:space="preserve">0.533216595649719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520661592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515491902828217</t>
+    <t xml:space="preserve">0.520661652088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515491962432861</t>
   </si>
   <si>
     <t xml:space="preserve">0.508106648921967</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">0.505152583122253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50219851732254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495551735162735</t>
+    <t xml:space="preserve">0.502198457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495551705360413</t>
   </si>
   <si>
     <t xml:space="preserve">0.498505830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502937018871307</t>
+    <t xml:space="preserve">0.502936959266663</t>
   </si>
   <si>
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771598815918</t>
+    <t xml:space="preserve">0.500721395015717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771539211273</t>
   </si>
   <si>
     <t xml:space="preserve">0.540601909160614</t>
@@ -2735,25 +2735,25 @@
     <t xml:space="preserve">0.538386285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530262470245361</t>
+    <t xml:space="preserve">0.530262529850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.539863348007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613716006278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641780138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622578382492065</t>
+    <t xml:space="preserve">0.613716125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641780078411102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62257844209671</t>
   </si>
   <si>
     <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612977504730225</t>
+    <t xml:space="preserve">0.612977623939514</t>
   </si>
   <si>
     <t xml:space="preserve">0.616670191287994</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">0.620362818241119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615193128585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601161062717438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594514429569244</t>
+    <t xml:space="preserve">0.61519318819046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601161122322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5945143699646</t>
   </si>
   <si>
     <t xml:space="preserve">0.599684000015259</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">0.600422561168671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607069313526154</t>
+    <t xml:space="preserve">0.607069373130798</t>
   </si>
   <si>
     <t xml:space="preserve">0.593037247657776</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">0.641041576862335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664674460887909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6668900847435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658766269683838</t>
+    <t xml:space="preserve">0.664674401283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66688996553421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658766210079193</t>
   </si>
   <si>
     <t xml:space="preserve">0.653596520423889</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">0.629225134849548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642518579959869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640303015708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63365626335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675752401351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649165391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655812084674835</t>
+    <t xml:space="preserve">0.642518639564514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640303075313568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633656322956085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675752341747284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649165332317352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65581214427948</t>
   </si>
   <si>
     <t xml:space="preserve">0.655073583126068</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">0.625532567501068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638087511062622</t>
+    <t xml:space="preserve">0.638087451457977</t>
   </si>
   <si>
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638825953006744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62627100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702197551727</t>
+    <t xml:space="preserve">0.638826012611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626271069049835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702137947083</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2879,49 +2879,49 @@
     <t xml:space="preserve">0.657289147377014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662458837032318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678706407546997</t>
+    <t xml:space="preserve">0.662458896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678706467151642</t>
   </si>
   <si>
     <t xml:space="preserve">0.676490843296051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673536777496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661720395088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635133326053619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576789736747742</t>
+    <t xml:space="preserve">0.673536717891693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661720335483551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635133385658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576789796352386</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587867677211761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507368147373199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529523909091949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711736679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564234733581543</t>
+    <t xml:space="preserve">0.587867617607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507368087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529524028301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711855888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564234793186188</t>
   </si>
   <si>
     <t xml:space="preserve">0.582697927951813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570881485939026</t>
+    <t xml:space="preserve">0.570881545543671</t>
   </si>
   <si>
     <t xml:space="preserve">0.559803605079651</t>
@@ -2936,52 +2936,52 @@
     <t xml:space="preserve">0.542078971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567188858985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579743802547455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562019109725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557588040828705</t>
+    <t xml:space="preserve">0.567188918590546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5797438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562019169330597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55758798122406</t>
   </si>
   <si>
     <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555372416973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569404423236847</t>
+    <t xml:space="preserve">0.555372357368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569404482841492</t>
   </si>
   <si>
     <t xml:space="preserve">0.574574112892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582576513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973668575287</t>
+    <t xml:space="preserve">0.58257657289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973728179932</t>
   </si>
   <si>
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572972297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568172216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169816017151</t>
+    <t xml:space="preserve">0.570572912693024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56817215681076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169756412506</t>
   </si>
   <si>
     <t xml:space="preserve">0.562570512294769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569772720336914</t>
+    <t xml:space="preserve">0.569772660732269</t>
   </si>
   <si>
     <t xml:space="preserve">0.578575372695923</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">0.571373164653778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564971208572388</t>
+    <t xml:space="preserve">0.564971268177032</t>
   </si>
   <si>
     <t xml:space="preserve">0.552967607975006</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">0.54656571149826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537762999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755679130554</t>
+    <t xml:space="preserve">0.537762939929962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755738735199</t>
   </si>
   <si>
     <t xml:space="preserve">0.516156435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525759339332581</t>
+    <t xml:space="preserve">0.525759398937225</t>
   </si>
   <si>
     <t xml:space="preserve">0.521758139133453</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">0.522558391094208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532961547374725</t>
+    <t xml:space="preserve">0.53296160697937</t>
   </si>
   <si>
     <t xml:space="preserve">0.524959087371826</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">0.48814794421196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56177031993866</t>
+    <t xml:space="preserve">0.561770260334015</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">0.588978469371796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568972527980804</t>
+    <t xml:space="preserve">0.56897246837616</t>
   </si>
   <si>
     <t xml:space="preserve">0.572173416614532</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">0.575374364852905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577775120735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565771460533142</t>
+    <t xml:space="preserve">0.577775061130524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565771520137787</t>
   </si>
   <si>
     <t xml:space="preserve">0.580976068973541</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">0.58337676525116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576974928379059</t>
+    <t xml:space="preserve">0.576974868774414</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">0.585777580738068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591379284858704</t>
+    <t xml:space="preserve">0.591379225254059</t>
   </si>
   <si>
     <t xml:space="preserve">0.564170956611633</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567371904850006</t>
+    <t xml:space="preserve">0.567371964454651</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">0.508954226970673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506553530693054</t>
+    <t xml:space="preserve">0.506553590297699</t>
   </si>
   <si>
     <t xml:space="preserve">0.502552330493927</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554790496826</t>
+    <t xml:space="preserve">0.510554730892181</t>
   </si>
   <si>
     <t xml:space="preserve">0.524158835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529760599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531361043453217</t>
+    <t xml:space="preserve">0.529760539531708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531360983848572</t>
   </si>
   <si>
     <t xml:space="preserve">0.550566852092743</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">0.532161295413971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530560791492462</t>
+    <t xml:space="preserve">0.530560731887817</t>
   </si>
   <si>
     <t xml:space="preserve">0.527359843254089</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">0.54736590385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552167356014252</t>
+    <t xml:space="preserve">0.552167415618896</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
@@ -3227,7 +3227,10 @@
     <t xml:space="preserve">0.556968748569489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558569252490997</t>
+    <t xml:space="preserve">0.558569312095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574574172496796</t>
   </si>
   <si>
     <t xml:space="preserve">0.584177076816559</t>
@@ -3236,7 +3239,7 @@
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773860931396</t>
+    <t xml:space="preserve">0.573773920536041</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
@@ -3248,13 +3251,13 @@
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788501739502</t>
+    <t xml:space="preserve">0.621788442134857</t>
   </si>
   <si>
     <t xml:space="preserve">0.624189138412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622588694095612</t>
+    <t xml:space="preserve">0.622588634490967</t>
   </si>
   <si>
     <t xml:space="preserve">0.620187938213348</t>
@@ -3266,7 +3269,7 @@
     <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602582693099976</t>
+    <t xml:space="preserve">0.602582633495331</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3308,22 +3311,22 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792042732239</t>
+    <t xml:space="preserve">0.633792102336884</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628990709781647</t>
+    <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
     <t xml:space="preserve">0.635921716690063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651516497135162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641986310482025</t>
+    <t xml:space="preserve">0.651516437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64198637008667</t>
   </si>
   <si>
     <t xml:space="preserve">0.631589770317078</t>
@@ -3332,34 +3335,31 @@
     <t xml:space="preserve">0.627257883548737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615128636360168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262163639069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663043498993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197629451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615995049476624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62119323015213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628990650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640253603458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723357200623</t>
+    <t xml:space="preserve">0.615128576755524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663103103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197569847107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464803218842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615994989871979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621193289756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64025354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723416805267</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732036590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.619460463523865</t>
+    <t xml:space="preserve">0.604732096195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61946052312851</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529456615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395810127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331216335297</t>
+    <t xml:space="preserve">0.612529516220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395869731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331156730652</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62032687664032</t>
+    <t xml:space="preserve">0.620326936244965</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801029682159</t>
+    <t xml:space="preserve">0.597801089286804</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658823013306</t>
+    <t xml:space="preserve">0.624658763408661</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861402988434</t>
+    <t xml:space="preserve">0.617727696895599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861343383789</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387190341949</t>
+    <t xml:space="preserve">0.639387130737305</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382910251617</t>
+    <t xml:space="preserve">0.652382850646973</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848383903503</t>
+    <t xml:space="preserve">0.655848443508148</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042344093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687037944793701</t>
+    <t xml:space="preserve">0.674042284488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687038004398346</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682706117630005</t>
+    <t xml:space="preserve">0.68270605802536</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637184143066</t>
+    <t xml:space="preserve">0.689637124538422</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739887058734894</t>
+    <t xml:space="preserve">0.739886999130249</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412905693054</t>
+    <t xml:space="preserve">0.762412965297699</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3587,118 +3587,121 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
+    <t xml:space="preserve">0.779740452766418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76846718788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757193803787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745920479297638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.751557111740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753435969352722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.742162644863129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7346470952034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.732768177986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.727131485939026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.723373711109161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73088926076889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725252628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729010403156281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712100386619568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.713979244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.719615936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717737019062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704584777355194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.708342611789703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691432535648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702705919742584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69894814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697069227695465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70082700252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706463634967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710221469402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715858161449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721494853496552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69519031047821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.676401436328888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.740283727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73652595281601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749678194522858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.760951578617096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.787256062030792</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.779740512371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76846718788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76658821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757193803787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745920479297638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.751557111740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753435969352722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.742162644863129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7346470952034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.732768177986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.727131485939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.723373711109161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73088926076889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725252628326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729010403156281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712100386619568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.713979244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.719615936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717737019062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704584777355194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.708342611789703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691432535648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702705919742584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697069227695465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70082700252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706463634967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710221469402313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.715858161449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721494853496552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69519031047821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.676401436328888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.740283727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73652595281601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.738404870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749678194522858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760951578617096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.787256062030792</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -51357,7 +51360,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="s">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51591,7 +51594,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1815" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51617,7 +51620,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51695,7 +51698,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1819" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51799,7 +51802,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="s">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51825,7 +51828,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="s">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51903,7 +51906,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52241,7 +52244,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G1840" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52267,7 +52270,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1841" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52293,7 +52296,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1842" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52319,7 +52322,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1843" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52345,7 +52348,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1844" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52371,7 +52374,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1845" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52397,7 +52400,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52423,7 +52426,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1847" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52449,7 +52452,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52475,7 +52478,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52501,7 +52504,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52527,7 +52530,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1851" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52553,7 +52556,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1852" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52579,7 +52582,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1853" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52605,7 +52608,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1854" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52631,7 +52634,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52657,7 +52660,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1856" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52683,7 +52686,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1857" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52709,7 +52712,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1858" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52735,7 +52738,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1859" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52761,7 +52764,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52787,7 +52790,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1861" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52813,7 +52816,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1862" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52839,7 +52842,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1863" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52865,7 +52868,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1864" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52891,7 +52894,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1865" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52917,7 +52920,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1866" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52943,7 +52946,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1867" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52969,7 +52972,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52995,7 +52998,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53021,7 +53024,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1870" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53047,7 +53050,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1871" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53073,7 +53076,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1872" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53099,7 +53102,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53125,7 +53128,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1874" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53151,7 +53154,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1875" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53177,7 +53180,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53203,7 +53206,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1877" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53229,7 +53232,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53255,7 +53258,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1879" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53281,7 +53284,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1880" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53307,7 +53310,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1881" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53333,7 +53336,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53359,7 +53362,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53385,7 +53388,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53411,7 +53414,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1885" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53437,7 +53440,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1886" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53463,7 +53466,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53489,7 +53492,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1888" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53515,7 +53518,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1889" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53541,7 +53544,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1890" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53567,7 +53570,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1891" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53593,7 +53596,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1892" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53619,7 +53622,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1893" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53645,7 +53648,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53671,7 +53674,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1895" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53697,7 +53700,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53723,7 +53726,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53853,7 +53856,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53983,7 +53986,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54035,7 +54038,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54165,7 +54168,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1914" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54191,7 +54194,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54243,7 +54246,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1917" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54321,7 +54324,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1920" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54373,7 +54376,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1922" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54451,7 +54454,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1925" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54477,7 +54480,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54607,7 +54610,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1931" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54633,7 +54636,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1932" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54659,7 +54662,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1933" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54711,7 +54714,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54815,7 +54818,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54841,7 +54844,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1940" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54945,7 +54948,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54971,7 +54974,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1945" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55023,7 +55026,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1947" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55257,7 +55260,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1956" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55387,7 +55390,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1961" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55413,7 +55416,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1962" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55439,7 +55442,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1963" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55465,7 +55468,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1964" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55491,7 +55494,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1965" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55647,7 +55650,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1971" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56037,7 +56040,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1986" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56271,7 +56274,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1995" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56349,7 +56352,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1998" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56401,7 +56404,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2000" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56479,7 +56482,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2003" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56505,7 +56508,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2004" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56531,7 +56534,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2005" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56557,7 +56560,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2006" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56583,7 +56586,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2007" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56687,7 +56690,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2011" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56869,7 +56872,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2018" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56895,7 +56898,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57207,7 +57210,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57233,7 +57236,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57311,7 +57314,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57337,7 +57340,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58143,7 +58146,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G2067" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58299,7 +58302,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58377,7 +58380,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58481,7 +58484,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58559,7 +58562,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -63239,7 +63242,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1191</v>
+        <v>1229</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63265,7 +63268,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63291,7 +63294,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63317,7 +63320,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63343,7 +63346,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63369,7 +63372,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63395,7 +63398,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63421,7 +63424,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63447,7 +63450,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63473,7 +63476,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63499,7 +63502,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63525,7 +63528,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63551,7 +63554,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63577,7 +63580,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63603,7 +63606,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63629,7 +63632,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63655,7 +63658,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63681,7 +63684,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63707,7 +63710,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63733,7 +63736,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63759,7 +63762,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63785,7 +63788,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63811,7 +63814,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63837,7 +63840,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63863,7 +63866,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63889,7 +63892,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63915,7 +63918,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63941,7 +63944,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63967,7 +63970,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63993,7 +63996,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64019,7 +64022,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64045,7 +64048,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64071,7 +64074,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64097,7 +64100,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64123,7 +64126,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64149,7 +64152,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64175,7 +64178,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64201,7 +64204,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64227,7 +64230,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64253,7 +64256,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64279,7 +64282,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64305,7 +64308,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64331,7 +64334,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64357,7 +64360,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64383,7 +64386,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64409,7 +64412,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64435,7 +64438,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64461,7 +64464,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64487,7 +64490,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64513,7 +64516,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64539,7 +64542,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64565,7 +64568,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64591,7 +64594,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64617,7 +64620,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64643,7 +64646,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64669,7 +64672,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64695,7 +64698,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64721,7 +64724,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64747,7 +64750,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64773,7 +64776,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64799,7 +64802,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64825,7 +64828,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64851,7 +64854,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64877,7 +64880,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64903,7 +64906,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64929,7 +64932,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64955,7 +64958,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64981,7 +64984,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65007,7 +65010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65033,7 +65036,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65059,7 +65062,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65085,7 +65088,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65111,7 +65114,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65137,7 +65140,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65163,7 +65166,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65189,7 +65192,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65215,7 +65218,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65241,7 +65244,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65267,7 +65270,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65293,7 +65296,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65319,7 +65322,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65345,7 +65348,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65371,7 +65374,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65397,7 +65400,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65423,7 +65426,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65449,7 +65452,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65475,7 +65478,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65501,7 +65504,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65527,7 +65530,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65553,7 +65556,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65579,7 +65582,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65605,7 +65608,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65631,7 +65634,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65657,7 +65660,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65683,7 +65686,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65709,7 +65712,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65735,7 +65738,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65761,7 +65764,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65787,7 +65790,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65813,7 +65816,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65839,7 +65842,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65865,7 +65868,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65891,7 +65894,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65917,7 +65920,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65943,7 +65946,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65969,7 +65972,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65995,7 +65998,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66021,7 +66024,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66047,7 +66050,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66073,7 +66076,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66099,7 +66102,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66125,7 +66128,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66151,7 +66154,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66177,7 +66180,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66203,7 +66206,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66229,7 +66232,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66255,7 +66258,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66281,7 +66284,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66307,7 +66310,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66333,7 +66336,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66359,7 +66362,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66385,7 +66388,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66411,7 +66414,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66437,7 +66440,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66463,7 +66466,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66489,7 +66492,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66515,7 +66518,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66541,7 +66544,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66567,7 +66570,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66593,7 +66596,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66619,7 +66622,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66645,7 +66648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66671,7 +66674,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66697,7 +66700,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66723,7 +66726,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66749,7 +66752,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66775,7 +66778,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66801,7 +66804,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66827,7 +66830,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66853,7 +66856,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66879,7 +66882,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66905,7 +66908,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66931,7 +66934,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66957,7 +66960,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66983,7 +66986,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67009,7 +67012,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67035,7 +67038,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67061,7 +67064,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67087,7 +67090,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67113,7 +67116,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67139,7 +67142,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67165,7 +67168,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67191,7 +67194,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67217,7 +67220,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67243,7 +67246,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67269,7 +67272,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67295,7 +67298,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67321,7 +67324,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67347,7 +67350,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67373,7 +67376,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67399,7 +67402,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67425,7 +67428,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67451,7 +67454,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67477,7 +67480,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67503,7 +67506,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67529,7 +67532,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67555,7 +67558,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67581,7 +67584,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67607,7 +67610,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67633,7 +67636,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67659,7 +67662,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67685,7 +67688,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67711,7 +67714,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67737,7 +67740,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67763,7 +67766,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67789,7 +67792,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67815,7 +67818,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67841,7 +67844,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67867,7 +67870,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67893,7 +67896,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67919,7 +67922,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67945,7 +67948,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67971,7 +67974,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67997,7 +68000,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68023,7 +68026,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68049,7 +68052,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68075,7 +68078,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68101,7 +68104,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68127,7 +68130,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68153,7 +68156,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68179,7 +68182,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68205,7 +68208,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68231,7 +68234,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68257,7 +68260,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68283,7 +68286,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68309,7 +68312,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68335,7 +68338,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68361,7 +68364,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68387,7 +68390,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68413,7 +68416,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68439,7 +68442,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68465,7 +68468,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68491,7 +68494,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68517,7 +68520,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68543,7 +68546,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68569,7 +68572,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68595,7 +68598,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68621,7 +68624,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68647,7 +68650,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68673,7 +68676,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68699,7 +68702,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68725,7 +68728,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68751,7 +68754,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68777,7 +68780,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68803,7 +68806,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68829,7 +68832,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68855,7 +68858,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68881,7 +68884,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68907,7 +68910,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68933,7 +68936,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68959,7 +68962,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68985,7 +68988,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69011,7 +69014,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69037,7 +69040,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69063,7 +69066,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69089,7 +69092,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69115,7 +69118,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69141,7 +69144,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69167,7 +69170,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2491" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69193,7 +69196,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2492" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69219,7 +69222,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2493" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69245,7 +69248,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2494" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69271,7 +69274,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2495" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69297,7 +69300,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69323,7 +69326,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2497" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69349,7 +69352,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2498" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69375,7 +69378,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2499" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69401,7 +69404,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2500" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69409,7 +69412,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911111111</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>107045</v>
@@ -69427,9 +69430,35 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2501" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6914583333</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>95390</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>1.03600001335144</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>1.02600002288818</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>1.03600001335144</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1354" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1353">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594636917114</t>
+    <t xml:space="preserve">0.378594607114792</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716715335846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367179721593857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380497127771378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789405345917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3522769510746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36813098192215</t>
+    <t xml:space="preserve">0.382716685533524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367179751396179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380497097969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789345741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352276921272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368131011724472</t>
   </si>
   <si>
     <t xml:space="preserve">0.387155801057816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410936862230301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390009582042694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373521387577057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886854887009</t>
+    <t xml:space="preserve">0.410936892032623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390009552240372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373521417379379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886884689331</t>
   </si>
   <si>
     <t xml:space="preserve">0.335471600294113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34561824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361472278833389</t>
+    <t xml:space="preserve">0.345618277788162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361472249031067</t>
   </si>
   <si>
     <t xml:space="preserve">0.341496169567108</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">0.357984393835068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350691497325897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.317080974578857</t>
+    <t xml:space="preserve">0.35069152712822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
     <t xml:space="preserve">0.291714459657669</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">0.297739028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275860458612442</t>
+    <t xml:space="preserve">0.27586042881012</t>
   </si>
   <si>
     <t xml:space="preserve">0.276240944862366</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">0.304461121559143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326593399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789066076279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329130053520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348471909761429</t>
+    <t xml:space="preserve">0.326593369245529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789095878601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32913002371788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348471969366074</t>
   </si>
   <si>
     <t xml:space="preserve">0.327544629573822</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">0.314671128988266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330081284046173</t>
+    <t xml:space="preserve">0.330081254243851</t>
   </si>
   <si>
     <t xml:space="preserve">0.334203332662582</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">0.368765115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325325071811676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318032205104828</t>
+    <t xml:space="preserve">0.325325042009354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31803223490715</t>
   </si>
   <si>
     <t xml:space="preserve">0.306236773729324</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.331032514572144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322788387537003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319934695959091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153974056244</t>
+    <t xml:space="preserve">0.322788417339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319934666156769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153944253922</t>
   </si>
   <si>
     <t xml:space="preserve">0.331666678190231</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">0.298880517482758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28588017821312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267743170261383</t>
+    <t xml:space="preserve">0.285880148410797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267743110656738</t>
   </si>
   <si>
     <t xml:space="preserve">0.260767370462418</t>
@@ -218,40 +218,40 @@
     <t xml:space="preserve">0.267489463090897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258738070726395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288543671369553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371618896722794</t>
+    <t xml:space="preserve">0.258738040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288543701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371618926525116</t>
   </si>
   <si>
     <t xml:space="preserve">0.364643096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367496848106384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369716376066208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.369399309158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388741254806519</t>
+    <t xml:space="preserve">0.367496818304062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36971640586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.369399279356003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388741225004196</t>
   </si>
   <si>
     <t xml:space="preserve">0.387790024280548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033472776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35703319311142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3741554915905</t>
+    <t xml:space="preserve">0.370033502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357033133506775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374155521392822</t>
   </si>
   <si>
     <t xml:space="preserve">0.377643406391144</t>
@@ -260,22 +260,22 @@
     <t xml:space="preserve">0.370984673500061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372253030538559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387472927570343</t>
+    <t xml:space="preserve">0.372253060340881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387472897768021</t>
   </si>
   <si>
     <t xml:space="preserve">0.377326339483261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439791262149811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453425735235214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454059958457947</t>
+    <t xml:space="preserve">0.439791291952133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453425765037537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454059898853302</t>
   </si>
   <si>
     <t xml:space="preserve">0.461669862270355</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">0.459133237600327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455645263195038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45627948641777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840680360794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485768049955368</t>
+    <t xml:space="preserve">0.455645322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456279546022415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840620756149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792250156403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485767990350723</t>
   </si>
   <si>
     <t xml:space="preserve">0.477841019630432</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.484816759824753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497817099094391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48925593495369</t>
+    <t xml:space="preserve">0.497817158699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4892558157444</t>
   </si>
   <si>
     <t xml:space="preserve">0.475621432065964</t>
@@ -323,52 +323,52 @@
     <t xml:space="preserve">0.488304644823074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493695050477982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48989000916481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548742055893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645662069321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084717988968</t>
+    <t xml:space="preserve">0.493694990873337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489890098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548801660538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468645721673965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084837198257</t>
   </si>
   <si>
     <t xml:space="preserve">0.49528044462204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486719280481339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48418265581131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497500091791153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507329523563385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50796365737915</t>
+    <t xml:space="preserve">0.486719220876694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48418253660202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497500032186508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50732958316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507963716983795</t>
   </si>
   <si>
     <t xml:space="preserve">0.514939486980438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510183274745941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515890598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526354432106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525720179080963</t>
+    <t xml:space="preserve">0.510183215141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515890717506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526354372501373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525720238685608</t>
   </si>
   <si>
     <t xml:space="preserve">0.52952516078949</t>
@@ -377,43 +377,43 @@
     <t xml:space="preserve">0.535866796970367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540305972099304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620844542980194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625917732715607</t>
+    <t xml:space="preserve">0.540305912494659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620844483375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625917792320251</t>
   </si>
   <si>
     <t xml:space="preserve">0.627503156661987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597697556018829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596112191677094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577087342739105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561867475509644</t>
+    <t xml:space="preserve">0.597697615623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596112132072449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57708740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561867415904999</t>
   </si>
   <si>
     <t xml:space="preserve">0.583428919315338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569160342216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566940784454346</t>
+    <t xml:space="preserve">0.569160282611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566940724849701</t>
   </si>
   <si>
     <t xml:space="preserve">0.559013724327087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551720917224884</t>
+    <t xml:space="preserve">0.551720857620239</t>
   </si>
   <si>
     <t xml:space="preserve">0.529208123683929</t>
@@ -422,22 +422,22 @@
     <t xml:space="preserve">0.516841948032379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517476141452789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516207814216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465791970491409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4835484623909</t>
+    <t xml:space="preserve">0.517476081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516207754611969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465791910886765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483548402786255</t>
   </si>
   <si>
     <t xml:space="preserve">0.549184203147888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547281742095947</t>
+    <t xml:space="preserve">0.547281682491302</t>
   </si>
   <si>
     <t xml:space="preserve">0.558379590511322</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">0.586599826812744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613868713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654455125331879</t>
+    <t xml:space="preserve">0.613868653774261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654455065727234</t>
   </si>
   <si>
     <t xml:space="preserve">0.665869951248169</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">0.623064041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633844792842865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622112929821014</t>
+    <t xml:space="preserve">0.63384473323822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622112810611725</t>
   </si>
   <si>
     <t xml:space="preserve">0.618942022323608</t>
@@ -482,22 +482,22 @@
     <t xml:space="preserve">0.628771543502808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634161949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629088580608368</t>
+    <t xml:space="preserve">0.63416188955307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629088640213013</t>
   </si>
   <si>
     <t xml:space="preserve">0.643674314022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644308626651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645576775074005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636064410209656</t>
+    <t xml:space="preserve">0.644308567047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64557683467865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636064469814301</t>
   </si>
   <si>
     <t xml:space="preserve">0.63479608297348</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">0.626234889030457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602453768253326</t>
+    <t xml:space="preserve">0.602453827857971</t>
   </si>
   <si>
     <t xml:space="preserve">0.588185131549835</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">0.589136362075806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.619893312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592941462993622</t>
+    <t xml:space="preserve">0.619893252849579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592941403388977</t>
   </si>
   <si>
     <t xml:space="preserve">0.600551307201385</t>
@@ -539,34 +539,34 @@
     <t xml:space="preserve">0.595795094966888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594526767730713</t>
+    <t xml:space="preserve">0.594526827335358</t>
   </si>
   <si>
     <t xml:space="preserve">0.591673076152802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601185441017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603087961673737</t>
+    <t xml:space="preserve">0.601185500621796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603087902069092</t>
   </si>
   <si>
     <t xml:space="preserve">0.609746634960175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611332058906555</t>
+    <t xml:space="preserve">0.6113321185112</t>
   </si>
   <si>
     <t xml:space="preserve">0.614185810089111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611966252326965</t>
+    <t xml:space="preserve">0.611966192722321</t>
   </si>
   <si>
     <t xml:space="preserve">0.605941712856293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598648905754089</t>
+    <t xml:space="preserve">0.5986487865448</t>
   </si>
   <si>
     <t xml:space="preserve">0.593258500099182</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">0.611015021800995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604039251804352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605307519435883</t>
+    <t xml:space="preserve">0.604039192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605307579040527</t>
   </si>
   <si>
     <t xml:space="preserve">0.61006373167038</t>
@@ -617,25 +617,25 @@
     <t xml:space="preserve">0.523183524608612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481963008642197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493377983570099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492109596729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508280813694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513988196849823</t>
+    <t xml:space="preserve">0.481963127851486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493377923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492109626531601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508280754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513988256454468</t>
   </si>
   <si>
     <t xml:space="preserve">0.509231984615326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509549140930176</t>
+    <t xml:space="preserve">0.509549081325531</t>
   </si>
   <si>
     <t xml:space="preserve">0.51779317855835</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">0.521598160266876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53047639131546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546013474464417</t>
+    <t xml:space="preserve">0.530476450920105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546013414859772</t>
   </si>
   <si>
     <t xml:space="preserve">0.54094010591507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532696068286896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.538720488548279</t>
+    <t xml:space="preserve">0.532696008682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.538720548152924</t>
   </si>
   <si>
     <t xml:space="preserve">0.539037644863129</t>
@@ -674,28 +674,28 @@
     <t xml:space="preserve">0.532061755657196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568843245506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570428669452667</t>
+    <t xml:space="preserve">0.568843305110931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570428609848022</t>
   </si>
   <si>
     <t xml:space="preserve">0.566306591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549501240253448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560599148273468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56440407037735</t>
+    <t xml:space="preserve">0.549501299858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560599088668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564404129981995</t>
   </si>
   <si>
     <t xml:space="preserve">0.550452530384064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542842626571655</t>
+    <t xml:space="preserve">0.54284256696701</t>
   </si>
   <si>
     <t xml:space="preserve">0.545062184333801</t>
@@ -704,22 +704,22 @@
     <t xml:space="preserve">0.521281123161316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516524851322174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50669538974762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528256893157959</t>
+    <t xml:space="preserve">0.516524910926819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506695449352264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528256833553314</t>
   </si>
   <si>
     <t xml:space="preserve">0.519695699214935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526037275791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518744349479675</t>
+    <t xml:space="preserve">0.526037335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51874440908432</t>
   </si>
   <si>
     <t xml:space="preserve">0.511451601982117</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">0.523817718029022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508597791194916</t>
+    <t xml:space="preserve">0.508597850799561</t>
   </si>
   <si>
     <t xml:space="preserve">0.522549390792847</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">0.513671159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511134505271912</t>
+    <t xml:space="preserve">0.511134564876556</t>
   </si>
   <si>
     <t xml:space="preserve">0.504158735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506061255931854</t>
+    <t xml:space="preserve">0.506061196327209</t>
   </si>
   <si>
     <t xml:space="preserve">0.505109965801239</t>
@@ -761,37 +761,37 @@
     <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54157429933548</t>
+    <t xml:space="preserve">0.541574239730835</t>
   </si>
   <si>
     <t xml:space="preserve">0.550769627094269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55362331867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560282051563263</t>
+    <t xml:space="preserve">0.553623378276825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560281991958618</t>
   </si>
   <si>
     <t xml:space="preserve">0.569794535636902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.575501978397369</t>
+    <t xml:space="preserve">0.575501918792725</t>
   </si>
   <si>
     <t xml:space="preserve">0.627820253372192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658894181251526</t>
+    <t xml:space="preserve">0.658894240856171</t>
   </si>
   <si>
     <t xml:space="preserve">0.655723392963409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.682358205318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262582778931</t>
+    <t xml:space="preserve">0.682358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262642383575</t>
   </si>
   <si>
     <t xml:space="preserve">0.736896097660065</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">0.707724690437317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696943819522858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733091115951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74894517660141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747676908969879</t>
+    <t xml:space="preserve">0.696943938732147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733091175556183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748945236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747676849365234</t>
   </si>
   <si>
     <t xml:space="preserve">0.754652678966522</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">0.755286812782288</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760360181331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81806880235672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799678146839142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771140873432159</t>
+    <t xml:space="preserve">0.76036012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818068861961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799678206443787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771140813827515</t>
   </si>
   <si>
     <t xml:space="preserve">0.768604159355164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720408022403717</t>
+    <t xml:space="preserve">0.720407962799072</t>
   </si>
   <si>
     <t xml:space="preserve">0.727383673191071</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">0.740701138973236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738164484500885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774945855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78382396697998</t>
+    <t xml:space="preserve">0.73816454410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774945795536041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.783824026584625</t>
   </si>
   <si>
     <t xml:space="preserve">0.801580667495728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.849777042865753</t>
+    <t xml:space="preserve">0.849776983261108</t>
   </si>
   <si>
     <t xml:space="preserve">0.884021699428558</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">0.878314197063446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894168198108673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876319408417</t>
+    <t xml:space="preserve">0.894168138504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876438617706</t>
   </si>
   <si>
     <t xml:space="preserve">0.924607932567596</t>
@@ -881,49 +881,49 @@
     <t xml:space="preserve">0.901778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881484985351562</t>
+    <t xml:space="preserve">0.881485044956207</t>
   </si>
   <si>
     <t xml:space="preserve">0.902412354946136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.87514328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896070718765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910656571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827180862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.9100221991539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729082584381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892899870872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.895436644554138</t>
+    <t xml:space="preserve">0.87514340877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896070659160614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9106565117836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827240467072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910022258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889729261398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892899930477142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.895436584949493</t>
   </si>
   <si>
     <t xml:space="preserve">0.863094329833984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860557675361633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533564567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87577760219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868167579174042</t>
+    <t xml:space="preserve">0.860557615756989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875777661800385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868167638778687</t>
   </si>
   <si>
     <t xml:space="preserve">0.756555140018463</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">0.788897335529327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812995493412018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80728816986084</t>
+    <t xml:space="preserve">0.812995433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807288229465485</t>
   </si>
   <si>
     <t xml:space="preserve">0.838362097740173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790165722370148</t>
+    <t xml:space="preserve">0.790165781974792</t>
   </si>
   <si>
     <t xml:space="preserve">0.786360740661621</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">0.811727285385132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.83011794090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814898073673248</t>
+    <t xml:space="preserve">0.830117881298065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814898014068604</t>
   </si>
   <si>
     <t xml:space="preserve">0.792702436447144</t>
@@ -962,31 +962,31 @@
     <t xml:space="preserve">0.803483128547668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.804117202758789</t>
+    <t xml:space="preserve">0.804117262363434</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848375797272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780019164085388</t>
+    <t xml:space="preserve">0.780019104480743</t>
   </si>
   <si>
     <t xml:space="preserve">0.781921684741974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791434049606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785092532634735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994993686676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970704078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531588554382</t>
+    <t xml:space="preserve">0.791433990001678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78509247303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786995053291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79397064447403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531528949738</t>
   </si>
   <si>
     <t xml:space="preserve">0.77367752790451</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">0.775580048561096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769872546195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.767335951328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.771775126457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76162850856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79587310552597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811093091964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843435347080231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654654979706</t>
+    <t xml:space="preserve">0.769872486591339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767335891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77177506685257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761628389358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79587322473526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811093151569366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435406684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654476165771</t>
   </si>
   <si>
     <t xml:space="preserve">0.872606813907623</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">0.862460136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866899311542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840264499187469</t>
+    <t xml:space="preserve">0.866899371147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840264558792114</t>
   </si>
   <si>
     <t xml:space="preserve">0.830752074718475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.855484485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142670631409</t>
+    <t xml:space="preserve">0.855484366416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801034450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142730236053</t>
   </si>
   <si>
     <t xml:space="preserve">0.820605576038361</t>
@@ -1055,40 +1055,40 @@
     <t xml:space="preserve">0.806019842624664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799043953418732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804751396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785726606845856</t>
+    <t xml:space="preserve">0.799043893814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804751515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785726547241211</t>
   </si>
   <si>
     <t xml:space="preserve">0.778750836849213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.777482509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802214741706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806653797626495</t>
+    <t xml:space="preserve">0.777482450008392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802214801311493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665385723114</t>
   </si>
   <si>
     <t xml:space="preserve">0.807922303676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.854850232601166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.857386887073517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85231351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.863728404045105</t>
+    <t xml:space="preserve">0.854850351810455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.857386946678162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.852313578128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.863728523254395</t>
   </si>
   <si>
     <t xml:space="preserve">0.86499685049057</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">0.840898752212524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.834556996822357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581167221069</t>
+    <t xml:space="preserve">0.834557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996112346649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581226825714</t>
   </si>
   <si>
     <t xml:space="preserve">0.826312899589539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.805385649204254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814263939857483</t>
+    <t xml:space="preserve">0.805385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814263880252838</t>
   </si>
   <si>
     <t xml:space="preserve">0.81870299577713</t>
@@ -1127,28 +1127,28 @@
     <t xml:space="preserve">0.79650741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809190571308136</t>
+    <t xml:space="preserve">0.809190630912781</t>
   </si>
   <si>
     <t xml:space="preserve">0.809824764728546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797775626182556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798409759998322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817434787750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823142230510712</t>
+    <t xml:space="preserve">0.797775685787201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.798409879207611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817434668540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823142111301422</t>
   </si>
   <si>
     <t xml:space="preserve">0.812361419200897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.819971203804016</t>
+    <t xml:space="preserve">0.819971323013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.797141492366791</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">0.716602921485901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.7045539021492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736261963844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772409200668335</t>
+    <t xml:space="preserve">0.704553842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736262023448944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759725868701935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77240914106369</t>
   </si>
   <si>
     <t xml:space="preserve">0.776214122772217</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">0.752116024494171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760994255542755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701638698578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790799975395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810458779335022</t>
+    <t xml:space="preserve">0.76099419593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823526859283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790799915790558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810458838939667</t>
   </si>
   <si>
     <t xml:space="preserve">0.774311602115631</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">0.764799237251282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731822848320007</t>
+    <t xml:space="preserve">0.731822907924652</t>
   </si>
   <si>
     <t xml:space="preserve">0.711529612541199</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">0.693773150444031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739432752132416</t>
+    <t xml:space="preserve">0.739432811737061</t>
   </si>
   <si>
     <t xml:space="preserve">0.70391970872879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695041358470917</t>
+    <t xml:space="preserve">0.695041418075562</t>
   </si>
   <si>
     <t xml:space="preserve">0.683626472949982</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">0.670943200588226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69123649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678553342819214</t>
+    <t xml:space="preserve">0.691236555576324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678553283214569</t>
   </si>
   <si>
     <t xml:space="preserve">0.687431514263153</t>
@@ -1262,67 +1262,67 @@
     <t xml:space="preserve">0.710261344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697578132152557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.714066386222839</t>
+    <t xml:space="preserve">0.697578191757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71406626701355</t>
   </si>
   <si>
     <t xml:space="preserve">0.729286193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753384232521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748310983181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757189273834229</t>
+    <t xml:space="preserve">0.753384292125702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748311042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757189214229584</t>
   </si>
   <si>
     <t xml:space="preserve">0.758457660675049</t>
   </si>
   <si>
-    <t xml:space="preserve">0.763530910015106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74957948923111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042775154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735627830028534</t>
+    <t xml:space="preserve">0.763530850410461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749579429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042834758759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735627889633179</t>
   </si>
   <si>
     <t xml:space="preserve">0.745774388313293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743237793445587</t>
+    <t xml:space="preserve">0.743237853050232</t>
   </si>
   <si>
     <t xml:space="preserve">0.741969347000122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.744506061077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722944557666779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.700114786624908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456303596497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846399784088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.725481271743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71533465385437</t>
+    <t xml:space="preserve">0.744506120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722944498062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700114727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456363201141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846340179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.72548121213913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715334713459015</t>
   </si>
   <si>
     <t xml:space="preserve">0.712797939777374</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">0.681089878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701382994651794</t>
+    <t xml:space="preserve">0.701383054256439</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686163187026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.679821610450745</t>
+    <t xml:space="preserve">0.688699781894684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686163246631622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6798215508461</t>
   </si>
   <si>
     <t xml:space="preserve">0.672211587429047</t>
@@ -1361,34 +1361,34 @@
     <t xml:space="preserve">0.677284836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658260107040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.659528315067291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651918411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.648113369941711</t>
+    <t xml:space="preserve">0.65826004743576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.659528374671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651918351650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648113429546356</t>
   </si>
   <si>
     <t xml:space="preserve">0.641771793365479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635430216789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643040239810944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639235198497772</t>
+    <t xml:space="preserve">0.63543027639389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643040180206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639235258102417</t>
   </si>
   <si>
     <t xml:space="preserve">0.637966930866241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594209671020508</t>
+    <t xml:space="preserve">0.594209611415863</t>
   </si>
   <si>
     <t xml:space="preserve">0.596746325492859</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">0.609429597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598014712333679</t>
+    <t xml:space="preserve">0.598014652729034</t>
   </si>
   <si>
     <t xml:space="preserve">0.599917113780975</t>
@@ -1409,16 +1409,16 @@
     <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478617191315</t>
+    <t xml:space="preserve">0.621478676795959</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274706363678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615771174430847</t>
+    <t xml:space="preserve">0.62274694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615771234035492</t>
   </si>
   <si>
     <t xml:space="preserve">0.6233811378479</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">0.591038882732391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.584063172340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580892324447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565672338008881</t>
+    <t xml:space="preserve">0.584063112735748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580892205238342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56567245721817</t>
   </si>
   <si>
     <t xml:space="preserve">0.570745766162872</t>
@@ -1445,43 +1445,43 @@
     <t xml:space="preserve">0.561233282089233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572648227214813</t>
+    <t xml:space="preserve">0.572648286819458</t>
   </si>
   <si>
     <t xml:space="preserve">0.559964954853058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135243415833</t>
+    <t xml:space="preserve">0.537135124206543</t>
   </si>
   <si>
     <t xml:space="preserve">0.528891086578369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573282361030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569477379322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608795464038849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307948112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630356907844543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604990482330322</t>
+    <t xml:space="preserve">0.573282420635223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569477438926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608795404434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307888507843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356967449188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604990422725677</t>
   </si>
   <si>
     <t xml:space="preserve">0.580258190631866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572014033794403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568209052085876</t>
+    <t xml:space="preserve">0.572013974189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568209111690521</t>
   </si>
   <si>
     <t xml:space="preserve">0.554891645908356</t>
@@ -1493,61 +1493,61 @@
     <t xml:space="preserve">0.721676230430603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.766067564487457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782555758953094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215360641479</t>
+    <t xml:space="preserve">0.766067504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78255569934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215420246124</t>
   </si>
   <si>
     <t xml:space="preserve">0.825678765773773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.873875021934509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871338427066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753252983093</t>
+    <t xml:space="preserve">0.873875200748444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871338307857513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753372192383</t>
   </si>
   <si>
     <t xml:space="preserve">0.880216777324677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903046548366547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.922071397304535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937291324138641</t>
+    <t xml:space="preserve">0.903046429157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922071278095245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937291443347931</t>
   </si>
   <si>
     <t xml:space="preserve">0.918266475200653</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866265177726746</t>
+    <t xml:space="preserve">0.86626523733139</t>
   </si>
   <si>
     <t xml:space="preserve">0.839630365371704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.896704912185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87641179561615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801891803741</t>
+    <t xml:space="preserve">0.896704971790314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876411736011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801951408386</t>
   </si>
   <si>
     <t xml:space="preserve">0.870070159435272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938559710979462</t>
+    <t xml:space="preserve">0.938559591770172</t>
   </si>
   <si>
     <t xml:space="preserve">0.934754550457001</t>
@@ -1559,31 +1559,31 @@
     <t xml:space="preserve">0.905583143234253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.929681360721588</t>
+    <t xml:space="preserve">0.929681241512299</t>
   </si>
   <si>
     <t xml:space="preserve">0.927144765853882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.906851470470428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930949687957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.891631782054901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.833288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873724460602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802849054336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755921065807343</t>
+    <t xml:space="preserve">0.906851530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930949568748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.891631662845612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.833288729190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873784065247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802848994731903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755921006202698</t>
   </si>
   <si>
     <t xml:space="preserve">0.640503525733948</t>
@@ -1592,25 +1592,25 @@
     <t xml:space="preserve">0.636698484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627019286155701</t>
+    <t xml:space="preserve">0.627019226551056</t>
   </si>
   <si>
     <t xml:space="preserve">0.641851961612701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625670731067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613535046577454</t>
+    <t xml:space="preserve">0.625670790672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534986972809</t>
   </si>
   <si>
     <t xml:space="preserve">0.616906046867371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618928670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595331192016602</t>
+    <t xml:space="preserve">0.618928611278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595331132411957</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">0.596005320549011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60207337141037</t>
+    <t xml:space="preserve">0.60207325220108</t>
   </si>
   <si>
     <t xml:space="preserve">0.598028004169464</t>
@@ -1649,28 +1649,28 @@
     <t xml:space="preserve">0.656684696674347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637132406234741</t>
+    <t xml:space="preserve">0.637132465839386</t>
   </si>
   <si>
     <t xml:space="preserve">0.626345038414001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62836766242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624322354793549</t>
+    <t xml:space="preserve">0.628367602825165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624322414398193</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716157913208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627693474292755</t>
+    <t xml:space="preserve">0.62769341468811</t>
   </si>
   <si>
     <t xml:space="preserve">0.614883363246918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608815431594849</t>
+    <t xml:space="preserve">0.608815491199493</t>
   </si>
   <si>
     <t xml:space="preserve">0.617580235004425</t>
@@ -1682,22 +1682,22 @@
     <t xml:space="preserve">0.624996602535248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614209115505219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605444431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606118559837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630390286445618</t>
+    <t xml:space="preserve">0.614209234714508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605444371700287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606118619441986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630390346050262</t>
   </si>
   <si>
     <t xml:space="preserve">0.643200397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656010389328003</t>
+    <t xml:space="preserve">0.656010448932648</t>
   </si>
   <si>
     <t xml:space="preserve">0.633761346340179</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">0.61218649148941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621625602245331</t>
+    <t xml:space="preserve">0.621625542640686</t>
   </si>
   <si>
     <t xml:space="preserve">0.608141243457794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610163927078247</t>
+    <t xml:space="preserve">0.610163867473602</t>
   </si>
   <si>
     <t xml:space="preserve">0.549484610557556</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">0.552855610847473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565665721893311</t>
+    <t xml:space="preserve">0.565665781497955</t>
   </si>
   <si>
     <t xml:space="preserve">0.578475773334503</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558923602104187</t>
+    <t xml:space="preserve">0.558923542499542</t>
   </si>
   <si>
     <t xml:space="preserve">0.563643097877502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569711089134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249354362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562294602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573082089424133</t>
+    <t xml:space="preserve">0.569711029529572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249413967133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562294661998749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573082149028778</t>
   </si>
   <si>
     <t xml:space="preserve">0.583869457244873</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">0.584543704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567014217376709</t>
+    <t xml:space="preserve">0.567014157772064</t>
   </si>
   <si>
     <t xml:space="preserve">0.566339910030365</t>
@@ -1763,52 +1763,52 @@
     <t xml:space="preserve">0.593308568000793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599376440048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586566388607025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591285824775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600050687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602747559547424</t>
+    <t xml:space="preserve">0.599376380443573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58656632900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591285884380341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600050628185272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60274749994278</t>
   </si>
   <si>
     <t xml:space="preserve">0.607466995716095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590611636638641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592634260654449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587914764881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618254423141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639829277992249</t>
+    <t xml:space="preserve">0.590611696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592634320259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587914824485779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618254363536835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639829337596893</t>
   </si>
   <si>
     <t xml:space="preserve">0.641177713871002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588589072227478</t>
+    <t xml:space="preserve">0.588589012622833</t>
   </si>
   <si>
     <t xml:space="preserve">0.598702251911163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620277106761932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62297397851944</t>
+    <t xml:space="preserve">0.620277047157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622973918914795</t>
   </si>
   <si>
     <t xml:space="preserve">0.609489679336548</t>
@@ -1817,16 +1817,16 @@
     <t xml:space="preserve">0.615557551383972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620951354503632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64859414100647</t>
+    <t xml:space="preserve">0.620951294898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648594081401825</t>
   </si>
   <si>
     <t xml:space="preserve">0.604770183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604095935821533</t>
+    <t xml:space="preserve">0.604095995426178</t>
   </si>
   <si>
     <t xml:space="preserve">0.603421688079834</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638480961322784</t>
+    <t xml:space="preserve">0.638480842113495</t>
   </si>
   <si>
     <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695789098739624</t>
+    <t xml:space="preserve">0.695789039134979</t>
   </si>
   <si>
     <t xml:space="preserve">0.714667022228241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.702531218528748</t>
+    <t xml:space="preserve">0.702531278133392</t>
   </si>
   <si>
     <t xml:space="preserve">0.699834406375885</t>
@@ -1856,55 +1856,55 @@
     <t xml:space="preserve">0.716015577316284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.728151500225067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717363953590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.726802885532379</t>
+    <t xml:space="preserve">0.728151440620422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717363893985748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.726802825927734</t>
   </si>
   <si>
     <t xml:space="preserve">0.722757637500763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.721409261226654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711970210075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701182782649994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694440603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.689046919345856</t>
+    <t xml:space="preserve">0.721409201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711970269680023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701182723045349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69444066286087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6890469789505</t>
   </si>
   <si>
     <t xml:space="preserve">0.683653235435486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67960798740387</t>
+    <t xml:space="preserve">0.679607927799225</t>
   </si>
   <si>
     <t xml:space="preserve">0.680956363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672191560268402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.685001730918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675562560558319</t>
+    <t xml:space="preserve">0.672191619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68500167131424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675562620162964</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146312236786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631738722324371</t>
+    <t xml:space="preserve">0.631738662719727</t>
   </si>
   <si>
     <t xml:space="preserve">0.632412970066071</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">0.645897269248962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636458277702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63308721780777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611512303352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574430465698242</t>
+    <t xml:space="preserve">0.636458218097687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633087158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611512243747711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.574430525302887</t>
   </si>
   <si>
     <t xml:space="preserve">0.589263260364532</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">0.560272037982941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553529918193817</t>
+    <t xml:space="preserve">0.553529858589172</t>
   </si>
   <si>
     <t xml:space="preserve">0.538697242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527235567569733</t>
+    <t xml:space="preserve">0.527235507965088</t>
   </si>
   <si>
     <t xml:space="preserve">0.478692084550858</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">0.458465665578842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391044199466705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419361263513565</t>
+    <t xml:space="preserve">0.39104425907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419361233711243</t>
   </si>
   <si>
     <t xml:space="preserve">0.394415289163589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387673139572144</t>
+    <t xml:space="preserve">0.387673199176788</t>
   </si>
   <si>
     <t xml:space="preserve">0.38834735751152</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">0.403180062770844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412619084119797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431497097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465207874774933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.469927281141281</t>
+    <t xml:space="preserve">0.412619113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431497067213058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465207785367966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.469927340745926</t>
   </si>
   <si>
     <t xml:space="preserve">0.479366362094879</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">0.464533567428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483411610126495</t>
+    <t xml:space="preserve">0.483411550521851</t>
   </si>
   <si>
     <t xml:space="preserve">0.498918533325195</t>
@@ -2009,19 +2009,19 @@
     <t xml:space="preserve">0.496895879507065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.495547533035278</t>
+    <t xml:space="preserve">0.495547473430634</t>
   </si>
   <si>
     <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482063204050064</t>
+    <t xml:space="preserve">0.482063144445419</t>
   </si>
   <si>
     <t xml:space="preserve">0.490827918052673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484760046005249</t>
+    <t xml:space="preserve">0.484760016202927</t>
   </si>
   <si>
     <t xml:space="preserve">0.480714738368988</t>
@@ -2045,40 +2045,40 @@
     <t xml:space="preserve">0.427451848983765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43486812710762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438239216804504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443632990121841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430148661136627</t>
+    <t xml:space="preserve">0.434868156909943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438239246606827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443632960319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43014869093895</t>
   </si>
   <si>
     <t xml:space="preserve">0.409248024225235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434212177991867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410049855709076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892371416092</t>
+    <t xml:space="preserve">0.434212207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410049796104431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892401218414</t>
   </si>
   <si>
     <t xml:space="preserve">0.449135959148407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451267927885056</t>
+    <t xml:space="preserve">0.4512679874897</t>
   </si>
   <si>
     <t xml:space="preserve">0.456953287124634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486800879240036</t>
+    <t xml:space="preserve">0.486800938844681</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">0.466191828250885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466902524232864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48040497303009</t>
+    <t xml:space="preserve">0.46690246462822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480405002832413</t>
   </si>
   <si>
     <t xml:space="preserve">0.498882085084915</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">0.445582687854767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.442740082740784</t>
+    <t xml:space="preserve">0.442740112543106</t>
   </si>
   <si>
     <t xml:space="preserve">0.452689319849014</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">0.447004020214081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450557321310043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44842529296875</t>
+    <t xml:space="preserve">0.450557351112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448425352573395</t>
   </si>
   <si>
     <t xml:space="preserve">0.442029416561127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42994824051857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438476145267487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429237574338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447714656591415</t>
+    <t xml:space="preserve">0.429948210716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438476085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429237604141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44771471619606</t>
   </si>
   <si>
     <t xml:space="preserve">0.439186781644821</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">0.458374559879303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.444161385297775</t>
+    <t xml:space="preserve">0.444161355495453</t>
   </si>
   <si>
     <t xml:space="preserve">0.456242650747299</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">0.449846684932709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.455531984567642</t>
+    <t xml:space="preserve">0.455531865358353</t>
   </si>
   <si>
     <t xml:space="preserve">0.443450778722763</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">0.430658876895905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420709699392319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.427816301584244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.413603067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417156368494034</t>
+    <t xml:space="preserve">0.420709669589996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427816212177277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.413603097200394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417156428098679</t>
   </si>
   <si>
     <t xml:space="preserve">0.416445732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427105605602264</t>
+    <t xml:space="preserve">0.427105635404587</t>
   </si>
   <si>
     <t xml:space="preserve">0.437054812908173</t>
@@ -2192,37 +2192,37 @@
     <t xml:space="preserve">0.432080209255219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434922814369202</t>
+    <t xml:space="preserve">0.434922873973846</t>
   </si>
   <si>
     <t xml:space="preserve">0.422841668128967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417866975069046</t>
+    <t xml:space="preserve">0.417867064476013</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496554613113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.40791779756546</t>
+    <t xml:space="preserve">0.407917827367783</t>
   </si>
   <si>
     <t xml:space="preserve">0.397968590259552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403653919696808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401521950960159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405075192451477</t>
+    <t xml:space="preserve">0.403653889894485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401521921157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405075162649155</t>
   </si>
   <si>
     <t xml:space="preserve">0.40081125497818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387308746576309</t>
+    <t xml:space="preserve">0.387308716773987</t>
   </si>
   <si>
     <t xml:space="preserve">0.385176748037338</t>
@@ -2237,34 +2237,34 @@
     <t xml:space="preserve">0.398679256439209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.409339129924774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395836621522903</t>
+    <t xml:space="preserve">0.409339100122452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395836651325226</t>
   </si>
   <si>
     <t xml:space="preserve">0.382334142923355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370963573455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383755505084991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366699635982513</t>
+    <t xml:space="preserve">0.370963603258133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383755475282669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366699606180191</t>
   </si>
   <si>
     <t xml:space="preserve">0.363146364688873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3539077937603</t>
+    <t xml:space="preserve">0.353907823562622</t>
   </si>
   <si>
     <t xml:space="preserve">0.356750428676605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359593063592911</t>
+    <t xml:space="preserve">0.359593033790588</t>
   </si>
   <si>
     <t xml:space="preserve">0.358882397413254</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151351690292</t>
+    <t xml:space="preserve">0.388730019330978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151381492615</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">0.372384905815125</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36385703086853</t>
+    <t xml:space="preserve">0.363857001066208</t>
   </si>
   <si>
     <t xml:space="preserve">0.361725032329559</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">0.351775795221329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065158843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.334009379148483</t>
+    <t xml:space="preserve">0.351065188646317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.334009349346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.323349505662918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342181950807571</t>
+    <t xml:space="preserve">0.342181921005249</t>
   </si>
   <si>
     <t xml:space="preserve">0.337207347154617</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">0.337562680244446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343958556652069</t>
+    <t xml:space="preserve">0.343958586454391</t>
   </si>
   <si>
     <t xml:space="preserve">0.361014395952225</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">0.36030375957489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.389440685510635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396547317504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41218176484108</t>
+    <t xml:space="preserve">0.38944074511528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396547347307205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412181794643402</t>
   </si>
   <si>
     <t xml:space="preserve">0.421420335769653</t>
@@ -2345,28 +2345,28 @@
     <t xml:space="preserve">0.415024399757385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419999063014984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313763380051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405785828828812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402232557535172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418577671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419288367033005</t>
+    <t xml:space="preserve">0.419999033212662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313733577728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405785858631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402232527732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418577700853348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419288337230682</t>
   </si>
   <si>
     <t xml:space="preserve">0.399389892816544</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393704682588577</t>
+    <t xml:space="preserve">0.393704652786255</t>
   </si>
   <si>
     <t xml:space="preserve">0.392993986606598</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">0.391572713851929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397257924079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.404364556074142</t>
+    <t xml:space="preserve">0.397257953882217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40436452627182</t>
   </si>
   <si>
     <t xml:space="preserve">0.395125955343246</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">0.386598110198975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380202174186707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806238174438</t>
+    <t xml:space="preserve">0.380202144384384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806267976761</t>
   </si>
   <si>
     <t xml:space="preserve">0.369542241096497</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">0.428526908159256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423552304506302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.436344116926193</t>
+    <t xml:space="preserve">0.423552334308624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.436344176530838</t>
   </si>
   <si>
     <t xml:space="preserve">0.426394939422607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440608084201813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897477626801</t>
+    <t xml:space="preserve">0.440608143806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897507429123</t>
   </si>
   <si>
     <t xml:space="preserve">0.464770466089249</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">0.478983670473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492486149072647</t>
+    <t xml:space="preserve">0.492486208677292</t>
   </si>
   <si>
     <t xml:space="preserve">0.515227258205414</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50669926404953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51735919713974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508120715618134</t>
+    <t xml:space="preserve">0.506699323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517359137535095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508120656013489</t>
   </si>
   <si>
     <t xml:space="preserve">0.5138059258461</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">0.507409989833832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513095200061798</t>
+    <t xml:space="preserve">0.513095259666443</t>
   </si>
   <si>
     <t xml:space="preserve">0.522333800792694</t>
@@ -2465,37 +2465,37 @@
     <t xml:space="preserve">0.537257611751556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523755073547363</t>
+    <t xml:space="preserve">0.523755133152008</t>
   </si>
   <si>
     <t xml:space="preserve">0.525887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526597738265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525176405906677</t>
+    <t xml:space="preserve">0.526597678661346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525176525115967</t>
   </si>
   <si>
     <t xml:space="preserve">0.530151009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524465680122375</t>
+    <t xml:space="preserve">0.52446573972702</t>
   </si>
   <si>
     <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544364213943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.541521608829498</t>
+    <t xml:space="preserve">0.544364154338837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.541521668434143</t>
   </si>
   <si>
     <t xml:space="preserve">0.536546945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528729736804962</t>
+    <t xml:space="preserve">0.528729677200317</t>
   </si>
   <si>
     <t xml:space="preserve">0.518780529499054</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">0.53157240152359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542942941188812</t>
+    <t xml:space="preserve">0.542942881584167</t>
   </si>
   <si>
     <t xml:space="preserve">0.54933887720108</t>
@@ -2522,28 +2522,28 @@
     <t xml:space="preserve">0.564973294734955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550941228866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549464225769043</t>
+    <t xml:space="preserve">0.550941288471222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549464166164398</t>
   </si>
   <si>
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647783756256</t>
+    <t xml:space="preserve">0.537647724151611</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569843292236</t>
+    <t xml:space="preserve">0.526569902896881</t>
   </si>
   <si>
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753401279449</t>
+    <t xml:space="preserve">0.514753460884094</t>
   </si>
   <si>
     <t xml:space="preserve">0.518446087837219</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">0.533955156803131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544294476509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556849479675293</t>
+    <t xml:space="preserve">0.544294536113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556849539279938</t>
   </si>
   <si>
     <t xml:space="preserve">0.546510100364685</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">0.563496232032776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566450417041779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572358548641205</t>
+    <t xml:space="preserve">0.566450297832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57235848903656</t>
   </si>
   <si>
     <t xml:space="preserve">0.581220865249634</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511799335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50958377122879</t>
+    <t xml:space="preserve">0.511799395084381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509583711624146</t>
   </si>
   <si>
     <t xml:space="preserve">0.506629586219788</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">0.488166451454163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483735263347626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48890495300293</t>
+    <t xml:space="preserve">0.483735203742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488905012607574</t>
   </si>
   <si>
     <t xml:space="preserve">0.480781197547913</t>
@@ -2648,25 +2648,25 @@
     <t xml:space="preserve">0.48151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492597639560699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522138774394989</t>
+    <t xml:space="preserve">0.492597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534693658351898</t>
+    <t xml:space="preserve">0.534693598747253</t>
   </si>
   <si>
     <t xml:space="preserve">0.532478094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519923150539398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.517707526683807</t>
+    <t xml:space="preserve">0.519923090934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.517707467079163</t>
   </si>
   <si>
     <t xml:space="preserve">0.512537837028503</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">0.525092840194702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545032978057861</t>
+    <t xml:space="preserve">0.545033037662506</t>
   </si>
   <si>
     <t xml:space="preserve">0.528785526752472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533216595649719</t>
+    <t xml:space="preserve">0.533216655254364</t>
   </si>
   <si>
     <t xml:space="preserve">0.520661652088165</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">0.515491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508106648921967</t>
+    <t xml:space="preserve">0.508106708526611</t>
   </si>
   <si>
     <t xml:space="preserve">0.505152583122253</t>
@@ -2714,19 +2714,19 @@
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721395015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771539211273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540601909160614</t>
+    <t xml:space="preserve">0.500721335411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771658420563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540601849555969</t>
   </si>
   <si>
     <t xml:space="preserve">0.553895354270935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55020272731781</t>
+    <t xml:space="preserve">0.550202786922455</t>
   </si>
   <si>
     <t xml:space="preserve">0.547987163066864</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">0.538386285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530262529850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539863348007202</t>
+    <t xml:space="preserve">0.530262470245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539863407611847</t>
   </si>
   <si>
     <t xml:space="preserve">0.613716125488281</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">0.641780078411102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62257844209671</t>
+    <t xml:space="preserve">0.622578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612977623939514</t>
+    <t xml:space="preserve">0.612977564334869</t>
   </si>
   <si>
     <t xml:space="preserve">0.616670191287994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629963636398315</t>
+    <t xml:space="preserve">0.62996369600296</t>
   </si>
   <si>
     <t xml:space="preserve">0.620362818241119</t>
@@ -2774,25 +2774,25 @@
     <t xml:space="preserve">0.5945143699646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599684000015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589344680309296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600422561168671</t>
+    <t xml:space="preserve">0.599684059619904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.589344620704651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600422620773315</t>
   </si>
   <si>
     <t xml:space="preserve">0.607069373130798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593037247657776</t>
+    <t xml:space="preserve">0.593037307262421</t>
   </si>
   <si>
     <t xml:space="preserve">0.597468495368958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592298746109009</t>
+    <t xml:space="preserve">0.592298805713654</t>
   </si>
   <si>
     <t xml:space="preserve">0.603376686573029</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">0.664674401283264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66688996553421</t>
+    <t xml:space="preserve">0.666890025138855</t>
   </si>
   <si>
     <t xml:space="preserve">0.658766210079193</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">0.642518639564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640303075313568</t>
+    <t xml:space="preserve">0.640303015708923</t>
   </si>
   <si>
     <t xml:space="preserve">0.633656322956085</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">0.675752341747284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649165332317352</t>
+    <t xml:space="preserve">0.649165391921997</t>
   </si>
   <si>
     <t xml:space="preserve">0.65581214427948</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">0.618147253990173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625532567501068</t>
+    <t xml:space="preserve">0.625532507896423</t>
   </si>
   <si>
     <t xml:space="preserve">0.638087451457977</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">0.626271069049835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.630702137947083</t>
+    <t xml:space="preserve">0.630702197551727</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2879,43 +2879,43 @@
     <t xml:space="preserve">0.657289147377014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662458896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678706467151642</t>
+    <t xml:space="preserve">0.662458837032318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678706526756287</t>
   </si>
   <si>
     <t xml:space="preserve">0.676490843296051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673536717891693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661720335483551</t>
+    <t xml:space="preserve">0.673536777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661720395088196</t>
   </si>
   <si>
     <t xml:space="preserve">0.635133385658264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576789796352386</t>
+    <t xml:space="preserve">0.576789736747742</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587867617607117</t>
+    <t xml:space="preserve">0.587867677211761</t>
   </si>
   <si>
     <t xml:space="preserve">0.507368087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711855888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564234793186188</t>
+    <t xml:space="preserve">0.529523968696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711796283722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564234733581543</t>
   </si>
   <si>
     <t xml:space="preserve">0.582697927951813</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">0.559803605079651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547248661518097</t>
+    <t xml:space="preserve">0.547248601913452</t>
   </si>
   <si>
     <t xml:space="preserve">0.536909222602844</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">0.567188918590546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5797438621521</t>
+    <t xml:space="preserve">0.579743921756744</t>
   </si>
   <si>
     <t xml:space="preserve">0.562019169330597</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555372357368469</t>
+    <t xml:space="preserve">0.555372416973114</t>
   </si>
   <si>
     <t xml:space="preserve">0.569404482841492</t>
@@ -2960,28 +2960,28 @@
     <t xml:space="preserve">0.574574112892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58257657289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973728179932</t>
+    <t xml:space="preserve">0.582576513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973668575287</t>
   </si>
   <si>
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572912693024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56817215681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169756412506</t>
+    <t xml:space="preserve">0.570572972297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568172216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169816017151</t>
   </si>
   <si>
     <t xml:space="preserve">0.562570512294769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569772660732269</t>
+    <t xml:space="preserve">0.569772720336914</t>
   </si>
   <si>
     <t xml:space="preserve">0.578575372695923</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">0.571373164653778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564971268177032</t>
+    <t xml:space="preserve">0.564971208572388</t>
   </si>
   <si>
     <t xml:space="preserve">0.552967607975006</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">0.54656571149826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537762939929962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755738735199</t>
+    <t xml:space="preserve">0.537762999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755679130554</t>
   </si>
   <si>
     <t xml:space="preserve">0.516156435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525759398937225</t>
+    <t xml:space="preserve">0.525759339332581</t>
   </si>
   <si>
     <t xml:space="preserve">0.521758139133453</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">0.522558391094208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53296160697937</t>
+    <t xml:space="preserve">0.532961547374725</t>
   </si>
   <si>
     <t xml:space="preserve">0.524959087371826</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">0.48814794421196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561770260334015</t>
+    <t xml:space="preserve">0.56177031993866</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">0.588978469371796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56897246837616</t>
+    <t xml:space="preserve">0.568972527980804</t>
   </si>
   <si>
     <t xml:space="preserve">0.572173416614532</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">0.575374364852905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577775061130524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565771520137787</t>
+    <t xml:space="preserve">0.577775120735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565771460533142</t>
   </si>
   <si>
     <t xml:space="preserve">0.580976068973541</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">0.58337676525116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576974868774414</t>
+    <t xml:space="preserve">0.576974928379059</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">0.585777580738068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591379225254059</t>
+    <t xml:space="preserve">0.591379284858704</t>
   </si>
   <si>
     <t xml:space="preserve">0.564170956611633</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567371964454651</t>
+    <t xml:space="preserve">0.567371904850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">0.508954226970673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506553590297699</t>
+    <t xml:space="preserve">0.506553530693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.502552330493927</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554730892181</t>
+    <t xml:space="preserve">0.510554790496826</t>
   </si>
   <si>
     <t xml:space="preserve">0.524158835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529760539531708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531360983848572</t>
+    <t xml:space="preserve">0.529760599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531361043453217</t>
   </si>
   <si>
     <t xml:space="preserve">0.550566852092743</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">0.532161295413971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530560731887817</t>
+    <t xml:space="preserve">0.530560791492462</t>
   </si>
   <si>
     <t xml:space="preserve">0.527359843254089</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">0.54736590385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552167415618896</t>
+    <t xml:space="preserve">0.552167356014252</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
@@ -3227,10 +3227,7 @@
     <t xml:space="preserve">0.556968748569489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558569312095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574172496796</t>
+    <t xml:space="preserve">0.558569252490997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584177076816559</t>
@@ -3239,7 +3236,7 @@
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773920536041</t>
+    <t xml:space="preserve">0.573773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
@@ -3251,13 +3248,13 @@
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788442134857</t>
+    <t xml:space="preserve">0.621788501739502</t>
   </si>
   <si>
     <t xml:space="preserve">0.624189138412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622588634490967</t>
+    <t xml:space="preserve">0.622588694095612</t>
   </si>
   <si>
     <t xml:space="preserve">0.620187938213348</t>
@@ -3269,7 +3266,7 @@
     <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602582633495331</t>
+    <t xml:space="preserve">0.602582693099976</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3311,55 +3308,58 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792102336884</t>
+    <t xml:space="preserve">0.633792042732239</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
+    <t xml:space="preserve">0.628990709781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635921716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651516497135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641986310482025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631589770317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627257883548737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615128636360168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262163639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663043498993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197629451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615995049476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62119323015213</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635921716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651516437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64198637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631589770317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627257883548737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615128576755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663103103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197569847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464803218842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615994989871979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621193289756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64025354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723416805267</t>
+    <t xml:space="preserve">0.640253603458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723357200623</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732096195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61946052312851</t>
+    <t xml:space="preserve">0.604732036590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619460463523865</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395869731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331156730652</t>
+    <t xml:space="preserve">0.612529456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395810127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331216335297</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3392,13 +3392,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620326936244965</t>
+    <t xml:space="preserve">0.62032687664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801089286804</t>
+    <t xml:space="preserve">0.597801029682159</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658763408661</t>
+    <t xml:space="preserve">0.624658823013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727696895599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861343383789</t>
+    <t xml:space="preserve">0.617727756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861402988434</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387130737305</t>
+    <t xml:space="preserve">0.639387190341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382850646973</t>
+    <t xml:space="preserve">0.652382910251617</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848443508148</t>
+    <t xml:space="preserve">0.655848383903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042284488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687038004398346</t>
+    <t xml:space="preserve">0.674042344093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68270605802536</t>
+    <t xml:space="preserve">0.682706117630005</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637124538422</t>
+    <t xml:space="preserve">0.689637184143066</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739886999130249</t>
+    <t xml:space="preserve">0.739887058734894</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412965297699</t>
+    <t xml:space="preserve">0.762412905693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779740452766418</t>
+    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.76846718788147</t>
@@ -3699,9 +3699,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.787256062030792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -51360,7 +51357,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51594,7 +51591,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1815" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51620,7 +51617,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51698,7 +51695,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1819" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51802,7 +51799,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51828,7 +51825,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="s">
-        <v>1072</v>
+        <v>981</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51906,7 +51903,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52244,7 +52241,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G1840" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52270,7 +52267,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1841" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52296,7 +52293,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1842" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52322,7 +52319,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1843" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52348,7 +52345,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1844" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52374,7 +52371,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1845" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52400,7 +52397,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52426,7 +52423,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1847" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52452,7 +52449,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52478,7 +52475,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52504,7 +52501,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52530,7 +52527,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1851" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52556,7 +52553,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1852" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52582,7 +52579,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1853" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52608,7 +52605,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1854" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52634,7 +52631,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52660,7 +52657,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1856" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52686,7 +52683,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1857" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52712,7 +52709,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1858" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52738,7 +52735,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1859" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52764,7 +52761,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52790,7 +52787,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1861" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52816,7 +52813,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1862" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52842,7 +52839,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1863" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52868,7 +52865,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1864" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52894,7 +52891,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1865" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52920,7 +52917,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1866" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52946,7 +52943,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1867" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52972,7 +52969,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52998,7 +52995,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53024,7 +53021,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1870" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53050,7 +53047,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1871" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53076,7 +53073,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1872" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53102,7 +53099,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53128,7 +53125,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1874" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53154,7 +53151,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1875" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53180,7 +53177,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53206,7 +53203,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1877" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53232,7 +53229,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53258,7 +53255,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1879" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53284,7 +53281,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1880" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53310,7 +53307,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1881" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53336,7 +53333,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53362,7 +53359,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53388,7 +53385,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53414,7 +53411,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1885" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53440,7 +53437,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1886" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53466,7 +53463,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53492,7 +53489,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1888" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53518,7 +53515,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1889" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53544,7 +53541,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1890" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53570,7 +53567,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1891" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53596,7 +53593,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1892" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53622,7 +53619,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1893" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53648,7 +53645,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53674,7 +53671,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1895" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53700,7 +53697,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53726,7 +53723,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53856,7 +53853,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53986,7 +53983,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54038,7 +54035,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54168,7 +54165,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1914" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54194,7 +54191,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54246,7 +54243,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1917" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54324,7 +54321,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1920" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54376,7 +54373,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1922" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54454,7 +54451,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1925" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54480,7 +54477,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54610,7 +54607,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1931" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54636,7 +54633,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1932" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54662,7 +54659,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1933" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54714,7 +54711,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54818,7 +54815,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54844,7 +54841,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1940" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54948,7 +54945,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54974,7 +54971,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1945" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55026,7 +55023,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1947" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55260,7 +55257,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1956" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55390,7 +55387,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1961" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55416,7 +55413,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1962" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55442,7 +55439,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1963" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55468,7 +55465,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1964" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55494,7 +55491,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1965" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55650,7 +55647,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1971" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56040,7 +56037,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1986" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56274,7 +56271,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1995" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56352,7 +56349,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1998" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56404,7 +56401,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2000" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56482,7 +56479,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2003" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56508,7 +56505,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2004" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56534,7 +56531,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2005" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56560,7 +56557,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2006" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56586,7 +56583,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2007" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56690,7 +56687,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2011" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56872,7 +56869,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2018" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56898,7 +56895,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57210,7 +57207,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57236,7 +57233,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57314,7 +57311,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57340,7 +57337,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58146,7 +58143,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G2067" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58302,7 +58299,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58380,7 +58377,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58484,7 +58481,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58562,7 +58559,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -63242,7 +63239,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1229</v>
+        <v>1191</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63268,7 +63265,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63294,7 +63291,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63320,7 +63317,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63346,7 +63343,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63372,7 +63369,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63398,7 +63395,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63424,7 +63421,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63450,7 +63447,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63476,7 +63473,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63502,7 +63499,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63528,7 +63525,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63554,7 +63551,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63580,7 +63577,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63606,7 +63603,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63632,7 +63629,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63658,7 +63655,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63684,7 +63681,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63710,7 +63707,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63736,7 +63733,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63762,7 +63759,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63788,7 +63785,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63814,7 +63811,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63840,7 +63837,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63866,7 +63863,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63892,7 +63889,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63918,7 +63915,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63944,7 +63941,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63970,7 +63967,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63996,7 +63993,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64022,7 +64019,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64048,7 +64045,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64074,7 +64071,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64100,7 +64097,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64126,7 +64123,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64152,7 +64149,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64178,7 +64175,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64204,7 +64201,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64230,7 +64227,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64256,7 +64253,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64282,7 +64279,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64308,7 +64305,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64334,7 +64331,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64360,7 +64357,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64386,7 +64383,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64412,7 +64409,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64438,7 +64435,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64464,7 +64461,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64490,7 +64487,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64516,7 +64513,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64542,7 +64539,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64568,7 +64565,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64594,7 +64591,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64620,7 +64617,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64646,7 +64643,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64672,7 +64669,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64698,7 +64695,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64724,7 +64721,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64750,7 +64747,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64776,7 +64773,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64802,7 +64799,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64828,7 +64825,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64854,7 +64851,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64880,7 +64877,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64906,7 +64903,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64932,7 +64929,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64958,7 +64955,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64984,7 +64981,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65010,7 +65007,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65036,7 +65033,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65062,7 +65059,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65088,7 +65085,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65114,7 +65111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65140,7 +65137,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65166,7 +65163,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65192,7 +65189,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65218,7 +65215,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65244,7 +65241,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65270,7 +65267,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65296,7 +65293,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65322,7 +65319,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65348,7 +65345,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65374,7 +65371,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65400,7 +65397,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65426,7 +65423,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65452,7 +65449,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65478,7 +65475,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65504,7 +65501,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65530,7 +65527,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65556,7 +65553,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65582,7 +65579,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65608,7 +65605,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65634,7 +65631,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65660,7 +65657,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65686,7 +65683,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65712,7 +65709,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65738,7 +65735,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65764,7 +65761,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65790,7 +65787,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65816,7 +65813,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65842,7 +65839,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65868,7 +65865,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65894,7 +65891,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65920,7 +65917,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65946,7 +65943,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65972,7 +65969,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65998,7 +65995,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66024,7 +66021,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66050,7 +66047,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66076,7 +66073,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66102,7 +66099,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66128,7 +66125,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66154,7 +66151,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66180,7 +66177,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66206,7 +66203,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66232,7 +66229,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66258,7 +66255,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66284,7 +66281,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66310,7 +66307,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66336,7 +66333,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66362,7 +66359,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66388,7 +66385,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66414,7 +66411,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66440,7 +66437,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66466,7 +66463,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66492,7 +66489,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66518,7 +66515,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66544,7 +66541,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66570,7 +66567,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66596,7 +66593,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66622,7 +66619,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66648,7 +66645,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66674,7 +66671,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66700,7 +66697,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66726,7 +66723,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66752,7 +66749,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66778,7 +66775,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66804,7 +66801,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66830,7 +66827,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66856,7 +66853,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66882,7 +66879,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66908,7 +66905,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66934,7 +66931,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66960,7 +66957,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66986,7 +66983,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67012,7 +67009,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67038,7 +67035,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67064,7 +67061,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67090,7 +67087,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67116,7 +67113,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67142,7 +67139,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67168,7 +67165,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67194,7 +67191,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67220,7 +67217,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67246,7 +67243,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67272,7 +67269,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67298,7 +67295,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67324,7 +67321,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67350,7 +67347,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67376,7 +67373,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67402,7 +67399,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67428,7 +67425,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67454,7 +67451,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67480,7 +67477,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67506,7 +67503,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67532,7 +67529,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67558,7 +67555,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67584,7 +67581,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67610,7 +67607,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67636,7 +67633,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67662,7 +67659,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67688,7 +67685,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67714,7 +67711,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67740,7 +67737,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67766,7 +67763,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67792,7 +67789,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67818,7 +67815,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67844,7 +67841,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67870,7 +67867,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67896,7 +67893,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67922,7 +67919,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67948,7 +67945,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67974,7 +67971,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68000,7 +67997,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68026,7 +68023,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68052,7 +68049,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68078,7 +68075,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68104,7 +68101,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68130,7 +68127,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68156,7 +68153,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68182,7 +68179,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68208,7 +68205,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68234,7 +68231,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68260,7 +68257,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68286,7 +68283,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68312,7 +68309,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68338,7 +68335,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68364,7 +68361,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68390,7 +68387,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68416,7 +68413,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68442,7 +68439,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68468,7 +68465,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68494,7 +68491,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68520,7 +68517,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68546,7 +68543,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68572,7 +68569,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68598,7 +68595,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68624,7 +68621,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68650,7 +68647,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68676,7 +68673,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68702,7 +68699,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68728,7 +68725,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68754,7 +68751,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68780,7 +68777,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68806,7 +68803,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68832,7 +68829,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68858,7 +68855,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68884,7 +68881,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68910,7 +68907,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68936,7 +68933,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68962,7 +68959,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68988,7 +68985,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69014,7 +69011,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69040,7 +69037,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69066,7 +69063,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69092,7 +69089,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69118,7 +69115,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69144,7 +69141,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69170,7 +69167,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2491" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69196,7 +69193,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2492" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69222,7 +69219,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2493" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69248,7 +69245,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2494" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69274,7 +69271,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2495" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69300,7 +69297,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69326,7 +69323,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2497" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69352,7 +69349,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2498" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69378,7 +69375,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2499" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69404,7 +69401,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2500" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69430,7 +69427,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2501" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69438,7 +69435,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6914583333</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>95390</v>
@@ -69456,9 +69453,35 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2502" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910648148</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>168210</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>1.0460000038147</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>1.02199995517731</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>1.02400004863739</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>1.0460000038147</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="1355">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378594636917114</t>
+    <t xml:space="preserve">0.378594666719437</t>
   </si>
   <si>
     <t xml:space="preserve">RCS.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382716745138168</t>
+    <t xml:space="preserve">0.382716774940491</t>
   </si>
   <si>
     <t xml:space="preserve">0.367179751396179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380497127771378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789375543594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352276921272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368131011724472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387155830860138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410936892032623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390009611845016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373521387577057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359886914491653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335471659898758</t>
+    <t xml:space="preserve">0.3804971575737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789405345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352276861667633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36813098192215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387155801057816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410936921834946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390009522438049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373521357774734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359886884689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335471630096436</t>
   </si>
   <si>
     <t xml:space="preserve">0.34561824798584</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.361472278833389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341496169567108</t>
+    <t xml:space="preserve">0.341496199369431</t>
   </si>
   <si>
     <t xml:space="preserve">0.355130642652512</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">0.352594017982483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342447429895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.360838115215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35735023021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357984393835068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350691497325897</t>
+    <t xml:space="preserve">0.342447459697723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360838145017624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357350260019302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357984364032745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35069152712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
@@ -116,106 +116,106 @@
     <t xml:space="preserve">0.291714519262314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.297738999128342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.275860458612442</t>
+    <t xml:space="preserve">0.297739028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27586042881012</t>
   </si>
   <si>
     <t xml:space="preserve">0.276240944862366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304461121559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326593369245529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789036273956</t>
+    <t xml:space="preserve">0.304461151361465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326593399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789066076279</t>
   </si>
   <si>
     <t xml:space="preserve">0.32913002371788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348471939563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.327544629573822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671128988266</t>
+    <t xml:space="preserve">0.348471999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3275445997715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671158790588</t>
   </si>
   <si>
     <t xml:space="preserve">0.330081284046173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334203362464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386838763952255</t>
+    <t xml:space="preserve">0.33420330286026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3868388235569</t>
   </si>
   <si>
     <t xml:space="preserve">0.356398969888687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368765145540237</t>
+    <t xml:space="preserve">0.36876517534256</t>
   </si>
   <si>
     <t xml:space="preserve">0.325325042009354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318032175302505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306236803531647</t>
+    <t xml:space="preserve">0.318032205104828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306236773729324</t>
   </si>
   <si>
     <t xml:space="preserve">0.308329522609711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331032484769821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322788417339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319934636354446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309153944253922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331666678190231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320251792669296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310802727937698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323422580957413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308836817741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306300193071365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298880517482758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285880208015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267743140459061</t>
+    <t xml:space="preserve">0.331032514572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322788387537003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319934666156769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309153914451599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331666707992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320251733064651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310802757740021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323422610759735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308836847543716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306300222873688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298880487680435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28588017821312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267743170261383</t>
   </si>
   <si>
     <t xml:space="preserve">0.260767370462418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267489463090897</t>
+    <t xml:space="preserve">0.267489492893219</t>
   </si>
   <si>
     <t xml:space="preserve">0.258738040924072</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643037319183</t>
+    <t xml:space="preserve">0.364643096923828</t>
   </si>
   <si>
     <t xml:space="preserve">0.367496848106384</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">0.36971640586853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369399309158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388741165399551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387789994478226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370033472776413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357033133506775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374155551195145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377643406391144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370984643697739</t>
+    <t xml:space="preserve">0.369399279356003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388741254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387790113687515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370033442974091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357033163309097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374155521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377643465995789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370984703302383</t>
   </si>
   <si>
     <t xml:space="preserve">0.372253030538559</t>
@@ -266,88 +266,88 @@
     <t xml:space="preserve">0.387472927570343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377326339483261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439791291952133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.453425765037537</t>
+    <t xml:space="preserve">0.377326399087906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439791232347488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.453425735235214</t>
   </si>
   <si>
     <t xml:space="preserve">0.454059928655624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.461669862270355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.459133148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45564529299736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456279516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464840710163116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478792279958725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485768020153046</t>
+    <t xml:space="preserve">0.461669892072678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.459133237600327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455645382404327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456279575824738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464840650558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478792250156403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485767960548401</t>
   </si>
   <si>
     <t xml:space="preserve">0.477841019630432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483231365680695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484816759824753</t>
+    <t xml:space="preserve">0.483231395483017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484816789627075</t>
   </si>
   <si>
     <t xml:space="preserve">0.497817128896713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489255964756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.475621402263641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.476889669895172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488304615020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493694990873337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489890038967133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548712253571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645662069321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084777593613</t>
+    <t xml:space="preserve">0.489255905151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.475621372461319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476889759302139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304674625397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493695050477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489890098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548742055893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468645721673965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473084807395935</t>
   </si>
   <si>
     <t xml:space="preserve">0.495280474424362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.486719250679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484182596206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497500002384186</t>
+    <t xml:space="preserve">0.486719161272049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48418265581131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.497500061988831</t>
   </si>
   <si>
     <t xml:space="preserve">0.507329523563385</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">0.50796365737915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514939427375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510183274745941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515890598297119</t>
+    <t xml:space="preserve">0.514939486980438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510183215141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515890717506409</t>
   </si>
   <si>
     <t xml:space="preserve">0.526354372501373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525720119476318</t>
+    <t xml:space="preserve">0.525720179080963</t>
   </si>
   <si>
     <t xml:space="preserve">0.529525220394135</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.627503216266632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597697556018829</t>
+    <t xml:space="preserve">0.597697496414185</t>
   </si>
   <si>
     <t xml:space="preserve">0.596112191677094</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">0.577087342739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561867475509644</t>
+    <t xml:space="preserve">0.561867415904999</t>
   </si>
   <si>
     <t xml:space="preserve">0.583429038524628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569160342216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566940724849701</t>
+    <t xml:space="preserve">0.569160282611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566940665245056</t>
   </si>
   <si>
     <t xml:space="preserve">0.559013724327087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551720917224884</t>
+    <t xml:space="preserve">0.551720857620239</t>
   </si>
   <si>
     <t xml:space="preserve">0.529208123683929</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">0.465791910886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483548402786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549184203147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547281682491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558379650115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585965633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586599826812744</t>
+    <t xml:space="preserve">0.4835484623909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549184262752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547281801700592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558379590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.585965573787689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586599707603455</t>
   </si>
   <si>
     <t xml:space="preserve">0.613868653774261</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">0.665869951248169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655089259147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623064041137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63384485244751</t>
+    <t xml:space="preserve">0.655089199542999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62306410074234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633844792842865</t>
   </si>
   <si>
     <t xml:space="preserve">0.62211287021637</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">0.618942022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615137040615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631625294685364</t>
+    <t xml:space="preserve">0.615137100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631625235080719</t>
   </si>
   <si>
     <t xml:space="preserve">0.628771543502808</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">0.644308507442474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64557683467865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.636064350605011</t>
+    <t xml:space="preserve">0.645576775074005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636064410209656</t>
   </si>
   <si>
     <t xml:space="preserve">0.63479608297348</t>
@@ -512,19 +512,19 @@
     <t xml:space="preserve">0.626551926136017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626234948635101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602453768253326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588185250759125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590087711811066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.589136362075806</t>
+    <t xml:space="preserve">0.626234889030457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602453827857971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58818519115448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590087652206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58913642168045</t>
   </si>
   <si>
     <t xml:space="preserve">0.619893252849579</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">0.592941343784332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.600551307201385</t>
+    <t xml:space="preserve">0.60055136680603</t>
   </si>
   <si>
     <t xml:space="preserve">0.595795094966888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594526767730713</t>
+    <t xml:space="preserve">0.594526827335358</t>
   </si>
   <si>
     <t xml:space="preserve">0.591673076152802</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">0.603087961673737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609746694564819</t>
+    <t xml:space="preserve">0.609746634960175</t>
   </si>
   <si>
     <t xml:space="preserve">0.6113321185112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614185869693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611966192722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605941653251648</t>
+    <t xml:space="preserve">0.614185810089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611966252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605941712856293</t>
   </si>
   <si>
     <t xml:space="preserve">0.598648846149445</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">0.593258500099182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58850222826004</t>
+    <t xml:space="preserve">0.588502287864685</t>
   </si>
   <si>
     <t xml:space="preserve">0.597380518913269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617673635482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611015021800995</t>
+    <t xml:space="preserve">0.617673695087433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61101496219635</t>
   </si>
   <si>
     <t xml:space="preserve">0.604039251804352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605307519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61006373167038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624649465084076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617039501667023</t>
+    <t xml:space="preserve">0.605307579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610063791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624649524688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617039561271667</t>
   </si>
   <si>
     <t xml:space="preserve">0.610380828380585</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">0.589770555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56535530090332</t>
+    <t xml:space="preserve">0.565355360507965</t>
   </si>
   <si>
     <t xml:space="preserve">0.523183584213257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481963068246841</t>
+    <t xml:space="preserve">0.481962978839874</t>
   </si>
   <si>
     <t xml:space="preserve">0.493377983570099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492109626531601</t>
+    <t xml:space="preserve">0.492109596729279</t>
   </si>
   <si>
     <t xml:space="preserve">0.508280754089355</t>
@@ -632,31 +632,31 @@
     <t xml:space="preserve">0.513988256454468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509231984615326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509549081325531</t>
+    <t xml:space="preserve">0.509232044219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509549140930176</t>
   </si>
   <si>
     <t xml:space="preserve">0.51779317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548550009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544110834598541</t>
+    <t xml:space="preserve">0.548550128936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544110894203186</t>
   </si>
   <si>
     <t xml:space="preserve">0.521598219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53047639131546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546013414859772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54094010591507</t>
+    <t xml:space="preserve">0.53047651052475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546013355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540940046310425</t>
   </si>
   <si>
     <t xml:space="preserve">0.532695949077606</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">0.538720488548279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539037644863129</t>
+    <t xml:space="preserve">0.539037585258484</t>
   </si>
   <si>
     <t xml:space="preserve">0.533330142498016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532061874866486</t>
+    <t xml:space="preserve">0.532061815261841</t>
   </si>
   <si>
     <t xml:space="preserve">0.568843245506287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570428669452667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566306531429291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549501299858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560599148273468</t>
+    <t xml:space="preserve">0.570428609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.566306591033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549501240253448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560599088668823</t>
   </si>
   <si>
     <t xml:space="preserve">0.564404129981995</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">0.550452530384064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542842626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545062184333801</t>
+    <t xml:space="preserve">0.54284256696701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545062124729156</t>
   </si>
   <si>
     <t xml:space="preserve">0.521281123161316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516524791717529</t>
+    <t xml:space="preserve">0.516524970531464</t>
   </si>
   <si>
     <t xml:space="preserve">0.506695330142975</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">0.526037335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518744468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511451601982117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514305233955383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523817718029022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.508597791194916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522549331188202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513671159744263</t>
+    <t xml:space="preserve">0.518744349479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511451661586761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514305293560028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.523817658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508597850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522549450397491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513671100139618</t>
   </si>
   <si>
     <t xml:space="preserve">0.511134505271912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504158735275269</t>
+    <t xml:space="preserve">0.504158675670624</t>
   </si>
   <si>
     <t xml:space="preserve">0.506061196327209</t>
@@ -755,73 +755,73 @@
     <t xml:space="preserve">0.510500371456146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.499719500541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512085795402527</t>
+    <t xml:space="preserve">0.499719560146332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512085735797882</t>
   </si>
   <si>
     <t xml:space="preserve">0.54157429933548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550769627094269</t>
+    <t xml:space="preserve">0.550769567489624</t>
   </si>
   <si>
     <t xml:space="preserve">0.553623378276825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560281991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569794535636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575501978397369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627820312976837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658894181251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655723452568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682358205318451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73689603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707724690437317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.696943879127502</t>
+    <t xml:space="preserve">0.560282051563263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569794476032257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575501918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627820253372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658894300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655723392963409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682358145713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262642383575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736896097660065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707724750041962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.696943998336792</t>
   </si>
   <si>
     <t xml:space="preserve">0.733091175556183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.748945236206055</t>
+    <t xml:space="preserve">0.748945295810699</t>
   </si>
   <si>
     <t xml:space="preserve">0.747676968574524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.754652678966522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.755286812782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760360181331635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818068742752075</t>
+    <t xml:space="preserve">0.754652798175812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.755286931991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76036012172699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818068861961365</t>
   </si>
   <si>
     <t xml:space="preserve">0.799678206443787</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">0.771140873432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768604338169098</t>
+    <t xml:space="preserve">0.768604278564453</t>
   </si>
   <si>
     <t xml:space="preserve">0.720407903194427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727383673191071</t>
+    <t xml:space="preserve">0.727383732795715</t>
   </si>
   <si>
     <t xml:space="preserve">0.740701079368591</t>
@@ -851,40 +851,40 @@
     <t xml:space="preserve">0.78382408618927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801580667495728</t>
+    <t xml:space="preserve">0.801580786705017</t>
   </si>
   <si>
     <t xml:space="preserve">0.849776983261108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884021699428558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.851045250892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.878314256668091</t>
+    <t xml:space="preserve">0.884021639823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.851045310497284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.878314197063446</t>
   </si>
   <si>
     <t xml:space="preserve">0.894168317317963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.925876498222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924607932567596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.887826681137085</t>
+    <t xml:space="preserve">0.925876438617706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924608051776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887826561927795</t>
   </si>
   <si>
     <t xml:space="preserve">0.901778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881485104560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412295341492</t>
+    <t xml:space="preserve">0.881485044956207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412354946136</t>
   </si>
   <si>
     <t xml:space="preserve">0.875143468379974</t>
@@ -893,46 +893,46 @@
     <t xml:space="preserve">0.896070778369904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9106565117836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827300071716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91002231836319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729082584381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892900049686432</t>
+    <t xml:space="preserve">0.91065639257431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827180862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910022258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889728963375092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892900109291077</t>
   </si>
   <si>
     <t xml:space="preserve">0.895436644554138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863094210624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.860557854175568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533504962921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875777661800385</t>
+    <t xml:space="preserve">0.863094329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.860557734966278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533445358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87577748298645</t>
   </si>
   <si>
     <t xml:space="preserve">0.868167638778687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756555140018463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788897335529327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812995553016663</t>
+    <t xml:space="preserve">0.756555080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788897454738617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812995612621307</t>
   </si>
   <si>
     <t xml:space="preserve">0.80728805065155</t>
@@ -941,70 +941,70 @@
     <t xml:space="preserve">0.838362038135529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790165781974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786360740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811727285385132</t>
+    <t xml:space="preserve">0.790165662765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786360800266266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811727166175842</t>
   </si>
   <si>
     <t xml:space="preserve">0.83011794090271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814898073673248</t>
+    <t xml:space="preserve">0.814898014068604</t>
   </si>
   <si>
     <t xml:space="preserve">0.792702376842499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.803483068943024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804117321968079</t>
+    <t xml:space="preserve">0.803483188152313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804117202758789</t>
   </si>
   <si>
     <t xml:space="preserve">0.776848375797272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780019223690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781921744346619</t>
+    <t xml:space="preserve">0.780019044876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781921625137329</t>
   </si>
   <si>
     <t xml:space="preserve">0.791434109210968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785092413425446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786994993686676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793970584869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.789531588554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77367752790451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.775579988956451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769872486591339</t>
+    <t xml:space="preserve">0.78509247303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786994934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79397064447403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.789531707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7736776471138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.775580227375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769872546195984</t>
   </si>
   <si>
     <t xml:space="preserve">0.767335951328278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77177506685257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628389358521</t>
+    <t xml:space="preserve">0.771775007247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761628568172455</t>
   </si>
   <si>
     <t xml:space="preserve">0.79587322473526</t>
@@ -1013,73 +1013,73 @@
     <t xml:space="preserve">0.811093091964722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.843435406684875</t>
+    <t xml:space="preserve">0.843435347080231</t>
   </si>
   <si>
     <t xml:space="preserve">0.832654595375061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.872606813907623</t>
+    <t xml:space="preserve">0.872606754302979</t>
   </si>
   <si>
     <t xml:space="preserve">0.862460136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866899192333221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840264499187469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830752074718475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855484426021576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.842801034450531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.849142909049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.820605576038361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824410438537598</t>
+    <t xml:space="preserve">0.866899311542511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.840264558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83075213432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855484366416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.842801153659821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.849142789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.820605516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824410498142242</t>
   </si>
   <si>
     <t xml:space="preserve">0.826947152614594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.806019842624664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.799044013023376</t>
+    <t xml:space="preserve">0.806019723415375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.799043953418732</t>
   </si>
   <si>
     <t xml:space="preserve">0.804751515388489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785726547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778750836849213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.777482330799103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.802214801311493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.806653916835785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.807922303676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.854850232601166</t>
+    <t xml:space="preserve">0.785726606845856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778750896453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777482509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.802214741706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80792224407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.854850292205811</t>
   </si>
   <si>
     <t xml:space="preserve">0.857386887073517</t>
@@ -1088,46 +1088,46 @@
     <t xml:space="preserve">0.852313578128815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.863728523254395</t>
+    <t xml:space="preserve">0.863728404045105</t>
   </si>
   <si>
     <t xml:space="preserve">0.864996910095215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.850410997867584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.840898633003235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834556996822357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581286430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826312839984894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80538547039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814263939857483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818702936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.819337248802185</t>
+    <t xml:space="preserve">0.850411057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84089869260788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834557116031647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996231555939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581346035004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826312899589539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.805385589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814263820648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.818703055381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819337129592896</t>
   </si>
   <si>
     <t xml:space="preserve">0.79650741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809190630912781</t>
+    <t xml:space="preserve">0.809190571308136</t>
   </si>
   <si>
     <t xml:space="preserve">0.809824705123901</t>
@@ -1139,169 +1139,169 @@
     <t xml:space="preserve">0.798409819602966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.817434728145599</t>
+    <t xml:space="preserve">0.817434787750244</t>
   </si>
   <si>
     <t xml:space="preserve">0.823142111301422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.812361538410187</t>
+    <t xml:space="preserve">0.812361419200897</t>
   </si>
   <si>
     <t xml:space="preserve">0.819971323013306</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797141432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71660304069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.704553842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736262023448944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240926027298</t>
+    <t xml:space="preserve">0.797141492366791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.716602921485901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.704553723335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.736261963844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.759725987911224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">0.776214182376862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.784458339214325</t>
+    <t xml:space="preserve">0.78445827960968</t>
   </si>
   <si>
     <t xml:space="preserve">0.783190011978149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.752116084098816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760994255542755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823526859283</t>
+    <t xml:space="preserve">0.752115964889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7609943151474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823407649994</t>
   </si>
   <si>
     <t xml:space="preserve">0.766701698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790799856185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.810458838939667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.774311661720276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781287372112274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.795239090919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.800312340259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815532267093658</t>
+    <t xml:space="preserve">0.790799915790558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.810458958148956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.774311602115631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781287491321564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.795238971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.800312280654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815532207489014</t>
   </si>
   <si>
     <t xml:space="preserve">0.764799177646637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731822907924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711529612541199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.693773090839386</t>
+    <t xml:space="preserve">0.731822788715363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711529672145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.693773150444031</t>
   </si>
   <si>
     <t xml:space="preserve">0.739432811737061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703919768333435</t>
+    <t xml:space="preserve">0.703919649124146</t>
   </si>
   <si>
     <t xml:space="preserve">0.695041418075562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683626532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660796701908112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684894859790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.670943319797516</t>
+    <t xml:space="preserve">0.683626472949982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660796761512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684894919395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.670943260192871</t>
   </si>
   <si>
     <t xml:space="preserve">0.69123649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.678553283214569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687431573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717871189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730554521083832</t>
+    <t xml:space="preserve">0.678553223609924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687431454658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717871248722076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730554461479187</t>
   </si>
   <si>
     <t xml:space="preserve">0.710261285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697578072547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71406626701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729286074638367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.753384232521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748311102390289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757189273834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.758457541465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763530969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.749579429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042775154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.735627889633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.745774328708649</t>
+    <t xml:space="preserve">0.697578132152557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714066326618195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.753384351730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748311042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757189333438873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758457601070404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763531029224396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74957948923111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042715549469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.735627830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.745774388313293</t>
   </si>
   <si>
     <t xml:space="preserve">0.743237793445587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.741969287395477</t>
+    <t xml:space="preserve">0.741969406604767</t>
   </si>
   <si>
     <t xml:space="preserve">0.744506061077118</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">0.722944557666779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700114786624908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.706456363201141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.698846459388733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72548121213913</t>
+    <t xml:space="preserve">0.700114727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.706456303596497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698846399784088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725481271743774</t>
   </si>
   <si>
     <t xml:space="preserve">0.71533465385437</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">0.712797939777374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6925048828125</t>
+    <t xml:space="preserve">0.69250476360321</t>
   </si>
   <si>
     <t xml:space="preserve">0.705188035964966</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">0.681089878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701382994651794</t>
+    <t xml:space="preserve">0.701383054256439</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309745311737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699841499329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.686163187026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6798215508461</t>
+    <t xml:space="preserve">0.688699781894684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.686163246631622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.679821610450745</t>
   </si>
   <si>
     <t xml:space="preserve">0.672211587429047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646845161914825</t>
+    <t xml:space="preserve">0.64684522151947</t>
   </si>
   <si>
     <t xml:space="preserve">0.677284836769104</t>
@@ -1364,31 +1364,31 @@
     <t xml:space="preserve">0.65826004743576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659528315067291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651918470859528</t>
+    <t xml:space="preserve">0.659528374671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651918411254883</t>
   </si>
   <si>
     <t xml:space="preserve">0.648113429546356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641771793365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63543027639389</t>
+    <t xml:space="preserve">0.641771852970123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635430216789246</t>
   </si>
   <si>
     <t xml:space="preserve">0.643040239810944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639235198497772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637966871261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594209730625153</t>
+    <t xml:space="preserve">0.639235258102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637966930866241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594209611415863</t>
   </si>
   <si>
     <t xml:space="preserve">0.596746325492859</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">0.598014712333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.59991717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603722095489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573916554450989</t>
+    <t xml:space="preserve">0.599917113780975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603722155094147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
     <t xml:space="preserve">0.621478676795959</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">0.622747004032135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615771234035492</t>
+    <t xml:space="preserve">0.615771174430847</t>
   </si>
   <si>
     <t xml:space="preserve">0.6233811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612600386142731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591038882732391</t>
+    <t xml:space="preserve">0.612600445747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591038942337036</t>
   </si>
   <si>
     <t xml:space="preserve">0.584063112735748</t>
@@ -1442,34 +1442,34 @@
     <t xml:space="preserve">0.570745706558228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561233282089233</t>
+    <t xml:space="preserve">0.561233341693878</t>
   </si>
   <si>
     <t xml:space="preserve">0.572648167610168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559964954853058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537135124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528891026973724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573282361030579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569477379322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608795464038849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618307888507843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630357027053833</t>
+    <t xml:space="preserve">0.559964895248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537135243415833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52889096736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573282420635223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569477438926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608795404434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618307828903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630356907844543</t>
   </si>
   <si>
     <t xml:space="preserve">0.604990482330322</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">0.580258131027222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572014093399048</t>
+    <t xml:space="preserve">0.572014033794403</t>
   </si>
   <si>
     <t xml:space="preserve">0.568209052085876</t>
@@ -1487,19 +1487,19 @@
     <t xml:space="preserve">0.554891586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629722714424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721676230430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766067504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78255569934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215479850769</t>
+    <t xml:space="preserve">0.629722774028778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721676290035248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766067564487457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782555758953094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215301036835</t>
   </si>
   <si>
     <t xml:space="preserve">0.825678825378418</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">0.873875081539154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.871338486671448</t>
+    <t xml:space="preserve">0.871338546276093</t>
   </si>
   <si>
     <t xml:space="preserve">0.882753312587738</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">0.880216717720032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.903046548366547</t>
+    <t xml:space="preserve">0.903046607971191</t>
   </si>
   <si>
     <t xml:space="preserve">0.922071397304535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.937291324138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.918266296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866265177726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630365371704</t>
+    <t xml:space="preserve">0.937291443347931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.918266475200653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86626523733139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630305767059</t>
   </si>
   <si>
     <t xml:space="preserve">0.896704912185669</t>
@@ -1541,82 +1541,82 @@
     <t xml:space="preserve">0.876411736011505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.868801951408386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.870070040225983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.938559532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934754550457001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314875602722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583143234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.929681420326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.927144706249237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.906851530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.930949628353119</t>
+    <t xml:space="preserve">0.868801891803741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.870070159435272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.938559591770172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.934754729270935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314815998077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583202838898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.929681301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.927144825458527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.906851470470428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.930949687957764</t>
   </si>
   <si>
     <t xml:space="preserve">0.891631603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833288788795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873784065247</t>
+    <t xml:space="preserve">0.833288729190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873843669891</t>
   </si>
   <si>
     <t xml:space="preserve">0.802849054336548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755921065807343</t>
+    <t xml:space="preserve">0.755920946598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640503466129303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636698544025421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627019226551056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641851961612701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625670850276947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613534927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616905987262726</t>
   </si>
   <si>
     <t xml:space="preserve">0.640503585338593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636698484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627019226551056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641851961612701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625670731067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613534927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616905987262726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640503525733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618928670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595331192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59667956829071</t>
+    <t xml:space="preserve">0.618928611278534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595331132411957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596679627895355</t>
   </si>
   <si>
     <t xml:space="preserve">0.597353756427765</t>
@@ -1625,55 +1625,55 @@
     <t xml:space="preserve">0.596005380153656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602073311805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598028004169464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594656944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593982696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631064414978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623648107051849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65398782491684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656684637069702</t>
+    <t xml:space="preserve">0.60207337141037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598028063774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594657003879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838055610657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593982756137848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631064534187317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623648166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.653987884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656684696674347</t>
   </si>
   <si>
     <t xml:space="preserve">0.637132465839386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626344978809357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628367602825165</t>
+    <t xml:space="preserve">0.626345038414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
     <t xml:space="preserve">0.624322354793549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629716038703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62769341468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614883303642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608815371990204</t>
+    <t xml:space="preserve">0.629716098308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627693474292755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614883422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608815431594849</t>
   </si>
   <si>
     <t xml:space="preserve">0.617580235004425</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">0.635784029960632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624996483325958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614209175109863</t>
+    <t xml:space="preserve">0.624996542930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614209115505219</t>
   </si>
   <si>
     <t xml:space="preserve">0.605444371700287</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">0.630390286445618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64320033788681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656010389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633761405944824</t>
+    <t xml:space="preserve">0.643200397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656010448932648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633761346340179</t>
   </si>
   <si>
     <t xml:space="preserve">0.61218649148941</t>
@@ -1718,46 +1718,46 @@
     <t xml:space="preserve">0.610163867473602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549484610557556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561620473861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552855730056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565665781497955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578475832939148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558923602104187</t>
+    <t xml:space="preserve">0.549484550952911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56162041425705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552855670452118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565665721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.578475773334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558923542499542</t>
   </si>
   <si>
     <t xml:space="preserve">0.563643157482147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569711029529572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558249354362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562294721603394</t>
+    <t xml:space="preserve">0.569710969924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558249413967133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562294602394104</t>
   </si>
   <si>
     <t xml:space="preserve">0.573082089424133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583869516849518</t>
+    <t xml:space="preserve">0.583869576454163</t>
   </si>
   <si>
     <t xml:space="preserve">0.584543704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567014217376709</t>
+    <t xml:space="preserve">0.567014157772064</t>
   </si>
   <si>
     <t xml:space="preserve">0.566339910030365</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">0.593308508396149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599376499652863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.586566388607025</t>
+    <t xml:space="preserve">0.599376440048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58656632900238</t>
   </si>
   <si>
     <t xml:space="preserve">0.591285884380341</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">0.600050628185272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60274749994278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60746705532074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590611636638641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592634260654449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587914824485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618254363536835</t>
+    <t xml:space="preserve">0.602747440338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607467114925385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.590611696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592634320259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587914764881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618254423141479</t>
   </si>
   <si>
     <t xml:space="preserve">0.639829277992249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641177654266357</t>
+    <t xml:space="preserve">0.641177713871002</t>
   </si>
   <si>
     <t xml:space="preserve">0.588589012622833</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">0.598702251911163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620277047157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622973918914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609489619731903</t>
+    <t xml:space="preserve">0.620277166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62297397851944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609489738941193</t>
   </si>
   <si>
     <t xml:space="preserve">0.615557610988617</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">0.620951294898987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648594081401825</t>
+    <t xml:space="preserve">0.64859414100647</t>
   </si>
   <si>
     <t xml:space="preserve">0.604770183563232</t>
@@ -1838,49 +1838,49 @@
     <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638480961322784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.655336260795593</t>
+    <t xml:space="preserve">0.63848090171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
     <t xml:space="preserve">0.695789039134979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714667022228241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702531218528748</t>
+    <t xml:space="preserve">0.714667081832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702531278133392</t>
   </si>
   <si>
     <t xml:space="preserve">0.69983434677124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.716015517711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728151500225067</t>
+    <t xml:space="preserve">0.716015577316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728151440620422</t>
   </si>
   <si>
     <t xml:space="preserve">0.717363953590393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726803004741669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722757637500763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.721409320831299</t>
+    <t xml:space="preserve">0.726802885532379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.722757697105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.721409201622009</t>
   </si>
   <si>
     <t xml:space="preserve">0.711970210075378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.701182723045349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.694440603256226</t>
+    <t xml:space="preserve">0.701182782649994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69444066286087</t>
   </si>
   <si>
     <t xml:space="preserve">0.689046919345856</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">0.67960798740387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.680956363677979</t>
+    <t xml:space="preserve">0.680956304073334</t>
   </si>
   <si>
     <t xml:space="preserve">0.672191560268402</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">0.68500167131424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675562620162964</t>
+    <t xml:space="preserve">0.675562679767609</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146252632141</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919833660126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645897209644318</t>
+    <t xml:space="preserve">0.647919952869415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645897269248962</t>
   </si>
   <si>
     <t xml:space="preserve">0.636458218097687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63308709859848</t>
+    <t xml:space="preserve">0.633087158203125</t>
   </si>
   <si>
     <t xml:space="preserve">0.611512303352356</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">0.574430525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589263200759888</t>
+    <t xml:space="preserve">0.589263260364532</t>
   </si>
   <si>
     <t xml:space="preserve">0.560272037982941</t>
@@ -1940,76 +1940,76 @@
     <t xml:space="preserve">0.553529858589172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538697183132172</t>
+    <t xml:space="preserve">0.538697123527527</t>
   </si>
   <si>
     <t xml:space="preserve">0.527235567569733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47869211435318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463859349489212</t>
+    <t xml:space="preserve">0.478692084550858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463859379291534</t>
   </si>
   <si>
     <t xml:space="preserve">0.458465665578842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391044229269028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419361233711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394415289163589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387673139572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388347417116165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380256861448288</t>
+    <t xml:space="preserve">0.39104425907135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419361263513565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394415318965912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387673169374466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38834735751152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380256831645966</t>
   </si>
   <si>
     <t xml:space="preserve">0.403180092573166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412619054317474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.431497126817703</t>
+    <t xml:space="preserve">0.412619084119797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.431497067213058</t>
   </si>
   <si>
     <t xml:space="preserve">0.46520784497261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469927281141281</t>
+    <t xml:space="preserve">0.469927310943604</t>
   </si>
   <si>
     <t xml:space="preserve">0.479366332292557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489479541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474646836519241</t>
+    <t xml:space="preserve">0.489479511976242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.474646866321564</t>
   </si>
   <si>
     <t xml:space="preserve">0.473298400640488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.464533537626266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411610126495</t>
+    <t xml:space="preserve">0.464533597230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411639928818</t>
   </si>
   <si>
     <t xml:space="preserve">0.498918533325195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49689581990242</t>
+    <t xml:space="preserve">0.496895909309387</t>
   </si>
   <si>
     <t xml:space="preserve">0.495547443628311</t>
@@ -2018,40 +2018,40 @@
     <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.482063204050064</t>
+    <t xml:space="preserve">0.482063144445419</t>
   </si>
   <si>
     <t xml:space="preserve">0.490827977657318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484760046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480714708566666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482737481594086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485434263944626</t>
+    <t xml:space="preserve">0.484759956598282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480714738368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482737362384796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485434293746948</t>
   </si>
   <si>
     <t xml:space="preserve">0.488131105899811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.481388986110687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.472624152898788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42745178937912</t>
+    <t xml:space="preserve">0.481388956308365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.472624182701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.427451759576797</t>
   </si>
   <si>
     <t xml:space="preserve">0.434868156909943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.438239216804504</t>
+    <t xml:space="preserve">0.438239246606827</t>
   </si>
   <si>
     <t xml:space="preserve">0.443632990121841</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">0.409248024225235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434212177991867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.410049855709076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412892401218414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449135959148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.451267927885056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456953287124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486800879240036</t>
+    <t xml:space="preserve">0.434212207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.410049825906754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412892431020737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449136048555374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4512679874897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456953227519989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486800849437714</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">0.453399956226349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466191798448563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466902494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480404943227768</t>
+    <t xml:space="preserve">0.466191828250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46690246462822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480404913425446</t>
   </si>
   <si>
     <t xml:space="preserve">0.498882085084915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488222122192383</t>
+    <t xml:space="preserve">0.48822221159935</t>
   </si>
   <si>
     <t xml:space="preserve">0.47756227850914</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">0.442740052938461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452689319849014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447004020214081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450557291507721</t>
+    <t xml:space="preserve">0.452689379453659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447004050016403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450557321310043</t>
   </si>
   <si>
     <t xml:space="preserve">0.448425322771072</t>
@@ -2132,37 +2132,37 @@
     <t xml:space="preserve">0.442029416561127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42994824051857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.438476115465164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429237574338913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447714656591415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439186751842499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463349163532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458374559879303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444161385297775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456242650747299</t>
+    <t xml:space="preserve">0.429948210716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438476145267487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429237514734268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447714686393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439186781644821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463349133729935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458374500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444161355495453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456242620944977</t>
   </si>
   <si>
     <t xml:space="preserve">0.449846655130386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45553195476532</t>
+    <t xml:space="preserve">0.455531895160675</t>
   </si>
   <si>
     <t xml:space="preserve">0.443450748920441</t>
@@ -2186,22 +2186,22 @@
     <t xml:space="preserve">0.416445732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.427105605602264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437054812908173</t>
+    <t xml:space="preserve">0.427105575799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437054842710495</t>
   </si>
   <si>
     <t xml:space="preserve">0.432080209255219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434922814369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.422841668128967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417867004871368</t>
+    <t xml:space="preserve">0.434922844171524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.422841638326645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417867064476013</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496554613113</t>
@@ -2210,97 +2210,97 @@
     <t xml:space="preserve">0.407917827367783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397968590259552</t>
+    <t xml:space="preserve">0.397968620061874</t>
   </si>
   <si>
     <t xml:space="preserve">0.403653919696808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.401521950960159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405075192451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400811284780502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.387308746576309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385176777839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.400100588798523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41573503613472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398679256439209</t>
+    <t xml:space="preserve">0.401521891355515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405075162649155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400811225175858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.387308716773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385176748037338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.400100648403168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415735065937042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398679286241531</t>
   </si>
   <si>
     <t xml:space="preserve">0.409339129924774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395836621522903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382334142923355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370963573455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383755505084991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366699635982513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363146364688873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3539077937603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356750428676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359593063592911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358882397413254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370252937078476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388730049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151381492615</t>
+    <t xml:space="preserve">0.395836591720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382334113121033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370963633060455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383755475282669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366699606180191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363146334886551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353907763957977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356750458478928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359593033790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358882427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370252996683121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388730019330978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151411294937</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372384905815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36385703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361725032329559</t>
+    <t xml:space="preserve">0.372384935617447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363857060670853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361725062131882</t>
   </si>
   <si>
     <t xml:space="preserve">0.355329126119614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353552460670471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354618459939957</t>
+    <t xml:space="preserve">0.353552520275116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354618489742279</t>
   </si>
   <si>
     <t xml:space="preserve">0.351775825023651</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">0.342181950807571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337207347154617</t>
+    <t xml:space="preserve">0.337207317352295</t>
   </si>
   <si>
     <t xml:space="preserve">0.337562650442123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343958556652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361014395952225</t>
+    <t xml:space="preserve">0.343958586454391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361014366149902</t>
   </si>
   <si>
     <t xml:space="preserve">0.36030375957489</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">0.389440685510635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396547317504883</t>
+    <t xml:space="preserve">0.39654728770256</t>
   </si>
   <si>
     <t xml:space="preserve">0.41218176484108</t>
@@ -2345,34 +2345,34 @@
     <t xml:space="preserve">0.421420365571976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415024399757385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419999033212662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.414313763380051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405785828828812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402232587337494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.418577700853348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.419288367033005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399389892816544</t>
+    <t xml:space="preserve">0.415024369955063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419999063014984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.414313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405785888433456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402232527732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.418577671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.419288337230682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399389922618866</t>
   </si>
   <si>
     <t xml:space="preserve">0.393704682588577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392993986606598</t>
+    <t xml:space="preserve">0.39299401640892</t>
   </si>
   <si>
     <t xml:space="preserve">0.391572713851929</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">0.397257953882217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.404364556074142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.395125985145569</t>
+    <t xml:space="preserve">0.40436452627182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395125955343246</t>
   </si>
   <si>
     <t xml:space="preserve">0.386598110198975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380202203989029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806238174438</t>
+    <t xml:space="preserve">0.380202144384384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806208372116</t>
   </si>
   <si>
     <t xml:space="preserve">0.369542241096497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368831634521484</t>
+    <t xml:space="preserve">0.368831604719162</t>
   </si>
   <si>
     <t xml:space="preserve">0.364567667245865</t>
@@ -2408,34 +2408,34 @@
     <t xml:space="preserve">0.428526937961578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423552334308624</t>
+    <t xml:space="preserve">0.423552304506302</t>
   </si>
   <si>
     <t xml:space="preserve">0.436344146728516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.426394939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440608084201813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897447824478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464770495891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.471876978874207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478983670473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492486178874969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515227258205414</t>
+    <t xml:space="preserve">0.426394999027252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.440608143806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897477626801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464770466089249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.471877038478851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478983640670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492486149072647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515227198600769</t>
   </si>
   <si>
     <t xml:space="preserve">0.512384593486786</t>
@@ -2450,46 +2450,46 @@
     <t xml:space="preserve">0.508120656013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5138059258461</t>
+    <t xml:space="preserve">0.51380580663681</t>
   </si>
   <si>
     <t xml:space="preserve">0.510963261127472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507409989833832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513095259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522333800792694</t>
+    <t xml:space="preserve">0.507409930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513095200061798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522333860397339</t>
   </si>
   <si>
     <t xml:space="preserve">0.537257611751556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523755073547363</t>
+    <t xml:space="preserve">0.523755133152008</t>
   </si>
   <si>
     <t xml:space="preserve">0.525887072086334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526597797870636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525176405906677</t>
+    <t xml:space="preserve">0.526597738265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525176465511322</t>
   </si>
   <si>
     <t xml:space="preserve">0.530151009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52446573972702</t>
+    <t xml:space="preserve">0.524465799331665</t>
   </si>
   <si>
     <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544364273548126</t>
+    <t xml:space="preserve">0.544364213943481</t>
   </si>
   <si>
     <t xml:space="preserve">0.541521608829498</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.536546945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528729736804962</t>
+    <t xml:space="preserve">0.528729796409607</t>
   </si>
   <si>
     <t xml:space="preserve">0.518780529499054</t>
@@ -2513,16 +2513,16 @@
     <t xml:space="preserve">0.54223221540451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53157240152359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542942941188812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54933887720108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564973294734955</t>
+    <t xml:space="preserve">0.531572461128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542942881584167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549338817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5649733543396</t>
   </si>
   <si>
     <t xml:space="preserve">0.550941228866577</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647783756256</t>
+    <t xml:space="preserve">0.537647724151611</t>
   </si>
   <si>
     <t xml:space="preserve">0.531739592552185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526569843292236</t>
+    <t xml:space="preserve">0.526569902896881</t>
   </si>
   <si>
     <t xml:space="preserve">0.516230523586273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514753401279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518446087837219</t>
+    <t xml:space="preserve">0.514753460884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">0.572358548641205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581220865249634</t>
+    <t xml:space="preserve">0.581220924854279</t>
   </si>
   <si>
     <t xml:space="preserve">0.584174990653992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583436489105225</t>
+    <t xml:space="preserve">0.58343642950058</t>
   </si>
   <si>
     <t xml:space="preserve">0.575312674045563</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">0.527308404445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522877275943756</t>
+    <t xml:space="preserve">0.522877216339111</t>
   </si>
   <si>
     <t xml:space="preserve">0.53543221950531</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">0.51696902513504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511060774326324</t>
+    <t xml:space="preserve">0.511060833930969</t>
   </si>
   <si>
     <t xml:space="preserve">0.511799335479736</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">0.487427949905396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488166451454163</t>
+    <t xml:space="preserve">0.48816642165184</t>
   </si>
   <si>
     <t xml:space="preserve">0.483735263347626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48890495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480781197547913</t>
+    <t xml:space="preserve">0.488905012607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48078116774559</t>
   </si>
   <si>
     <t xml:space="preserve">0.48151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492597639560699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522138774394989</t>
+    <t xml:space="preserve">0.492597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522138714790344</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">0.534693658351898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.532478094100952</t>
+    <t xml:space="preserve">0.532478153705597</t>
   </si>
   <si>
     <t xml:space="preserve">0.519923150539398</t>
@@ -2672,28 +2672,28 @@
     <t xml:space="preserve">0.517707526683807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512537837028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514014899730682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525092840194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545032978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528785526752472</t>
+    <t xml:space="preserve">0.512537896633148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514014840126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525092899799347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545033037662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528785467147827</t>
   </si>
   <si>
     <t xml:space="preserve">0.533216595649719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520661652088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515491962432861</t>
+    <t xml:space="preserve">0.520661592483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515491902828217</t>
   </si>
   <si>
     <t xml:space="preserve">0.508106648921967</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">0.505152583122253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502198457717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495551705360413</t>
+    <t xml:space="preserve">0.50219851732254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495551735162735</t>
   </si>
   <si>
     <t xml:space="preserve">0.498505830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502936959266663</t>
+    <t xml:space="preserve">0.502937018871307</t>
   </si>
   <si>
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721395015717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771539211273</t>
+    <t xml:space="preserve">0.500721454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771598815918</t>
   </si>
   <si>
     <t xml:space="preserve">0.540601909160614</t>
@@ -2738,25 +2738,25 @@
     <t xml:space="preserve">0.538386285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530262529850006</t>
+    <t xml:space="preserve">0.530262470245361</t>
   </si>
   <si>
     <t xml:space="preserve">0.539863348007202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613716125488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641780078411102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62257844209671</t>
+    <t xml:space="preserve">0.613716006278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641780138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612977623939514</t>
+    <t xml:space="preserve">0.612977504730225</t>
   </si>
   <si>
     <t xml:space="preserve">0.616670191287994</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">0.620362818241119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61519318819046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.601161122322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5945143699646</t>
+    <t xml:space="preserve">0.615193128585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601161062717438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594514429569244</t>
   </si>
   <si>
     <t xml:space="preserve">0.599684000015259</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">0.600422561168671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607069373130798</t>
+    <t xml:space="preserve">0.607069313526154</t>
   </si>
   <si>
     <t xml:space="preserve">0.593037247657776</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">0.641041576862335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.664674401283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66688996553421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658766210079193</t>
+    <t xml:space="preserve">0.664674460887909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6668900847435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658766269683838</t>
   </si>
   <si>
     <t xml:space="preserve">0.653596520423889</t>
@@ -2831,22 +2831,22 @@
     <t xml:space="preserve">0.629225134849548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642518639564514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640303075313568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633656322956085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.675752341747284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649165332317352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65581214427948</t>
+    <t xml:space="preserve">0.642518579959869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640303015708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63365626335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675752401351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649165391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.655812084674835</t>
   </si>
   <si>
     <t xml:space="preserve">0.655073583126068</t>
@@ -2861,19 +2861,19 @@
     <t xml:space="preserve">0.625532567501068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638087451457977</t>
+    <t xml:space="preserve">0.638087511062622</t>
   </si>
   <si>
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638826012611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626271069049835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702137947083</t>
+    <t xml:space="preserve">0.638825953006744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62627100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702197551727</t>
   </si>
   <si>
     <t xml:space="preserve">0.649903893470764</t>
@@ -2882,49 +2882,49 @@
     <t xml:space="preserve">0.657289147377014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662458896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678706467151642</t>
+    <t xml:space="preserve">0.662458837032318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678706407546997</t>
   </si>
   <si>
     <t xml:space="preserve">0.676490843296051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673536717891693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.661720335483551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635133385658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576789796352386</t>
+    <t xml:space="preserve">0.673536777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.661720395088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635133326053619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576789736747742</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587867617607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.507368087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711855888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564234793186188</t>
+    <t xml:space="preserve">0.587867677211761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.507368147373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529523909091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711736679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.564234733581543</t>
   </si>
   <si>
     <t xml:space="preserve">0.582697927951813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570881545543671</t>
+    <t xml:space="preserve">0.570881485939026</t>
   </si>
   <si>
     <t xml:space="preserve">0.559803605079651</t>
@@ -2939,52 +2939,52 @@
     <t xml:space="preserve">0.542078971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567188918590546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5797438621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562019169330597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55758798122406</t>
+    <t xml:space="preserve">0.567188858985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579743802547455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562019109725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557588040828705</t>
   </si>
   <si>
     <t xml:space="preserve">0.543555974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555372357368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569404482841492</t>
+    <t xml:space="preserve">0.555372416973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569404423236847</t>
   </si>
   <si>
     <t xml:space="preserve">0.574574112892151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58257657289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973728179932</t>
+    <t xml:space="preserve">0.582576513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973668575287</t>
   </si>
   <si>
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572912693024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56817215681076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.560169756412506</t>
+    <t xml:space="preserve">0.570572972297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568172216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.560169816017151</t>
   </si>
   <si>
     <t xml:space="preserve">0.562570512294769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569772660732269</t>
+    <t xml:space="preserve">0.569772720336914</t>
   </si>
   <si>
     <t xml:space="preserve">0.578575372695923</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">0.571373164653778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564971268177032</t>
+    <t xml:space="preserve">0.564971208572388</t>
   </si>
   <si>
     <t xml:space="preserve">0.552967607975006</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">0.54656571149826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537762939929962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755738735199</t>
+    <t xml:space="preserve">0.537762999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755679130554</t>
   </si>
   <si>
     <t xml:space="preserve">0.516156435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525759398937225</t>
+    <t xml:space="preserve">0.525759339332581</t>
   </si>
   <si>
     <t xml:space="preserve">0.521758139133453</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">0.522558391094208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53296160697937</t>
+    <t xml:space="preserve">0.532961547374725</t>
   </si>
   <si>
     <t xml:space="preserve">0.524959087371826</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">0.48814794421196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561770260334015</t>
+    <t xml:space="preserve">0.56177031993866</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">0.588978469371796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56897246837616</t>
+    <t xml:space="preserve">0.568972527980804</t>
   </si>
   <si>
     <t xml:space="preserve">0.572173416614532</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">0.575374364852905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577775061130524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565771520137787</t>
+    <t xml:space="preserve">0.577775120735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565771460533142</t>
   </si>
   <si>
     <t xml:space="preserve">0.580976068973541</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">0.58337676525116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.576974868774414</t>
+    <t xml:space="preserve">0.576974928379059</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">0.585777580738068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591379225254059</t>
+    <t xml:space="preserve">0.591379284858704</t>
   </si>
   <si>
     <t xml:space="preserve">0.564170956611633</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567371964454651</t>
+    <t xml:space="preserve">0.567371904850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">0.508954226970673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506553590297699</t>
+    <t xml:space="preserve">0.506553530693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.502552330493927</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554730892181</t>
+    <t xml:space="preserve">0.510554790496826</t>
   </si>
   <si>
     <t xml:space="preserve">0.524158835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529760539531708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.531360983848572</t>
+    <t xml:space="preserve">0.529760599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531361043453217</t>
   </si>
   <si>
     <t xml:space="preserve">0.550566852092743</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">0.532161295413971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530560731887817</t>
+    <t xml:space="preserve">0.530560791492462</t>
   </si>
   <si>
     <t xml:space="preserve">0.527359843254089</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">0.54736590385437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552167415618896</t>
+    <t xml:space="preserve">0.552167356014252</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
@@ -3230,10 +3230,7 @@
     <t xml:space="preserve">0.556968748569489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.558569312095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574574172496796</t>
+    <t xml:space="preserve">0.558569252490997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584177076816559</t>
@@ -3242,7 +3239,7 @@
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773920536041</t>
+    <t xml:space="preserve">0.573773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
@@ -3254,13 +3251,13 @@
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788442134857</t>
+    <t xml:space="preserve">0.621788501739502</t>
   </si>
   <si>
     <t xml:space="preserve">0.624189138412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622588634490967</t>
+    <t xml:space="preserve">0.622588694095612</t>
   </si>
   <si>
     <t xml:space="preserve">0.620187938213348</t>
@@ -3272,7 +3269,7 @@
     <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602582633495331</t>
+    <t xml:space="preserve">0.602582693099976</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3314,55 +3311,58 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792102336884</t>
+    <t xml:space="preserve">0.633792042732239</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
+    <t xml:space="preserve">0.628990709781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635921716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651516497135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641986310482025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631589770317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627257883548737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615128636360168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262163639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663043498993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197629451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615995049476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62119323015213</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635921716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651516437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64198637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631589770317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627257883548737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615128576755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663103103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197569847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464803218842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615994989871979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621193289756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64025354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723416805267</t>
+    <t xml:space="preserve">0.640253603458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723357200623</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3371,22 +3371,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732096195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61946052312851</t>
+    <t xml:space="preserve">0.604732036590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619460463523865</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395869731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331156730652</t>
+    <t xml:space="preserve">0.612529456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395810127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331216335297</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620326936244965</t>
+    <t xml:space="preserve">0.62032687664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801089286804</t>
+    <t xml:space="preserve">0.597801029682159</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658763408661</t>
+    <t xml:space="preserve">0.624658823013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3431,10 +3431,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727696895599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861343383789</t>
+    <t xml:space="preserve">0.617727756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861402988434</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387130737305</t>
+    <t xml:space="preserve">0.639387190341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382850646973</t>
+    <t xml:space="preserve">0.652382910251617</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848443508148</t>
+    <t xml:space="preserve">0.655848383903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042284488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687038004398346</t>
+    <t xml:space="preserve">0.674042344093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68270605802536</t>
+    <t xml:space="preserve">0.682706117630005</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637124538422</t>
+    <t xml:space="preserve">0.689637184143066</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739886999130249</t>
+    <t xml:space="preserve">0.739887058734894</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412965297699</t>
+    <t xml:space="preserve">0.762412905693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779740452766418</t>
+    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.76846718788147</t>
@@ -3702,9 +3702,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.787256062030792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -51366,7 +51363,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="s">
-        <v>1073</v>
+        <v>982</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51600,7 +51597,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1815" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51626,7 +51623,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51704,7 +51701,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1819" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51808,7 +51805,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="s">
-        <v>1073</v>
+        <v>982</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51834,7 +51831,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="s">
-        <v>1073</v>
+        <v>982</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51912,7 +51909,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52250,7 +52247,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G1840" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52276,7 +52273,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1841" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52302,7 +52299,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1842" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52328,7 +52325,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1843" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52354,7 +52351,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1844" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52380,7 +52377,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1845" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52406,7 +52403,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52432,7 +52429,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1847" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52458,7 +52455,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52484,7 +52481,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52510,7 +52507,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52536,7 +52533,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G1851" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52562,7 +52559,7 @@
         <v>0.77700001001358</v>
       </c>
       <c r="G1852" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52588,7 +52585,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1853" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52614,7 +52611,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1854" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52640,7 +52637,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52666,7 +52663,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G1856" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52692,7 +52689,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1857" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52718,7 +52715,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1858" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52744,7 +52741,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1859" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52770,7 +52767,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52796,7 +52793,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1861" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52822,7 +52819,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1862" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52848,7 +52845,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1863" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52874,7 +52871,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1864" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52900,7 +52897,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1865" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52926,7 +52923,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1866" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52952,7 +52949,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1867" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52978,7 +52975,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53004,7 +53001,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53030,7 +53027,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1870" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53056,7 +53053,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1871" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53082,7 +53079,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1872" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53108,7 +53105,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53134,7 +53131,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1874" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53160,7 +53157,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1875" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53186,7 +53183,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53212,7 +53209,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1877" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53238,7 +53235,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53264,7 +53261,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1879" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53290,7 +53287,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1880" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53316,7 +53313,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1881" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53342,7 +53339,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53368,7 +53365,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53394,7 +53391,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53420,7 +53417,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1885" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53446,7 +53443,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1886" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53472,7 +53469,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53498,7 +53495,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1888" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53524,7 +53521,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1889" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53550,7 +53547,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1890" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53576,7 +53573,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1891" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53602,7 +53599,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1892" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53628,7 +53625,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1893" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53654,7 +53651,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53680,7 +53677,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1895" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53706,7 +53703,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53732,7 +53729,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53862,7 +53859,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53992,7 +53989,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54044,7 +54041,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54174,7 +54171,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1914" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54200,7 +54197,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54252,7 +54249,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1917" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54330,7 +54327,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1920" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54382,7 +54379,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1922" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54460,7 +54457,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1925" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54486,7 +54483,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54616,7 +54613,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1931" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54642,7 +54639,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1932" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54668,7 +54665,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1933" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54720,7 +54717,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54824,7 +54821,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54850,7 +54847,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1940" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54954,7 +54951,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54980,7 +54977,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1945" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55032,7 +55029,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1947" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55266,7 +55263,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1956" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55396,7 +55393,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1961" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55422,7 +55419,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1962" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55448,7 +55445,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1963" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55474,7 +55471,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1964" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -55500,7 +55497,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1965" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -55656,7 +55653,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1971" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56046,7 +56043,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1986" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56280,7 +56277,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1995" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56358,7 +56355,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1998" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -56410,7 +56407,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2000" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -56488,7 +56485,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2003" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -56514,7 +56511,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2004" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -56540,7 +56537,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2005" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -56566,7 +56563,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2006" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -56592,7 +56589,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2007" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -56696,7 +56693,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2011" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -56878,7 +56875,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2018" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56904,7 +56901,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2019" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57216,7 +57213,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57242,7 +57239,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57320,7 +57317,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -57346,7 +57343,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58152,7 +58149,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G2067" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58308,7 +58305,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58386,7 +58383,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -58490,7 +58487,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -58568,7 +58565,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -63248,7 +63245,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G2263" t="s">
-        <v>1230</v>
+        <v>1192</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63274,7 +63271,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2264" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63300,7 +63297,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2265" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63326,7 +63323,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2266" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -63352,7 +63349,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G2267" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -63378,7 +63375,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2268" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63404,7 +63401,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G2269" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63430,7 +63427,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2270" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63456,7 +63453,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G2271" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63482,7 +63479,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G2272" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63508,7 +63505,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G2273" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -63534,7 +63531,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2274" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63560,7 +63557,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2275" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -63586,7 +63583,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2276" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -63612,7 +63609,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2277" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -63638,7 +63635,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2278" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -63664,7 +63661,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2279" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63690,7 +63687,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G2280" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63716,7 +63713,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2281" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63742,7 +63739,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2282" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63768,7 +63765,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2283" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63794,7 +63791,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2284" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63820,7 +63817,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2285" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63846,7 +63843,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G2286" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63872,7 +63869,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G2287" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63898,7 +63895,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G2288" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63924,7 +63921,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G2289" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63950,7 +63947,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2290" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63976,7 +63973,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2291" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64002,7 +63999,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G2292" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64028,7 +64025,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2293" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64054,7 +64051,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2294" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64080,7 +64077,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2295" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64106,7 +64103,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G2296" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64132,7 +64129,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2297" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64158,7 +64155,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2298" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64184,7 +64181,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G2299" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64210,7 +64207,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G2300" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64236,7 +64233,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G2301" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64262,7 +64259,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2302" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64288,7 +64285,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2303" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64314,7 +64311,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2304" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64340,7 +64337,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2305" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64366,7 +64363,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G2306" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64392,7 +64389,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2307" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64418,7 +64415,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G2308" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64444,7 +64441,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2309" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64470,7 +64467,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G2310" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64496,7 +64493,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G2311" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64522,7 +64519,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G2312" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64548,7 +64545,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2313" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64574,7 +64571,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2314" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64600,7 +64597,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G2315" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64626,7 +64623,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G2316" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64652,7 +64649,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2317" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64678,7 +64675,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64704,7 +64701,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2319" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64730,7 +64727,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2320" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64756,7 +64753,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64782,7 +64779,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G2322" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64808,7 +64805,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G2323" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64834,7 +64831,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G2324" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64860,7 +64857,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2325" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64886,7 +64883,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2326" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64912,7 +64909,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2327" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64938,7 +64935,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2328" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64964,7 +64961,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2329" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64990,7 +64987,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2330" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65016,7 +65013,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2331" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65042,7 +65039,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2332" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65068,7 +65065,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2333" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65094,7 +65091,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2334" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65120,7 +65117,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2335" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65146,7 +65143,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2336" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65172,7 +65169,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2337" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65198,7 +65195,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G2338" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65224,7 +65221,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G2339" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65250,7 +65247,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2340" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65276,7 +65273,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2341" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65302,7 +65299,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2342" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65328,7 +65325,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2343" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65354,7 +65351,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2344" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65380,7 +65377,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2345" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65406,7 +65403,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65432,7 +65429,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2347" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65458,7 +65455,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65484,7 +65481,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2349" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65510,7 +65507,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2350" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65536,7 +65533,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2351" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65562,7 +65559,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2352" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65588,7 +65585,7 @@
         <v>1</v>
       </c>
       <c r="G2353" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65614,7 +65611,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2354" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65640,7 +65637,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2355" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65666,7 +65663,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G2356" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65692,7 +65689,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G2357" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65718,7 +65715,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2358" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65744,7 +65741,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G2359" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65770,7 +65767,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G2360" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65796,7 +65793,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G2361" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65822,7 +65819,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G2362" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65848,7 +65845,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2363" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65874,7 +65871,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G2364" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65900,7 +65897,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G2365" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65926,7 +65923,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G2366" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65952,7 +65949,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G2367" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65978,7 +65975,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2368" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66004,7 +66001,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2369" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66030,7 +66027,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2370" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66056,7 +66053,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G2371" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66082,7 +66079,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G2372" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66108,7 +66105,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G2373" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66134,7 +66131,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G2374" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66160,7 +66157,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2375" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66186,7 +66183,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2376" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66212,7 +66209,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2377" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66238,7 +66235,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2378" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66264,7 +66261,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2379" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66290,7 +66287,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2380" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66316,7 +66313,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G2381" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66342,7 +66339,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G2382" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66368,7 +66365,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G2383" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66394,7 +66391,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66420,7 +66417,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G2385" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66446,7 +66443,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G2386" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66472,7 +66469,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2387" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66498,7 +66495,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2388" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66524,7 +66521,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2389" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66550,7 +66547,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2390" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66576,7 +66573,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2391" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66602,7 +66599,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2392" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66628,7 +66625,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2393" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66654,7 +66651,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2394" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66680,7 +66677,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G2395" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66706,7 +66703,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2396" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66732,7 +66729,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2397" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66758,7 +66755,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2398" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66784,7 +66781,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2399" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66810,7 +66807,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2400" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66836,7 +66833,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G2401" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66862,7 +66859,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2402" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66888,7 +66885,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G2403" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66914,7 +66911,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G2404" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66940,7 +66937,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2405" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66966,7 +66963,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G2406" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66992,7 +66989,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G2407" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67018,7 +67015,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G2408" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67044,7 +67041,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G2409" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67070,7 +67067,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2410" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67096,7 +67093,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2411" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67122,7 +67119,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2412" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67148,7 +67145,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G2413" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67174,7 +67171,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2414" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67200,7 +67197,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2415" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67226,7 +67223,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2416" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67252,7 +67249,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G2417" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67278,7 +67275,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G2418" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67304,7 +67301,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G2419" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67330,7 +67327,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G2420" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67356,7 +67353,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G2421" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67382,7 +67379,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G2422" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67408,7 +67405,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2423" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67434,7 +67431,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2424" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67460,7 +67457,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G2425" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67486,7 +67483,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2426" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67512,7 +67509,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2427" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67538,7 +67535,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2428" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67564,7 +67561,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2429" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67590,7 +67587,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2430" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67616,7 +67613,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2431" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67642,7 +67639,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2432" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67668,7 +67665,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2433" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67694,7 +67691,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2434" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67720,7 +67717,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67746,7 +67743,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G2436" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67772,7 +67769,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2437" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67798,7 +67795,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2438" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67824,7 +67821,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G2439" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67850,7 +67847,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2440" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67876,7 +67873,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2441" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67902,7 +67899,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67928,7 +67925,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2443" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67954,7 +67951,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G2444" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67980,7 +67977,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G2445" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68006,7 +68003,7 @@
         <v>1</v>
       </c>
       <c r="G2446" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68032,7 +68029,7 @@
         <v>1</v>
       </c>
       <c r="G2447" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68058,7 +68055,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68084,7 +68081,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2449" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68110,7 +68107,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G2450" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68136,7 +68133,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2451" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68162,7 +68159,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G2452" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68188,7 +68185,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2453" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68214,7 +68211,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G2454" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68240,7 +68237,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G2455" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68266,7 +68263,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2456" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68292,7 +68289,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2457" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68318,7 +68315,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2458" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68344,7 +68341,7 @@
         <v>1</v>
       </c>
       <c r="G2459" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68370,7 +68367,7 @@
         <v>1</v>
       </c>
       <c r="G2460" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68396,7 +68393,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G2461" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68422,7 +68419,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G2462" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68448,7 +68445,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G2463" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68474,7 +68471,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G2464" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68500,7 +68497,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G2465" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68526,7 +68523,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2466" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68552,7 +68549,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2467" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68578,7 +68575,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2468" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68604,7 +68601,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2469" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68630,7 +68627,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G2470" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68656,7 +68653,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G2471" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68682,7 +68679,7 @@
         <v>1.08599996566772</v>
       </c>
       <c r="G2472" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68708,7 +68705,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G2473" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68734,7 +68731,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2474" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68760,7 +68757,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2475" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68786,7 +68783,7 @@
         <v>1.05400002002716</v>
       </c>
       <c r="G2476" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68812,7 +68809,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2477" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68838,7 +68835,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2478" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68864,7 +68861,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2479" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68890,7 +68887,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G2480" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68916,7 +68913,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2481" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68942,7 +68939,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2482" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68968,7 +68965,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68994,7 +68991,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2484" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69020,7 +69017,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2485" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69046,7 +69043,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G2486" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69072,7 +69069,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2487" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69098,7 +69095,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69124,7 +69121,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2489" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69150,7 +69147,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69176,7 +69173,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2491" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69202,7 +69199,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2492" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69228,7 +69225,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G2493" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69254,7 +69251,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G2494" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69280,7 +69277,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G2495" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69306,7 +69303,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69332,7 +69329,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2497" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69358,7 +69355,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G2498" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69384,7 +69381,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G2499" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69410,7 +69407,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G2500" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69436,7 +69433,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G2501" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69462,7 +69459,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G2502" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69488,7 +69485,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G2503" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69496,7 +69493,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6911111111</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>175043</v>
@@ -69514,9 +69511,35 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G2504" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.69125</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>50050</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>1.0440000295639</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>1.03400003910065</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>1.0440000295639</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>1.0440000295639</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">0.367179721593857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3804971575737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361789405345917</t>
+    <t xml:space="preserve">0.380497097969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.361789345741272</t>
   </si>
   <si>
     <t xml:space="preserve">0.352276921272278</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">0.387155830860138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410936921834946</t>
+    <t xml:space="preserve">0.410936892032623</t>
   </si>
   <si>
     <t xml:space="preserve">0.390009552240372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373521327972412</t>
+    <t xml:space="preserve">0.373521357774734</t>
   </si>
   <si>
     <t xml:space="preserve">0.359886884689331</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">0.335471630096436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345618218183517</t>
+    <t xml:space="preserve">0.345618277788162</t>
   </si>
   <si>
     <t xml:space="preserve">0.361472278833389</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">0.341496169567108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355130702257156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352594017982483</t>
+    <t xml:space="preserve">0.355130672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352594047784805</t>
   </si>
   <si>
     <t xml:space="preserve">0.342447429895401</t>
@@ -101,52 +101,52 @@
     <t xml:space="preserve">0.360838145017624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35735023021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357984364032745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350691556930542</t>
+    <t xml:space="preserve">0.357350260019302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357984393835068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35069152712822</t>
   </si>
   <si>
     <t xml:space="preserve">0.317080944776535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291714459657669</t>
+    <t xml:space="preserve">0.291714489459991</t>
   </si>
   <si>
     <t xml:space="preserve">0.297739028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.275860458612442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276240974664688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304461121559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326593369245529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348789095878601</t>
+    <t xml:space="preserve">0.27586042881012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.276240944862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304461151361465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326593339443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348789066076279</t>
   </si>
   <si>
     <t xml:space="preserve">0.32913002371788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348471969366074</t>
+    <t xml:space="preserve">0.348471939563751</t>
   </si>
   <si>
     <t xml:space="preserve">0.327544629573822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671128988266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330081254243851</t>
+    <t xml:space="preserve">0.314671158790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330081284046173</t>
   </si>
   <si>
     <t xml:space="preserve">0.334203332662582</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">0.386838763952255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356398969888687</t>
+    <t xml:space="preserve">0.35639899969101</t>
   </si>
   <si>
     <t xml:space="preserve">0.368765145540237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325325042009354</t>
+    <t xml:space="preserve">0.325325071811676</t>
   </si>
   <si>
     <t xml:space="preserve">0.318032205104828</t>
@@ -170,52 +170,52 @@
     <t xml:space="preserve">0.306236773729324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308329522609711</t>
+    <t xml:space="preserve">0.308329492807388</t>
   </si>
   <si>
     <t xml:space="preserve">0.331032544374466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322788387537003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319934636354446</t>
+    <t xml:space="preserve">0.322788447141647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319934695959091</t>
   </si>
   <si>
     <t xml:space="preserve">0.309153944253922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331666648387909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320251762866974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310802727937698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323422580957413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308836877346039</t>
+    <t xml:space="preserve">0.331666678190231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320251733064651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310802787542343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32342255115509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308836817741394</t>
   </si>
   <si>
     <t xml:space="preserve">0.306300193071365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298880487680435</t>
+    <t xml:space="preserve">0.29888054728508</t>
   </si>
   <si>
     <t xml:space="preserve">0.285880208015442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.267743170261383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260767340660095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.267489492893219</t>
+    <t xml:space="preserve">0.267743140459061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.260767370462418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.267489463090897</t>
   </si>
   <si>
     <t xml:space="preserve">0.258738070726395</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">0.371618896722794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364643067121506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36749678850174</t>
+    <t xml:space="preserve">0.364643096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367496848106384</t>
   </si>
   <si>
     <t xml:space="preserve">0.36971640586853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369399309158325</t>
+    <t xml:space="preserve">0.369399279356003</t>
   </si>
   <si>
     <t xml:space="preserve">0.388741225004196</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.38779005408287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370033413171768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357033133506775</t>
+    <t xml:space="preserve">0.370033502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357033163309097</t>
   </si>
   <si>
     <t xml:space="preserve">0.3741554915905</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">0.377643376588821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370984703302383</t>
+    <t xml:space="preserve">0.370984673500061</t>
   </si>
   <si>
     <t xml:space="preserve">0.372253030538559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387472897768021</t>
+    <t xml:space="preserve">0.387472957372665</t>
   </si>
   <si>
     <t xml:space="preserve">0.377326369285583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439791232347488</t>
+    <t xml:space="preserve">0.439791291952133</t>
   </si>
   <si>
     <t xml:space="preserve">0.453425765037537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454059958457947</t>
+    <t xml:space="preserve">0.454059898853302</t>
   </si>
   <si>
     <t xml:space="preserve">0.461669862270355</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">0.459133207798004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45564529299736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45627948641777</t>
+    <t xml:space="preserve">0.455645322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456279546022415</t>
   </si>
   <si>
     <t xml:space="preserve">0.464840680360794</t>
@@ -296,55 +296,55 @@
     <t xml:space="preserve">0.47879222035408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.485768049955368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.477840930223465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483231395483017</t>
+    <t xml:space="preserve">0.485767990350723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47784098982811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483231365680695</t>
   </si>
   <si>
     <t xml:space="preserve">0.484816789627075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.497817128896713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489255905151367</t>
+    <t xml:space="preserve">0.497817069292068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48925593495369</t>
   </si>
   <si>
     <t xml:space="preserve">0.475621402263641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476889699697495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488304615020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493695020675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489890098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496548712253571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468645662069321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473084777593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495280474424362</t>
+    <t xml:space="preserve">0.476889789104462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488304674625397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493695050477982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489890158176422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496548742055893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468645691871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47308474779129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495280504226685</t>
   </si>
   <si>
     <t xml:space="preserve">0.486719280481339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484182626008987</t>
+    <t xml:space="preserve">0.484182596206665</t>
   </si>
   <si>
     <t xml:space="preserve">0.497500002384186</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">0.507329523563385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50796377658844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514939367771149</t>
+    <t xml:space="preserve">0.507963716983795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514939427375793</t>
   </si>
   <si>
     <t xml:space="preserve">0.510183274745941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515890717506409</t>
+    <t xml:space="preserve">0.515890657901764</t>
   </si>
   <si>
     <t xml:space="preserve">0.526354372501373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525720179080963</t>
+    <t xml:space="preserve">0.525720238685608</t>
   </si>
   <si>
     <t xml:space="preserve">0.52952516078949</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">0.625917792320251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627503156661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.597697615623474</t>
+    <t xml:space="preserve">0.627503216266632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.597697556018829</t>
   </si>
   <si>
     <t xml:space="preserve">0.596112191677094</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">0.577087342739105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.561867535114288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583428919315338</t>
+    <t xml:space="preserve">0.561867415904999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583428978919983</t>
   </si>
   <si>
     <t xml:space="preserve">0.569160342216492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.566940784454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559013724327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.551720917224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529208123683929</t>
+    <t xml:space="preserve">0.566940724849701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559013783931732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.551720857620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529208183288574</t>
   </si>
   <si>
     <t xml:space="preserve">0.516841948032379</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">0.465791910886765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4835484623909</t>
+    <t xml:space="preserve">0.483548432588577</t>
   </si>
   <si>
     <t xml:space="preserve">0.549184262752533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547281742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558379590511322</t>
+    <t xml:space="preserve">0.547281682491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558379650115967</t>
   </si>
   <si>
     <t xml:space="preserve">0.585965633392334</t>
@@ -449,28 +449,28 @@
     <t xml:space="preserve">0.586599767208099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613868772983551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654455065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.665869951248169</t>
+    <t xml:space="preserve">0.613868713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654455006122589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.665870010852814</t>
   </si>
   <si>
     <t xml:space="preserve">0.655089259147644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62306410074234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63384485244751</t>
+    <t xml:space="preserve">0.623064160346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633844792842865</t>
   </si>
   <si>
     <t xml:space="preserve">0.62211287021637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618942022323608</t>
+    <t xml:space="preserve">0.618942081928253</t>
   </si>
   <si>
     <t xml:space="preserve">0.615137100219727</t>
@@ -491,70 +491,70 @@
     <t xml:space="preserve">0.643674314022064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644308567047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645576775074005</t>
+    <t xml:space="preserve">0.644308507442474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645576894283295</t>
   </si>
   <si>
     <t xml:space="preserve">0.636064410209656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634796142578125</t>
+    <t xml:space="preserve">0.63479608297348</t>
   </si>
   <si>
     <t xml:space="preserve">0.628454446792603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632259368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.626551985740662</t>
+    <t xml:space="preserve">0.632259428501129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626551926136017</t>
   </si>
   <si>
     <t xml:space="preserve">0.626234889030457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602453827857971</t>
+    <t xml:space="preserve">0.602453768253326</t>
   </si>
   <si>
     <t xml:space="preserve">0.588185131549835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590087652206421</t>
+    <t xml:space="preserve">0.590087592601776</t>
   </si>
   <si>
     <t xml:space="preserve">0.58913642168045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.619893252849579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592941343784332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60055136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595795094966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594526767730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591673016548157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60118556022644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603088021278381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609746694564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61133199930191</t>
+    <t xml:space="preserve">0.619893312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592941403388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600551307201385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595795035362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594526827335358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591673135757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.601185500621796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603087961673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609746634960175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611332058906555</t>
   </si>
   <si>
     <t xml:space="preserve">0.614185810089111</t>
@@ -563,34 +563,34 @@
     <t xml:space="preserve">0.611966192722321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605941712856293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5986487865448</t>
+    <t xml:space="preserve">0.605941772460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598648846149445</t>
   </si>
   <si>
     <t xml:space="preserve">0.593258500099182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588502287864685</t>
+    <t xml:space="preserve">0.58850222826004</t>
   </si>
   <si>
     <t xml:space="preserve">0.597380518913269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617673754692078</t>
+    <t xml:space="preserve">0.617673635482788</t>
   </si>
   <si>
     <t xml:space="preserve">0.611015021800995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604039192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605307519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61006373167038</t>
+    <t xml:space="preserve">0.604039251804352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.605307579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610063791275024</t>
   </si>
   <si>
     <t xml:space="preserve">0.624649465084076</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">0.565355360507965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523183584213257</t>
+    <t xml:space="preserve">0.523183524608612</t>
   </si>
   <si>
     <t xml:space="preserve">0.481963038444519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493378013372421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492109626531601</t>
+    <t xml:space="preserve">0.493377923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492109686136246</t>
   </si>
   <si>
     <t xml:space="preserve">0.508280754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513988256454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509231925010681</t>
+    <t xml:space="preserve">0.513988196849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.509231984615326</t>
   </si>
   <si>
     <t xml:space="preserve">0.509549081325531</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.51779317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548550009727478</t>
+    <t xml:space="preserve">0.548550069332123</t>
   </si>
   <si>
     <t xml:space="preserve">0.544110953807831</t>
@@ -650,28 +650,28 @@
     <t xml:space="preserve">0.521598160266876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53047639131546</t>
+    <t xml:space="preserve">0.530476450920105</t>
   </si>
   <si>
     <t xml:space="preserve">0.546013414859772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.540940165519714</t>
+    <t xml:space="preserve">0.54094010591507</t>
   </si>
   <si>
     <t xml:space="preserve">0.532696008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538720607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539037704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533330202102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.532061874866486</t>
+    <t xml:space="preserve">0.538720548152924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539037585258484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533330142498016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.532061815261841</t>
   </si>
   <si>
     <t xml:space="preserve">0.568843245506287</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">0.549501299858093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560599148273468</t>
+    <t xml:space="preserve">0.560599088668823</t>
   </si>
   <si>
     <t xml:space="preserve">0.56440407037735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550452470779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54284256696701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545062124729156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521281182765961</t>
+    <t xml:space="preserve">0.550452530384064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542842626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545062184333801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521281063556671</t>
   </si>
   <si>
     <t xml:space="preserve">0.516524910926819</t>
@@ -710,52 +710,52 @@
     <t xml:space="preserve">0.50669538974762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528256893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.519695639610291</t>
+    <t xml:space="preserve">0.528256833553314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.519695699214935</t>
   </si>
   <si>
     <t xml:space="preserve">0.526037395000458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51874440908432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511451601982117</t>
+    <t xml:space="preserve">0.518744468688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511451661586761</t>
   </si>
   <si>
     <t xml:space="preserve">0.514305353164673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523817718029022</t>
+    <t xml:space="preserve">0.523817777633667</t>
   </si>
   <si>
     <t xml:space="preserve">0.508597850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522549450397491</t>
+    <t xml:space="preserve">0.522549390792847</t>
   </si>
   <si>
     <t xml:space="preserve">0.513671159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511134445667267</t>
+    <t xml:space="preserve">0.511134505271912</t>
   </si>
   <si>
     <t xml:space="preserve">0.504158735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506061196327209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.505109965801239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510500371456146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499719530344009</t>
+    <t xml:space="preserve">0.506061255931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.505110025405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.510500311851501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.499719500541687</t>
   </si>
   <si>
     <t xml:space="preserve">0.512085735797882</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">0.560282051563263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569794476032257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.575501918792725</t>
+    <t xml:space="preserve">0.569794535636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.575501978397369</t>
   </si>
   <si>
     <t xml:space="preserve">0.627820312976837</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">0.658894240856171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655723392963409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.682358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.762262582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.736896157264709</t>
+    <t xml:space="preserve">0.655723452568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.682358205318451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.762262642383575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.73689603805542</t>
   </si>
   <si>
     <t xml:space="preserve">0.707724690437317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.696943938732147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.733091115951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.748945295810699</t>
+    <t xml:space="preserve">0.696943879127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.733091175556183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.748945236206055</t>
   </si>
   <si>
     <t xml:space="preserve">0.747676908969879</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.755286753177643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.760360062122345</t>
+    <t xml:space="preserve">0.760360181331635</t>
   </si>
   <si>
     <t xml:space="preserve">0.818068861961365</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">0.771140873432159</t>
   </si>
   <si>
-    <t xml:space="preserve">0.768604218959808</t>
+    <t xml:space="preserve">0.768604159355164</t>
   </si>
   <si>
     <t xml:space="preserve">0.720407962799072</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">0.727383673191071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.740701138973236</t>
+    <t xml:space="preserve">0.740701079368591</t>
   </si>
   <si>
     <t xml:space="preserve">0.738164484500885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.774945795536041</t>
+    <t xml:space="preserve">0.774945914745331</t>
   </si>
   <si>
     <t xml:space="preserve">0.78382396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.801580548286438</t>
+    <t xml:space="preserve">0.801580667495728</t>
   </si>
   <si>
     <t xml:space="preserve">0.849776983261108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.884021759033203</t>
+    <t xml:space="preserve">0.884021699428558</t>
   </si>
   <si>
     <t xml:space="preserve">0.851045250892639</t>
@@ -866,25 +866,25 @@
     <t xml:space="preserve">0.878314256668091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.894168198108673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.925876379013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.924608170986176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88782674074173</t>
+    <t xml:space="preserve">0.894168317317963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.925876438617706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.924608111381531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.887826681137085</t>
   </si>
   <si>
     <t xml:space="preserve">0.901778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.881484985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902412295341492</t>
+    <t xml:space="preserve">0.881485044956207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.902412354946136</t>
   </si>
   <si>
     <t xml:space="preserve">0.87514340877533</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">0.896070778369904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9106565117836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.913827359676361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.910022377967834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.889729142189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.892899990081787</t>
+    <t xml:space="preserve">0.910656571388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.913827300071716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.910022139549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.889729201793671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.892899870872498</t>
   </si>
   <si>
     <t xml:space="preserve">0.895436584949493</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">0.863094329833984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.860557734966278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.867533564567566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.875777542591095</t>
+    <t xml:space="preserve">0.860557675361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.867533385753632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.875777721405029</t>
   </si>
   <si>
     <t xml:space="preserve">0.868167638778687</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.756555199623108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.788897395133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812995553016663</t>
+    <t xml:space="preserve">0.788897454738617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812995493412018</t>
   </si>
   <si>
     <t xml:space="preserve">0.80728816986084</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">0.838362097740173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.790165781974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.786360740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.811727166175842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.830118000507355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.814897954463959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.792702436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.803483068943024</t>
+    <t xml:space="preserve">0.790165662765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.786360800266266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.811727225780487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83011794090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.814898014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.792702496051788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.803483128547668</t>
   </si>
   <si>
     <t xml:space="preserve">0.804117262363434</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">0.781921625137329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.791434049606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78509247303009</t>
+    <t xml:space="preserve">0.791433990001678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785092532634735</t>
   </si>
   <si>
     <t xml:space="preserve">0.786994993686676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.793970704078674</t>
+    <t xml:space="preserve">0.79397064447403</t>
   </si>
   <si>
     <t xml:space="preserve">0.789531528949738</t>
@@ -995,46 +995,46 @@
     <t xml:space="preserve">0.775580108165741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.769872605800629</t>
+    <t xml:space="preserve">0.769872546195984</t>
   </si>
   <si>
     <t xml:space="preserve">0.767335951328278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771775186061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.761628448963165</t>
+    <t xml:space="preserve">0.77177494764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.761628389358521</t>
   </si>
   <si>
     <t xml:space="preserve">0.795873165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.811093091964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.843435347080231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.832654595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.872606933116913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.862460196018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.866899371147156</t>
+    <t xml:space="preserve">0.811093151569366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.843435406684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.832654535770416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.872606873512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.862460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.866899251937866</t>
   </si>
   <si>
     <t xml:space="preserve">0.840264618396759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.830752015113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.855484426021576</t>
+    <t xml:space="preserve">0.830752074718475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.855484485626221</t>
   </si>
   <si>
     <t xml:space="preserve">0.842801153659821</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">0.849142730236053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.820605516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.824410438537598</t>
+    <t xml:space="preserve">0.820605456829071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.824410498142242</t>
   </si>
   <si>
     <t xml:space="preserve">0.826947093009949</t>
@@ -1055,34 +1055,34 @@
     <t xml:space="preserve">0.806019842624664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.799043953418732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.804751455783844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.785726487636566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778750836849213</t>
+    <t xml:space="preserve">0.799044013023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.804751515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785726547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778750896453857</t>
   </si>
   <si>
     <t xml:space="preserve">0.777482450008392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.802214920520782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80665385723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80792224407196</t>
+    <t xml:space="preserve">0.802214741706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80665397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.807922303676605</t>
   </si>
   <si>
     <t xml:space="preserve">0.854850172996521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.857386946678162</t>
+    <t xml:space="preserve">0.857386887073517</t>
   </si>
   <si>
     <t xml:space="preserve">0.852313578128815</t>
@@ -1091,43 +1091,43 @@
     <t xml:space="preserve">0.86372846364975</t>
   </si>
   <si>
-    <t xml:space="preserve">0.864996671676636</t>
+    <t xml:space="preserve">0.86499685049057</t>
   </si>
   <si>
     <t xml:space="preserve">0.850411117076874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.840898633003235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.834557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.838996112346649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.827581346035004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.826312959194183</t>
+    <t xml:space="preserve">0.84089857339859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.834556996822357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.838996171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.827581226825714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.826312899589539</t>
   </si>
   <si>
     <t xml:space="preserve">0.805385589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.814263939857483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.818702876567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81933730840683</t>
+    <t xml:space="preserve">0.814263820648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81870299577713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.819337248802185</t>
   </si>
   <si>
     <t xml:space="preserve">0.79650741815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.809190571308136</t>
+    <t xml:space="preserve">0.809190630912781</t>
   </si>
   <si>
     <t xml:space="preserve">0.809824764728546</t>
@@ -1136,25 +1136,25 @@
     <t xml:space="preserve">0.797775626182556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.798409819602966</t>
+    <t xml:space="preserve">0.798409879207611</t>
   </si>
   <si>
     <t xml:space="preserve">0.817434787750244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.823142170906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.812361419200897</t>
+    <t xml:space="preserve">0.823142230510712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.812361359596252</t>
   </si>
   <si>
     <t xml:space="preserve">0.819971263408661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.797141432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.716602981090546</t>
+    <t xml:space="preserve">0.797141492366791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.71660304069519</t>
   </si>
   <si>
     <t xml:space="preserve">0.704553842544556</t>
@@ -1163,34 +1163,34 @@
     <t xml:space="preserve">0.736261963844299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75972592830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77240914106369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.776214182376862</t>
+    <t xml:space="preserve">0.759725987911224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77240926027298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.776214122772217</t>
   </si>
   <si>
     <t xml:space="preserve">0.78445827960968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.783190011978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.752115905284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.7609943151474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.757823526859283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.766701638698578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.790799856185913</t>
+    <t xml:space="preserve">0.783189952373505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.752116084098816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76099419593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.757823586463928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.766701698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.790799915790558</t>
   </si>
   <si>
     <t xml:space="preserve">0.810458898544312</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">0.774311661720276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.781287431716919</t>
+    <t xml:space="preserve">0.781287550926208</t>
   </si>
   <si>
     <t xml:space="preserve">0.795238971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.800312399864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.815532207489014</t>
+    <t xml:space="preserve">0.800312340259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.815532267093658</t>
   </si>
   <si>
     <t xml:space="preserve">0.764799237251282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.731822907924652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.711529672145844</t>
+    <t xml:space="preserve">0.731822967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711529612541199</t>
   </si>
   <si>
     <t xml:space="preserve">0.693773090839386</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">0.739432811737061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.703919649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.695041477680206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.683626532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660796701908112</t>
+    <t xml:space="preserve">0.70391970872879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.695041358470917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.683626472949982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660796761512756</t>
   </si>
   <si>
     <t xml:space="preserve">0.684894859790802</t>
@@ -1244,31 +1244,31 @@
     <t xml:space="preserve">0.670943260192871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.691236436367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678553283214569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687431454658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717871189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.730554461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.710261404514313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697578191757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71406626701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.729286134243011</t>
+    <t xml:space="preserve">0.691236555576324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678553342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687431514263153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717871248722076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730554401874542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.710261344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697578132152557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.714066326618195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.729286193847656</t>
   </si>
   <si>
     <t xml:space="preserve">0.753384292125702</t>
@@ -1280,28 +1280,28 @@
     <t xml:space="preserve">0.757189273834229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.758457660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.763531029224396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74957937002182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747042655944824</t>
+    <t xml:space="preserve">0.758457720279694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.763530910015106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749579310417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.747042715549469</t>
   </si>
   <si>
     <t xml:space="preserve">0.735627830028534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745774388313293</t>
+    <t xml:space="preserve">0.745774447917938</t>
   </si>
   <si>
     <t xml:space="preserve">0.743237793445587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.741969406604767</t>
+    <t xml:space="preserve">0.741969347000122</t>
   </si>
   <si>
     <t xml:space="preserve">0.744506061077118</t>
@@ -1313,37 +1313,37 @@
     <t xml:space="preserve">0.700114667415619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706456303596497</t>
+    <t xml:space="preserve">0.706456363201141</t>
   </si>
   <si>
     <t xml:space="preserve">0.698846459388733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.725481331348419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71533465385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.712797939777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69250476360321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.705188035964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.681089818477631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.701383113861084</t>
+    <t xml:space="preserve">0.725481271743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.715334594249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.712797999382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.692504823207855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.705188095569611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.681089878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.701383054256439</t>
   </si>
   <si>
     <t xml:space="preserve">0.696309804916382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688699781894684</t>
+    <t xml:space="preserve">0.688699722290039</t>
   </si>
   <si>
     <t xml:space="preserve">0.686163246631622</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">0.672211647033691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646845161914825</t>
+    <t xml:space="preserve">0.646845102310181</t>
   </si>
   <si>
     <t xml:space="preserve">0.677284836769104</t>
@@ -1367,13 +1367,13 @@
     <t xml:space="preserve">0.659528374671936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.651918351650238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.648113429546356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.641771852970123</t>
+    <t xml:space="preserve">0.651918411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.648113369941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641771793365479</t>
   </si>
   <si>
     <t xml:space="preserve">0.635430216789246</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">0.643040239810944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639235138893127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637966811656952</t>
+    <t xml:space="preserve">0.639235258102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.637966930866241</t>
   </si>
   <si>
     <t xml:space="preserve">0.594209671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596746265888214</t>
+    <t xml:space="preserve">0.596746325492859</t>
   </si>
   <si>
     <t xml:space="preserve">0.609429597854614</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">0.598014712333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599917113780975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.603722155094147</t>
+    <t xml:space="preserve">0.59991717338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.603722214698792</t>
   </si>
   <si>
     <t xml:space="preserve">0.573916494846344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621478617191315</t>
+    <t xml:space="preserve">0.621478676795959</t>
   </si>
   <si>
     <t xml:space="preserve">0.649381816387177</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">0.62274694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615771293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6233811378479</t>
+    <t xml:space="preserve">0.615771234035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623381078243256</t>
   </si>
   <si>
     <t xml:space="preserve">0.612600386142731</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">0.584063112735748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580892324447632</t>
+    <t xml:space="preserve">0.580892264842987</t>
   </si>
   <si>
     <t xml:space="preserve">0.56567245721817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570745646953583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561233282089233</t>
+    <t xml:space="preserve">0.570745706558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561233341693878</t>
   </si>
   <si>
     <t xml:space="preserve">0.572648227214813</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">0.559965014457703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537135183811188</t>
+    <t xml:space="preserve">0.537135124206543</t>
   </si>
   <si>
     <t xml:space="preserve">0.528891026973724</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">0.569477379322052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608795404434204</t>
+    <t xml:space="preserve">0.608795464038849</t>
   </si>
   <si>
     <t xml:space="preserve">0.618307888507843</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">0.630356967449188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604990541934967</t>
+    <t xml:space="preserve">0.604990482330322</t>
   </si>
   <si>
     <t xml:space="preserve">0.580258190631866</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">0.572014033794403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568209052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554891645908356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.629722774028778</t>
+    <t xml:space="preserve">0.568209111690521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554891705513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.629722714424133</t>
   </si>
   <si>
     <t xml:space="preserve">0.721676290035248</t>
@@ -1496,103 +1496,103 @@
     <t xml:space="preserve">0.766067624092102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.78255569934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.828215479850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.825678706169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.873875200748444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.871338427066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.882753312587738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.880216717720032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.903046607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92207133769989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.937291324138641</t>
+    <t xml:space="preserve">0.782555758953094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.828215420246124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.825678765773773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.873875141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.871338367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.882753372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.880216777324677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.903046667575836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.922071397304535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.937291383743286</t>
   </si>
   <si>
     <t xml:space="preserve">0.918266415596008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.866265058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.839630365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.896704971790314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87641167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.868801891803741</t>
+    <t xml:space="preserve">0.86626523733139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.839630484580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.896704912185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.876411736011505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.868801772594452</t>
   </si>
   <si>
     <t xml:space="preserve">0.870070099830627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.938559651374817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.934754610061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.904314815998077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.905583083629608</t>
+    <t xml:space="preserve">0.938559591770172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93475466966629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.904314935207367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.905583024024963</t>
   </si>
   <si>
     <t xml:space="preserve">0.929681360721588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.927144765853882</t>
+    <t xml:space="preserve">0.927144646644592</t>
   </si>
   <si>
     <t xml:space="preserve">0.906851530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.930949687957764</t>
+    <t xml:space="preserve">0.930949747562408</t>
   </si>
   <si>
     <t xml:space="preserve">0.891631603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.833288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.821873843669891</t>
+    <t xml:space="preserve">0.833288729190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.821873784065247</t>
   </si>
   <si>
     <t xml:space="preserve">0.802848994731903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.755921006202698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640503525733948</t>
+    <t xml:space="preserve">0.755921065807343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640503466129303</t>
   </si>
   <si>
     <t xml:space="preserve">0.636698484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627019226551056</t>
+    <t xml:space="preserve">0.627019286155701</t>
   </si>
   <si>
     <t xml:space="preserve">0.641851961612701</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">0.625670790672302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613534927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616906046867371</t>
+    <t xml:space="preserve">0.613534986972809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616905927658081</t>
   </si>
   <si>
     <t xml:space="preserve">0.618928611278534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595331132411957</t>
+    <t xml:space="preserve">0.595331192016602</t>
   </si>
   <si>
     <t xml:space="preserve">0.59667956829071</t>
@@ -1619,64 +1619,64 @@
     <t xml:space="preserve">0.597353756427765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596005380153656</t>
+    <t xml:space="preserve">0.596005439758301</t>
   </si>
   <si>
     <t xml:space="preserve">0.602073311805725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.598028063774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.594656944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.610838115215302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593982696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631064534187317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623648107051849</t>
+    <t xml:space="preserve">0.598028004169464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594657003879547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.610838055610657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593982756137848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631064474582672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623648166656494</t>
   </si>
   <si>
     <t xml:space="preserve">0.65398782491684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656684577465057</t>
+    <t xml:space="preserve">0.656684637069702</t>
   </si>
   <si>
     <t xml:space="preserve">0.637132465839386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626345038414001</t>
+    <t xml:space="preserve">0.626344978809357</t>
   </si>
   <si>
     <t xml:space="preserve">0.62836766242981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624322414398193</t>
+    <t xml:space="preserve">0.624322354793549</t>
   </si>
   <si>
     <t xml:space="preserve">0.629716098308563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62769341468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614883422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608815431594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61758017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635784029960632</t>
+    <t xml:space="preserve">0.6276935338974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614883363246918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608815491199493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617580235004425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635783970355988</t>
   </si>
   <si>
     <t xml:space="preserve">0.624996542930603</t>
@@ -1685,43 +1685,43 @@
     <t xml:space="preserve">0.614209175109863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605444371700287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606118619441986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630390346050262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643200397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.656010389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.633761346340179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612186551094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621625423431396</t>
+    <t xml:space="preserve">0.605444431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606118500232697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630390286445618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64320033788681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.656010448932648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.633761405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612186431884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.621625483036041</t>
   </si>
   <si>
     <t xml:space="preserve">0.608141243457794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610163867473602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549484550952911</t>
+    <t xml:space="preserve">0.610163807868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549484610557556</t>
   </si>
   <si>
     <t xml:space="preserve">0.561620473861694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552855670452118</t>
+    <t xml:space="preserve">0.552855610847473</t>
   </si>
   <si>
     <t xml:space="preserve">0.565665721893311</t>
@@ -1736,55 +1736,55 @@
     <t xml:space="preserve">0.563643097877502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.569710969924927</t>
+    <t xml:space="preserve">0.569711089134216</t>
   </si>
   <si>
     <t xml:space="preserve">0.558249413967133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.562294602394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.573082149028778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.583869576454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.584543645381927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567014217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566339910030365</t>
+    <t xml:space="preserve">0.562294661998749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.573082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.583869516849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.584543704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567014157772064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56633996963501</t>
   </si>
   <si>
     <t xml:space="preserve">0.593308508396149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599376380443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58656632900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591285884380341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.600050687789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60274749994278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60746705532074</t>
+    <t xml:space="preserve">0.599376499652863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.586566388607025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591285824775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.600050628185272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602747559547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607466995716095</t>
   </si>
   <si>
     <t xml:space="preserve">0.590611636638641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592634320259094</t>
+    <t xml:space="preserve">0.592634260654449</t>
   </si>
   <si>
     <t xml:space="preserve">0.587914764881134</t>
@@ -1796,25 +1796,25 @@
     <t xml:space="preserve">0.639829277992249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641177713871002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.588589012622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.598702192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.620277166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622973918914795</t>
+    <t xml:space="preserve">0.641177654266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.588589072227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.598702251911163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.620277106761932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62297397851944</t>
   </si>
   <si>
     <t xml:space="preserve">0.609489619731903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615557491779327</t>
+    <t xml:space="preserve">0.615557551383972</t>
   </si>
   <si>
     <t xml:space="preserve">0.620951294898987</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">0.604095995426178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603421747684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.639155149459839</t>
+    <t xml:space="preserve">0.603421807289124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.639155089855194</t>
   </si>
   <si>
     <t xml:space="preserve">0.63848090171814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655336260795593</t>
+    <t xml:space="preserve">0.655336201190948</t>
   </si>
   <si>
     <t xml:space="preserve">0.695789039134979</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">0.69983434677124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.716015517711639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728151381015778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717363893985748</t>
+    <t xml:space="preserve">0.716015458106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.728151440620422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.717363953590393</t>
   </si>
   <si>
     <t xml:space="preserve">0.726802945137024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722757756710052</t>
+    <t xml:space="preserve">0.722757697105408</t>
   </si>
   <si>
     <t xml:space="preserve">0.721409261226654</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">0.701182723045349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.694440722465515</t>
+    <t xml:space="preserve">0.694440603256226</t>
   </si>
   <si>
     <t xml:space="preserve">0.689046919345856</t>
@@ -1886,19 +1886,19 @@
     <t xml:space="preserve">0.683653235435486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.679607927799225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.680956304073334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.672191619873047</t>
+    <t xml:space="preserve">0.67960798740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.680956363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.672191560268402</t>
   </si>
   <si>
     <t xml:space="preserve">0.68500167131424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675562679767609</t>
+    <t xml:space="preserve">0.675562620162964</t>
   </si>
   <si>
     <t xml:space="preserve">0.668146252632141</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">0.632412970066071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647919893264771</t>
+    <t xml:space="preserve">0.647919952869415</t>
   </si>
   <si>
     <t xml:space="preserve">0.645897209644318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636458277702332</t>
+    <t xml:space="preserve">0.636458218097687</t>
   </si>
   <si>
     <t xml:space="preserve">0.63308721780777</t>
@@ -1925,37 +1925,37 @@
     <t xml:space="preserve">0.611512243747711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574430525302887</t>
+    <t xml:space="preserve">0.574430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">0.589263260364532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560272037982941</t>
+    <t xml:space="preserve">0.560271978378296</t>
   </si>
   <si>
     <t xml:space="preserve">0.553529798984528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538697123527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.527235567569733</t>
+    <t xml:space="preserve">0.538697183132172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.527235507965088</t>
   </si>
   <si>
     <t xml:space="preserve">0.478692084550858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463859379291534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45846563577652</t>
+    <t xml:space="preserve">0.463859409093857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458465695381165</t>
   </si>
   <si>
     <t xml:space="preserve">0.39104425907135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419361263513565</t>
+    <t xml:space="preserve">0.419361233711243</t>
   </si>
   <si>
     <t xml:space="preserve">0.394415318965912</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">0.388347387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380256831645966</t>
+    <t xml:space="preserve">0.380256801843643</t>
   </si>
   <si>
     <t xml:space="preserve">0.403180092573166</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">0.431497067213058</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465207815170288</t>
+    <t xml:space="preserve">0.465207785367966</t>
   </si>
   <si>
     <t xml:space="preserve">0.469927310943604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479366332292557</t>
+    <t xml:space="preserve">0.479366362094879</t>
   </si>
   <si>
     <t xml:space="preserve">0.489479511976242</t>
@@ -1994,49 +1994,49 @@
     <t xml:space="preserve">0.474646866321564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.473298370838165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464533627033234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483411639928818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498918533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.496895849704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495547473430634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511054337024689</t>
+    <t xml:space="preserve">0.473298460245132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464533597230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483411580324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.498918563127518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.496895909309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495547384023666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.511054396629333</t>
   </si>
   <si>
     <t xml:space="preserve">0.482063144445419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490827947854996</t>
+    <t xml:space="preserve">0.490827888250351</t>
   </si>
   <si>
     <t xml:space="preserve">0.484760016202927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48071476817131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482737392187119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485434323549271</t>
+    <t xml:space="preserve">0.480714738368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482737362384796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.485434234142303</t>
   </si>
   <si>
     <t xml:space="preserve">0.488131076097488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48138889670372</t>
+    <t xml:space="preserve">0.481388956308365</t>
   </si>
   <si>
     <t xml:space="preserve">0.472624182701111</t>
@@ -2045,40 +2045,40 @@
     <t xml:space="preserve">0.42745178937912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.434868156909943</t>
+    <t xml:space="preserve">0.434868186712265</t>
   </si>
   <si>
     <t xml:space="preserve">0.438239216804504</t>
   </si>
   <si>
-    <t xml:space="preserve">0.443632990121841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43014869093895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409247994422913</t>
+    <t xml:space="preserve">0.443632960319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430148720741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409248054027557</t>
   </si>
   <si>
     <t xml:space="preserve">0.434212177991867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410049796104431</t>
+    <t xml:space="preserve">0.410049825906754</t>
   </si>
   <si>
     <t xml:space="preserve">0.412892401218414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.449136078357697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.4512679874897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.456953227519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.486800909042358</t>
+    <t xml:space="preserve">0.449136018753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.451267927885056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.456953316926956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486800879240036</t>
   </si>
   <si>
     <t xml:space="preserve">0.469034463167191</t>
@@ -2090,46 +2090,46 @@
     <t xml:space="preserve">0.453399986028671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466191858053207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.466902434825897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480404943227768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.498882085084915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48822221159935</t>
+    <t xml:space="preserve">0.466191828250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.466902524232864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48040497303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49888214468956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488222181797028</t>
   </si>
   <si>
     <t xml:space="preserve">0.477562308311462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.445582717657089</t>
+    <t xml:space="preserve">0.445582687854767</t>
   </si>
   <si>
     <t xml:space="preserve">0.442740112543106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.452689319849014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447004020214081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.450557321310043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44842529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442029446363449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429948210716248</t>
+    <t xml:space="preserve">0.452689349651337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.447004079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.450557291507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448425322771072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.442029416561127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429948270320892</t>
   </si>
   <si>
     <t xml:space="preserve">0.438476115465164</t>
@@ -2144,40 +2144,40 @@
     <t xml:space="preserve">0.439186781644821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463349163532257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458374500274658</t>
+    <t xml:space="preserve">0.463349193334579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458374559879303</t>
   </si>
   <si>
     <t xml:space="preserve">0.444161385297775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.456242620944977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449846655130386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.455531924962997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.443450719118118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.430658876895905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.420709699392319</t>
+    <t xml:space="preserve">0.456242561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449846684932709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.455531865358353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.443450808525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.430658906698227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420709639787674</t>
   </si>
   <si>
     <t xml:space="preserve">0.427816241979599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.413603127002716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.417156368494034</t>
+    <t xml:space="preserve">0.413603097200394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.417156428098679</t>
   </si>
   <si>
     <t xml:space="preserve">0.416445761919022</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">0.437054842710495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432080179452896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434922844171524</t>
+    <t xml:space="preserve">0.432080239057541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434922814369202</t>
   </si>
   <si>
     <t xml:space="preserve">0.422841638326645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417867004871368</t>
+    <t xml:space="preserve">0.417867034673691</t>
   </si>
   <si>
     <t xml:space="preserve">0.406496554613113</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">0.401521891355515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405075222253799</t>
+    <t xml:space="preserve">0.405075162649155</t>
   </si>
   <si>
     <t xml:space="preserve">0.400811225175858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387308746576309</t>
+    <t xml:space="preserve">0.387308716773987</t>
   </si>
   <si>
     <t xml:space="preserve">0.385176748037338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400100618600845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.415735006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.398679256439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.409339100122452</t>
+    <t xml:space="preserve">0.400100588798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.415735065937042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398679286241531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.409339129924774</t>
   </si>
   <si>
     <t xml:space="preserve">0.395836651325226</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">0.382334113121033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370963633060455</t>
+    <t xml:space="preserve">0.370963603258133</t>
   </si>
   <si>
     <t xml:space="preserve">0.383755475282669</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">0.366699635982513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363146364688873</t>
+    <t xml:space="preserve">0.363146334886551</t>
   </si>
   <si>
     <t xml:space="preserve">0.3539077937603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356750428676605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359593063592911</t>
+    <t xml:space="preserve">0.356750398874283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359593033790588</t>
   </si>
   <si>
     <t xml:space="preserve">0.358882397413254</t>
@@ -2273,37 +2273,37 @@
     <t xml:space="preserve">0.370252966880798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388730049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.390151351690292</t>
+    <t xml:space="preserve">0.388730019330978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.390151411294937</t>
   </si>
   <si>
     <t xml:space="preserve">0.376648843288422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372384935617447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363857060670853</t>
+    <t xml:space="preserve">0.372384876012802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36385703086853</t>
   </si>
   <si>
     <t xml:space="preserve">0.361725062131882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355329126119614</t>
+    <t xml:space="preserve">0.355329096317291</t>
   </si>
   <si>
     <t xml:space="preserve">0.353552460670471</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354618489742279</t>
+    <t xml:space="preserve">0.354618459939957</t>
   </si>
   <si>
     <t xml:space="preserve">0.351775825023651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351065158843994</t>
+    <t xml:space="preserve">0.351065188646317</t>
   </si>
   <si>
     <t xml:space="preserve">0.334009379148483</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">0.323349505662918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.342181950807571</t>
+    <t xml:space="preserve">0.342181921005249</t>
   </si>
   <si>
     <t xml:space="preserve">0.337207317352295</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">0.389440715312958</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396547317504883</t>
+    <t xml:space="preserve">0.396547347307205</t>
   </si>
   <si>
     <t xml:space="preserve">0.412181794643402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.421420365571976</t>
+    <t xml:space="preserve">0.421420335769653</t>
   </si>
   <si>
     <t xml:space="preserve">0.415024369955063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419999063014984</t>
+    <t xml:space="preserve">0.419999003410339</t>
   </si>
   <si>
     <t xml:space="preserve">0.414313763380051</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">0.402232527732849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.418577700853348</t>
+    <t xml:space="preserve">0.418577671051025</t>
   </si>
   <si>
     <t xml:space="preserve">0.419288337230682</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">0.399389922618866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393704652786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39299401640892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391572713851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.397257953882217</t>
+    <t xml:space="preserve">0.393704682588577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.392993986606598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391572684049606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39725798368454</t>
   </si>
   <si>
     <t xml:space="preserve">0.40436452627182</t>
@@ -2384,13 +2384,13 @@
     <t xml:space="preserve">0.395125955343246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.386598080396652</t>
+    <t xml:space="preserve">0.386598110198975</t>
   </si>
   <si>
     <t xml:space="preserve">0.380202174186707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806208372116</t>
+    <t xml:space="preserve">0.373806238174438</t>
   </si>
   <si>
     <t xml:space="preserve">0.369542241096497</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">0.368831604719162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364567667245865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428526967763901</t>
+    <t xml:space="preserve">0.364567697048187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428526878356934</t>
   </si>
   <si>
     <t xml:space="preserve">0.423552334308624</t>
@@ -2414,40 +2414,40 @@
     <t xml:space="preserve">0.42639496922493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440608143806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439897418022156</t>
+    <t xml:space="preserve">0.44060805439949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439897477626801</t>
   </si>
   <si>
     <t xml:space="preserve">0.464770466089249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471877068281174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478983640670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492486149072647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515227258205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512384533882141</t>
+    <t xml:space="preserve">0.471877038478851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478983670473099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492486208677292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515227198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.512384593486786</t>
   </si>
   <si>
     <t xml:space="preserve">0.506699323654175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51735919713974</t>
+    <t xml:space="preserve">0.517359137535095</t>
   </si>
   <si>
     <t xml:space="preserve">0.508120596408844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513805866241455</t>
+    <t xml:space="preserve">0.5138059258461</t>
   </si>
   <si>
     <t xml:space="preserve">0.510963261127472</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">0.513095259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522333800792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.537257552146912</t>
+    <t xml:space="preserve">0.522333741188049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537257611751556</t>
   </si>
   <si>
     <t xml:space="preserve">0.523755133152008</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">0.525887131690979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526597678661346</t>
+    <t xml:space="preserve">0.526597738265991</t>
   </si>
   <si>
     <t xml:space="preserve">0.525176465511322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530151069164276</t>
+    <t xml:space="preserve">0.530151009559631</t>
   </si>
   <si>
     <t xml:space="preserve">0.524465799331665</t>
@@ -2486,82 +2486,82 @@
     <t xml:space="preserve">0.53867894411087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.544364213943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.541521549224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536547005176544</t>
+    <t xml:space="preserve">0.544364154338837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.541521608829498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536546945571899</t>
   </si>
   <si>
     <t xml:space="preserve">0.528729736804962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518780469894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515937924385071</t>
+    <t xml:space="preserve">0.518780529499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515937864780426</t>
   </si>
   <si>
     <t xml:space="preserve">0.523044466972351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54223221540451</t>
+    <t xml:space="preserve">0.542232155799866</t>
   </si>
   <si>
     <t xml:space="preserve">0.53157240152359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542942881584167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549338757991791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.564973294734955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550941288471222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549464285373688</t>
+    <t xml:space="preserve">0.542942821979523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549338817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5649733543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550941228866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549464225769043</t>
   </si>
   <si>
     <t xml:space="preserve">0.539124846458435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537647783756256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53173953294754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526569843292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516230523586273</t>
+    <t xml:space="preserve">0.537647724151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.531739592552185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526569902896881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516230463981628</t>
   </si>
   <si>
     <t xml:space="preserve">0.514753460884094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518446087837219</t>
+    <t xml:space="preserve">0.518446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">0.52435427904129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533955097198486</t>
+    <t xml:space="preserve">0.533955156803131</t>
   </si>
   <si>
     <t xml:space="preserve">0.544294476509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.556849539279938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.546510100364685</t>
+    <t xml:space="preserve">0.556849479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54651015996933</t>
   </si>
   <si>
     <t xml:space="preserve">0.553156852722168</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">0.575312674045563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568665862083435</t>
+    <t xml:space="preserve">0.56866592168808</t>
   </si>
   <si>
     <t xml:space="preserve">0.54281747341156</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">0.548725664615631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536170661449432</t>
+    <t xml:space="preserve">0.536170721054077</t>
   </si>
   <si>
     <t xml:space="preserve">0.527308404445648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.522877275943756</t>
+    <t xml:space="preserve">0.522877216339111</t>
   </si>
   <si>
     <t xml:space="preserve">0.53543221950531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531001031398773</t>
+    <t xml:space="preserve">0.531001091003418</t>
   </si>
   <si>
     <t xml:space="preserve">0.51696902513504</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">0.511060774326324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511799335479736</t>
+    <t xml:space="preserve">0.511799395084381</t>
   </si>
   <si>
     <t xml:space="preserve">0.509583711624146</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">0.506629586219788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487427920103073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48816642165184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483735293149948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488904982805252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480781227350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.481519669294357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492597639560699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.522138714790344</t>
+    <t xml:space="preserve">0.487427949905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488166391849518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483735263347626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488905012607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480781197547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48151969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492597579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.522138655185699</t>
   </si>
   <si>
     <t xml:space="preserve">0.525831341743469</t>
@@ -2663,28 +2663,28 @@
     <t xml:space="preserve">0.532478094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519923150539398</t>
+    <t xml:space="preserve">0.519923090934753</t>
   </si>
   <si>
     <t xml:space="preserve">0.517707526683807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512537837028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.514014840126038</t>
+    <t xml:space="preserve">0.512537896633148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.514014899730682</t>
   </si>
   <si>
     <t xml:space="preserve">0.525092840194702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545032978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.528785526752472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533216595649719</t>
+    <t xml:space="preserve">0.545033037662506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.528785467147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533216655254364</t>
   </si>
   <si>
     <t xml:space="preserve">0.520661652088165</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">0.515491962432861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508106648921967</t>
+    <t xml:space="preserve">0.508106708526611</t>
   </si>
   <si>
     <t xml:space="preserve">0.505152583122253</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">0.504414081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500721454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545771598815918</t>
+    <t xml:space="preserve">0.500721335411072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545771658420563</t>
   </si>
   <si>
     <t xml:space="preserve">0.540601849555969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55389541387558</t>
+    <t xml:space="preserve">0.553895354270935</t>
   </si>
   <si>
     <t xml:space="preserve">0.55020272731781</t>
@@ -2735,22 +2735,22 @@
     <t xml:space="preserve">0.538386285305023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530262529850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539863348007202</t>
+    <t xml:space="preserve">0.530262470245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539863407611847</t>
   </si>
   <si>
     <t xml:space="preserve">0.613716065883636</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641780138015747</t>
+    <t xml:space="preserve">0.641780078411102</t>
   </si>
   <si>
     <t xml:space="preserve">0.62257844209671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627009510993958</t>
+    <t xml:space="preserve">0.627009570598602</t>
   </si>
   <si>
     <t xml:space="preserve">0.612977564334869</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">0.616670191287994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629963636398315</t>
+    <t xml:space="preserve">0.62996369600296</t>
   </si>
   <si>
     <t xml:space="preserve">0.620362818241119</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">0.615193128585815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601161062717438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5945143699646</t>
+    <t xml:space="preserve">0.601161122322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.594514429569244</t>
   </si>
   <si>
     <t xml:space="preserve">0.599684000015259</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">0.600422620773315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607069313526154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593037247657776</t>
+    <t xml:space="preserve">0.607069373130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593037307262421</t>
   </si>
   <si>
     <t xml:space="preserve">0.597468495368958</t>
@@ -2816,19 +2816,19 @@
     <t xml:space="preserve">0.667628467082977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64842689037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647688269615173</t>
+    <t xml:space="preserve">0.648426830768585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647688329219818</t>
   </si>
   <si>
     <t xml:space="preserve">0.639564514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629225075244904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642518699169159</t>
+    <t xml:space="preserve">0.629225134849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642518639564514</t>
   </si>
   <si>
     <t xml:space="preserve">0.640303015708923</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">0.675752341747284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649165391921997</t>
+    <t xml:space="preserve">0.649165332317352</t>
   </si>
   <si>
     <t xml:space="preserve">0.655812084674835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655073642730713</t>
+    <t xml:space="preserve">0.655073583126068</t>
   </si>
   <si>
     <t xml:space="preserve">0.635871887207031</t>
@@ -2864,25 +2864,25 @@
     <t xml:space="preserve">0.643995702266693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638825953006744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62627100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630702137947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.649903953075409</t>
+    <t xml:space="preserve">0.638826012611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.626271069049835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630702197551727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649903893470764</t>
   </si>
   <si>
     <t xml:space="preserve">0.657289147377014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662458896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.678706526756287</t>
+    <t xml:space="preserve">0.662458837032318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.678706467151642</t>
   </si>
   <si>
     <t xml:space="preserve">0.676490902900696</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">0.661720335483551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635133326053619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576789677143097</t>
+    <t xml:space="preserve">0.635133385658264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576789736747742</t>
   </si>
   <si>
     <t xml:space="preserve">0.60411524772644</t>
@@ -2906,37 +2906,37 @@
     <t xml:space="preserve">0.587867677211761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.507368147373199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.529524028301239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565711796283722</t>
+    <t xml:space="preserve">0.507368087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.529523968696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565711736679077</t>
   </si>
   <si>
     <t xml:space="preserve">0.564234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582697868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.570881485939026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559803664684296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547248661518097</t>
+    <t xml:space="preserve">0.582697927951813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.570881545543671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559803605079651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547248601913452</t>
   </si>
   <si>
     <t xml:space="preserve">0.536909222602844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542078912258148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.567188858985901</t>
+    <t xml:space="preserve">0.542078971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.567188918590546</t>
   </si>
   <si>
     <t xml:space="preserve">0.5797438621521</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">0.562019169330597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557588040828705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543555974960327</t>
+    <t xml:space="preserve">0.55758798122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.543556034564972</t>
   </si>
   <si>
     <t xml:space="preserve">0.555372416973114</t>
@@ -2957,31 +2957,31 @@
     <t xml:space="preserve">0.569404482841492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.574574053287506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58257657289505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.572973728179932</t>
+    <t xml:space="preserve">0.574574172496796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.582576513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572973668575287</t>
   </si>
   <si>
     <t xml:space="preserve">0.576174676418304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570572912693024</t>
+    <t xml:space="preserve">0.570572972297668</t>
   </si>
   <si>
     <t xml:space="preserve">0.568172216415405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560169756412506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562570571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.569772660732269</t>
+    <t xml:space="preserve">0.560169816017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562570512294769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.569772720336914</t>
   </si>
   <si>
     <t xml:space="preserve">0.578575372695923</t>
@@ -3002,28 +3002,28 @@
     <t xml:space="preserve">0.54656571149826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537762939929962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.513755738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.516156375408173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.525759398937225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.521758079528809</t>
+    <t xml:space="preserve">0.537762999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.513755679130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.516156435012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.525759339332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.521758139133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.536962747573853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54816609621048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52655953168869</t>
+    <t xml:space="preserve">0.548166155815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526559591293335</t>
   </si>
   <si>
     <t xml:space="preserve">0.522558391094208</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">0.532961547374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524959146976471</t>
+    <t xml:space="preserve">0.524959087371826</t>
   </si>
   <si>
     <t xml:space="preserve">0.508153975009918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504152834415436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484146773815155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.480945736169815</t>
+    <t xml:space="preserve">0.504152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.484146744012833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.480945765972137</t>
   </si>
   <si>
     <t xml:space="preserve">0.5057532787323</t>
@@ -3053,22 +3053,22 @@
     <t xml:space="preserve">0.493749648332596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487347722053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488147974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.561770260334015</t>
+    <t xml:space="preserve">0.48734775185585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48814794421196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56177031993866</t>
   </si>
   <si>
     <t xml:space="preserve">0.56097000837326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58897852897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.568972408771515</t>
+    <t xml:space="preserve">0.588978469371796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.568972527980804</t>
   </si>
   <si>
     <t xml:space="preserve">0.572173416614532</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">0.577775120735168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.565771520137787</t>
+    <t xml:space="preserve">0.565771460533142</t>
   </si>
   <si>
     <t xml:space="preserve">0.580976068973541</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">0.581776320934296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583376824855804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.576974868774414</t>
+    <t xml:space="preserve">0.58337676525116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.576974928379059</t>
   </si>
   <si>
     <t xml:space="preserve">0.579375565052032</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">0.586577773094177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585777521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591379225254059</t>
+    <t xml:space="preserve">0.585777580738068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.591379284858704</t>
   </si>
   <si>
     <t xml:space="preserve">0.564170956611633</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">0.555368363857269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.567371964454651</t>
+    <t xml:space="preserve">0.567371904850006</t>
   </si>
   <si>
     <t xml:space="preserve">0.563370764255524</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">0.543364703655243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542564392089844</t>
+    <t xml:space="preserve">0.542564451694489</t>
   </si>
   <si>
     <t xml:space="preserve">0.535362303256989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536162555217743</t>
+    <t xml:space="preserve">0.536162495613098</t>
   </si>
   <si>
     <t xml:space="preserve">0.520957887172699</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">0.516956686973572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515356242656708</t>
+    <t xml:space="preserve">0.515356183052063</t>
   </si>
   <si>
     <t xml:space="preserve">0.508954226970673</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">0.517756938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.510554730892181</t>
+    <t xml:space="preserve">0.510554790496826</t>
   </si>
   <si>
     <t xml:space="preserve">0.524158835411072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.529760539531708</t>
+    <t xml:space="preserve">0.529760599136353</t>
   </si>
   <si>
     <t xml:space="preserve">0.531361043453217</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">0.530560791492462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527359783649445</t>
+    <t xml:space="preserve">0.527359843254089</t>
   </si>
   <si>
     <t xml:space="preserve">0.51215523481369</t>
@@ -3206,25 +3206,25 @@
     <t xml:space="preserve">0.540163695812225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547365963459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.552167415618896</t>
+    <t xml:space="preserve">0.54736590385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.552167356014252</t>
   </si>
   <si>
     <t xml:space="preserve">0.556168556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557769119739532</t>
+    <t xml:space="preserve">0.557769060134888</t>
   </si>
   <si>
     <t xml:space="preserve">0.548966348171234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559369504451752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556968808174133</t>
+    <t xml:space="preserve">0.559369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556968748569489</t>
   </si>
   <si>
     <t xml:space="preserve">0.558569252490997</t>
@@ -3239,25 +3239,25 @@
     <t xml:space="preserve">0.587378084659576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573773920536041</t>
+    <t xml:space="preserve">0.573773860931396</t>
   </si>
   <si>
     <t xml:space="preserve">0.600982129573822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612185478210449</t>
+    <t xml:space="preserve">0.612185537815094</t>
   </si>
   <si>
     <t xml:space="preserve">0.616986989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.621788442134857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62418919801712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622588634490967</t>
+    <t xml:space="preserve">0.621788501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624189138412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622588694095612</t>
   </si>
   <si>
     <t xml:space="preserve">0.620187938213348</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">0.60418313741684</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602582633495331</t>
+    <t xml:space="preserve">0.602582693099976</t>
   </si>
   <si>
     <t xml:space="preserve">0.627390146255493</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">0.640194058418274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643395006656647</t>
+    <t xml:space="preserve">0.643394947052002</t>
   </si>
   <si>
     <t xml:space="preserve">0.637793302536011</t>
@@ -3311,55 +3311,58 @@
     <t xml:space="preserve">0.649796903133392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.633792102336884</t>
+    <t xml:space="preserve">0.633792042732239</t>
   </si>
   <si>
     <t xml:space="preserve">0.620988190174103</t>
   </si>
   <si>
+    <t xml:space="preserve">0.628990709781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635921716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.651516497135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.641986310482025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.631589770317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627257883548737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615128636360168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.614262163639069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.611663043498993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.608197629451752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.606464862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.615995049476624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62119323015213</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.628990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635921716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.651516437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64198637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.631589770317078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627257883548737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615128576755524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.614262223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.611663103103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.608197569847107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.606464803218842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.615994989871979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.621193289756775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64025354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630723416805267</t>
+    <t xml:space="preserve">0.640253603458405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630723357200623</t>
   </si>
   <si>
     <t xml:space="preserve">0.623792409896851</t>
@@ -3368,22 +3371,22 @@
     <t xml:space="preserve">0.609063982963562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604732096195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61946052312851</t>
+    <t xml:space="preserve">0.604732036590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.619460463523865</t>
   </si>
   <si>
     <t xml:space="preserve">0.632456183433533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612529516220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613395869731903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607331156730652</t>
+    <t xml:space="preserve">0.612529456615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613395810127258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607331216335297</t>
   </si>
   <si>
     <t xml:space="preserve">0.609930336475372</t>
@@ -3392,13 +3395,13 @@
     <t xml:space="preserve">0.6021329164505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620326936244965</t>
+    <t xml:space="preserve">0.62032687664032</t>
   </si>
   <si>
     <t xml:space="preserve">0.610796689987183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597801089286804</t>
+    <t xml:space="preserve">0.597801029682159</t>
   </si>
   <si>
     <t xml:space="preserve">0.60040020942688</t>
@@ -3413,7 +3416,7 @@
     <t xml:space="preserve">0.629857003688812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.624658763408661</t>
+    <t xml:space="preserve">0.624658823013306</t>
   </si>
   <si>
     <t xml:space="preserve">0.602999269962311</t>
@@ -3428,10 +3431,10 @@
     <t xml:space="preserve">0.605598449707031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617727696895599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.616861343383789</t>
+    <t xml:space="preserve">0.617727756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.616861402988434</t>
   </si>
   <si>
     <t xml:space="preserve">0.618594110012054</t>
@@ -3452,7 +3455,7 @@
     <t xml:space="preserve">0.634188950061798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639387130737305</t>
+    <t xml:space="preserve">0.639387190341949</t>
   </si>
   <si>
     <t xml:space="preserve">0.644585490226746</t>
@@ -3479,13 +3482,13 @@
     <t xml:space="preserve">0.646318197250366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652382850646973</t>
+    <t xml:space="preserve">0.652382910251617</t>
   </si>
   <si>
     <t xml:space="preserve">0.649783730506897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.655848443508148</t>
+    <t xml:space="preserve">0.655848383903503</t>
   </si>
   <si>
     <t xml:space="preserve">0.650650084018707</t>
@@ -3518,10 +3521,10 @@
     <t xml:space="preserve">0.670576810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674042284488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687038004398346</t>
+    <t xml:space="preserve">0.674042344093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687037944793701</t>
   </si>
   <si>
     <t xml:space="preserve">0.68443888425827</t>
@@ -3536,13 +3539,13 @@
     <t xml:space="preserve">0.700033724308014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68270605802536</t>
+    <t xml:space="preserve">0.682706117630005</t>
   </si>
   <si>
     <t xml:space="preserve">0.691369891166687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689637124538422</t>
+    <t xml:space="preserve">0.689637184143066</t>
   </si>
   <si>
     <t xml:space="preserve">0.701766431331635</t>
@@ -3566,13 +3569,13 @@
     <t xml:space="preserve">0.732956051826477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739886999130249</t>
+    <t xml:space="preserve">0.739887058734894</t>
   </si>
   <si>
     <t xml:space="preserve">0.771076679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.762412965297699</t>
+    <t xml:space="preserve">0.762412905693054</t>
   </si>
   <si>
     <t xml:space="preserve">0.753749132156372</t>
@@ -3587,7 +3590,7 @@
     <t xml:space="preserve">0.767611145973206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.779740452766418</t>
+    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.76846718788147</t>
@@ -3699,9 +3702,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.787256062030792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.779740512371063</t>
   </si>
   <si>
     <t xml:space="preserve">0.789134919643402</t>
@@ -53729,7 +53729,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1897" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53755,7 +53755,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1898" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53781,7 +53781,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1899" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53807,7 +53807,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1900" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53833,7 +53833,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1901" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53885,7 +53885,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1903" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53911,7 +53911,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53937,7 +53937,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1905" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53963,7 +53963,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1906" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54015,7 +54015,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1908" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54067,7 +54067,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1910" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54093,7 +54093,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1911" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54119,7 +54119,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1912" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54145,7 +54145,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1913" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54223,7 +54223,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1916" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54275,7 +54275,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1918" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54301,7 +54301,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1919" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54353,7 +54353,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1921" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54405,7 +54405,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G1923" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54431,7 +54431,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1924" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54509,7 +54509,7 @@
         <v>0.703000009059906</v>
       </c>
       <c r="G1927" t="s"